--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE34458-C95D-4930-A06E-FFEFBDC87396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A8742B-358F-4169-BFC2-7F4F9DCDAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="415">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2315,6 +2315,18 @@
   </si>
   <si>
     <t>中国石油股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2989,7 +3001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3693,6 +3705,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3728,9 +3744,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4062,7 +4075,7 @@
       <c r="B5" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="351" t="s">
+      <c r="C5" s="339" t="s">
         <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
@@ -4074,7 +4087,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.55</v>
+        <v>5.39</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4119,7 +4132,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1015766.4268899</v>
+        <v>986483.07043901994</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4129,13 +4142,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4169,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>0.94030000000000002</v>
+        <v>1.06349396</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4202,7 +4215,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>6.0900083579883226</v>
+        <v>5.6787033353656637</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4217,7 +4230,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24044193847338047</v>
+        <v>0.22246108266706432</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4237,22 +4250,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="341" t="s">
         <v>378</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="343" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4264,13 +4277,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4290,13 +4303,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4304,7 +4317,7 @@
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
-        <v>0</v>
+        <v>229584</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4317,7 +4330,7 @@
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
-        <v>0</v>
+        <v>-252845.35040534919</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4325,13 +4338,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4347,13 +4360,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4361,7 +4374,7 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>6696.7819249050754</v>
+        <v>6666.227894779714</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4391,7 +4404,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>-17366.218075094926</v>
+        <v>-17396.772105220287</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4417,13 +4430,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4431,7 +4444,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-56962.576642364453</v>
+        <v>-56954.938134833108</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4439,13 +4452,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="345"/>
+      <c r="D50" s="345"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4461,22 +4474,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="341" t="s">
         <v>379</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4484,7 +4497,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>191229.78192490508</v>
+        <v>305486.2278947797</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4497,7 +4510,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>155258.28084593726</v>
+        <v>131974.01491799403</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4509,8 +4522,8 @@
         <v>408</v>
       </c>
       <c r="C58" s="94">
-        <f>Normalized_FCF!C121</f>
-        <v>0.14372335766838523</v>
+        <f>Normalized_FCF!C125</f>
+        <v>0.14227671203700865</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4519,7 +4532,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>9.0061347106970835E-2</v>
+        <v>8.1992488015582468E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4537,22 +4550,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
+      <c r="B63" s="341" t="s">
         <v>380</v>
       </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4610,22 +4623,22 @@
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="341" t="s">
         <v>381</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
+      <c r="B74" s="341" t="s">
         <v>382</v>
       </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4641,7 +4654,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.9708079382442296</v>
+        <v>9.5858934734934564</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4662,13 +4675,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
+      <c r="B81" s="341" t="s">
         <v>383</v>
       </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4681,13 +4694,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
+      <c r="B85" s="341" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4708,7 +4721,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2623955841267334</v>
+        <v>1.4277890873651522</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4739,7 +4752,7 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>45325.581824401161</v>
+        <v>46208.672776167194</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4752,7 +4765,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.23286753845161021</v>
+        <v>0.26850826054453025</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4783,7 +4796,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.2638541828468509E-2</v>
+        <v>3.6914699667960876E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4791,13 +4804,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
+      <c r="B98" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4805,7 +4818,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4823,13 +4836,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
+      <c r="B104" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4863,7 +4876,7 @@
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>11.11 HKD</v>
+        <v>10.51 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
@@ -4885,7 +4898,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>9.3 HKD</v>
+        <v>8.77 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
@@ -4907,7 +4920,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.97 HKD</v>
+        <v>8.46 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
@@ -4929,7 +4942,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.5 HKD</v>
+        <v>7.04 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
@@ -4951,7 +4964,7 @@
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>5.61 HKD</v>
+        <v>5.23 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
@@ -4964,7 +4977,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>8.7041151083487964</v>
+        <v>8.2041395456413451</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -4972,13 +4985,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="344" t="s">
+      <c r="B115" s="346" t="s">
         <v>388</v>
       </c>
-      <c r="C115" s="344"/>
-      <c r="D115" s="344"/>
-      <c r="E115" s="344"/>
-      <c r="F115" s="344"/>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
@@ -4991,22 +5004,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
+      <c r="B119" s="344" t="s">
         <v>386</v>
       </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
+      <c r="B120" s="341" t="s">
         <v>387</v>
       </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5037,7 +5050,7 @@
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>0.49984047644368812</v>
+        <v>0.44193951040398949</v>
       </c>
       <c r="D124" s="242" t="str">
         <f>Market_currency</f>
@@ -5056,7 +5069,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>1.0529047073235096</v>
+        <v>0.93093739460099634</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5066,7 +5079,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>5.0371036506648128</v>
+        <v>4.7477659407646673</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5075,7 +5088,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>6.0900083579883226</v>
+        <v>5.6787033353656637</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5088,7 +5101,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.30032998390072763</v>
+        <v>0.30782462880185679</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5102,13 +5115,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>394</v>
       </c>
-      <c r="C134" s="339"/>
-      <c r="D134" s="339"/>
-      <c r="E134" s="339"/>
-      <c r="F134" s="339"/>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
@@ -5116,13 +5129,13 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="343" t="s">
+      <c r="B137" s="345" t="s">
         <v>398</v>
       </c>
-      <c r="C137" s="343"/>
-      <c r="D137" s="343"/>
-      <c r="E137" s="343"/>
-      <c r="F137" s="343"/>
+      <c r="C137" s="345"/>
+      <c r="D137" s="345"/>
+      <c r="E137" s="345"/>
+      <c r="F137" s="345"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
@@ -5145,13 +5158,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="340" t="s">
+      <c r="B143" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5159,22 +5172,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="345" t="s">
+      <c r="B146" s="347" t="s">
         <v>400</v>
       </c>
-      <c r="C146" s="345"/>
-      <c r="D146" s="345"/>
-      <c r="E146" s="345"/>
-      <c r="F146" s="345"/>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="345" t="s">
+      <c r="B147" s="347" t="s">
         <v>401</v>
       </c>
-      <c r="C147" s="345"/>
-      <c r="D147" s="345"/>
-      <c r="E147" s="345"/>
-      <c r="F147" s="345"/>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5227,7 +5240,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5248,7 +5261,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M79"/>
+  <dimension ref="B1:M80"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -5652,10 +5665,18 @@
       <c r="B19" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="184"/>
-      <c r="D19" s="184"/>
-      <c r="E19" s="184"/>
-      <c r="F19" s="184"/>
+      <c r="C19" s="184">
+        <v>229584</v>
+      </c>
+      <c r="D19" s="184">
+        <v>222648</v>
+      </c>
+      <c r="E19" s="184">
+        <v>238036</v>
+      </c>
+      <c r="F19" s="184">
+        <v>236818</v>
+      </c>
       <c r="G19" s="184"/>
       <c r="H19" s="184"/>
       <c r="I19" s="184"/>
@@ -5668,10 +5689,18 @@
       <c r="B20" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="184"/>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
+      <c r="C20" s="184">
+        <v>115297</v>
+      </c>
+      <c r="D20" s="184">
+        <v>282508</v>
+      </c>
+      <c r="E20" s="184">
+        <v>245237</v>
+      </c>
+      <c r="F20" s="184">
+        <v>265563</v>
+      </c>
       <c r="G20" s="184"/>
       <c r="H20" s="184"/>
       <c r="I20" s="184"/>
@@ -5684,10 +5713,18 @@
       <c r="B21" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="184"/>
-      <c r="D21" s="184"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="184"/>
+      <c r="C21" s="184">
+        <v>31061</v>
+      </c>
+      <c r="D21" s="184">
+        <v>3456</v>
+      </c>
+      <c r="E21" s="184">
+        <v>46237</v>
+      </c>
+      <c r="F21" s="184">
+        <v>34899</v>
+      </c>
       <c r="G21" s="184"/>
       <c r="H21" s="184"/>
       <c r="I21" s="184"/>
@@ -5700,10 +5737,18 @@
       <c r="B22" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="C22" s="184"/>
-      <c r="D22" s="184"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="184"/>
+      <c r="C22" s="184">
+        <v>456596</v>
+      </c>
+      <c r="D22" s="184">
+        <v>393768</v>
+      </c>
+      <c r="E22" s="184">
+        <v>276599</v>
+      </c>
+      <c r="F22" s="184">
+        <v>256657</v>
+      </c>
       <c r="G22" s="184"/>
       <c r="H22" s="184"/>
       <c r="I22" s="184"/>
@@ -5716,10 +5761,18 @@
       <c r="B23" s="27" t="s">
         <v>391</v>
       </c>
-      <c r="C23" s="184"/>
-      <c r="D23" s="184"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="184"/>
+      <c r="C23" s="184">
+        <v>-255789</v>
+      </c>
+      <c r="D23" s="184">
+        <v>-232971</v>
+      </c>
+      <c r="E23" s="184">
+        <v>-149026</v>
+      </c>
+      <c r="F23" s="184">
+        <v>-140250</v>
+      </c>
       <c r="G23" s="184"/>
       <c r="H23" s="184"/>
       <c r="I23" s="184"/>
@@ -5732,10 +5785,18 @@
       <c r="B24" s="27" t="s">
         <v>390</v>
       </c>
-      <c r="C24" s="184"/>
-      <c r="D24" s="184"/>
-      <c r="E24" s="184"/>
-      <c r="F24" s="184"/>
+      <c r="C24" s="184">
+        <v>-146572</v>
+      </c>
+      <c r="D24" s="184">
+        <v>-113713</v>
+      </c>
+      <c r="E24" s="184">
+        <v>-135729</v>
+      </c>
+      <c r="F24" s="184">
+        <v>-79554</v>
+      </c>
       <c r="G24" s="184"/>
       <c r="H24" s="184"/>
       <c r="I24" s="184"/>
@@ -5751,19 +5812,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.25+0.22)/Exchange_Rate</f>
-        <v>0.49984047644368812</v>
+        <v>0.44193951040398949</v>
       </c>
       <c r="D25" s="39">
         <f>(0.23+0.21)/Exchange_Rate</f>
-        <v>0.46793576518132513</v>
+        <v>0.41373060548458596</v>
       </c>
       <c r="E25" s="39">
         <f>(0.22+0.20258)/Exchange_Rate</f>
-        <v>0.4494097628416463</v>
+        <v>0.39735063469471893</v>
       </c>
       <c r="F25" s="39">
         <f>(0.09622+0.1304)/Exchange_Rate</f>
-        <v>0.24100818887589065</v>
+        <v>0.21309006776117467</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -6877,19 +6938,19 @@
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
-        <v>0</v>
+        <v>-229584</v>
       </c>
       <c r="D61" s="186">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-222648</v>
       </c>
       <c r="E61" s="186">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-238036</v>
       </c>
       <c r="F61" s="186">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-236818</v>
       </c>
       <c r="G61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6926,19 +6987,19 @@
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>0</v>
+        <v>-115297</v>
       </c>
       <c r="D62" s="186">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-282508</v>
       </c>
       <c r="E62" s="186">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-245237</v>
       </c>
       <c r="F62" s="186">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-265563</v>
       </c>
       <c r="G62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -6975,19 +7036,19 @@
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>0</v>
+        <v>-31061</v>
       </c>
       <c r="D63" s="186">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-3456</v>
       </c>
       <c r="E63" s="186">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-46237</v>
       </c>
       <c r="F63" s="186">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>-34899</v>
       </c>
       <c r="G63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -7019,440 +7080,455 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" s="186">
+        <f>IF(C$4="","",C22+C23+C24)</f>
+        <v>54235</v>
+      </c>
+      <c r="D64" s="186">
+        <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
+        <v>47084</v>
+      </c>
+      <c r="E64" s="186">
+        <f t="shared" si="32"/>
+        <v>-8156</v>
+      </c>
+      <c r="F64" s="186">
+        <f t="shared" si="32"/>
+        <v>36853</v>
+      </c>
+      <c r="G64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="H64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="I64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="L64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="M64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
-        <v>0.49984047644368812</v>
-      </c>
-      <c r="D64" s="75">
-        <f t="shared" si="32"/>
-        <v>0.46793576518132513</v>
-      </c>
-      <c r="E64" s="75">
-        <f t="shared" si="32"/>
-        <v>0.4494097628416463</v>
-      </c>
-      <c r="F64" s="75">
-        <f t="shared" si="32"/>
-        <v>0.24100818887589065</v>
-      </c>
-      <c r="G64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="H64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="93" t="s">
+      <c r="C65" s="75">
+        <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
+        <v>0.44193951040398949</v>
+      </c>
+      <c r="D65" s="75">
+        <f t="shared" si="33"/>
+        <v>0.41373060548458596</v>
+      </c>
+      <c r="E65" s="75">
+        <f t="shared" si="33"/>
+        <v>0.39735063469471893</v>
+      </c>
+      <c r="F65" s="75">
+        <f t="shared" si="33"/>
+        <v>0.21309006776117467</v>
+      </c>
+      <c r="G65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="H65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="I65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="L65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="M65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="str">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94">
-        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
+      <c r="C68" s="94">
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
         <v>-7.0436318967191269E-2</v>
       </c>
-      <c r="D67" s="94">
-        <f t="shared" si="33"/>
+      <c r="D68" s="94">
+        <f t="shared" si="34"/>
         <v>0.74949486547839661</v>
       </c>
-      <c r="E67" s="94">
-        <f t="shared" si="33"/>
+      <c r="E68" s="94">
+        <f t="shared" si="34"/>
         <v>7.0387660537596819E-2</v>
       </c>
-      <c r="F67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="G67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="82" t="str">
+      <c r="F68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="G68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="L68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="M68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="82" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104">
-        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
+      <c r="C69" s="104">
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
         <v>-8.9223021952700488E-2</v>
       </c>
-      <c r="D68" s="104">
-        <f t="shared" si="34"/>
+      <c r="D69" s="104">
+        <f t="shared" si="35"/>
         <v>0.83246902554794255</v>
       </c>
-      <c r="E68" s="104">
-        <f t="shared" si="34"/>
+      <c r="E69" s="104">
+        <f t="shared" si="35"/>
         <v>7.8780494861903749E-2</v>
       </c>
-      <c r="F68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="G68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="str">
+      <c r="F69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="G69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="H69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="L69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="M69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="str">
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94">
-        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
+      <c r="C70" s="94">
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
         <v>-3.6626585980383819E-3</v>
       </c>
-      <c r="D69" s="94">
-        <f t="shared" si="35"/>
+      <c r="D70" s="94">
+        <f t="shared" si="36"/>
         <v>0.50696558840417572</v>
       </c>
-      <c r="E69" s="94">
-        <f t="shared" si="35"/>
+      <c r="E70" s="94">
+        <f t="shared" si="36"/>
         <v>4.6587900317992537E-2</v>
       </c>
-      <c r="F69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="G69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="I69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="82" t="str">
+      <c r="F70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="G70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="H70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="I70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="L70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="M70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B71" s="82" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104">
-        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
+      <c r="C71" s="104">
+        <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
         <v>6.2147149651508915E-2</v>
       </c>
-      <c r="D70" s="104">
-        <f t="shared" si="36"/>
+      <c r="D71" s="104">
+        <f t="shared" si="37"/>
         <v>0.33600958860171848</v>
       </c>
-      <c r="E70" s="104">
-        <f t="shared" si="36"/>
+      <c r="E71" s="104">
+        <f t="shared" si="37"/>
         <v>3.5727773736921709E-2</v>
       </c>
-      <c r="F70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="G70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="str">
+      <c r="F71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="G71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="str">
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94">
-        <f>IF(D$36="","",C64/D64-1)</f>
-        <v>6.8181818181817899E-2</v>
-      </c>
-      <c r="D71" s="94">
-        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
+      <c r="C72" s="94">
+        <f>IF(D$36="","",C65/D65-1)</f>
+        <v>6.8181818181818121E-2</v>
+      </c>
+      <c r="D72" s="94">
+        <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
         <v>4.1222963699181214E-2</v>
       </c>
-      <c r="E71" s="94">
-        <f t="shared" si="37"/>
+      <c r="E72" s="94">
+        <f t="shared" si="38"/>
         <v>0.86470743976701114</v>
       </c>
-      <c r="F71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="G71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="36" t="s">
+      <c r="F72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="G72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="H72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="I72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="L72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="M72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-      <c r="M73" s="37"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="9"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="78">
-        <f>IF(C$4="","",C78+C79)</f>
+      <c r="C76" s="78">
+        <f>IF(C$4="","",C79+C80)</f>
         <v>2752710</v>
       </c>
-      <c r="D75" s="78">
-        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
+      <c r="D76" s="78">
+        <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
         <v>2670666</v>
       </c>
-      <c r="E75" s="78">
-        <f t="shared" si="38"/>
+      <c r="E76" s="78">
+        <f t="shared" si="39"/>
         <v>1981074</v>
       </c>
-      <c r="F75" s="78">
-        <f t="shared" si="38"/>
+      <c r="F76" s="78">
+        <f t="shared" si="39"/>
         <v>1946908</v>
       </c>
-      <c r="G75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="H75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
-        <v>99851</v>
-      </c>
-      <c r="D76" s="74">
+      <c r="G76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>117877</v>
-      </c>
-      <c r="E76" s="74">
+        <v/>
+      </c>
+      <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>23709</v>
-      </c>
-      <c r="F76" s="74">
+        <v/>
+      </c>
+      <c r="I76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>27379</v>
-      </c>
-      <c r="G76" s="74" t="str">
+        <v/>
+      </c>
+      <c r="J76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="H76" s="74" t="str">
+      <c r="K76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="96"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
-      <c r="L76" s="96"/>
-      <c r="M76" s="96"/>
+      <c r="L76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="M76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="39"/>
-        <v>180533</v>
+        <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
+        <v>99851</v>
       </c>
       <c r="D77" s="74">
-        <f t="shared" si="39"/>
-        <v>167751</v>
+        <f t="shared" si="40"/>
+        <v>117877</v>
       </c>
       <c r="E77" s="74">
-        <f t="shared" si="39"/>
-        <v>110386</v>
+        <f t="shared" si="40"/>
+        <v>23709</v>
       </c>
       <c r="F77" s="74">
-        <f t="shared" si="39"/>
-        <v>109354</v>
+        <f t="shared" si="40"/>
+        <v>27379</v>
       </c>
       <c r="G77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7462,73 +7538,58 @@
       <c r="M77" s="96"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
-        <v>1122089</v>
-      </c>
-      <c r="D78" s="58">
+      <c r="B78" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>1136250</v>
-      </c>
-      <c r="E78" s="58">
+        <v>180533</v>
+      </c>
+      <c r="D78" s="74">
         <f t="shared" si="40"/>
-        <v>689466</v>
-      </c>
-      <c r="F78" s="58">
+        <v>167751</v>
+      </c>
+      <c r="E78" s="74">
         <f t="shared" si="40"/>
-        <v>707978</v>
-      </c>
-      <c r="G78" s="58" t="str">
+        <v>110386</v>
+      </c>
+      <c r="F78" s="74">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="H78" s="58" t="str">
+        <v>109354</v>
+      </c>
+      <c r="G78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="58" t="str">
+      <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="J78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="I78" s="96"/>
+      <c r="J78" s="96"/>
+      <c r="K78" s="96"/>
+      <c r="L78" s="96"/>
+      <c r="M78" s="96"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
-        <v>1630621</v>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <v>1122089</v>
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
-        <v>1534416</v>
+        <v>1136250</v>
       </c>
       <c r="E79" s="58">
         <f t="shared" si="41"/>
-        <v>1291608</v>
+        <v>689466</v>
       </c>
       <c r="F79" s="58">
         <f t="shared" si="41"/>
-        <v>1238930</v>
+        <v>707978</v>
       </c>
       <c r="G79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7559,9 +7620,58 @@
         <v/>
       </c>
     </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B80" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="58">
+        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <v>1630621</v>
+      </c>
+      <c r="D80" s="58">
+        <f t="shared" si="42"/>
+        <v>1534416</v>
+      </c>
+      <c r="E80" s="58">
+        <f t="shared" si="42"/>
+        <v>1291608</v>
+      </c>
+      <c r="F80" s="58">
+        <f t="shared" si="42"/>
+        <v>1238930</v>
+      </c>
+      <c r="G80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="H80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="I80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -7571,7 +7681,7 @@
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:M37 C61:M64">
+  <conditionalFormatting sqref="C36:M37 C61:M65">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
@@ -8380,11 +8490,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>7.6546237917772562</v>
+        <v>8.657498849970656</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.3316826296620832</v>
+        <v>-3.7681849976417547</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8494,7 +8604,7 @@
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>0</v>
+        <v>0.14105183094472606</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -8575,7 +8685,7 @@
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>45325.581824401161</v>
+        <v>46208.672776167194</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8642,11 +8752,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-236343.44106264491</v>
+        <v>-235460.35011087885</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-193554.41817559884</v>
+        <v>-192671.32722383281</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>365</v>
@@ -8658,11 +8768,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>1.0107325125078581</v>
+        <v>1.0145232515262583</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>1.2341748757358788</v>
+        <v>1.2398316004876273</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>332</v>
@@ -8675,7 +8785,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>193554.41817559884</v>
+        <v>192671.32722383281</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>366</v>
@@ -8790,11 +8900,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-231044.87420000002</v>
+        <v>-261315.35488743999</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.2623955841267334</v>
+        <v>-1.4277890873651522</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8807,11 +8917,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>42619.644589484415</v>
+        <v>49142.644397070238</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>0.23286753845161021</v>
+        <v>0.26850826054453025</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8824,11 +8934,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5973.53784</v>
+        <v>6756.1644290880004</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>3.2638541828468509E-2</v>
+        <v>3.6914699667960883E-2</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8841,11 +8951,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>-182451.69177051561</v>
+        <v>-205416.54606128176</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>-0.99688950384665476</v>
+        <v>-1.1223661271526613</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8865,7 +8975,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q808"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -9258,24 +9368,24 @@
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
-        <v>0</v>
+        <v>229584</v>
       </c>
       <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>0</v>
+        <v>229584</v>
       </c>
       <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>0</v>
+        <v>222648</v>
       </c>
       <c r="I9" s="197">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>0</v>
+        <v>238036</v>
       </c>
       <c r="J9" s="197">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v>0</v>
+        <v>236818</v>
       </c>
       <c r="K9" s="197" t="str">
         <f>IF(Data!G61="","",-Data!G61)</f>
@@ -9313,24 +9423,24 @@
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
-        <v>0</v>
+        <v>-252845.35040534919</v>
       </c>
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>0</v>
+        <v>-115297</v>
       </c>
       <c r="H10" s="197">
         <f>Data!D62</f>
-        <v>0</v>
+        <v>-282508</v>
       </c>
       <c r="I10" s="197">
         <f>Data!E62</f>
-        <v>0</v>
+        <v>-245237</v>
       </c>
       <c r="J10" s="197">
         <f>Data!F62</f>
-        <v>0</v>
+        <v>-265563</v>
       </c>
       <c r="K10" s="197" t="str">
         <f>Data!G62</f>
@@ -9425,24 +9535,24 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>-17366.218075094926</v>
+        <v>-17396.772105220287</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>-17366.218075094926</v>
+        <v>-17396.772105220287</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-17714.997851155444</v>
+        <v>-17732.513277015572</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
-        <v>-13323.894425551851</v>
+        <v>-13331.1401483644</v>
       </c>
       <c r="J12" s="197">
         <f t="shared" si="6"/>
-        <v>-13693.63323727337</v>
+        <v>-13700.036090289357</v>
       </c>
       <c r="K12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -9480,24 +9590,24 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>227850.30656945781</v>
+        <v>204558.40213398324</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>267543.78192490508</v>
+        <v>381800.2278947797</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>293046.00214884453</v>
+        <v>233168.48672298444</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
-        <v>158535.10557444816</v>
+        <v>151326.85985163559</v>
       </c>
       <c r="J13" s="187">
         <f t="shared" si="7"/>
-        <v>147371.36676272663</v>
+        <v>118619.96390971064</v>
       </c>
       <c r="K13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -9535,7 +9645,7 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-56962.576642364453</v>
+        <v>-56954.938134833108</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
@@ -9647,26 +9757,26 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>155258.28084593726</v>
+        <v>131974.01491799403</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>191229.78192490508</v>
+        <v>305486.2278947797</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>228512.00214884453</v>
+        <v>168634.48672298444</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
-        <v>134397.10557444816</v>
+        <v>127188.85985163559</v>
       </c>
       <c r="J16" s="187">
         <f t="shared" si="8"/>
-        <v>130304.36676272663</v>
+        <v>101552.96390971064</v>
       </c>
       <c r="K16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9755,26 +9865,26 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>155258.28084593726</v>
+        <v>131974.01491799403</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>191229.78192490508</v>
+        <v>305486.2278947797</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>228512.00214884453</v>
+        <v>168634.48672298444</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
-        <v>134397.10557444816</v>
+        <v>127188.85985163559</v>
       </c>
       <c r="J19" s="189">
         <f t="shared" si="9"/>
-        <v>130304.36676272663</v>
+        <v>101552.96390971064</v>
       </c>
       <c r="K19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -10616,19 +10726,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.2136734391234919</v>
+        <v>0.21369784384077392</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.17037939311193864</v>
+        <v>0.17038957733553248</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.15225649809571537</v>
+        <v>0.15226345717775083</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.11580947082806461</v>
+        <v>0.11581450262802505</v>
       </c>
       <c r="K43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10754,24 +10864,24 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>6696.7819249050754</v>
+        <v>6666.227894779714</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>6696.7819249050754</v>
+        <v>6666.227894779714</v>
       </c>
       <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>3839.002148844555</v>
+        <v>3821.4867229844263</v>
       </c>
       <c r="I48" s="334">
         <f t="shared" si="19"/>
-        <v>1588.1055744481484</v>
+        <v>1580.8598516356005</v>
       </c>
       <c r="J48" s="334">
         <f t="shared" si="19"/>
-        <v>1403.3667627266291</v>
+        <v>1396.9639097106431</v>
       </c>
       <c r="K48" s="334" t="str">
         <f t="shared" si="19"/>
@@ -10866,24 +10976,24 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>-17366.218075094926</v>
+        <v>-17396.772105220287</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-17366.218075094926</v>
+        <v>-17396.772105220287</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-17714.997851155444</v>
+        <v>-17732.513277015572</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
-        <v>-13323.894425551851</v>
+        <v>-13331.1401483644</v>
       </c>
       <c r="J50" s="187">
         <f t="shared" si="20"/>
-        <v>-13693.63323727337</v>
+        <v>-13700.036090289357</v>
       </c>
       <c r="K50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -11780,26 +11890,26 @@
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>0</v>
+        <v>9.3408457248361651E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>0</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="H77" s="6">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.873619050823869E-2</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>0.12856476983095208</v>
       </c>
       <c r="J77" s="6">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>0.13690998910237695</v>
       </c>
       <c r="K77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11837,7 +11947,7 @@
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>0</v>
+        <v>0.10287256125768818</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
@@ -11846,19 +11956,19 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>0</v>
+        <v>3.8291776983950913E-2</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>8.7216250350784633E-2</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.13245407610207363</v>
       </c>
       <c r="J78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.15352814159394357</v>
       </c>
       <c r="K78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -11953,26 +12063,26 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>7.0656127545178663E-3</v>
+        <v>7.0780439553712786E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.7675685367892674E-3</v>
+        <v>5.7777159656687812E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>5.4689980020034296E-3</v>
+        <v>5.474405387871503E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.1963208089237734E-3</v>
+        <v>7.2002342702727051E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9166075943849033E-3</v>
+        <v>7.9203092325063427E-3</v>
       </c>
       <c r="K80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12010,26 +12120,26 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>9.270308741122768E-2</v>
+        <v>8.3226552201047743E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>8.8855103176242761E-2</v>
+        <v>0.12680129733617126</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>9.0469556570823464E-2</v>
+        <v>7.1984089342409463E-2</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
-        <v>8.5625827010639644E-2</v>
+        <v>8.1732607278169167E-2</v>
       </c>
       <c r="J81" s="66">
         <f t="shared" si="32"/>
-        <v>8.5198811819571563E-2</v>
+        <v>6.8576957689883505E-2</v>
       </c>
       <c r="K81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -12067,7 +12177,7 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>2.317577185280692E-2</v>
+        <v>2.3172664052593564E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
@@ -12182,26 +12292,26 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>6.3168323963568265E-2</v>
+        <v>5.3694896553601684E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>6.3510136102049766E-2</v>
+        <v>0.10145633026197827</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>7.0546533151530796E-2</v>
+        <v>5.2061065923116788E-2</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
-        <v>7.2588738443450138E-2</v>
+        <v>6.8695518710979647E-2</v>
       </c>
       <c r="J84" s="66">
         <f t="shared" si="35"/>
-        <v>7.5331982507567133E-2</v>
+        <v>5.8710128377879062E-2</v>
       </c>
       <c r="K84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12289,26 +12399,26 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>6.3168323963568265E-2</v>
+        <v>5.3694896553601684E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>6.3510136102049766E-2</v>
+        <v>0.10145633026197827</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>7.0546533151530796E-2</v>
+        <v>5.2061065923116788E-2</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
-        <v>7.2588738443450138E-2</v>
+        <v>6.8695518710979647E-2</v>
       </c>
       <c r="J87" s="66">
         <f t="shared" si="36"/>
-        <v>7.5331982507567133E-2</v>
+        <v>5.8710128377879062E-2</v>
       </c>
       <c r="K87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12358,51 +12468,51 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>0.49984047644368812</v>
+        <v>0.44193951040398949</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
-        <f>Data!C64</f>
-        <v>0.49984047644368812</v>
+        <f>Data!C65</f>
+        <v>0.44193951040398949</v>
       </c>
       <c r="H90" s="116">
-        <f>Data!D64</f>
-        <v>0.46793576518132513</v>
+        <f>Data!D65</f>
+        <v>0.41373060548458596</v>
       </c>
       <c r="I90" s="116">
-        <f>Data!E64</f>
-        <v>0.4494097628416463</v>
+        <f>Data!E65</f>
+        <v>0.39735063469471893</v>
       </c>
       <c r="J90" s="116">
-        <f>Data!F64</f>
-        <v>0.24100818887589065</v>
+        <f>Data!F65</f>
+        <v>0.21309006776117467</v>
       </c>
       <c r="K90" s="116" t="str">
-        <f>Data!G64</f>
+        <f>Data!G65</f>
         <v/>
       </c>
       <c r="L90" s="116" t="str">
-        <f>Data!H64</f>
+        <f>Data!H65</f>
         <v/>
       </c>
       <c r="M90" s="116" t="str">
-        <f>Data!I64</f>
+        <f>Data!I65</f>
         <v/>
       </c>
       <c r="N90" s="116" t="str">
-        <f>Data!J64</f>
+        <f>Data!J65</f>
         <v/>
       </c>
       <c r="O90" s="116" t="str">
-        <f>Data!K64</f>
+        <f>Data!K65</f>
         <v/>
       </c>
       <c r="P90" s="116" t="str">
-        <f>Data!L64</f>
+        <f>Data!L65</f>
         <v/>
       </c>
       <c r="Q90" s="116" t="str">
-        <f>Data!M64</f>
+        <f>Data!M65</f>
         <v/>
       </c>
     </row>
@@ -12414,24 +12524,24 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>91481.292751738802</v>
+        <v>80884.201330546348</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>91481.292751738802</v>
+        <v>80884.201330546348</v>
       </c>
       <c r="H91" s="76">
         <f t="shared" si="37"/>
-        <v>85642.061299500172</v>
+        <v>75721.379969022106</v>
       </c>
       <c r="I91" s="76">
         <f t="shared" si="37"/>
-        <v>82251.414236233584</v>
+        <v>72723.50169843038</v>
       </c>
       <c r="J91" s="76">
         <f t="shared" si="37"/>
-        <v>44109.554390210738</v>
+        <v>38999.952564954066</v>
       </c>
       <c r="K91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12469,24 +12579,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.5892200548228127</v>
+        <v>0.61287975046304477</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.47838412945355452</v>
+        <v>0.2647720058869748</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>0.37478145784095834</v>
+        <v>0.44902665783547285</v>
       </c>
       <c r="I92" s="174">
         <f t="shared" si="38"/>
-        <v>0.6120028692929782</v>
+        <v>0.5717757182764398</v>
       </c>
       <c r="J92" s="174">
         <f t="shared" si="38"/>
-        <v>0.33851171289240484</v>
+        <v>0.38403559151290151</v>
       </c>
       <c r="K92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12524,24 +12634,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.0061347106970835E-2</v>
+        <v>8.1992488015582468E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.0061347106970835E-2</v>
+        <v>8.1992488015582468E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4312750483121646E-2</v>
+        <v>7.6758924950758062E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.0974732043539874E-2</v>
+        <v>7.3719969331116686E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3424898896556874E-2</v>
+        <v>3.9534335391683613E-2</v>
       </c>
       <c r="K93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12661,22 +12771,22 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.14836254115069858</v>
+        <v>-0.46422661070187343</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-8.7024631071357605E-2</v>
+        <v>0.63744352103797386</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.84846126721901349</v>
+        <v>0.54082683636988382</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>7.5752427740563455E-2</v>
+        <v>0.27572842600778635</v>
       </c>
       <c r="J97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12817,47 +12927,47 @@
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
-        <f>IF(G$4="","",Data!D76)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v>117877</v>
       </c>
       <c r="H102" s="188">
-        <f>IF(H$4="","",Data!E76)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v>23709</v>
       </c>
       <c r="I102" s="188">
-        <f>IF(I$4="","",Data!F76)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v>27379</v>
       </c>
       <c r="J102" s="188" t="str">
-        <f>IF(J$4="","",Data!G76)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v/>
       </c>
       <c r="K102" s="188" t="str">
-        <f>IF(K$4="","",Data!H76)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L102" s="188" t="str">
-        <f>IF(L$4="","",Data!I76)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M102" s="188" t="str">
-        <f>IF(M$4="","",Data!J76)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N102" s="188" t="str">
-        <f>IF(N$4="","",Data!K76)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O102" s="188" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P102" s="188" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q102" s="188" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
@@ -12874,47 +12984,47 @@
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
-        <f>IF(G$4="","",Data!D77)</f>
+        <f>IF(G$4="","",Data!D78)</f>
         <v>167751</v>
       </c>
       <c r="H103" s="188">
-        <f>IF(H$4="","",Data!E77)</f>
+        <f>IF(H$4="","",Data!E78)</f>
         <v>110386</v>
       </c>
       <c r="I103" s="188">
-        <f>IF(I$4="","",Data!F77)</f>
+        <f>IF(I$4="","",Data!F78)</f>
         <v>109354</v>
       </c>
       <c r="J103" s="188" t="str">
-        <f>IF(J$4="","",Data!G77)</f>
+        <f>IF(J$4="","",Data!G78)</f>
         <v/>
       </c>
       <c r="K103" s="188" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
+        <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
       <c r="L103" s="188" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
+        <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
       <c r="M103" s="188" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
+        <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
       <c r="N103" s="188" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
+        <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
       <c r="O103" s="188" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
+        <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
       <c r="P103" s="188" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
+        <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
       <c r="Q103" s="188" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
@@ -12931,47 +13041,47 @@
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
-        <f>Data!C78</f>
+        <f>Data!C79</f>
         <v>1122089</v>
       </c>
       <c r="H104" s="186">
-        <f>Data!D78</f>
+        <f>Data!D79</f>
         <v>1136250</v>
       </c>
       <c r="I104" s="186">
-        <f>Data!E78</f>
+        <f>Data!E79</f>
         <v>689466</v>
       </c>
       <c r="J104" s="186">
-        <f>Data!F78</f>
+        <f>Data!F79</f>
         <v>707978</v>
       </c>
       <c r="K104" s="186" t="str">
-        <f>Data!G78</f>
+        <f>Data!G79</f>
         <v/>
       </c>
       <c r="L104" s="186" t="str">
-        <f>Data!H78</f>
+        <f>Data!H79</f>
         <v/>
       </c>
       <c r="M104" s="186" t="str">
-        <f>Data!I78</f>
+        <f>Data!I79</f>
         <v/>
       </c>
       <c r="N104" s="186" t="str">
-        <f>Data!J78</f>
+        <f>Data!J79</f>
         <v/>
       </c>
       <c r="O104" s="186" t="str">
-        <f>Data!K78</f>
+        <f>Data!K79</f>
         <v/>
       </c>
       <c r="P104" s="186" t="str">
-        <f>Data!L78</f>
+        <f>Data!L79</f>
         <v/>
       </c>
       <c r="Q104" s="186" t="str">
-        <f>Data!M78</f>
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
@@ -12988,47 +13098,47 @@
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
-        <f>Data!C79</f>
+        <f>Data!C80</f>
         <v>1630621</v>
       </c>
       <c r="H105" s="186">
-        <f>Data!D79</f>
+        <f>Data!D80</f>
         <v>1534416</v>
       </c>
       <c r="I105" s="186">
-        <f>Data!E79</f>
+        <f>Data!E80</f>
         <v>1291608</v>
       </c>
       <c r="J105" s="186">
-        <f>Data!F79</f>
+        <f>Data!F80</f>
         <v>1238930</v>
       </c>
       <c r="K105" s="186" t="str">
-        <f>Data!G79</f>
+        <f>Data!G80</f>
         <v/>
       </c>
       <c r="L105" s="186" t="str">
-        <f>Data!H79</f>
+        <f>Data!H80</f>
         <v/>
       </c>
       <c r="M105" s="186" t="str">
-        <f>Data!I79</f>
+        <f>Data!I80</f>
         <v/>
       </c>
       <c r="N105" s="186" t="str">
-        <f>Data!J79</f>
+        <f>Data!J80</f>
         <v/>
       </c>
       <c r="O105" s="186" t="str">
-        <f>Data!K79</f>
+        <f>Data!K80</f>
         <v/>
       </c>
       <c r="P105" s="186" t="str">
-        <f>Data!L79</f>
+        <f>Data!L80</f>
         <v/>
       </c>
       <c r="Q105" s="186" t="str">
-        <f>Data!M79</f>
+        <f>Data!M80</f>
         <v/>
       </c>
     </row>
@@ -13206,462 +13316,573 @@
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
-      <c r="B112" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H114*(1/#REF!)=H116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I114*(1/#REF!)=I116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J114*(1/#REF!)=J116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K114*(1/#REF!)=K116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L114*(1/#REF!)=L116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M114*(1/#REF!)=M116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N114*(1/#REF!)=N116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O114*(1/#REF!)=O116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P114*(1/#REF!)=P116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q114*(1/#REF!)=Q116,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B112" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="308"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C113" s="173"/>
+      <c r="E113" s="308"/>
+      <c r="G113" s="340">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>2.5325501550271508</v>
+      </c>
+      <c r="H113" s="340">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>2.4106818167904347</v>
+      </c>
+      <c r="I113" s="340">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>2.089210991434657</v>
+      </c>
+      <c r="J113" s="340">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>1.9893115689283667</v>
+      </c>
+      <c r="K113" s="340" t="str">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v/>
+      </c>
+      <c r="L113" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M113" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N113" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O113" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P113" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="10"/>
+      <c r="B114" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C114" s="173"/>
+      <c r="E114" s="308"/>
+      <c r="G114" s="340">
+        <f>IF(G$4="","",Data!C$22/G19)</f>
+        <v>1.4946533044928882</v>
+      </c>
+      <c r="H114" s="340">
+        <f>IF(H$4="","",Data!D$22/H19)</f>
+        <v>2.3350383877696497</v>
+      </c>
+      <c r="I114" s="340">
+        <f>IF(I$4="","",Data!E$22/I19)</f>
+        <v>2.1747109009597989</v>
+      </c>
+      <c r="J114" s="340">
+        <f>IF(J$4="","",Data!F$22/J19)</f>
+        <v>2.5273216075523925</v>
+      </c>
+      <c r="K114" s="340" t="str">
+        <f>IF(K$4="","",Data!G$22/K19)</f>
+        <v/>
+      </c>
+      <c r="L114" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/L19)</f>
+        <v/>
+      </c>
+      <c r="M114" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/M19)</f>
+        <v/>
+      </c>
+      <c r="N114" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/N19)</f>
+        <v/>
+      </c>
+      <c r="O114" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/O19)</f>
+        <v/>
+      </c>
+      <c r="P114" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/P19)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Q19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="10"/>
+      <c r="E115" s="308"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10"/>
+      <c r="B116" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
+      <c r="E116" s="311"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10"/>
+      <c r="B117" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C113" s="23">
+      <c r="C117" s="23">
         <f>C81</f>
-        <v>9.270308741122768E-2</v>
-      </c>
-      <c r="E113" s="308"/>
-      <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>8.8855103176242761E-2</v>
-      </c>
-      <c r="H113" s="23">
+        <v>8.3226552201047743E-2</v>
+      </c>
+      <c r="E117" s="308"/>
+      <c r="G117" s="23">
+        <f t="shared" ref="G117:Q117" si="45">G81</f>
+        <v>0.12680129733617126</v>
+      </c>
+      <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>9.0469556570823464E-2</v>
-      </c>
-      <c r="I113" s="23">
+        <v>7.1984089342409463E-2</v>
+      </c>
+      <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>8.5625827010639644E-2</v>
-      </c>
-      <c r="J113" s="23">
+        <v>8.1732607278169167E-2</v>
+      </c>
+      <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>8.5198811819571563E-2</v>
-      </c>
-      <c r="K113" s="23" t="str">
+        <v>6.8576957689883505E-2</v>
+      </c>
+      <c r="K117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="L113" s="23" t="str">
+      <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="M113" s="23" t="str">
+      <c r="M117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="N113" s="23" t="str">
+      <c r="N117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="O113" s="23" t="str">
+      <c r="O117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="P113" s="23" t="str">
+      <c r="P117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="Q113" s="23" t="str">
+      <c r="Q117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C114" s="42">
+      <c r="C118" s="42">
         <f>C4/C101</f>
         <v>0.88785641497281542</v>
       </c>
-      <c r="E114" s="308"/>
-      <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
+      <c r="E118" s="308"/>
+      <c r="G118" s="42">
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.0938355293510758</v>
       </c>
-      <c r="H114" s="42">
+      <c r="H118" s="42">
         <f t="shared" si="46"/>
         <v>1.2128686252792376</v>
       </c>
-      <c r="I114" s="42">
+      <c r="I118" s="42">
         <f t="shared" si="46"/>
         <v>0.93458750152694947</v>
       </c>
-      <c r="J114" s="42">
+      <c r="J118" s="42">
         <f t="shared" si="46"/>
         <v>0.88845235624898555</v>
       </c>
-      <c r="K114" s="42" t="str">
+      <c r="K118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="L114" s="42" t="str">
+      <c r="L118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="M114" s="42" t="str">
+      <c r="M118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="N114" s="42" t="str">
+      <c r="N118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="O114" s="42" t="str">
+      <c r="O118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="P114" s="42" t="str">
+      <c r="P118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="Q114" s="42" t="str">
+      <c r="Q118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C119" s="15">
         <f>C101/C105</f>
         <v>1.6496094217869288</v>
       </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="312"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D119" s="11"/>
+      <c r="E119" s="312"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="15">
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.6881359923611925</v>
       </c>
-      <c r="H115" s="15">
+      <c r="H119" s="15">
         <f t="shared" si="47"/>
         <v>1.7405097444239372</v>
       </c>
-      <c r="I115" s="15">
+      <c r="I119" s="15">
         <f t="shared" si="47"/>
         <v>1.5338043740825389</v>
       </c>
-      <c r="J115" s="15">
+      <c r="J119" s="15">
         <f t="shared" si="47"/>
         <v>1.5714431000944362</v>
       </c>
-      <c r="K115" s="15" t="str">
+      <c r="K119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="L115" s="15" t="str">
+      <c r="L119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="M115" s="15" t="str">
+      <c r="M119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="N115" s="15" t="str">
+      <c r="N119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O115" s="15" t="str">
+      <c r="O119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P115" s="15" t="str">
+      <c r="P119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q115" s="15" t="str">
+      <c r="Q119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="10"/>
-      <c r="B116" s="71" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="10"/>
+      <c r="B120" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="C116" s="105">
+      <c r="C120" s="105">
         <f>C8/C105</f>
         <v>0.13507619665462728</v>
       </c>
-      <c r="D116" s="106"/>
-      <c r="E116" s="311"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
+      <c r="D120" s="106"/>
+      <c r="E120" s="311"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="105">
+        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
         <v>0.16335616921406015</v>
       </c>
-      <c r="H116" s="105">
+      <c r="H120" s="105">
         <f t="shared" si="48"/>
         <v>0.19258792921867343</v>
       </c>
-      <c r="I116" s="105">
+      <c r="I120" s="105">
         <f t="shared" si="48"/>
         <v>0.12308842930672464</v>
       </c>
-      <c r="J116" s="105">
+      <c r="J120" s="105">
         <f t="shared" si="48"/>
         <v>0.12088576432889671</v>
       </c>
-      <c r="K116" s="105" t="str">
+      <c r="K120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="L116" s="105" t="str">
+      <c r="L120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="M116" s="105" t="str">
+      <c r="M120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="N116" s="105" t="str">
+      <c r="N120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="O116" s="105" t="str">
+      <c r="O120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="P116" s="105" t="str">
+      <c r="P120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="Q116" s="105" t="str">
+      <c r="Q120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="10"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="54" t="s">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="10"/>
+      <c r="B122" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="C118" s="54"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="67" t="s">
+      <c r="C122" s="54"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="F118" s="56"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
-      <c r="K118" s="37"/>
-      <c r="L118" s="37"/>
-      <c r="M118" s="37"/>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
-    </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="10"/>
-      <c r="B119" s="182" t="s">
+      <c r="F122" s="56"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="C119" s="183"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="305"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
-    </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="10"/>
-      <c r="B120" s="27" t="str">
+      <c r="C123" s="183"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="305"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10"/>
+      <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="181">
+      <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.79766463505953811</v>
-      </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="305"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="181">
-        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.98247406438183571</v>
-      </c>
-      <c r="H120" s="181">
+        <v>0.76687147787947652</v>
+      </c>
+      <c r="D124" s="27"/>
+      <c r="E124" s="305"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="181">
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>1.7751121325138595</v>
+      </c>
+      <c r="H124" s="181">
         <f t="shared" si="49"/>
-        <v>1.1740175261998091</v>
-      </c>
-      <c r="I120" s="181">
+        <v>0.97989727852910624</v>
+      </c>
+      <c r="I124" s="181">
         <f t="shared" si="49"/>
-        <v>0.69048695880819866</v>
-      </c>
-      <c r="J120" s="181">
+        <v>0.7390660122360998</v>
+      </c>
+      <c r="J124" s="181">
         <f t="shared" si="49"/>
-        <v>0.6694598484160299</v>
-      </c>
-      <c r="K120" s="181" t="str">
+        <v>0.59010155571059042</v>
+      </c>
+      <c r="K124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="L120" s="181" t="str">
+      <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="181" t="str">
+      <c r="M124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="181" t="str">
+      <c r="N124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="181" t="str">
+      <c r="O124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="181" t="str">
+      <c r="P124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="181" t="str">
+      <c r="Q124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27" t="s">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10"/>
+      <c r="B125" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="79">
+      <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.14372335766838523</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="305"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="79">
-        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.1770223539426731</v>
-      </c>
-      <c r="H121" s="79">
-        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.21153468940537101</v>
-      </c>
-      <c r="I121" s="79">
-        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12441206465012589</v>
-      </c>
-      <c r="J121" s="79">
-        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.12062339611099639</v>
-      </c>
-      <c r="K121" s="79" t="str">
-        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>0.14227671203700865</v>
+      </c>
+      <c r="D125" s="27"/>
+      <c r="E125" s="305"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="79">
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <v>0.32933434740516876</v>
+      </c>
+      <c r="H125" s="79">
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <v>0.18179912403137408</v>
+      </c>
+      <c r="I125" s="79">
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <v>0.13711799855957327</v>
+      </c>
+      <c r="J125" s="79">
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <v>0.10948080810957152</v>
+      </c>
+      <c r="K125" s="79" t="str">
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="L125" s="79" t="str">
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M125" s="79" t="str">
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N125" s="79" t="str">
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O125" s="79" t="str">
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P125" s="79" t="str">
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="79" t="str">
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14341,6 +14562,10 @@
     <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14402,7 +14627,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>155258.28084593726</v>
+        <v>131974.01491799403</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14434,16 +14659,16 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1940728.5105742158</v>
+        <v>1649675.1864749254</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="347" t="s">
+      <c r="E6" s="349" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="347"/>
+      <c r="F6" s="349"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14458,8 +14683,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14468,14 +14693,14 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>45325.581824401161</v>
+        <v>46208.672776167194</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14490,8 +14715,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14500,7 +14725,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>1746692.892398617</v>
+        <v>1456522.6592510927</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14514,7 +14739,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>0.94030000000000002</v>
+        <v>1.06349396</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14528,7 +14753,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14581,7 +14806,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>8.7000589400070361</v>
+        <v>8.2002399621897837</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14616,7 +14841,7 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>153843.22264710895</v>
+        <v>130771.17465192598</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14628,7 +14853,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>142447.42837695271</v>
+        <v>121084.42097400552</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14638,7 +14863,7 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>152441.06160065898</v>
+        <v>129579.29733721295</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14650,7 +14875,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>130693.63991826044</v>
+        <v>111093.36191462015</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14660,7 +14885,7 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>151051.68015909739</v>
+        <v>128398.28305509948</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14672,7 +14897,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>119909.69377055817</v>
+        <v>101926.69678077169</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14682,7 +14907,7 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>149674.96184628789</v>
+        <v>127228.03279751168</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14694,7 +14919,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>110015.56517319175</v>
+        <v>93516.402218737334</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14704,7 +14929,7 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>148310.7912476834</v>
+        <v>126068.44845875706</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14716,7 +14941,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>100937.83246195393</v>
+        <v>85800.067697145802</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14726,7 +14951,7 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>146959.0540006505</v>
+        <v>124919.43282730001</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14738,7 +14963,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>92609.132226683942</v>
+        <v>78720.432375228687</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14748,7 +14973,7 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>145619.63678488199</v>
+        <v>123780.88957761235</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14760,7 +14985,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>84967.659425539168</v>
+        <v>72224.960185539574</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14770,7 +14995,7 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>144292.42731289691</v>
+        <v>122652.72326209795</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14782,7 +15007,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>77956.708746421224</v>
+        <v>66265.449977943194</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14792,7 +15017,7 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>142977.31432062719</v>
+        <v>121534.83930309111</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14804,7 +15029,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>71524.253812123716</v>
+        <v>60797.677831859182</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14814,7 +15039,7 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>141674.18755808999</v>
+        <v>120427.14398492787</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14826,7 +15051,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>65622.561106595473</v>
+        <v>55781.068882455242</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15276,7 +15501,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1923040.283088862</v>
+        <v>1634639.6831490747</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15288,7 +15513,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>890739.73645128857</v>
+        <v>757154.45659946289</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15299,7 +15524,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>1887424.2114695692</v>
+        <v>1604364.9954377692</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15320,7 +15545,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>1887424.2114695692</v>
+        <v>1604364.9954377692</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -15350,19 +15575,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1523214.3982047057</v>
+        <v>1294776.1537527773</v>
       </c>
       <c r="C56" s="127">
-        <v>1653061.792391649</v>
+        <v>1405150.1823979535</v>
       </c>
       <c r="D56" s="127">
-        <v>1940728.5105742156</v>
+        <v>1649675.1864749249</v>
       </c>
       <c r="E56" s="127">
-        <v>2003346.5715186202</v>
+        <v>1702902.3435977912</v>
       </c>
       <c r="F56" s="127">
-        <v>2134291.1420977451</v>
+        <v>1814209.0038086427</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15371,19 +15596,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>1285549.8963933</v>
+        <v>1092754.475188269</v>
       </c>
       <c r="C57" s="127">
-        <v>1459955.5359116325</v>
+        <v>1241004.2970088164</v>
       </c>
       <c r="D57" s="127">
-        <v>1940728.5105742151</v>
+        <v>1649675.1864749247</v>
       </c>
       <c r="E57" s="127">
-        <v>2066022.2938019421</v>
+        <v>1756178.5145211511</v>
       </c>
       <c r="F57" s="127">
-        <v>2355786.2458907785</v>
+        <v>2002486.2278830931</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15392,19 +15617,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>1078008.7889148002</v>
+        <v>916338.55028411746</v>
       </c>
       <c r="C58" s="127">
-        <v>1276524.5526965042</v>
+        <v>1085082.6728393636</v>
       </c>
       <c r="D58" s="127">
-        <v>1940728.5105742151</v>
+        <v>1649675.1864749244</v>
       </c>
       <c r="E58" s="127">
-        <v>2143600.8784768814</v>
+        <v>1822122.5481367675</v>
       </c>
       <c r="F58" s="127">
-        <v>2660461.3066923148</v>
+        <v>2261468.8135479582</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15413,19 +15638,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>922932.01487291814</v>
+        <v>784518.82138253155</v>
       </c>
       <c r="C59" s="127">
-        <v>1130784.4185633431</v>
+        <v>961199.35704169539</v>
       </c>
       <c r="D59" s="127">
-        <v>1940728.5105742149</v>
+        <v>1649675.1864749244</v>
       </c>
       <c r="E59" s="127">
-        <v>2222641.0151735893</v>
+        <v>1889308.9431083992</v>
       </c>
       <c r="F59" s="127">
-        <v>3008012.7361043701</v>
+        <v>2556897.5486858366</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15434,19 +15659,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>813213.67651813768</v>
+        <v>691255.07052868966</v>
       </c>
       <c r="C60" s="127">
-        <v>1023196.8550597288</v>
+        <v>869746.82624299312</v>
       </c>
       <c r="D60" s="127">
-        <v>1940728.5105742146</v>
+        <v>1649675.1864749242</v>
       </c>
       <c r="E60" s="127">
-        <v>2296152.7282394725</v>
+        <v>1951796.0186057189</v>
       </c>
       <c r="F60" s="127">
-        <v>3372236.0668624863</v>
+        <v>2866497.8806298133</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15455,19 +15680,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>737280.25041446881</v>
+        <v>626709.46912966296</v>
       </c>
       <c r="C61" s="127">
-        <v>946599.08605010877</v>
+        <v>804636.51422046276</v>
       </c>
       <c r="D61" s="127">
-        <v>1940728.5105742146</v>
+        <v>1649675.1864749244</v>
       </c>
       <c r="E61" s="127">
-        <v>2361000.2852441529</v>
+        <v>2006918.3116576658</v>
       </c>
       <c r="F61" s="127">
-        <v>3736413.1119646057</v>
+        <v>3176058.8684317451</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15517,23 +15742,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15544,23 +15769,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.8288718690172443</v>
+        <v>6.4012884587026022</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>7.4959839466032196</v>
+        <v>7.0426472483039735</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>8.9739184343975715</v>
+        <v>8.4635273463407916</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>9.2956288929908766</v>
+        <v>8.7728184493772456</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>9.9683778924962319</v>
+        <v>9.4195965523755056</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15571,23 +15796,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>5.60783188924239</v>
+        <v>5.2273856771533396</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>6.5038691894155249</v>
+        <v>6.0888322280181892</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>8.9739184343975698</v>
+        <v>8.4635273463407916</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>9.6176355960782836</v>
+        <v>9.0823943606438959</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>11.106344963701037</v>
+        <v>10.513633383540615</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15598,23 +15823,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>4.541555740526281</v>
+        <v>4.2022722020742727</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>5.561462720094271</v>
+        <v>5.1828065498989311</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>8.9739184343975698</v>
+        <v>8.4635273463407898</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>10.016208175241234</v>
+        <v>9.4655803881930698</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>12.67166257421327</v>
+        <v>12.01852325399938</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15625,23 +15850,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>3.7448236261531029</v>
+        <v>3.4362972457221024</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>4.8126991097190359</v>
+        <v>4.4629483147046747</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>8.973918434397568</v>
+        <v>8.4635273463407898</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>10.422289715302838</v>
+        <v>9.8559854996637242</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>14.457264492487008</v>
+        <v>13.735193545980923</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15652,23 +15877,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>3.1811278422873177</v>
+        <v>2.8943624527682705</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>4.259950527733813</v>
+        <v>3.9315381163182881</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>8.9739184343975662</v>
+        <v>8.4635273463407881</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>10.799968081028693</v>
+        <v>10.219083916914821</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>16.32852101179391</v>
+        <v>15.534211816792675</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15678,23 +15903,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.7910075324926571</v>
+        <v>2.5193024019980603</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>3.8664170483565532</v>
+        <v>3.5531966584416144</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>8.9739184343975662</v>
+        <v>8.4635273463407898</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>11.133132937748764</v>
+        <v>10.539387230890066</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>18.199539731025368</v>
+        <v>17.333001467596354</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15729,7 +15954,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>11.106344963701037</v>
+        <v>10.513633383540615</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15751,7 +15976,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>9.2956288929908766</v>
+        <v>8.7728184493772456</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15774,7 +15999,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.9739184343975715</v>
+        <v>8.4635273463407916</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15797,7 +16022,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.4959839466032196</v>
+        <v>7.0426472483039735</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15820,7 +16045,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>5.60783188924239</v>
+        <v>5.2273856771533396</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15921,7 +16146,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-5.55</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15941,7 +16166,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.49984047644368812</v>
+        <v>0.44193951040398949</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15950,7 +16175,7 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>0.49984047644368812</v>
+        <v>0.44193951040398949</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15970,7 +16195,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>9.2039555847924852</v>
+        <v>8.646079056045334</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15985,11 +16210,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="349" t="str">
+      <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="349"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -16004,14 +16229,14 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>191229.78192490508</v>
+        <v>305486.2278947797</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -16026,14 +16251,14 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>155258.28084593726</v>
+        <v>131974.01491799403</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -16043,8 +16268,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -16057,8 +16282,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="349"/>
-      <c r="F11" s="349"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -16076,8 +16301,8 @@
         <v>0.20294093668232471</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -16094,8 +16319,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.21158962892889099</v>
       </c>
-      <c r="E13" s="349"/>
-      <c r="F13" s="349"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -16110,10 +16335,10 @@
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.13640251598693887</v>
-      </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349"/>
+        <v>0.44355392169299579</v>
+      </c>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16139,21 +16364,21 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="351" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="350"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="350"/>
-      <c r="F19" s="350"/>
+      <c r="E19" s="352"/>
+      <c r="F19" s="352"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="350"/>
-      <c r="F20" s="350"/>
+      <c r="E20" s="352"/>
+      <c r="F20" s="352"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16161,14 +16386,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>5.39</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="350"/>
-      <c r="F21" s="350"/>
+      <c r="E21" s="352"/>
+      <c r="F21" s="352"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16176,14 +16401,14 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>8.9739184343975733</v>
+        <v>8.463527346340797</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16203,8 +16428,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
+      <c r="E25" s="350"/>
+      <c r="F25" s="350"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -16214,8 +16439,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
+      <c r="E26" s="350"/>
+      <c r="F26" s="350"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16223,14 +16448,14 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>8.9739184343975715</v>
+        <v>8.4635273463407916</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="348"/>
-      <c r="F27" s="348"/>
+      <c r="E27" s="350"/>
+      <c r="F27" s="350"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16240,8 +16465,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="348"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16261,8 +16486,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -16272,8 +16497,8 @@
         <v>-0.1</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16281,14 +16506,14 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>7.4959839466032196</v>
+        <v>7.0426472483039735</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="348"/>
-      <c r="F33" s="348"/>
+      <c r="E33" s="350"/>
+      <c r="F33" s="350"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16298,8 +16523,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="350"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16319,8 +16544,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -16330,8 +16555,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="348"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16339,14 +16564,14 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>9.2956288929908766</v>
+        <v>8.7728184493772456</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="348"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16357,8 +16582,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16366,7 +16591,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.7426736285573625</v>
+        <v>8.2412095473407199</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16420,8 +16645,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="348"/>
-      <c r="F49" s="348"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16431,8 +16656,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16440,14 +16665,14 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>5.60783188924239</v>
+        <v>5.2273856771533396</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16457,8 +16682,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16478,8 +16703,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="348"/>
-      <c r="F55" s="348"/>
+      <c r="E55" s="350"/>
+      <c r="F55" s="350"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16489,8 +16714,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
+      <c r="E56" s="350"/>
+      <c r="F56" s="350"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16498,14 +16723,14 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>11.106344963701037</v>
+        <v>10.513633383540615</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="348"/>
-      <c r="F57" s="348"/>
+      <c r="E57" s="350"/>
+      <c r="F57" s="350"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16515,8 +16740,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16524,7 +16749,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>8.7041151083487964</v>
+        <v>8.2041395456413451</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16585,7 +16810,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>8.7000589400070361</v>
+        <v>8.2002399621897837</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16648,7 +16873,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>-0.11453082725094711</v>
+        <v>-0.13680485575710941</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16681,7 +16906,7 @@
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>0.49984047644368812</v>
+        <v>0.44193951040398949</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16708,7 +16933,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.0529047073235096</v>
+        <v>0.93093739460099634</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16720,7 +16945,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>5.0371036506648128</v>
+        <v>4.7477659407646673</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16730,7 +16955,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>6.0900083579883226</v>
+        <v>5.6787033353656637</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16966,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.30032998390072763</v>
+        <v>0.30782462880185679</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16758,7 +16983,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>5.39</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16771,7 +16996,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24044193847338047</v>
+        <v>0.22246108266706432</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A8742B-358F-4169-BFC2-7F4F9DCDAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6124126D-961A-4C35-9A4A-D22622A18342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="416">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1805,10 +1805,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNS_05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2306,27 +2302,35 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>CNY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Income/Market Cap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国石油股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>0857.HK</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国石油股份</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CFO/Net Income</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CFO/FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Net Change in Cash</t>
+    <t>ENG_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4076,10 +4080,10 @@
         <v>328</v>
       </c>
       <c r="C5" s="339" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4143,7 +4147,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="341" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C12" s="341"/>
       <c r="D12" s="341"/>
@@ -4172,7 +4176,7 @@
         <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4195,7 +4199,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4226,7 +4230,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -4241,7 +4245,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4251,7 +4255,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="341" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C25" s="341"/>
       <c r="D25" s="341"/>
@@ -4484,7 +4488,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="341" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C54" s="341"/>
       <c r="D54" s="341"/>
@@ -4519,7 +4523,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
@@ -4537,7 +4541,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4551,7 +4555,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="341" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C63" s="341"/>
       <c r="D63" s="341"/>
@@ -4618,13 +4622,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="341" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C73" s="341"/>
       <c r="D73" s="341"/>
@@ -4633,7 +4637,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="341" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C74" s="341"/>
       <c r="D74" s="341"/>
@@ -4663,7 +4667,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4676,7 +4680,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="341" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C81" s="341"/>
       <c r="D81" s="341"/>
@@ -4805,7 +4809,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="341" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C98" s="341"/>
       <c r="D98" s="341"/>
@@ -4827,7 +4831,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4837,7 +4841,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="342" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C104" s="342"/>
       <c r="D104" s="342"/>
@@ -4986,7 +4990,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="346" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C115" s="346"/>
       <c r="D115" s="346"/>
@@ -4995,7 +4999,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -5005,7 +5009,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="344" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C119" s="344"/>
       <c r="D119" s="344"/>
@@ -5014,7 +5018,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="341" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C120" s="341"/>
       <c r="D120" s="341"/>
@@ -5106,7 +5110,7 @@
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="253" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5116,7 +5120,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B134" s="348" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C134" s="341"/>
       <c r="D134" s="341"/>
@@ -5125,12 +5129,12 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="345" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C137" s="345"/>
       <c r="D137" s="345"/>
@@ -5139,27 +5143,27 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="244" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="244" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="342" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C143" s="342"/>
       <c r="D143" s="342"/>
@@ -5168,12 +5172,12 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="347" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C146" s="347"/>
       <c r="D146" s="347"/>
@@ -5182,7 +5186,7 @@
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="347" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C147" s="347"/>
       <c r="D147" s="347"/>
@@ -5191,22 +5195,22 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="244" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="244" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="244" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -5735,7 +5739,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C22" s="184">
         <v>456596</v>
@@ -5759,7 +5763,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C23" s="184">
         <v>-255789</v>
@@ -5783,7 +5787,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C24" s="184">
         <v>-146572</v>
@@ -5838,13 +5842,13 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="100"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="184">
+      <c r="C28" s="186">
         <f>68761+31090</f>
         <v>99851</v>
       </c>
@@ -5872,7 +5876,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="184">
+      <c r="C29" s="186">
         <v>180533</v>
       </c>
       <c r="D29" s="184">
@@ -5896,7 +5900,7 @@
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="185">
+      <c r="C30" s="189">
         <v>1122089</v>
       </c>
       <c r="D30" s="185">
@@ -5920,7 +5924,7 @@
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="185">
+      <c r="C31" s="189">
         <v>1630621</v>
       </c>
       <c r="D31" s="185">
@@ -5944,7 +5948,7 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184">
+      <c r="C32" s="186">
         <v>184211</v>
       </c>
       <c r="D32" s="184">
@@ -7081,7 +7085,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C64" s="186">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7686,7 +7690,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11951,7 +11955,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13324,7 +13328,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C113" s="173"/>
       <c r="E113" s="308"/>
@@ -13376,7 +13380,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C114" s="173"/>
       <c r="E114" s="308"/>
@@ -13883,7 +13887,56 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C126" s="173"/>
+      <c r="G126" s="23">
+        <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.18276137259990091</v>
+      </c>
+      <c r="H126" s="23">
+        <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.16558114872392748</v>
+      </c>
+      <c r="I126" s="23">
+        <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.13420808117982194</v>
+      </c>
+      <c r="J126" s="23">
+        <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.1307858227537371</v>
+      </c>
+      <c r="K126" s="23" t="str">
+        <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="L126" s="23" t="str">
+        <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="M126" s="23" t="str">
+        <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="N126" s="23" t="str">
+        <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="O126" s="23" t="str">
+        <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="P126" s="23" t="str">
+        <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="23" t="str">
+        <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+    </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6124126D-961A-4C35-9A4A-D22622A18342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5127F26-5E27-4DC8-9729-A6E825288D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="417">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2332,6 +2332,9 @@
   <si>
     <t>ENG_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -4091,7 +4094,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4127,7 @@
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -4136,7 +4139,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>986483.07043901994</v>
+        <v>984652.86066083994</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06349396</v>
+        <v>1.0598962000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4208,7 +4211,7 @@
         <v>280</v>
       </c>
       <c r="C19" s="255">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -4219,7 +4222,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>5.6787033353656637</v>
+        <v>4.8893162027611039</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4234,7 +4237,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22246108266706432</v>
+        <v>0.20806555381768388</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4295,7 +4298,7 @@
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
-        <v>226678.52464455273</v>
+        <v>247357.8376927129</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4321,7 +4324,7 @@
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
-        <v>229584</v>
+        <v>243208.99999999997</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4334,7 +4337,7 @@
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
-        <v>-252845.35040534919</v>
+        <v>-283919.19056768838</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4356,7 +4359,7 @@
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
-        <v>18538.000000000004</v>
+        <v>18644</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4378,7 +4381,7 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>6666.227894779714</v>
+        <v>8793.8666926784372</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
-        <v>-24063</v>
+        <v>-20731</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4408,7 +4411,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>-17396.772105220287</v>
+        <v>-11937.133307321563</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4426,7 +4429,7 @@
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
-        <v>-15629.449081156103</v>
+        <v>-17915.118234001515</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4448,7 +4451,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-56954.938134833108</v>
+        <v>-63516.176096347837</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4501,7 +4504,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>305486.2278947797</v>
+        <v>418605.86669267842</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4514,7 +4517,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>131974.01491799403</v>
+        <v>131923.21948735364</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4527,7 +4530,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
-        <v>0.14227671203700865</v>
+        <v>0.14200427847492361</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4536,7 +4539,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>8.1992488015582468E-2</v>
+        <v>8.2144890409663482E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4658,7 +4661,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.5858934734934564</v>
+        <v>9.5497877274386127</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4712,7 +4715,7 @@
       </c>
       <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
-        <v>245714</v>
+        <v>279749</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4725,7 +4728,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.4277890873651522</v>
+        <v>1.6200596543017649</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4743,7 +4746,7 @@
       </c>
       <c r="C90" s="191">
         <f>BS!C66</f>
-        <v>238880</v>
+        <v>216246</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4756,7 +4759,7 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>46208.672776167194</v>
+        <v>126.15719684722717</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4769,7 +4772,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.26850826054453025</v>
+        <v>7.3059129688398717E-4</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4787,7 +4790,7 @@
       </c>
       <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
-        <v>6352.8</v>
+        <v>2113.7999999999997</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4800,7 +4803,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.6914699667960876E-2</v>
+        <v>1.2241266625664684E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4822,7 +4825,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4880,7 +4883,7 @@
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.51 HKD</v>
+        <v>9.99 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
@@ -4902,7 +4905,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.77 HKD</v>
+        <v>8.25 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
@@ -4916,7 +4919,7 @@
       </c>
       <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
@@ -4924,7 +4927,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.46 HKD</v>
+        <v>8.1 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
@@ -4938,7 +4941,7 @@
       </c>
       <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
@@ -4946,7 +4949,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.04 HKD</v>
+        <v>7.07 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
@@ -4968,7 +4971,7 @@
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>5.23 HKD</v>
+        <v>4.72 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
@@ -4981,7 +4984,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>8.2041395456413451</v>
+        <v>7.8645513251025703</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -5045,7 +5048,7 @@
       </c>
       <c r="C123" s="256">
         <f>C19</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5073,7 +5076,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>0.93093739460099634</v>
+        <v>0.86266592430858746</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5083,7 +5086,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>4.7477659407646673</v>
+        <v>4.0266502784525162</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5092,7 +5095,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>5.6787033353656637</v>
+        <v>4.8893162027611039</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5105,7 +5108,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.30782462880185679</v>
+        <v>0.37830958173607732</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5280,47 +5283,47 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="107">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="D1" s="38">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="E1" s="38">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="F1" s="38">
         <f t="shared" si="0"/>
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="G1" s="38">
         <f t="shared" si="0"/>
-        <v>43830</v>
+        <v>44196</v>
       </c>
       <c r="H1" s="38">
         <f t="shared" si="0"/>
-        <v>43465</v>
+        <v>43830</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" si="0"/>
-        <v>43100</v>
+        <v>43465</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>42735</v>
+        <v>43100</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>42369</v>
+        <v>42735</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>42004</v>
+        <v>42369</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>41639</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
@@ -5352,18 +5355,20 @@
         <v>2</v>
       </c>
       <c r="C4" s="193">
+        <v>2937981</v>
+      </c>
+      <c r="D4" s="184">
         <v>3011012</v>
       </c>
-      <c r="D4" s="184">
+      <c r="E4" s="184">
         <v>3239167</v>
       </c>
-      <c r="E4" s="184">
+      <c r="F4" s="184">
         <v>1851487</v>
       </c>
-      <c r="F4" s="184">
+      <c r="G4" s="184">
         <v>1729735</v>
       </c>
-      <c r="G4" s="184"/>
       <c r="H4" s="184"/>
       <c r="I4" s="184"/>
       <c r="J4" s="184"/>
@@ -5376,18 +5381,21 @@
         <v>44</v>
       </c>
       <c r="C5" s="193">
+        <f>2275223</f>
+        <v>2275223</v>
+      </c>
+      <c r="D5" s="184">
         <v>2302385</v>
       </c>
-      <c r="D5" s="184">
+      <c r="E5" s="184">
         <v>2527935</v>
       </c>
-      <c r="E5" s="184">
+      <c r="F5" s="184">
         <v>1379524</v>
       </c>
-      <c r="F5" s="184">
+      <c r="G5" s="184">
         <v>1278781</v>
       </c>
-      <c r="G5" s="184"/>
       <c r="H5" s="184"/>
       <c r="I5" s="184"/>
       <c r="J5" s="184"/>
@@ -5400,18 +5408,21 @@
         <v>55</v>
       </c>
       <c r="C6" s="193">
+        <f>266012+65026+C7</f>
+        <v>394228</v>
+      </c>
+      <c r="D6" s="184">
         <v>420298</v>
       </c>
-      <c r="D6" s="184">
+      <c r="E6" s="184">
         <v>395706</v>
       </c>
-      <c r="E6" s="184">
+      <c r="F6" s="184">
         <v>296185</v>
       </c>
-      <c r="F6" s="184">
+      <c r="G6" s="184">
         <v>285968</v>
       </c>
-      <c r="G6" s="184"/>
       <c r="H6" s="184"/>
       <c r="I6" s="184"/>
       <c r="J6" s="184"/>
@@ -5424,18 +5435,20 @@
         <v>62</v>
       </c>
       <c r="C7" s="194">
+        <v>63190</v>
+      </c>
+      <c r="D7" s="192">
         <v>70260</v>
       </c>
-      <c r="D7" s="192">
+      <c r="E7" s="192">
         <v>68352</v>
       </c>
-      <c r="E7" s="192">
+      <c r="F7" s="192">
         <v>48552</v>
       </c>
-      <c r="F7" s="192">
+      <c r="G7" s="192">
         <v>47670</v>
       </c>
-      <c r="G7" s="192"/>
       <c r="H7" s="192"/>
       <c r="I7" s="192"/>
       <c r="J7" s="192"/>
@@ -5448,18 +5461,20 @@
         <v>50</v>
       </c>
       <c r="C8" s="193">
+        <v>23014</v>
+      </c>
+      <c r="D8" s="184">
         <v>21957</v>
       </c>
-      <c r="D8" s="184">
+      <c r="E8" s="184">
         <v>20016</v>
       </c>
-      <c r="E8" s="184">
+      <c r="F8" s="184">
         <v>16796</v>
       </c>
-      <c r="F8" s="184">
+      <c r="G8" s="184">
         <v>15217</v>
       </c>
-      <c r="G8" s="184"/>
       <c r="H8" s="184"/>
       <c r="I8" s="184"/>
       <c r="J8" s="184"/>
@@ -5472,18 +5487,20 @@
         <v>161</v>
       </c>
       <c r="C9" s="193">
+        <v>18644</v>
+      </c>
+      <c r="D9" s="184">
         <v>18538</v>
       </c>
-      <c r="D9" s="184">
+      <c r="E9" s="184">
         <v>15251</v>
       </c>
-      <c r="E9" s="184">
+      <c r="F9" s="184">
         <v>12877</v>
       </c>
-      <c r="F9" s="184">
+      <c r="G9" s="184">
         <v>11296</v>
       </c>
-      <c r="G9" s="184"/>
       <c r="H9" s="184"/>
       <c r="I9" s="184"/>
       <c r="J9" s="184"/>
@@ -5495,9 +5512,7 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="184">
-        <v>0</v>
-      </c>
+      <c r="C10" s="184"/>
       <c r="D10" s="184">
         <v>0</v>
       </c>
@@ -5507,7 +5522,9 @@
       <c r="F10" s="184">
         <v>0</v>
       </c>
-      <c r="G10" s="184"/>
+      <c r="G10" s="184">
+        <v>0</v>
+      </c>
       <c r="H10" s="184"/>
       <c r="I10" s="184"/>
       <c r="J10" s="184"/>
@@ -5519,9 +5536,7 @@
       <c r="B11" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="193">
-        <v>0</v>
-      </c>
+      <c r="C11" s="193"/>
       <c r="D11" s="184">
         <v>0</v>
       </c>
@@ -5531,7 +5546,9 @@
       <c r="F11" s="184">
         <v>0</v>
       </c>
-      <c r="G11" s="184"/>
+      <c r="G11" s="184">
+        <v>0</v>
+      </c>
       <c r="H11" s="184"/>
       <c r="I11" s="184"/>
       <c r="J11" s="184"/>
@@ -5544,18 +5561,20 @@
         <v>39</v>
       </c>
       <c r="C12" s="193">
+        <v>20731</v>
+      </c>
+      <c r="D12" s="184">
         <v>24063</v>
       </c>
-      <c r="D12" s="184">
+      <c r="E12" s="184">
         <v>21554</v>
       </c>
-      <c r="E12" s="184">
+      <c r="F12" s="184">
         <v>14912</v>
       </c>
-      <c r="F12" s="184">
+      <c r="G12" s="184">
         <v>15097</v>
       </c>
-      <c r="G12" s="184"/>
       <c r="H12" s="184"/>
       <c r="I12" s="184"/>
       <c r="J12" s="184"/>
@@ -5568,18 +5587,20 @@
         <v>68</v>
       </c>
       <c r="C13" s="193">
+        <v>8799</v>
+      </c>
+      <c r="D13" s="184">
         <v>8265</v>
       </c>
-      <c r="D13" s="184">
+      <c r="E13" s="184">
         <v>4738</v>
       </c>
-      <c r="E13" s="184">
+      <c r="F13" s="184">
         <v>1960</v>
       </c>
-      <c r="F13" s="184">
+      <c r="G13" s="184">
         <v>1732</v>
       </c>
-      <c r="G13" s="184"/>
       <c r="H13" s="184"/>
       <c r="I13" s="184"/>
       <c r="J13" s="184"/>
@@ -5592,18 +5613,20 @@
         <v>51</v>
       </c>
       <c r="C14" s="193">
+        <v>57755</v>
+      </c>
+      <c r="D14" s="184">
         <v>57167</v>
       </c>
-      <c r="D14" s="184">
+      <c r="E14" s="184">
         <v>49929</v>
       </c>
-      <c r="E14" s="184">
+      <c r="F14" s="184">
         <v>24138</v>
       </c>
-      <c r="F14" s="184">
+      <c r="G14" s="184">
         <v>17067</v>
       </c>
-      <c r="G14" s="184"/>
       <c r="H14" s="184"/>
       <c r="I14" s="184"/>
       <c r="J14" s="184"/>
@@ -5616,18 +5639,20 @@
         <v>43</v>
       </c>
       <c r="C15" s="195">
-        <v>180291</v>
+        <v>183747</v>
       </c>
       <c r="D15" s="185">
+        <v>180561</v>
+      </c>
+      <c r="E15" s="185">
         <v>163343</v>
       </c>
-      <c r="E15" s="185">
+      <c r="F15" s="185">
         <v>132394</v>
       </c>
-      <c r="F15" s="185">
+      <c r="G15" s="185">
         <v>129018</v>
       </c>
-      <c r="G15" s="185"/>
       <c r="H15" s="185"/>
       <c r="I15" s="185"/>
       <c r="J15" s="185"/>
@@ -5640,18 +5665,20 @@
         <v>45</v>
       </c>
       <c r="C16" s="193">
+        <v>19071</v>
+      </c>
+      <c r="D16" s="184">
         <v>19147</v>
       </c>
-      <c r="D16" s="184">
+      <c r="E16" s="184">
         <v>14605</v>
-      </c>
-      <c r="E16" s="184">
-        <v>0</v>
       </c>
       <c r="F16" s="184">
         <v>0</v>
       </c>
-      <c r="G16" s="184"/>
+      <c r="G16" s="184">
+        <v>0</v>
+      </c>
       <c r="H16" s="184"/>
       <c r="I16" s="184"/>
       <c r="J16" s="184"/>
@@ -5670,18 +5697,20 @@
         <v>48</v>
       </c>
       <c r="C19" s="184">
+        <v>243209</v>
+      </c>
+      <c r="D19" s="184">
         <v>229584</v>
       </c>
-      <c r="D19" s="184">
+      <c r="E19" s="184">
         <v>222648</v>
       </c>
-      <c r="E19" s="184">
+      <c r="F19" s="184">
         <v>238036</v>
       </c>
-      <c r="F19" s="184">
+      <c r="G19" s="184">
         <v>236818</v>
       </c>
-      <c r="G19" s="184"/>
       <c r="H19" s="184"/>
       <c r="I19" s="184"/>
       <c r="J19" s="184"/>
@@ -5693,19 +5722,19 @@
       <c r="B20" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="184">
+      <c r="C20" s="184"/>
+      <c r="D20" s="184">
         <v>115297</v>
       </c>
-      <c r="D20" s="184">
+      <c r="E20" s="184">
         <v>282508</v>
       </c>
-      <c r="E20" s="184">
+      <c r="F20" s="184">
         <v>245237</v>
       </c>
-      <c r="F20" s="184">
+      <c r="G20" s="184">
         <v>265563</v>
       </c>
-      <c r="G20" s="184"/>
       <c r="H20" s="184"/>
       <c r="I20" s="184"/>
       <c r="J20" s="184"/>
@@ -5717,19 +5746,19 @@
       <c r="B21" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="184">
+      <c r="C21" s="184"/>
+      <c r="D21" s="184">
         <v>31061</v>
       </c>
-      <c r="D21" s="184">
+      <c r="E21" s="184">
         <v>3456</v>
       </c>
-      <c r="E21" s="184">
+      <c r="F21" s="184">
         <v>46237</v>
       </c>
-      <c r="F21" s="184">
+      <c r="G21" s="184">
         <v>34899</v>
       </c>
-      <c r="G21" s="184"/>
       <c r="H21" s="184"/>
       <c r="I21" s="184"/>
       <c r="J21" s="184"/>
@@ -5742,18 +5771,20 @@
         <v>388</v>
       </c>
       <c r="C22" s="184">
+        <v>406532</v>
+      </c>
+      <c r="D22" s="184">
         <v>456596</v>
       </c>
-      <c r="D22" s="184">
+      <c r="E22" s="184">
         <v>393768</v>
       </c>
-      <c r="E22" s="184">
+      <c r="F22" s="184">
         <v>276599</v>
       </c>
-      <c r="F22" s="184">
+      <c r="G22" s="184">
         <v>256657</v>
       </c>
-      <c r="G22" s="184"/>
       <c r="H22" s="184"/>
       <c r="I22" s="184"/>
       <c r="J22" s="184"/>
@@ -5766,18 +5797,20 @@
         <v>390</v>
       </c>
       <c r="C23" s="184">
+        <v>-307347</v>
+      </c>
+      <c r="D23" s="184">
         <v>-255789</v>
       </c>
-      <c r="D23" s="184">
+      <c r="E23" s="184">
         <v>-232971</v>
       </c>
-      <c r="E23" s="184">
+      <c r="F23" s="184">
         <v>-149026</v>
       </c>
-      <c r="F23" s="184">
+      <c r="G23" s="184">
         <v>-140250</v>
       </c>
-      <c r="G23" s="184"/>
       <c r="H23" s="184"/>
       <c r="I23" s="184"/>
       <c r="J23" s="184"/>
@@ -5790,18 +5823,20 @@
         <v>389</v>
       </c>
       <c r="C24" s="184">
+        <v>-178876</v>
+      </c>
+      <c r="D24" s="184">
         <v>-146572</v>
       </c>
-      <c r="D24" s="184">
+      <c r="E24" s="184">
         <v>-113713</v>
       </c>
-      <c r="E24" s="184">
+      <c r="F24" s="184">
         <v>-135729</v>
       </c>
-      <c r="F24" s="184">
+      <c r="G24" s="184">
         <v>-79554</v>
       </c>
-      <c r="G24" s="184"/>
       <c r="H24" s="184"/>
       <c r="I24" s="184"/>
       <c r="J24" s="184"/>
@@ -5815,22 +5850,21 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
-        <f>(0.25+0.22)/Exchange_Rate</f>
         <v>0.44193951040398949</v>
       </c>
       <c r="D25" s="39">
-        <f>(0.23+0.21)/Exchange_Rate</f>
         <v>0.41373060548458596</v>
       </c>
       <c r="E25" s="39">
-        <f>(0.22+0.20258)/Exchange_Rate</f>
         <v>0.39735063469471893</v>
       </c>
       <c r="F25" s="39">
-        <f>(0.09622+0.1304)/Exchange_Rate</f>
         <v>0.21309006776117467</v>
       </c>
-      <c r="G25" s="39"/>
+      <c r="G25" s="39">
+        <f>(0.08742+0.08742)/Exchange_Rate</f>
+        <v>0.16495954981251937</v>
+      </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
       <c r="J25" s="39"/>
@@ -5842,29 +5876,30 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="100"/>
+      <c r="C27" s="100" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="186">
-        <f>68761+31090</f>
-        <v>99851</v>
+        <f>BS!C4</f>
+        <v>114865</v>
       </c>
       <c r="D28" s="184">
-        <f>72028+45849</f>
+        <v>142879</v>
+      </c>
+      <c r="E28" s="184">
         <v>117877</v>
       </c>
-      <c r="E28" s="184">
-        <f>8474+15235</f>
+      <c r="F28" s="184">
         <v>23709</v>
       </c>
-      <c r="F28" s="184">
-        <f>17969+9410</f>
+      <c r="G28" s="184">
         <v>27379</v>
       </c>
-      <c r="G28" s="184"/>
       <c r="H28" s="184"/>
       <c r="I28" s="184"/>
       <c r="J28" s="184"/>
@@ -5877,18 +5912,21 @@
         <v>32</v>
       </c>
       <c r="C29" s="186">
-        <v>180533</v>
+        <f>BS!C6</f>
+        <v>168338</v>
       </c>
       <c r="D29" s="184">
+        <v>182674</v>
+      </c>
+      <c r="E29" s="184">
         <v>167751</v>
       </c>
-      <c r="E29" s="184">
+      <c r="F29" s="184">
         <v>110386</v>
       </c>
-      <c r="F29" s="184">
+      <c r="G29" s="184">
         <v>109354</v>
       </c>
-      <c r="G29" s="184"/>
       <c r="H29" s="184"/>
       <c r="I29" s="184"/>
       <c r="J29" s="184"/>
@@ -5901,18 +5939,21 @@
         <v>40</v>
       </c>
       <c r="C30" s="189">
-        <v>1122089</v>
+        <f>BS!C33+BS!C42</f>
+        <v>1043144</v>
       </c>
       <c r="D30" s="185">
+        <v>1090144</v>
+      </c>
+      <c r="E30" s="185">
         <v>1136250</v>
       </c>
-      <c r="E30" s="185">
+      <c r="F30" s="185">
         <v>689466</v>
       </c>
-      <c r="F30" s="185">
+      <c r="G30" s="185">
         <v>707978</v>
       </c>
-      <c r="G30" s="185"/>
       <c r="H30" s="185"/>
       <c r="I30" s="185"/>
       <c r="J30" s="185"/>
@@ -5925,18 +5966,21 @@
         <v>30</v>
       </c>
       <c r="C31" s="189">
-        <v>1630621</v>
+        <f>BS!G27</f>
+        <v>1709863</v>
       </c>
       <c r="D31" s="185">
+        <v>1678153</v>
+      </c>
+      <c r="E31" s="185">
         <v>1534416</v>
       </c>
-      <c r="E31" s="185">
+      <c r="F31" s="185">
         <v>1291608</v>
       </c>
-      <c r="F31" s="185">
+      <c r="G31" s="185">
         <v>1238930</v>
       </c>
-      <c r="G31" s="185"/>
       <c r="H31" s="185"/>
       <c r="I31" s="185"/>
       <c r="J31" s="185"/>
@@ -5949,18 +5993,21 @@
         <v>174</v>
       </c>
       <c r="C32" s="186">
-        <v>184211</v>
+        <f>BS!G28</f>
+        <v>194492</v>
       </c>
       <c r="D32" s="184">
+        <v>188249</v>
+      </c>
+      <c r="E32" s="184">
         <v>168550</v>
-      </c>
-      <c r="E32" s="184">
-        <v>0</v>
       </c>
       <c r="F32" s="184">
         <v>0</v>
       </c>
-      <c r="G32" s="185"/>
+      <c r="G32" s="185">
+        <v>0</v>
+      </c>
       <c r="H32" s="185"/>
       <c r="I32" s="185"/>
       <c r="J32" s="185"/>
@@ -5995,23 +6042,23 @@
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
-        <v>3011012</v>
+        <v>2937981</v>
       </c>
       <c r="D36" s="186">
         <f t="shared" si="1"/>
-        <v>3239167</v>
+        <v>3011012</v>
       </c>
       <c r="E36" s="186">
         <f t="shared" si="1"/>
-        <v>1851487</v>
+        <v>3239167</v>
       </c>
       <c r="F36" s="186">
         <f t="shared" si="1"/>
+        <v>1851487</v>
+      </c>
+      <c r="G36" s="186">
+        <f t="shared" si="1"/>
         <v>1729735</v>
-      </c>
-      <c r="G36" s="186" t="str">
-        <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="H36" s="186" t="str">
         <f t="shared" si="1"/>
@@ -6044,23 +6091,23 @@
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-2302385</v>
+        <v>-2275223</v>
       </c>
       <c r="D37" s="186">
         <f t="shared" si="2"/>
-        <v>-2527935</v>
+        <v>-2302385</v>
       </c>
       <c r="E37" s="186">
         <f t="shared" si="2"/>
-        <v>-1379524</v>
+        <v>-2527935</v>
       </c>
       <c r="F37" s="186">
         <f t="shared" si="2"/>
+        <v>-1379524</v>
+      </c>
+      <c r="G37" s="186">
+        <f t="shared" si="2"/>
         <v>-1278781</v>
-      </c>
-      <c r="G37" s="186" t="str">
-        <f t="shared" si="2"/>
-        <v/>
       </c>
       <c r="H37" s="186" t="str">
         <f t="shared" si="2"/>
@@ -6093,23 +6140,23 @@
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
-        <v>708627</v>
+        <v>662758</v>
       </c>
       <c r="D38" s="187">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
-        <v>711232</v>
+        <v>708627</v>
       </c>
       <c r="E38" s="187">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
-        <v>471963</v>
+        <v>711232</v>
       </c>
       <c r="F38" s="187">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
+        <v>471963</v>
+      </c>
+      <c r="G38" s="187">
+        <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>450954</v>
-      </c>
-      <c r="G38" s="187" t="str">
-        <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v/>
       </c>
       <c r="H38" s="187" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
@@ -6142,23 +6189,23 @@
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-420298</v>
+        <v>-394228</v>
       </c>
       <c r="D39" s="186">
         <f t="shared" si="13"/>
-        <v>-395706</v>
+        <v>-420298</v>
       </c>
       <c r="E39" s="186">
         <f t="shared" si="13"/>
-        <v>-296185</v>
+        <v>-395706</v>
       </c>
       <c r="F39" s="186">
         <f t="shared" si="13"/>
+        <v>-296185</v>
+      </c>
+      <c r="G39" s="186">
+        <f t="shared" si="13"/>
         <v>-285968</v>
-      </c>
-      <c r="G39" s="186" t="str">
-        <f t="shared" si="13"/>
-        <v/>
       </c>
       <c r="H39" s="186" t="str">
         <f t="shared" si="13"/>
@@ -6191,23 +6238,23 @@
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
-        <v>-70260</v>
+        <v>-63190</v>
       </c>
       <c r="D40" s="188">
         <f t="shared" si="14"/>
-        <v>-68352</v>
+        <v>-70260</v>
       </c>
       <c r="E40" s="188">
         <f t="shared" si="14"/>
-        <v>-48552</v>
+        <v>-68352</v>
       </c>
       <c r="F40" s="188">
         <f t="shared" si="14"/>
+        <v>-48552</v>
+      </c>
+      <c r="G40" s="188">
+        <f t="shared" si="14"/>
         <v>-47670</v>
-      </c>
-      <c r="G40" s="188" t="str">
-        <f t="shared" si="14"/>
-        <v/>
       </c>
       <c r="H40" s="188" t="str">
         <f t="shared" si="14"/>
@@ -6240,23 +6287,23 @@
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-350038</v>
+        <v>-331038</v>
       </c>
       <c r="D41" s="188">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
-        <v>-327354</v>
+        <v>-350038</v>
       </c>
       <c r="E41" s="188">
         <f t="shared" si="15"/>
-        <v>-247633</v>
+        <v>-327354</v>
       </c>
       <c r="F41" s="188">
         <f t="shared" si="15"/>
+        <v>-247633</v>
+      </c>
+      <c r="G41" s="188">
+        <f t="shared" si="15"/>
         <v>-238298</v>
-      </c>
-      <c r="G41" s="188" t="str">
-        <f t="shared" si="15"/>
-        <v/>
       </c>
       <c r="H41" s="188" t="str">
         <f t="shared" si="15"/>
@@ -6289,23 +6336,23 @@
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
-        <v>-21957</v>
+        <v>-23014</v>
       </c>
       <c r="D42" s="186">
         <f t="shared" si="16"/>
-        <v>-20016</v>
+        <v>-21957</v>
       </c>
       <c r="E42" s="186">
         <f t="shared" si="16"/>
-        <v>-16796</v>
+        <v>-20016</v>
       </c>
       <c r="F42" s="186">
         <f t="shared" si="16"/>
+        <v>-16796</v>
+      </c>
+      <c r="G42" s="186">
+        <f t="shared" si="16"/>
         <v>-15217</v>
-      </c>
-      <c r="G42" s="186" t="str">
-        <f t="shared" si="16"/>
-        <v/>
       </c>
       <c r="H42" s="186" t="str">
         <f t="shared" si="16"/>
@@ -6338,23 +6385,23 @@
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>266372</v>
+        <v>245516</v>
       </c>
       <c r="D43" s="189">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
-        <v>295510</v>
+        <v>266372</v>
       </c>
       <c r="E43" s="189">
         <f t="shared" si="17"/>
-        <v>158982</v>
+        <v>295510</v>
       </c>
       <c r="F43" s="189">
         <f t="shared" si="17"/>
+        <v>158982</v>
+      </c>
+      <c r="G43" s="189">
+        <f t="shared" si="17"/>
         <v>149769</v>
-      </c>
-      <c r="G43" s="189" t="str">
-        <f t="shared" si="17"/>
-        <v/>
       </c>
       <c r="H43" s="189" t="str">
         <f t="shared" si="17"/>
@@ -6387,23 +6434,23 @@
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>-13116</v>
+        <v>7918</v>
       </c>
       <c r="D44" s="190">
         <f t="shared" si="18"/>
-        <v>-65422</v>
+        <v>-12846</v>
       </c>
       <c r="E44" s="190">
         <f t="shared" si="18"/>
-        <v>10502</v>
+        <v>-65422</v>
       </c>
       <c r="F44" s="190">
         <f t="shared" si="18"/>
+        <v>10502</v>
+      </c>
+      <c r="G44" s="190">
+        <f t="shared" si="18"/>
         <v>9681</v>
-      </c>
-      <c r="G44" s="190" t="str">
-        <f t="shared" si="18"/>
-        <v/>
       </c>
       <c r="H44" s="190" t="str">
         <f t="shared" si="18"/>
@@ -6436,23 +6483,23 @@
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>-15798</v>
+        <v>-11932</v>
       </c>
       <c r="D45" s="191">
         <f t="shared" si="19"/>
-        <v>-16816</v>
+        <v>-15798</v>
       </c>
       <c r="E45" s="191">
         <f t="shared" si="19"/>
-        <v>-12952</v>
+        <v>-16816</v>
       </c>
       <c r="F45" s="191">
         <f t="shared" si="19"/>
+        <v>-12952</v>
+      </c>
+      <c r="G45" s="191">
+        <f t="shared" si="19"/>
         <v>-13365</v>
-      </c>
-      <c r="G45" s="191" t="str">
-        <f t="shared" si="19"/>
-        <v/>
       </c>
       <c r="H45" s="191" t="str">
         <f t="shared" si="19"/>
@@ -6485,23 +6532,23 @@
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
-        <v>-57167</v>
+        <v>-57755</v>
       </c>
       <c r="D46" s="186">
         <f t="shared" si="20"/>
-        <v>-49929</v>
+        <v>-57167</v>
       </c>
       <c r="E46" s="186">
         <f t="shared" si="20"/>
-        <v>-24138</v>
+        <v>-49929</v>
       </c>
       <c r="F46" s="186">
         <f t="shared" si="20"/>
+        <v>-24138</v>
+      </c>
+      <c r="G46" s="186">
+        <f t="shared" si="20"/>
         <v>-17067</v>
-      </c>
-      <c r="G46" s="186" t="str">
-        <f t="shared" si="20"/>
-        <v/>
       </c>
       <c r="H46" s="186" t="str">
         <f t="shared" si="20"/>
@@ -6534,23 +6581,23 @@
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
-        <v>180291</v>
+        <v>183747</v>
       </c>
       <c r="D47" s="189">
         <f t="shared" si="21"/>
-        <v>163343</v>
+        <v>180561</v>
       </c>
       <c r="E47" s="189">
         <f t="shared" si="21"/>
-        <v>132394</v>
+        <v>163343</v>
       </c>
       <c r="F47" s="189">
         <f t="shared" si="21"/>
+        <v>132394</v>
+      </c>
+      <c r="G47" s="189">
+        <f t="shared" si="21"/>
         <v>129018</v>
-      </c>
-      <c r="G47" s="189" t="str">
-        <f t="shared" si="21"/>
-        <v/>
       </c>
       <c r="H47" s="189" t="str">
         <f t="shared" si="21"/>
@@ -6583,23 +6630,23 @@
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
-        <v>-19147</v>
+        <v>-19071</v>
       </c>
       <c r="D48" s="186">
         <f t="shared" si="22"/>
-        <v>-14605</v>
+        <v>-19147</v>
       </c>
       <c r="E48" s="186">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-14605</v>
       </c>
       <c r="F48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="186" t="str">
+      <c r="G48" s="186">
         <f t="shared" si="22"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="186" t="str">
         <f t="shared" si="22"/>
@@ -6637,23 +6684,23 @@
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
-        <v>-24063</v>
+        <v>-20731</v>
       </c>
       <c r="D51" s="186">
         <f t="shared" si="23"/>
-        <v>-21554</v>
+        <v>-24063</v>
       </c>
       <c r="E51" s="186">
         <f t="shared" si="23"/>
-        <v>-14912</v>
+        <v>-21554</v>
       </c>
       <c r="F51" s="186">
         <f t="shared" si="23"/>
+        <v>-14912</v>
+      </c>
+      <c r="G51" s="186">
+        <f t="shared" si="23"/>
         <v>-15097</v>
-      </c>
-      <c r="G51" s="186" t="str">
-        <f t="shared" si="23"/>
-        <v/>
       </c>
       <c r="H51" s="186" t="str">
         <f t="shared" si="23"/>
@@ -6686,23 +6733,23 @@
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>8265</v>
+        <v>8799</v>
       </c>
       <c r="D52" s="186">
         <f t="shared" si="24"/>
-        <v>4738</v>
+        <v>8265</v>
       </c>
       <c r="E52" s="186">
         <f t="shared" si="24"/>
-        <v>1960</v>
+        <v>4738</v>
       </c>
       <c r="F52" s="186">
         <f t="shared" si="24"/>
+        <v>1960</v>
+      </c>
+      <c r="G52" s="186">
+        <f t="shared" si="24"/>
         <v>1732</v>
-      </c>
-      <c r="G52" s="186" t="str">
-        <f t="shared" si="24"/>
-        <v/>
       </c>
       <c r="H52" s="186" t="str">
         <f t="shared" si="24"/>
@@ -6740,23 +6787,23 @@
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
-        <v>18538</v>
+        <v>18644</v>
       </c>
       <c r="D55" s="191">
         <f t="shared" si="25"/>
-        <v>15251</v>
+        <v>18538</v>
       </c>
       <c r="E55" s="191">
         <f t="shared" si="25"/>
-        <v>12877</v>
+        <v>15251</v>
       </c>
       <c r="F55" s="191">
         <f t="shared" si="25"/>
+        <v>12877</v>
+      </c>
+      <c r="G55" s="191">
+        <f t="shared" si="25"/>
         <v>11296</v>
-      </c>
-      <c r="G55" s="191" t="str">
-        <f t="shared" si="25"/>
-        <v/>
       </c>
       <c r="H55" s="191" t="str">
         <f t="shared" si="25"/>
@@ -6803,9 +6850,9 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="G56" s="191" t="str">
+      <c r="G56" s="191">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="191" t="str">
         <f t="shared" si="26"/>
@@ -6852,9 +6899,9 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G57" s="191" t="str">
+      <c r="G57" s="191">
         <f t="shared" si="27"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H57" s="191" t="str">
         <f t="shared" si="27"/>
@@ -6887,23 +6934,23 @@
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>-31654</v>
+        <v>-10726</v>
       </c>
       <c r="D58" s="191">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
-        <v>-80673</v>
+        <v>-31384</v>
       </c>
       <c r="E58" s="191">
         <f t="shared" si="28"/>
-        <v>-2375</v>
+        <v>-80673</v>
       </c>
       <c r="F58" s="191">
         <f t="shared" si="28"/>
+        <v>-2375</v>
+      </c>
+      <c r="G58" s="191">
+        <f t="shared" si="28"/>
         <v>-1615</v>
-      </c>
-      <c r="G58" s="191" t="str">
-        <f t="shared" si="28"/>
-        <v/>
       </c>
       <c r="H58" s="191" t="str">
         <f t="shared" si="28"/>
@@ -6942,23 +6989,23 @@
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
-        <v>-229584</v>
+        <v>-243209</v>
       </c>
       <c r="D61" s="186">
         <f t="shared" si="29"/>
-        <v>-222648</v>
+        <v>-229584</v>
       </c>
       <c r="E61" s="186">
         <f t="shared" si="29"/>
-        <v>-238036</v>
+        <v>-222648</v>
       </c>
       <c r="F61" s="186">
         <f t="shared" si="29"/>
+        <v>-238036</v>
+      </c>
+      <c r="G61" s="186">
+        <f t="shared" si="29"/>
         <v>-236818</v>
-      </c>
-      <c r="G61" s="186" t="str">
-        <f t="shared" si="29"/>
-        <v/>
       </c>
       <c r="H61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6991,23 +7038,23 @@
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>-115297</v>
+        <v>0</v>
       </c>
       <c r="D62" s="186">
         <f t="shared" si="30"/>
-        <v>-282508</v>
+        <v>-115297</v>
       </c>
       <c r="E62" s="186">
         <f t="shared" si="30"/>
-        <v>-245237</v>
+        <v>-282508</v>
       </c>
       <c r="F62" s="186">
         <f t="shared" si="30"/>
+        <v>-245237</v>
+      </c>
+      <c r="G62" s="186">
+        <f t="shared" si="30"/>
         <v>-265563</v>
-      </c>
-      <c r="G62" s="186" t="str">
-        <f t="shared" si="30"/>
-        <v/>
       </c>
       <c r="H62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -7040,23 +7087,23 @@
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>-31061</v>
+        <v>0</v>
       </c>
       <c r="D63" s="186">
         <f t="shared" si="31"/>
-        <v>-3456</v>
+        <v>-31061</v>
       </c>
       <c r="E63" s="186">
         <f t="shared" si="31"/>
-        <v>-46237</v>
+        <v>-3456</v>
       </c>
       <c r="F63" s="186">
         <f t="shared" si="31"/>
+        <v>-46237</v>
+      </c>
+      <c r="G63" s="186">
+        <f t="shared" si="31"/>
         <v>-34899</v>
-      </c>
-      <c r="G63" s="186" t="str">
-        <f t="shared" si="31"/>
-        <v/>
       </c>
       <c r="H63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -7089,23 +7136,23 @@
       </c>
       <c r="C64" s="186">
         <f>IF(C$4="","",C22+C23+C24)</f>
-        <v>54235</v>
+        <v>-79691</v>
       </c>
       <c r="D64" s="186">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
-        <v>47084</v>
+        <v>54235</v>
       </c>
       <c r="E64" s="186">
         <f t="shared" si="32"/>
-        <v>-8156</v>
+        <v>47084</v>
       </c>
       <c r="F64" s="186">
         <f t="shared" si="32"/>
+        <v>-8156</v>
+      </c>
+      <c r="G64" s="186">
+        <f t="shared" si="32"/>
         <v>36853</v>
-      </c>
-      <c r="G64" s="186" t="str">
-        <f t="shared" si="32"/>
-        <v/>
       </c>
       <c r="H64" s="186" t="str">
         <f t="shared" si="32"/>
@@ -7152,9 +7199,9 @@
         <f t="shared" si="33"/>
         <v>0.21309006776117467</v>
       </c>
-      <c r="G65" s="75" t="str">
+      <c r="G65" s="75">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0.16495954981251937</v>
       </c>
       <c r="H65" s="75" t="str">
         <f t="shared" si="33"/>
@@ -7193,19 +7240,19 @@
       </c>
       <c r="C68" s="94">
         <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
-        <v>-7.0436318967191269E-2</v>
+        <v>-2.4254635982852268E-2</v>
       </c>
       <c r="D68" s="94">
         <f t="shared" si="34"/>
-        <v>0.74949486547839661</v>
+        <v>-7.0436318967191269E-2</v>
       </c>
       <c r="E68" s="94">
         <f t="shared" si="34"/>
+        <v>0.74949486547839661</v>
+      </c>
+      <c r="F68" s="94">
+        <f t="shared" si="34"/>
         <v>7.0387660537596819E-2</v>
-      </c>
-      <c r="F68" s="94" t="str">
-        <f t="shared" si="34"/>
-        <v/>
       </c>
       <c r="G68" s="94" t="str">
         <f t="shared" si="34"/>
@@ -7243,19 +7290,19 @@
       </c>
       <c r="C69" s="104">
         <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
-        <v>-8.9223021952700488E-2</v>
+        <v>-1.1797331897141494E-2</v>
       </c>
       <c r="D69" s="104">
         <f t="shared" si="35"/>
-        <v>0.83246902554794255</v>
+        <v>-8.9223021952700488E-2</v>
       </c>
       <c r="E69" s="104">
         <f t="shared" si="35"/>
+        <v>0.83246902554794255</v>
+      </c>
+      <c r="F69" s="104">
+        <f t="shared" si="35"/>
         <v>7.8780494861903749E-2</v>
-      </c>
-      <c r="F69" s="104" t="str">
-        <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="G69" s="104" t="str">
         <f t="shared" si="35"/>
@@ -7293,19 +7340,19 @@
       </c>
       <c r="C70" s="94">
         <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
-        <v>-3.6626585980383819E-3</v>
+        <v>-6.4729399246712283E-2</v>
       </c>
       <c r="D70" s="94">
         <f t="shared" si="36"/>
-        <v>0.50696558840417572</v>
+        <v>-3.6626585980383819E-3</v>
       </c>
       <c r="E70" s="94">
         <f t="shared" si="36"/>
+        <v>0.50696558840417572</v>
+      </c>
+      <c r="F70" s="94">
+        <f t="shared" si="36"/>
         <v>4.6587900317992537E-2</v>
-      </c>
-      <c r="F70" s="94" t="str">
-        <f t="shared" si="36"/>
-        <v/>
       </c>
       <c r="G70" s="94" t="str">
         <f t="shared" si="36"/>
@@ -7343,19 +7390,19 @@
       </c>
       <c r="C71" s="104">
         <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
-        <v>6.2147149651508915E-2</v>
+        <v>-6.2027418641059429E-2</v>
       </c>
       <c r="D71" s="104">
         <f t="shared" si="37"/>
-        <v>0.33600958860171848</v>
+        <v>6.2147149651508915E-2</v>
       </c>
       <c r="E71" s="104">
         <f t="shared" si="37"/>
+        <v>0.33600958860171848</v>
+      </c>
+      <c r="F71" s="104">
+        <f t="shared" si="37"/>
         <v>3.5727773736921709E-2</v>
-      </c>
-      <c r="F71" s="104" t="str">
-        <f t="shared" si="37"/>
-        <v/>
       </c>
       <c r="G71" s="104" t="str">
         <f t="shared" si="37"/>
@@ -7403,9 +7450,9 @@
         <f t="shared" si="38"/>
         <v>0.86470743976701114</v>
       </c>
-      <c r="F72" s="94" t="str">
+      <c r="F72" s="94">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0.29177163737023304</v>
       </c>
       <c r="G72" s="94" t="str">
         <f t="shared" si="38"/>
@@ -7464,23 +7511,23 @@
       </c>
       <c r="C76" s="78">
         <f>IF(C$4="","",C79+C80)</f>
-        <v>2752710</v>
+        <v>2753007</v>
       </c>
       <c r="D76" s="78">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
-        <v>2670666</v>
+        <v>2768297</v>
       </c>
       <c r="E76" s="78">
         <f t="shared" si="39"/>
-        <v>1981074</v>
+        <v>2670666</v>
       </c>
       <c r="F76" s="78">
         <f t="shared" si="39"/>
+        <v>1981074</v>
+      </c>
+      <c r="G76" s="78">
+        <f t="shared" si="39"/>
         <v>1946908</v>
-      </c>
-      <c r="G76" s="78" t="str">
-        <f t="shared" si="39"/>
-        <v/>
       </c>
       <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
@@ -7513,23 +7560,23 @@
       </c>
       <c r="C77" s="74">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>99851</v>
+        <v>114865</v>
       </c>
       <c r="D77" s="74">
         <f t="shared" si="40"/>
-        <v>117877</v>
+        <v>142879</v>
       </c>
       <c r="E77" s="74">
         <f t="shared" si="40"/>
-        <v>23709</v>
+        <v>117877</v>
       </c>
       <c r="F77" s="74">
         <f t="shared" si="40"/>
+        <v>23709</v>
+      </c>
+      <c r="G77" s="74">
+        <f t="shared" si="40"/>
         <v>27379</v>
-      </c>
-      <c r="G77" s="74" t="str">
-        <f t="shared" si="40"/>
-        <v/>
       </c>
       <c r="H77" s="74" t="str">
         <f t="shared" si="40"/>
@@ -7547,23 +7594,23 @@
       </c>
       <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>180533</v>
+        <v>168338</v>
       </c>
       <c r="D78" s="74">
         <f t="shared" si="40"/>
-        <v>167751</v>
+        <v>182674</v>
       </c>
       <c r="E78" s="74">
         <f t="shared" si="40"/>
-        <v>110386</v>
+        <v>167751</v>
       </c>
       <c r="F78" s="74">
         <f t="shared" si="40"/>
+        <v>110386</v>
+      </c>
+      <c r="G78" s="74">
+        <f t="shared" si="40"/>
         <v>109354</v>
-      </c>
-      <c r="G78" s="74" t="str">
-        <f t="shared" si="40"/>
-        <v/>
       </c>
       <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
@@ -7581,23 +7628,23 @@
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
-        <v>1122089</v>
+        <v>1043144</v>
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
-        <v>1136250</v>
+        <v>1090144</v>
       </c>
       <c r="E79" s="58">
         <f t="shared" si="41"/>
-        <v>689466</v>
+        <v>1136250</v>
       </c>
       <c r="F79" s="58">
         <f t="shared" si="41"/>
+        <v>689466</v>
+      </c>
+      <c r="G79" s="58">
+        <f t="shared" si="41"/>
         <v>707978</v>
-      </c>
-      <c r="G79" s="58" t="str">
-        <f t="shared" si="41"/>
-        <v/>
       </c>
       <c r="H79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7630,23 +7677,23 @@
       </c>
       <c r="C80" s="58">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
-        <v>1630621</v>
+        <v>1709863</v>
       </c>
       <c r="D80" s="58">
         <f t="shared" si="42"/>
-        <v>1534416</v>
+        <v>1678153</v>
       </c>
       <c r="E80" s="58">
         <f t="shared" si="42"/>
-        <v>1291608</v>
+        <v>1534416</v>
       </c>
       <c r="F80" s="58">
         <f t="shared" si="42"/>
+        <v>1291608</v>
+      </c>
+      <c r="G80" s="58">
+        <f t="shared" si="42"/>
         <v>1238930</v>
-      </c>
-      <c r="G80" s="58" t="str">
-        <f t="shared" si="42"/>
-        <v/>
       </c>
       <c r="H80" s="58" t="str">
         <f t="shared" si="42"/>
@@ -7690,7 +7737,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7721,11 +7768,12 @@
         <v>37</v>
       </c>
       <c r="C1" s="102">
-        <v>45473</v>
+        <f>Data!C1</f>
+        <v>45657</v>
       </c>
       <c r="F1" s="88" t="str">
         <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
-        <v>Quarter Report</v>
+        <v>FY Report</v>
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
@@ -7768,8 +7816,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <f>90108+11142+41629</f>
-        <v>142879</v>
+        <f>71610+8868+34387</f>
+        <v>114865</v>
       </c>
       <c r="D4" s="300">
         <v>0.6</v>
@@ -7779,7 +7827,7 @@
         <v>79</v>
       </c>
       <c r="G4" s="19">
-        <v>238880</v>
+        <v>216246</v>
       </c>
       <c r="H4" s="300">
         <v>0.9</v>
@@ -7790,7 +7838,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="19">
-        <v>11851</v>
+        <v>9020</v>
       </c>
       <c r="D5" s="300">
         <v>0.6</v>
@@ -7811,7 +7859,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>182674</v>
+        <v>168338</v>
       </c>
       <c r="D6" s="300">
         <v>0.5</v>
@@ -7842,7 +7890,7 @@
         <v>180</v>
       </c>
       <c r="G7" s="19">
-        <v>9895</v>
+        <v>2816</v>
       </c>
       <c r="H7" s="300">
         <v>0.6</v>
@@ -7874,7 +7922,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>24847</v>
+        <v>14192</v>
       </c>
       <c r="D9" s="300">
         <v>0.1</v>
@@ -7907,7 +7955,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="19">
-        <v>61345</v>
+        <v>65367</v>
       </c>
       <c r="D11" s="300">
         <v>0.05</v>
@@ -7920,22 +7968,22 @@
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>423596</v>
+        <v>371782</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>189726.95</v>
+        <v>163187.55000000002</v>
       </c>
       <c r="F12" s="82" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>248775</v>
+        <v>219062</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>220929</v>
+        <v>196311</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8017,7 +8065,7 @@
         <v>180</v>
       </c>
       <c r="G17" s="19">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="H17" s="300">
         <v>0.6</v>
@@ -8037,8 +8085,7 @@
         <v>183</v>
       </c>
       <c r="G18" s="19">
-        <f>292606</f>
-        <v>292606</v>
+        <v>290077</v>
       </c>
       <c r="H18" s="300">
         <v>0.1</v>
@@ -8049,8 +8096,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <f>458868+831001+201156+123479+13153</f>
-        <v>1627657</v>
+        <f>480407+875436+214967+120865+14018</f>
+        <v>1705693</v>
       </c>
       <c r="D19" s="300">
         <v>0.1</v>
@@ -8090,7 +8137,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>91529</v>
+        <v>92790</v>
       </c>
       <c r="D21" s="300">
         <v>0.05</v>
@@ -8110,7 +8157,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>24707</v>
+        <v>26765</v>
       </c>
       <c r="D22" s="300">
         <v>0.9</v>
@@ -8122,8 +8169,8 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <f>7476+51258</f>
-        <v>58734</v>
+        <f>7436+38695</f>
+        <v>46131</v>
       </c>
       <c r="D23" s="300">
         <v>0</v>
@@ -8136,22 +8183,22 @@
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>1802627</v>
+        <v>1871379</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>189578.45</v>
+        <v>199297.30000000002</v>
       </c>
       <c r="F24" s="82" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>293299</v>
+        <v>290784</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>29676.400000000001</v>
+        <v>29431.9</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8176,18 +8223,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>40594</v>
+        <v>45955</v>
       </c>
       <c r="F27" s="214" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>1678153</v>
+        <v>1709863</v>
       </c>
       <c r="H27" s="215">
         <f>H32-G30</f>
-        <v>-460233.19999999995</v>
+        <v>-454916.25</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8201,7 +8248,7 @@
         <v>246</v>
       </c>
       <c r="G28" s="184">
-        <v>188249</v>
+        <v>194492</v>
       </c>
       <c r="H28" s="215"/>
     </row>
@@ -8217,11 +8264,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>1489904</v>
+        <v>1515371</v>
       </c>
       <c r="H29" s="215">
         <f>H27-G28</f>
-        <v>-648482.19999999995</v>
+        <v>-649408.25</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8229,15 +8276,15 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <f>4685+7139</f>
-        <v>11824</v>
+        <f>3808+7051+14895</f>
+        <v>25754</v>
       </c>
       <c r="F30" s="214" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
-        <v>1090144</v>
+        <v>1043144</v>
       </c>
       <c r="H30" s="215"/>
     </row>
@@ -8247,14 +8294,14 @@
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
-        <v>52418</v>
+        <v>71709</v>
       </c>
       <c r="F31" s="217" t="s">
         <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
-        <v>245714</v>
+        <v>279749</v>
       </c>
       <c r="H31" s="215"/>
     </row>
@@ -8264,18 +8311,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>664223</v>
+        <v>565608</v>
       </c>
       <c r="F32" s="219" t="s">
         <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
-        <v>2768297</v>
+        <v>2753007</v>
       </c>
       <c r="H32" s="215">
         <f>H35+H40</f>
-        <v>629910.80000000005</v>
+        <v>588227.75</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8283,7 +8330,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="86">
-        <v>716641</v>
+        <v>637317</v>
       </c>
       <c r="F33" s="221"/>
       <c r="G33" s="2"/>
@@ -8314,11 +8361,11 @@
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
-        <v>2226223</v>
+        <v>2243161</v>
       </c>
       <c r="H35" s="227">
         <f>D12+D24</f>
-        <v>379305.4</v>
+        <v>362484.85000000003</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8326,15 +8373,14 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <f>70126+11000</f>
-        <v>81126</v>
+        <v>74072</v>
       </c>
       <c r="F36" s="217" t="s">
         <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
-        <v>142879</v>
+        <v>114865</v>
       </c>
       <c r="H36" s="222"/>
     </row>
@@ -8343,14 +8389,14 @@
         <v>14</v>
       </c>
       <c r="C37" s="19">
-        <v>112170</v>
+        <v>109968</v>
       </c>
       <c r="F37" s="217" t="s">
         <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
-        <v>182674</v>
+        <v>168338</v>
       </c>
       <c r="H37" s="222"/>
     </row>
@@ -8375,18 +8421,18 @@
         <v>16</v>
       </c>
       <c r="C39" s="19">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="F39" s="217" t="s">
         <v>81</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
-        <v>1627657</v>
+        <v>1705693</v>
       </c>
       <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>162765.70000000001</v>
+        <v>170569.30000000002</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8395,18 +8441,18 @@
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
-        <v>193296</v>
+        <v>208040</v>
       </c>
       <c r="F40" s="226" t="s">
         <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
-        <v>542074</v>
+        <v>509846</v>
       </c>
       <c r="H40" s="227">
         <f>H12+H24</f>
-        <v>250605.4</v>
+        <v>225742.9</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8415,18 +8461,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>180207</v>
+        <v>197787</v>
       </c>
       <c r="F41" s="217" t="s">
         <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
-        <v>531486</v>
+        <v>506323</v>
       </c>
       <c r="H41" s="227">
         <f>H40-H42</f>
-        <v>244252.6</v>
+        <v>223629.1</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8434,18 +8480,18 @@
         <v>22</v>
       </c>
       <c r="C42" s="86">
-        <v>373503</v>
+        <v>405827</v>
       </c>
       <c r="F42" s="228" t="s">
         <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
-        <v>10588</v>
+        <v>3523</v>
       </c>
       <c r="H42" s="230">
         <f>D82</f>
-        <v>6352.8</v>
+        <v>2113.7999999999997</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8479,11 +8525,11 @@
       </c>
       <c r="C46" s="191">
         <f>G29</f>
-        <v>1489904</v>
+        <v>1515371</v>
       </c>
       <c r="D46" s="191">
         <f>H29</f>
-        <v>-648482.19999999995</v>
+        <v>-649408.25</v>
       </c>
       <c r="F46" s="289"/>
     </row>
@@ -8494,11 +8540,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.657498849970656</v>
+        <v>8.7756932764689761</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7681849976417547</v>
+        <v>-3.760800235195529</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8524,11 +8570,11 @@
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.0839756451798694</v>
+        <v>1.1309485990394448</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>0.9224468037181085</v>
+        <v>1.1394328679189951</v>
       </c>
       <c r="F50" s="289"/>
     </row>
@@ -8539,7 +8585,7 @@
       <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.5382023677372767</v>
+        <v>0.55044211656563169</v>
       </c>
       <c r="F51" s="289"/>
     </row>
@@ -8564,11 +8610,11 @@
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.10182202081487467</v>
+        <v>0.11027199460614415</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>0.11965198454961611</v>
+        <v>0.1094509043265285</v>
       </c>
       <c r="F54" s="289"/>
     </row>
@@ -8578,11 +8624,11 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
-        <v>3.4198282891265773E-2</v>
+        <v>3.656790481831769E-2</v>
       </c>
       <c r="D55" s="94">
         <f>Normalized_FCF!G11/G40</f>
-        <v>3.4198282891265766E-2</v>
+        <v>3.656790481831769E-2</v>
       </c>
       <c r="F55" s="289"/>
     </row>
@@ -8608,7 +8654,7 @@
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>0.14105183094472606</v>
+        <v>0.14258662021829249</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -8619,7 +8665,7 @@
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>0.58796328573126366</v>
+        <v>0.6195745234211173</v>
       </c>
       <c r="F59" s="289"/>
     </row>
@@ -8644,11 +8690,11 @@
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>0.12634975139337837</v>
+        <v>0.12834612777992979</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>0.12634975139337837</v>
+        <v>0.12834612777992979</v>
       </c>
       <c r="F62" s="289" t="s">
         <v>276</v>
@@ -8685,11 +8731,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>238880</v>
+        <v>216246</v>
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>46208.672776167194</v>
+        <v>126.15719684722717</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8711,7 +8757,7 @@
       </c>
       <c r="C68" s="20">
         <f>G18</f>
-        <v>292606</v>
+        <v>290077</v>
       </c>
       <c r="F68" s="289"/>
     </row>
@@ -8731,7 +8777,7 @@
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>531486</v>
+        <v>506323</v>
       </c>
       <c r="F70" s="289"/>
     </row>
@@ -8756,11 +8802,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-235460.35011087885</v>
+        <v>-231112.43344421219</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-192671.32722383281</v>
+        <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>365</v>
@@ -8772,11 +8818,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>1.0145232515262583</v>
+        <v>0.93567445410590266</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>1.2398316004876273</v>
+        <v>1.0005837372228803</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>332</v>
@@ -8789,7 +8835,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>192671.32722383281</v>
+        <v>216119.84280315277</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>366</v>
@@ -8829,11 +8875,11 @@
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>10588</v>
+        <v>3523</v>
       </c>
       <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
-        <v>6352.8</v>
+        <v>2113.7999999999997</v>
       </c>
       <c r="F79" s="289"/>
     </row>
@@ -8871,11 +8917,11 @@
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>10588</v>
+        <v>3523</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>6352.8</v>
+        <v>2113.7999999999997</v>
       </c>
       <c r="F82" s="289"/>
     </row>
@@ -8904,11 +8950,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-261315.35488743999</v>
+        <v>-296504.9020538</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.4277890873651522</v>
+        <v>-1.6200596543017645</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8921,11 +8967,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>49142.644397070238</v>
+        <v>133.71353354102806</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>0.26850826054453025</v>
+        <v>7.3059129688398707E-4</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8938,11 +8984,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>6756.1644290880004</v>
+        <v>2240.4085875599999</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>3.6914699667960883E-2</v>
+        <v>1.2241266625664684E-2</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8955,11 +9001,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>-205416.54606128176</v>
+        <v>-294130.77993269899</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>-1.1223661271526613</v>
+        <v>-1.6070877963792158</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -9006,47 +9052,47 @@
       <c r="F1" s="53"/>
       <c r="G1" s="38">
         <f>Data!C1</f>
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="H1" s="38">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>43830</v>
+        <v>44196</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>43465</v>
+        <v>43830</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>43100</v>
+        <v>43465</v>
       </c>
       <c r="N1" s="38">
         <f t="shared" si="0"/>
-        <v>42735</v>
+        <v>43100</v>
       </c>
       <c r="O1" s="38">
         <f t="shared" si="0"/>
-        <v>42369</v>
+        <v>42735</v>
       </c>
       <c r="P1" s="38">
         <f t="shared" si="0"/>
-        <v>42004</v>
+        <v>42369</v>
       </c>
       <c r="Q1" s="38">
         <f t="shared" si="0"/>
-        <v>41639</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -9093,30 +9139,30 @@
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:J4)</f>
-        <v>2457850.25</v>
+        <v>2759911.75</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
-        <v>3011012</v>
+        <v>2937981</v>
       </c>
       <c r="H4" s="186">
         <f>Data!D36</f>
-        <v>3239167</v>
+        <v>3011012</v>
       </c>
       <c r="I4" s="186">
         <f>Data!E36</f>
-        <v>1851487</v>
+        <v>3239167</v>
       </c>
       <c r="J4" s="186">
         <f>Data!F36</f>
+        <v>1851487</v>
+      </c>
+      <c r="K4" s="186">
+        <f>Data!G36</f>
         <v>1729735</v>
-      </c>
-      <c r="K4" s="186" t="str">
-        <f>Data!G36</f>
-        <v/>
       </c>
       <c r="L4" s="186" t="str">
         <f>Data!H36</f>
@@ -9150,28 +9196,28 @@
       </c>
       <c r="C5" s="197">
         <f>C25</f>
-        <v>-1921844.4753554473</v>
+        <v>-2178092.4123072871</v>
       </c>
       <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-2372645</v>
+        <v>-2338413</v>
       </c>
       <c r="H5" s="186">
         <f t="shared" si="1"/>
-        <v>-2596287</v>
+        <v>-2372645</v>
       </c>
       <c r="I5" s="186">
         <f t="shared" si="1"/>
-        <v>-1428076</v>
+        <v>-2596287</v>
       </c>
       <c r="J5" s="186">
         <f t="shared" si="1"/>
+        <v>-1428076</v>
+      </c>
+      <c r="K5" s="186">
+        <f t="shared" si="1"/>
         <v>-1326451</v>
-      </c>
-      <c r="K5" s="186" t="str">
-        <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="L5" s="186" t="str">
         <f t="shared" si="1"/>
@@ -9205,28 +9251,28 @@
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
-        <v>536005.77464455273</v>
+        <v>581819.3376927129</v>
       </c>
       <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
-        <v>638367</v>
+        <v>599568</v>
       </c>
       <c r="H6" s="187">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
-        <v>642880</v>
+        <v>638367</v>
       </c>
       <c r="I6" s="187">
         <f t="shared" si="2"/>
-        <v>423411</v>
+        <v>642880</v>
       </c>
       <c r="J6" s="187">
         <f t="shared" si="2"/>
+        <v>423411</v>
+      </c>
+      <c r="K6" s="187">
+        <f t="shared" si="2"/>
         <v>403284</v>
-      </c>
-      <c r="K6" s="187" t="str">
-        <f t="shared" si="2"/>
-        <v/>
       </c>
       <c r="L6" s="187" t="str">
         <f t="shared" si="2"/>
@@ -9260,28 +9306,28 @@
       </c>
       <c r="C7" s="197">
         <f>C35</f>
-        <v>-309327.25</v>
+        <v>-334461.5</v>
       </c>
       <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-371995</v>
+        <v>-354052</v>
       </c>
       <c r="H7" s="197">
         <f t="shared" si="3"/>
-        <v>-347370</v>
+        <v>-371995</v>
       </c>
       <c r="I7" s="197">
         <f t="shared" si="3"/>
-        <v>-264429</v>
+        <v>-347370</v>
       </c>
       <c r="J7" s="197">
         <f t="shared" si="3"/>
+        <v>-264429</v>
+      </c>
+      <c r="K7" s="197">
+        <f t="shared" si="3"/>
         <v>-253515</v>
-      </c>
-      <c r="K7" s="197" t="str">
-        <f t="shared" si="3"/>
-        <v/>
       </c>
       <c r="L7" s="197" t="str">
         <f t="shared" si="3"/>
@@ -9315,30 +9361,30 @@
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
-        <v>226678.52464455273</v>
+        <v>247357.8376927129</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>266372</v>
+        <v>245516</v>
       </c>
       <c r="H8" s="187">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
-        <v>295510</v>
+        <v>266372</v>
       </c>
       <c r="I8" s="187">
         <f t="shared" si="4"/>
-        <v>158982</v>
+        <v>295510</v>
       </c>
       <c r="J8" s="187">
         <f t="shared" si="4"/>
+        <v>158982</v>
+      </c>
+      <c r="K8" s="187">
+        <f t="shared" si="4"/>
         <v>149769</v>
-      </c>
-      <c r="K8" s="187" t="str">
-        <f t="shared" si="4"/>
-        <v/>
       </c>
       <c r="L8" s="187" t="str">
         <f t="shared" si="4"/>
@@ -9372,28 +9418,28 @@
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
-        <v>229584</v>
+        <v>243208.99999999997</v>
       </c>
       <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>229584</v>
+        <v>243209</v>
       </c>
       <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>222648</v>
+        <v>229584</v>
       </c>
       <c r="I9" s="197">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>238036</v>
+        <v>222648</v>
       </c>
       <c r="J9" s="197">
         <f>IF(Data!F61="","",-Data!F61)</f>
+        <v>238036</v>
+      </c>
+      <c r="K9" s="197">
+        <f>IF(Data!G61="","",-Data!G61)</f>
         <v>236818</v>
-      </c>
-      <c r="K9" s="197" t="str">
-        <f>IF(Data!G61="","",-Data!G61)</f>
-        <v/>
       </c>
       <c r="L9" s="197" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
@@ -9427,28 +9473,28 @@
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
-        <v>-252845.35040534919</v>
+        <v>-283919.19056768838</v>
       </c>
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>-115297</v>
+        <v>0</v>
       </c>
       <c r="H10" s="197">
         <f>Data!D62</f>
-        <v>-282508</v>
+        <v>-115297</v>
       </c>
       <c r="I10" s="197">
         <f>Data!E62</f>
-        <v>-245237</v>
+        <v>-282508</v>
       </c>
       <c r="J10" s="197">
         <f>Data!F62</f>
+        <v>-245237</v>
+      </c>
+      <c r="K10" s="197">
+        <f>Data!G62</f>
         <v>-265563</v>
-      </c>
-      <c r="K10" s="197" t="str">
-        <f>Data!G62</f>
-        <v/>
       </c>
       <c r="L10" s="197" t="str">
         <f>Data!H62</f>
@@ -9482,30 +9528,30 @@
       </c>
       <c r="C11" s="199">
         <f>C63</f>
-        <v>18538.000000000004</v>
+        <v>18644</v>
       </c>
       <c r="D11" s="172"/>
       <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
-        <v>18538</v>
+        <v>18644</v>
       </c>
       <c r="H11" s="189">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
-        <v>15251</v>
+        <v>18538</v>
       </c>
       <c r="I11" s="189">
         <f t="shared" si="5"/>
-        <v>12877</v>
+        <v>15251</v>
       </c>
       <c r="J11" s="189">
         <f t="shared" si="5"/>
+        <v>12877</v>
+      </c>
+      <c r="K11" s="189">
+        <f t="shared" si="5"/>
         <v>11296</v>
-      </c>
-      <c r="K11" s="189" t="str">
-        <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="L11" s="189" t="str">
         <f t="shared" si="5"/>
@@ -9539,28 +9585,28 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>-17396.772105220287</v>
+        <v>-11937.133307321563</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>-17396.772105220287</v>
+        <v>-11937.133307321563</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-17732.513277015572</v>
+        <v>-15802.821773498434</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
-        <v>-13331.1401483644</v>
+        <v>-16818.76413343443</v>
       </c>
       <c r="J12" s="197">
         <f t="shared" si="6"/>
-        <v>-13700.036090289357</v>
-      </c>
-      <c r="K12" s="197" t="str">
+        <v>-12953.143457478152</v>
+      </c>
+      <c r="K12" s="197">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-13366.010443036816</v>
       </c>
       <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -9594,28 +9640,28 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>204558.40213398324</v>
+        <v>213354.51381770297</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>381800.2278947797</v>
+        <v>495431.86669267842</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>233168.48672298444</v>
+        <v>383394.17822650156</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
-        <v>151326.85985163559</v>
+        <v>234082.23586656558</v>
       </c>
       <c r="J13" s="187">
         <f t="shared" si="7"/>
-        <v>118619.96390971064</v>
-      </c>
-      <c r="K13" s="187" t="str">
+        <v>151704.85654252185</v>
+      </c>
+      <c r="K13" s="187">
         <f t="shared" si="7"/>
-        <v/>
+        <v>118953.98955696318</v>
       </c>
       <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -9649,28 +9695,28 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-56954.938134833108</v>
+        <v>-63516.176096347837</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
-        <v>-57167</v>
+        <v>-57755</v>
       </c>
       <c r="H14" s="197">
         <f>Data!D46</f>
-        <v>-49929</v>
+        <v>-57167</v>
       </c>
       <c r="I14" s="197">
         <f>Data!E46</f>
-        <v>-24138</v>
+        <v>-49929</v>
       </c>
       <c r="J14" s="197">
         <f>Data!F46</f>
+        <v>-24138</v>
+      </c>
+      <c r="K14" s="197">
+        <f>Data!G46</f>
         <v>-17067</v>
-      </c>
-      <c r="K14" s="197" t="str">
-        <f>Data!G46</f>
-        <v/>
       </c>
       <c r="L14" s="197" t="str">
         <f>Data!H46</f>
@@ -9704,30 +9750,30 @@
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
-        <v>-15629.449081156103</v>
+        <v>-17915.118234001515</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
-        <v>-19147</v>
+        <v>-19071</v>
       </c>
       <c r="H15" s="186">
         <f>Data!D48</f>
-        <v>-14605</v>
+        <v>-19147</v>
       </c>
       <c r="I15" s="186">
         <f>Data!E48</f>
-        <v>0</v>
+        <v>-14605</v>
       </c>
       <c r="J15" s="186">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="186" t="str">
+      <c r="K15" s="186">
         <f>Data!G48</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L15" s="186" t="str">
         <f>Data!H48</f>
@@ -9761,30 +9807,30 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>131974.01491799403</v>
+        <v>131923.21948735364</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>305486.2278947797</v>
+        <v>418605.86669267842</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>168634.48672298444</v>
+        <v>307080.17822650156</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
-        <v>127188.85985163559</v>
+        <v>169548.23586656558</v>
       </c>
       <c r="J16" s="187">
         <f t="shared" si="8"/>
-        <v>101552.96390971064</v>
-      </c>
-      <c r="K16" s="187" t="str">
+        <v>127566.85654252185</v>
+      </c>
+      <c r="K16" s="187">
         <f t="shared" si="8"/>
-        <v/>
+        <v>101886.98955696318</v>
       </c>
       <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9869,30 +9915,30 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>131974.01491799403</v>
+        <v>131923.21948735364</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>305486.2278947797</v>
+        <v>418605.86669267842</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>168634.48672298444</v>
+        <v>307080.17822650156</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
-        <v>127188.85985163559</v>
+        <v>169548.23586656558</v>
       </c>
       <c r="J19" s="189">
         <f t="shared" si="9"/>
-        <v>101552.96390971064</v>
-      </c>
-      <c r="K19" s="189" t="str">
+        <v>127566.85654252185</v>
+      </c>
+      <c r="K19" s="189">
         <f t="shared" si="9"/>
-        <v/>
+        <v>101886.98955696318</v>
       </c>
       <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -9989,30 +10035,30 @@
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
-        <v>-1861492.9147629351</v>
+        <v>-2114499.0205040863</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
-        <v>-2302385</v>
+        <v>-2275223</v>
       </c>
       <c r="H23" s="186">
         <f>Data!D37</f>
-        <v>-2527935</v>
+        <v>-2302385</v>
       </c>
       <c r="I23" s="186">
         <f>Data!E37</f>
-        <v>-1379524</v>
+        <v>-2527935</v>
       </c>
       <c r="J23" s="186">
         <f>Data!F37</f>
+        <v>-1379524</v>
+      </c>
+      <c r="K23" s="186">
+        <f>Data!G37</f>
         <v>-1278781</v>
-      </c>
-      <c r="K23" s="186" t="str">
-        <f>Data!G37</f>
-        <v/>
       </c>
       <c r="L23" s="186" t="str">
         <f>Data!H37</f>
@@ -10046,30 +10092,30 @@
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
-        <v>-60351.560592512084</v>
+        <v>-63593.391803200633</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
-        <v>-70260</v>
+        <v>-63190</v>
       </c>
       <c r="H24" s="186">
         <f>Data!D40</f>
-        <v>-68352</v>
+        <v>-70260</v>
       </c>
       <c r="I24" s="186">
         <f>Data!E40</f>
-        <v>-48552</v>
+        <v>-68352</v>
       </c>
       <c r="J24" s="186">
         <f>Data!F40</f>
+        <v>-48552</v>
+      </c>
+      <c r="K24" s="186">
+        <f>Data!G40</f>
         <v>-47670</v>
-      </c>
-      <c r="K24" s="186" t="str">
-        <f>Data!G40</f>
-        <v/>
       </c>
       <c r="L24" s="186" t="str">
         <f>Data!H40</f>
@@ -10103,30 +10149,30 @@
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
-        <v>-1921844.4753554473</v>
+        <v>-2178092.4123072871</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-2372645</v>
+        <v>-2338413</v>
       </c>
       <c r="H25" s="187">
         <f t="shared" si="10"/>
-        <v>-2596287</v>
+        <v>-2372645</v>
       </c>
       <c r="I25" s="187">
         <f t="shared" si="10"/>
-        <v>-1428076</v>
+        <v>-2596287</v>
       </c>
       <c r="J25" s="187">
         <f t="shared" si="10"/>
+        <v>-1428076</v>
+      </c>
+      <c r="K25" s="187">
+        <f t="shared" si="10"/>
         <v>-1326451</v>
-      </c>
-      <c r="K25" s="187" t="str">
-        <f t="shared" si="10"/>
-        <v/>
       </c>
       <c r="L25" s="187" t="str">
         <f t="shared" si="10"/>
@@ -10171,7 +10217,7 @@
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
-        <v>0.75736628574622689</v>
+        <v>0.76614733079928599</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
@@ -10180,23 +10226,23 @@
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.76465487351096573</v>
+        <v>0.77441719330383685</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="11"/>
-        <v>0.7804274987983022</v>
+        <v>0.76465487351096573</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="11"/>
-        <v>0.74508975758403917</v>
+        <v>0.7804274987983022</v>
       </c>
       <c r="J28" s="13">
         <f t="shared" si="11"/>
+        <v>0.74508975758403917</v>
+      </c>
+      <c r="K28" s="13">
+        <f t="shared" si="11"/>
         <v>0.73929301309160078</v>
-      </c>
-      <c r="K28" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v/>
       </c>
       <c r="L28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -10231,7 +10277,7 @@
       </c>
       <c r="C29" s="64">
         <f>AVERAGE(G29:J29)</f>
-        <v>2.4554612549121772E-2</v>
+        <v>2.3041820740536588E-2</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
@@ -10240,23 +10286,23 @@
       <c r="F29" s="26"/>
       <c r="G29" s="13">
         <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
-        <v>2.3334347388851324E-2</v>
+        <v>2.1507967546420485E-2</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="12"/>
-        <v>2.1101721522848314E-2</v>
+        <v>2.3334347388851324E-2</v>
       </c>
       <c r="I29" s="13">
         <f t="shared" si="12"/>
-        <v>2.6223246504026222E-2</v>
+        <v>2.1101721522848314E-2</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="12"/>
+        <v>2.6223246504026222E-2</v>
+      </c>
+      <c r="K29" s="13">
+        <f t="shared" si="12"/>
         <v>2.7559134780761215E-2</v>
-      </c>
-      <c r="K29" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
       </c>
       <c r="L29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -10290,28 +10336,28 @@
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
-        <v>0.78192089829534861</v>
+        <v>0.78918915153982261</v>
       </c>
       <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.78798922089981704</v>
+        <v>0.79592516085025733</v>
       </c>
       <c r="H30" s="30">
         <f t="shared" si="13"/>
-        <v>0.80152922032115048</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="I30" s="30">
         <f t="shared" si="13"/>
-        <v>0.77131300408806547</v>
+        <v>0.80152922032115048</v>
       </c>
       <c r="J30" s="30">
         <f t="shared" si="13"/>
+        <v>0.77131300408806547</v>
+      </c>
+      <c r="K30" s="30">
+        <f t="shared" si="13"/>
         <v>0.766852147872362</v>
-      </c>
-      <c r="K30" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v/>
       </c>
       <c r="L30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -10356,30 +10402,30 @@
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
-        <v>-290830.75</v>
+        <v>-314015.75</v>
       </c>
       <c r="E33" s="306" t="s">
         <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
-        <v>-350038</v>
+        <v>-331038</v>
       </c>
       <c r="H33" s="197">
         <f>Data!D41</f>
-        <v>-327354</v>
+        <v>-350038</v>
       </c>
       <c r="I33" s="197">
         <f>Data!E41</f>
-        <v>-247633</v>
+        <v>-327354</v>
       </c>
       <c r="J33" s="197">
         <f>Data!F41</f>
+        <v>-247633</v>
+      </c>
+      <c r="K33" s="197">
+        <f>Data!G41</f>
         <v>-238298</v>
-      </c>
-      <c r="K33" s="197" t="str">
-        <f>Data!G41</f>
-        <v/>
       </c>
       <c r="L33" s="197" t="str">
         <f>Data!H41</f>
@@ -10413,7 +10459,7 @@
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
-        <v>-18496.5</v>
+        <v>-20445.75</v>
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
@@ -10422,23 +10468,23 @@
       <c r="F34" s="59"/>
       <c r="G34" s="186">
         <f>Data!C42</f>
-        <v>-21957</v>
+        <v>-23014</v>
       </c>
       <c r="H34" s="186">
         <f>Data!D42</f>
-        <v>-20016</v>
+        <v>-21957</v>
       </c>
       <c r="I34" s="186">
         <f>Data!E42</f>
-        <v>-16796</v>
+        <v>-20016</v>
       </c>
       <c r="J34" s="186">
         <f>Data!F42</f>
+        <v>-16796</v>
+      </c>
+      <c r="K34" s="186">
+        <f>Data!G42</f>
         <v>-15217</v>
-      </c>
-      <c r="K34" s="186" t="str">
-        <f>Data!G42</f>
-        <v/>
       </c>
       <c r="L34" s="186" t="str">
         <f>Data!H42</f>
@@ -10472,30 +10518,30 @@
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
-        <v>-309327.25</v>
+        <v>-334461.5</v>
       </c>
       <c r="D35" s="59"/>
       <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-371995</v>
+        <v>-354052</v>
       </c>
       <c r="H35" s="187">
         <f t="shared" si="14"/>
-        <v>-347370</v>
+        <v>-371995</v>
       </c>
       <c r="I35" s="187">
         <f t="shared" si="14"/>
-        <v>-264429</v>
+        <v>-347370</v>
       </c>
       <c r="J35" s="187">
         <f t="shared" si="14"/>
+        <v>-264429</v>
+      </c>
+      <c r="K35" s="187">
+        <f t="shared" si="14"/>
         <v>-253515</v>
-      </c>
-      <c r="K35" s="187" t="str">
-        <f t="shared" si="14"/>
-        <v/>
       </c>
       <c r="L35" s="187" t="str">
         <f t="shared" si="14"/>
@@ -10541,30 +10587,30 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>0.11832728621281952</v>
+        <v>0.11377746045684251</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>0.1162526087574543</v>
+        <v>0.11267533724690527</v>
       </c>
       <c r="H38" s="13">
         <f t="shared" si="15"/>
-        <v>0.10106116788668197</v>
+        <v>0.1162526087574543</v>
       </c>
       <c r="I38" s="13">
         <f t="shared" si="15"/>
-        <v>0.13374817106466316</v>
+        <v>0.10106116788668197</v>
       </c>
       <c r="J38" s="13">
         <f t="shared" si="15"/>
+        <v>0.13374817106466316</v>
+      </c>
+      <c r="K38" s="13">
+        <f t="shared" si="15"/>
         <v>0.13776561149540248</v>
-      </c>
-      <c r="K38" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
       </c>
       <c r="L38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -10599,30 +10645,30 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>7.525478820363446E-3</v>
+        <v>7.4081173066493887E-3</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
-        <v>7.2922326447055008E-3</v>
+        <v>7.8332705351055708E-3</v>
       </c>
       <c r="H39" s="13">
         <f t="shared" si="16"/>
-        <v>6.1793664852722941E-3</v>
+        <v>7.2922326447055008E-3</v>
       </c>
       <c r="I39" s="13">
         <f t="shared" si="16"/>
-        <v>9.0716272920090719E-3</v>
+        <v>6.1793664852722941E-3</v>
       </c>
       <c r="J39" s="13">
         <f t="shared" si="16"/>
+        <v>9.0716272920090719E-3</v>
+      </c>
+      <c r="K39" s="13">
+        <f t="shared" si="16"/>
         <v>8.7973013207225392E-3</v>
-      </c>
-      <c r="K39" s="13" t="str">
-        <f t="shared" si="16"/>
-        <v/>
       </c>
       <c r="L39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -10656,28 +10702,28 @@
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
-        <v>0.12585276503318296</v>
+        <v>0.1211855777634919</v>
       </c>
       <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>0.12354484140215981</v>
+        <v>0.12050860778201085</v>
       </c>
       <c r="H40" s="30">
         <f t="shared" si="17"/>
-        <v>0.10724053437195427</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="I40" s="30">
         <f t="shared" si="17"/>
-        <v>0.14281979835667225</v>
+        <v>0.10724053437195427</v>
       </c>
       <c r="J40" s="30">
         <f t="shared" si="17"/>
+        <v>0.14281979835667225</v>
+      </c>
+      <c r="K40" s="30">
+        <f t="shared" si="17"/>
         <v>0.14656291281612502</v>
-      </c>
-      <c r="K40" s="30" t="str">
-        <f t="shared" si="17"/>
-        <v/>
       </c>
       <c r="L40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10730,23 +10776,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.21369784384077392</v>
+        <v>0.22898399640494022</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.17038957733553248</v>
+        <v>0.21243208886789264</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.15226345717775083</v>
+        <v>0.16985990411621268</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.11581450262802505</v>
-      </c>
-      <c r="K43" s="6" t="str">
+        <v>0.15190126106863075</v>
+      </c>
+      <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0.11555258469400535</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10813,28 +10859,28 @@
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>-24063</v>
+        <v>-20731</v>
       </c>
       <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
-        <v>-24063</v>
+        <v>-20731</v>
       </c>
       <c r="H47" s="197">
         <f>Data!D51</f>
-        <v>-21554</v>
+        <v>-24063</v>
       </c>
       <c r="I47" s="197">
         <f>Data!E51</f>
-        <v>-14912</v>
+        <v>-21554</v>
       </c>
       <c r="J47" s="197">
         <f>Data!F51</f>
+        <v>-14912</v>
+      </c>
+      <c r="K47" s="197">
+        <f>Data!G51</f>
         <v>-15097</v>
-      </c>
-      <c r="K47" s="197" t="str">
-        <f>Data!G51</f>
-        <v/>
       </c>
       <c r="L47" s="197" t="str">
         <f>Data!H51</f>
@@ -10868,28 +10914,28 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>6666.227894779714</v>
+        <v>8793.8666926784372</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>6666.227894779714</v>
+        <v>8793.8666926784372</v>
       </c>
       <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>3821.4867229844263</v>
+        <v>8260.1782265015663</v>
       </c>
       <c r="I48" s="334">
         <f t="shared" si="19"/>
-        <v>1580.8598516356005</v>
+        <v>4735.2358665655684</v>
       </c>
       <c r="J48" s="334">
         <f t="shared" si="19"/>
-        <v>1396.9639097106431</v>
-      </c>
-      <c r="K48" s="334" t="str">
+        <v>1958.8565425218476</v>
+      </c>
+      <c r="K48" s="334">
         <f t="shared" si="19"/>
-        <v/>
+        <v>1730.9895569631838</v>
       </c>
       <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
@@ -10923,30 +10969,30 @@
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
-        <v>8265</v>
+        <v>8799</v>
       </c>
       <c r="D49" s="331"/>
       <c r="E49" s="332"/>
       <c r="F49" s="331"/>
       <c r="G49" s="330">
         <f>Data!C52</f>
-        <v>8265</v>
+        <v>8799</v>
       </c>
       <c r="H49" s="330">
         <f>Data!D52</f>
-        <v>4738</v>
+        <v>8265</v>
       </c>
       <c r="I49" s="330">
         <f>Data!E52</f>
-        <v>1960</v>
+        <v>4738</v>
       </c>
       <c r="J49" s="330">
         <f>Data!F52</f>
+        <v>1960</v>
+      </c>
+      <c r="K49" s="330">
+        <f>Data!G52</f>
         <v>1732</v>
-      </c>
-      <c r="K49" s="330" t="str">
-        <f>Data!G52</f>
-        <v/>
       </c>
       <c r="L49" s="330" t="str">
         <f>Data!H52</f>
@@ -10980,28 +11026,28 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>-17396.772105220287</v>
+        <v>-11937.133307321563</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-17396.772105220287</v>
+        <v>-11937.133307321563</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-17732.513277015572</v>
+        <v>-15802.821773498434</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
-        <v>-13331.1401483644</v>
+        <v>-16818.76413343443</v>
       </c>
       <c r="J50" s="187">
         <f t="shared" si="20"/>
-        <v>-13700.036090289357</v>
-      </c>
-      <c r="K50" s="187" t="str">
+        <v>-12953.143457478152</v>
+      </c>
+      <c r="K50" s="187">
         <f t="shared" si="20"/>
-        <v/>
+        <v>-13366.010443036816</v>
       </c>
       <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -11049,14 +11095,14 @@
       </c>
       <c r="C53" s="89">
         <f>G53</f>
-        <v>3.4598961821835229E-2</v>
+        <v>4.0689769984184679E-2</v>
       </c>
       <c r="E53" s="305" t="s">
         <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>3.4598961821835229E-2</v>
+        <v>4.0689769984184679E-2</v>
       </c>
       <c r="H53" s="173"/>
       <c r="I53" s="173"/>
@@ -11076,14 +11122,14 @@
       </c>
       <c r="C54" s="84">
         <f>G54</f>
-        <v>9.7930927826660269E-2</v>
+        <v>7.4105716195589616E-2</v>
       </c>
       <c r="E54" s="305" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>9.7930927826660269E-2</v>
+        <v>7.4105716195589616E-2</v>
       </c>
       <c r="H54" s="173"/>
       <c r="I54" s="173"/>
@@ -11103,28 +11149,28 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>9.4202104743611663</v>
+        <v>11.931785137847326</v>
       </c>
       <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>11.069775173502888</v>
+        <v>11.842940523853168</v>
       </c>
       <c r="H55" s="42">
         <f t="shared" si="21"/>
-        <v>13.710216201169157</v>
+        <v>11.069775173502888</v>
       </c>
       <c r="I55" s="42">
         <f t="shared" si="21"/>
-        <v>10.661346566523605</v>
+        <v>13.710216201169157</v>
       </c>
       <c r="J55" s="42">
         <f t="shared" si="21"/>
+        <v>10.661346566523605</v>
+      </c>
+      <c r="K55" s="42">
+        <f t="shared" si="21"/>
         <v>9.9204477710803474</v>
-      </c>
-      <c r="K55" s="42" t="str">
-        <f t="shared" si="21"/>
-        <v/>
       </c>
       <c r="L55" s="42" t="str">
         <f t="shared" si="21"/>
@@ -11191,9 +11237,9 @@
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="197" t="str">
+      <c r="K58" s="197">
         <f>Data!G56</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L58" s="197" t="str">
         <f>Data!H56</f>
@@ -11227,28 +11273,28 @@
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
-        <v>18538.000000000004</v>
+        <v>18644</v>
       </c>
       <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
-        <v>18538</v>
+        <v>18644</v>
       </c>
       <c r="H59" s="197">
         <f>Data!D55</f>
-        <v>15251</v>
+        <v>18538</v>
       </c>
       <c r="I59" s="197">
         <f>Data!E55</f>
-        <v>12877</v>
+        <v>15251</v>
       </c>
       <c r="J59" s="197">
         <f>Data!F55</f>
+        <v>12877</v>
+      </c>
+      <c r="K59" s="197">
+        <f>Data!G55</f>
         <v>11296</v>
-      </c>
-      <c r="K59" s="197" t="str">
-        <f>Data!G55</f>
-        <v/>
       </c>
       <c r="L59" s="197" t="str">
         <f>Data!H55</f>
@@ -11301,9 +11347,9 @@
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="197" t="str">
+      <c r="K60" s="197">
         <f>Data!G57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L60" s="197" t="str">
         <f>Data!H57</f>
@@ -11337,28 +11383,28 @@
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
-        <v>18538.000000000004</v>
+        <v>18644</v>
       </c>
       <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
-        <v>18538</v>
+        <v>18644</v>
       </c>
       <c r="H61" s="187">
         <f t="shared" si="22"/>
-        <v>15251</v>
+        <v>18538</v>
       </c>
       <c r="I61" s="187">
         <f t="shared" si="22"/>
-        <v>12877</v>
+        <v>15251</v>
       </c>
       <c r="J61" s="187">
         <f t="shared" si="22"/>
+        <v>12877</v>
+      </c>
+      <c r="K61" s="187">
+        <f t="shared" si="22"/>
         <v>11296</v>
-      </c>
-      <c r="K61" s="187" t="str">
-        <f t="shared" si="22"/>
-        <v/>
       </c>
       <c r="L61" s="187" t="str">
         <f t="shared" si="22"/>
@@ -11398,23 +11444,23 @@
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
-        <v>-31654</v>
+        <v>-10726</v>
       </c>
       <c r="H62" s="197">
         <f>Data!D58</f>
-        <v>-80673</v>
+        <v>-31384</v>
       </c>
       <c r="I62" s="197">
         <f>Data!E58</f>
-        <v>-2375</v>
+        <v>-80673</v>
       </c>
       <c r="J62" s="197">
         <f>Data!F58</f>
+        <v>-2375</v>
+      </c>
+      <c r="K62" s="197">
+        <f>Data!G58</f>
         <v>-1615</v>
-      </c>
-      <c r="K62" s="197" t="str">
-        <f>Data!G58</f>
-        <v/>
       </c>
       <c r="L62" s="197" t="str">
         <f>Data!H58</f>
@@ -11448,28 +11494,28 @@
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
-        <v>18538.000000000004</v>
+        <v>18644</v>
       </c>
       <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>-13116</v>
+        <v>7918</v>
       </c>
       <c r="H63" s="187">
         <f t="shared" si="23"/>
-        <v>-65422</v>
+        <v>-12846</v>
       </c>
       <c r="I63" s="187">
         <f t="shared" si="23"/>
-        <v>10502</v>
+        <v>-65422</v>
       </c>
       <c r="J63" s="187">
         <f t="shared" si="23"/>
+        <v>10502</v>
+      </c>
+      <c r="K63" s="187">
+        <f t="shared" si="23"/>
         <v>9681</v>
-      </c>
-      <c r="K63" s="187" t="str">
-        <f t="shared" si="23"/>
-        <v/>
       </c>
       <c r="L63" s="187" t="str">
         <f t="shared" si="23"/>
@@ -11542,12 +11588,12 @@
       </c>
       <c r="C67" s="180">
         <f>G67</f>
-        <v>6.3354818424775985E-2</v>
+        <v>6.4272589691702547E-2</v>
       </c>
       <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
-        <v>6.3354818424775985E-2</v>
+        <v>6.4272589691702547E-2</v>
       </c>
       <c r="H67" s="179"/>
       <c r="I67" s="179"/>
@@ -11592,14 +11638,14 @@
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
-        <v>3.4879564090117152E-2</v>
+        <v>3.6822344629811404E-2</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
-        <v>3.4879564090117145E-2</v>
+        <v>3.6822344629811404E-2</v>
       </c>
       <c r="H69" s="179"/>
       <c r="I69" s="179"/>
@@ -11666,30 +11712,30 @@
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
-        <v>0.78192089829534861</v>
+        <v>0.78918915153982261</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.78798922089981704</v>
+        <v>0.79592516085025733</v>
       </c>
       <c r="H73" s="6">
         <f t="shared" si="24"/>
-        <v>0.80152922032115048</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="I73" s="6">
         <f t="shared" si="24"/>
-        <v>0.77131300408806547</v>
+        <v>0.80152922032115048</v>
       </c>
       <c r="J73" s="6">
         <f t="shared" si="24"/>
+        <v>0.77131300408806547</v>
+      </c>
+      <c r="K73" s="6">
+        <f t="shared" si="24"/>
         <v>0.766852147872362</v>
-      </c>
-      <c r="K73" s="6" t="str">
-        <f t="shared" si="24"/>
-        <v/>
       </c>
       <c r="L73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -11723,30 +11769,30 @@
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
-        <v>0.21807910170465133</v>
+        <v>0.21081084846017736</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.21201077910018293</v>
+        <v>0.20407483914974264</v>
       </c>
       <c r="H74" s="66">
         <f t="shared" si="25"/>
-        <v>0.19847077967884952</v>
+        <v>0.21201077910018293</v>
       </c>
       <c r="I74" s="66">
         <f t="shared" si="25"/>
-        <v>0.22868699591193456</v>
+        <v>0.19847077967884952</v>
       </c>
       <c r="J74" s="66">
         <f t="shared" si="25"/>
+        <v>0.22868699591193456</v>
+      </c>
+      <c r="K74" s="66">
+        <f t="shared" si="25"/>
         <v>0.23314785212763806</v>
-      </c>
-      <c r="K74" s="66" t="str">
-        <f t="shared" si="25"/>
-        <v/>
       </c>
       <c r="L74" s="66" t="str">
         <f t="shared" si="25"/>
@@ -11780,30 +11826,30 @@
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
-        <v>0.12585276503318296</v>
+        <v>0.1211855777634919</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>0.12354484140215981</v>
+        <v>0.12050860778201085</v>
       </c>
       <c r="H75" s="6">
         <f t="shared" si="26"/>
-        <v>0.10724053437195427</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" si="26"/>
-        <v>0.14281979835667225</v>
+        <v>0.10724053437195427</v>
       </c>
       <c r="J75" s="6">
         <f t="shared" si="26"/>
+        <v>0.14281979835667225</v>
+      </c>
+      <c r="K75" s="6">
+        <f t="shared" si="26"/>
         <v>0.14656291281612502</v>
-      </c>
-      <c r="K75" s="6" t="str">
-        <f t="shared" si="26"/>
-        <v/>
       </c>
       <c r="L75" s="6" t="str">
         <f t="shared" si="26"/>
@@ -11837,30 +11883,30 @@
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
-        <v>9.2226336671468387E-2</v>
+        <v>8.9625270696685466E-2</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>8.846593769802312E-2</v>
+        <v>8.356623136773178E-2</v>
       </c>
       <c r="H76" s="66">
         <f t="shared" si="27"/>
-        <v>9.1230245306895261E-2</v>
+        <v>8.846593769802312E-2</v>
       </c>
       <c r="I76" s="66">
         <f t="shared" si="27"/>
-        <v>8.5867197555262342E-2</v>
+        <v>9.1230245306895261E-2</v>
       </c>
       <c r="J76" s="66">
         <f t="shared" si="27"/>
+        <v>8.5867197555262342E-2</v>
+      </c>
+      <c r="K76" s="66">
+        <f t="shared" si="27"/>
         <v>8.6584939311513037E-2</v>
-      </c>
-      <c r="K76" s="66" t="str">
-        <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="L76" s="66" t="str">
         <f t="shared" si="27"/>
@@ -11894,30 +11940,30 @@
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>9.3408457248361651E-2</v>
+        <v>8.8122020568230111E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>7.6248118572758927E-2</v>
+        <v>8.2780998243351472E-2</v>
       </c>
       <c r="H77" s="6">
         <f t="shared" si="28"/>
-        <v>6.873619050823869E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="28"/>
-        <v>0.12856476983095208</v>
+        <v>6.873619050823869E-2</v>
       </c>
       <c r="J77" s="6">
         <f t="shared" si="28"/>
+        <v>0.12856476983095208</v>
+      </c>
+      <c r="K77" s="6">
+        <f t="shared" si="28"/>
         <v>0.13690998910237695</v>
-      </c>
-      <c r="K77" s="6" t="str">
-        <f t="shared" si="28"/>
-        <v/>
       </c>
       <c r="L77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11950,7 +11996,7 @@
         <v>82</v>
       </c>
       <c r="C78" s="90">
-        <f>MAX(AVERAGE(G78:J78),C77)</f>
+        <f>MAX(AVERAGE(H78:K78),C77)</f>
         <v>0.10287256125768818</v>
       </c>
       <c r="D78" s="27"/>
@@ -11960,23 +12006,23 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>3.8291776983950913E-2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
-        <v>8.7216250350784633E-2</v>
+        <v>3.8291776983950913E-2</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="29"/>
-        <v>0.13245407610207363</v>
+        <v>8.7216250350784633E-2</v>
       </c>
       <c r="J78" s="6">
         <f t="shared" si="29"/>
+        <v>0.13245407610207363</v>
+      </c>
+      <c r="K78" s="6">
+        <f t="shared" si="29"/>
         <v>0.15352814159394357</v>
-      </c>
-      <c r="K78" s="6" t="str">
-        <f t="shared" si="29"/>
-        <v/>
       </c>
       <c r="L78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -12010,30 +12056,30 @@
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
-        <v>7.542363494277165E-3</v>
+        <v>6.7552884616691091E-3</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>6.156734015008907E-3</v>
+        <v>6.3458545170986466E-3</v>
       </c>
       <c r="H79" s="66">
         <f t="shared" si="30"/>
-        <v>4.7083092659316421E-3</v>
+        <v>6.156734015008907E-3</v>
       </c>
       <c r="I79" s="66">
         <f t="shared" si="30"/>
-        <v>6.9549502643010729E-3</v>
+        <v>4.7083092659316421E-3</v>
       </c>
       <c r="J79" s="66">
         <f t="shared" si="30"/>
+        <v>6.9549502643010729E-3</v>
+      </c>
+      <c r="K79" s="66">
+        <f t="shared" si="30"/>
         <v>6.5304801024434382E-3</v>
-      </c>
-      <c r="K79" s="66" t="str">
-        <f t="shared" si="30"/>
-        <v/>
       </c>
       <c r="L79" s="66" t="str">
         <f t="shared" si="30"/>
@@ -12067,30 +12113,30 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>7.0780439553712786E-3</v>
+        <v>4.3251865960285008E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.7777159656687812E-3</v>
+        <v>4.0630396545524167E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>5.474405387871503E-3</v>
+        <v>5.2483423425407913E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2002342702727051E-3</v>
+        <v>5.1923115212752016E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9203092325063427E-3</v>
-      </c>
-      <c r="K80" s="6" t="str">
+        <v>6.9960758338989968E-3</v>
+      </c>
+      <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v/>
+        <v>7.7272012435643696E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12124,30 +12170,30 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>8.3226552201047743E-2</v>
+        <v>7.7304831872868032E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12680129733617126</v>
+        <v>0.16863004447362948</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>7.1984089342409463E-2</v>
+        <v>0.12733067095929926</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
-        <v>8.1732607278169167E-2</v>
+        <v>7.2266183209005769E-2</v>
       </c>
       <c r="J81" s="66">
         <f t="shared" si="32"/>
-        <v>6.8576957689883505E-2</v>
-      </c>
-      <c r="K81" s="66" t="str">
+        <v>8.1936765714542878E-2</v>
+      </c>
+      <c r="K81" s="66">
         <f t="shared" si="32"/>
-        <v/>
+        <v>6.8770065678825473E-2</v>
       </c>
       <c r="L81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -12181,30 +12227,30 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>2.3172664052593564E-2</v>
+        <v>2.3013843140581518E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>1.89859754793405E-2</v>
+        <v>1.9658057693361531E-2</v>
       </c>
       <c r="H82" s="6">
         <f t="shared" si="33"/>
-        <v>1.5414148143643103E-2</v>
+        <v>1.89859754793405E-2</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" si="33"/>
-        <v>1.3037088567189508E-2</v>
+        <v>1.5414148143643103E-2</v>
       </c>
       <c r="J82" s="6">
         <f t="shared" si="33"/>
+        <v>1.3037088567189508E-2</v>
+      </c>
+      <c r="K82" s="6">
+        <f t="shared" si="33"/>
         <v>9.8668293120044402E-3</v>
-      </c>
-      <c r="K82" s="6" t="str">
-        <f t="shared" si="33"/>
-        <v/>
       </c>
       <c r="L82" s="6" t="str">
         <f t="shared" si="33"/>
@@ -12239,30 +12285,30 @@
       </c>
       <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>6.358991594852495E-3</v>
+        <v>6.4911924209176304E-3</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
-        <v>6.358991594852495E-3</v>
+        <v>6.4911924209176304E-3</v>
       </c>
       <c r="H83" s="6">
         <f t="shared" si="34"/>
-        <v>4.5088752756495725E-3</v>
+        <v>6.358991594852495E-3</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>4.5088752756495725E-3</v>
       </c>
       <c r="J83" s="6">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="K83" s="6" t="str">
+      <c r="K83" s="6">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L83" s="6" t="str">
         <f t="shared" si="34"/>
@@ -12296,30 +12342,30 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>5.3694896553601684E-2</v>
+        <v>4.7799796311368881E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.10145633026197827</v>
+        <v>0.14248079435935032</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>5.2061065923116788E-2</v>
+        <v>0.10198570388510626</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
-        <v>6.8695518710979647E-2</v>
+        <v>5.2343159789713087E-2</v>
       </c>
       <c r="J84" s="66">
         <f t="shared" si="35"/>
-        <v>5.8710128377879062E-2</v>
-      </c>
-      <c r="K84" s="66" t="str">
+        <v>6.8899677147353372E-2</v>
+      </c>
+      <c r="K84" s="66">
         <f t="shared" si="35"/>
-        <v/>
+        <v>5.890323636682103E-2</v>
       </c>
       <c r="L84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12403,30 +12449,30 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>5.3694896553601684E-2</v>
+        <v>4.7799796311368881E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.10145633026197827</v>
+        <v>0.14248079435935032</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>5.2061065923116788E-2</v>
+        <v>0.10198570388510626</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
-        <v>6.8695518710979647E-2</v>
+        <v>5.2343159789713087E-2</v>
       </c>
       <c r="J87" s="66">
         <f t="shared" si="36"/>
-        <v>5.8710128377879062E-2</v>
-      </c>
-      <c r="K87" s="66" t="str">
+        <v>6.8899677147353372E-2</v>
+      </c>
+      <c r="K87" s="66">
         <f t="shared" si="36"/>
-        <v/>
+        <v>5.890323636682103E-2</v>
       </c>
       <c r="L87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12491,9 +12537,9 @@
         <f>Data!F65</f>
         <v>0.21309006776117467</v>
       </c>
-      <c r="K90" s="116" t="str">
+      <c r="K90" s="116">
         <f>Data!G65</f>
-        <v/>
+        <v>0.16495954981251937</v>
       </c>
       <c r="L90" s="116" t="str">
         <f>Data!H65</f>
@@ -12547,9 +12593,9 @@
         <f t="shared" si="37"/>
         <v>38999.952564954066</v>
       </c>
-      <c r="K91" s="76" t="str">
+      <c r="K91" s="76">
         <f t="shared" si="37"/>
-        <v/>
+        <v>30191.058107104374</v>
       </c>
       <c r="L91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12583,28 +12629,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.61287975046304477</v>
+        <v>0.61311573235445505</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.2647720058869748</v>
+        <v>0.19322280877140188</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>0.44902665783547285</v>
+        <v>0.24658504631051181</v>
       </c>
       <c r="I92" s="174">
         <f t="shared" si="38"/>
-        <v>0.5717757182764398</v>
+        <v>0.42892514526464171</v>
       </c>
       <c r="J92" s="174">
         <f t="shared" si="38"/>
-        <v>0.38403559151290151</v>
-      </c>
-      <c r="K92" s="174" t="str">
+        <v>0.30572167114546883</v>
+      </c>
+      <c r="K92" s="174">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0.29631907114327971</v>
       </c>
       <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12638,28 +12684,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.1992488015582468E-2</v>
+        <v>8.2144890409663482E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.1992488015582468E-2</v>
+        <v>8.2144890409663482E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6758924950758062E-2</v>
+        <v>7.6901599532450918E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3719969331116686E-2</v>
+        <v>7.3856995296416164E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.9534335391683613E-2</v>
-      </c>
-      <c r="K93" s="23" t="str">
+        <v>3.9607819286463695E-2</v>
+      </c>
+      <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v/>
+        <v>3.0661626359204344E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12718,26 +12764,26 @@
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
-        <v>-0.18371290117741146</v>
+        <v>-6.0609394682947237E-2</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="305"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-7.0436318967191269E-2</v>
+        <v>-2.4254635982852268E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>0.74949486547839661</v>
+        <v>-7.0436318967191269E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
+        <v>0.74949486547839661</v>
+      </c>
+      <c r="J96" s="6">
+        <f t="shared" si="40"/>
         <v>7.0387660537596819E-2</v>
-      </c>
-      <c r="J96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
       </c>
       <c r="K96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -12775,26 +12821,26 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.46422661070187343</v>
+        <v>-0.569356498519202</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.63744352103797386</v>
+        <v>0.29222584699757026</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.54082683636988382</v>
+        <v>0.63786105685118555</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27572842600778635</v>
-      </c>
-      <c r="J97" s="6" t="str">
+        <v>0.54301082510798793</v>
+      </c>
+      <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.2753238214837288</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12868,30 +12914,30 @@
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
-        <v>2768297</v>
+        <v>2753007</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>2752710</v>
+        <v>2753007</v>
       </c>
       <c r="H101" s="186">
         <f t="shared" si="42"/>
-        <v>2670666</v>
+        <v>2768297</v>
       </c>
       <c r="I101" s="186">
         <f t="shared" si="42"/>
-        <v>1981074</v>
+        <v>2670666</v>
       </c>
       <c r="J101" s="186">
         <f t="shared" si="42"/>
+        <v>1981074</v>
+      </c>
+      <c r="K101" s="186">
+        <f t="shared" si="42"/>
         <v>1946908</v>
-      </c>
-      <c r="K101" s="186" t="str">
-        <f t="shared" si="42"/>
-        <v/>
       </c>
       <c r="L101" s="186" t="str">
         <f t="shared" si="42"/>
@@ -12925,26 +12971,26 @@
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
-        <v>142879</v>
+        <v>114865</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
         <f>IF(G$4="","",Data!D77)</f>
-        <v>117877</v>
+        <v>142879</v>
       </c>
       <c r="H102" s="188">
         <f>IF(H$4="","",Data!E77)</f>
-        <v>23709</v>
+        <v>117877</v>
       </c>
       <c r="I102" s="188">
         <f>IF(I$4="","",Data!F77)</f>
+        <v>23709</v>
+      </c>
+      <c r="J102" s="188">
+        <f>IF(J$4="","",Data!G77)</f>
         <v>27379</v>
-      </c>
-      <c r="J102" s="188" t="str">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v/>
       </c>
       <c r="K102" s="188" t="str">
         <f>IF(K$4="","",Data!H77)</f>
@@ -12982,26 +13028,26 @@
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
-        <v>182674</v>
+        <v>168338</v>
       </c>
       <c r="D103" s="91"/>
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
         <f>IF(G$4="","",Data!D78)</f>
-        <v>167751</v>
+        <v>182674</v>
       </c>
       <c r="H103" s="188">
         <f>IF(H$4="","",Data!E78)</f>
-        <v>110386</v>
+        <v>167751</v>
       </c>
       <c r="I103" s="188">
         <f>IF(I$4="","",Data!F78)</f>
+        <v>110386</v>
+      </c>
+      <c r="J103" s="188">
+        <f>IF(J$4="","",Data!G78)</f>
         <v>109354</v>
-      </c>
-      <c r="J103" s="188" t="str">
-        <f>IF(J$4="","",Data!G78)</f>
-        <v/>
       </c>
       <c r="K103" s="188" t="str">
         <f>IF(K$4="","",Data!H78)</f>
@@ -13039,30 +13085,30 @@
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
-        <v>1090144</v>
+        <v>1043144</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C79</f>
-        <v>1122089</v>
+        <v>1043144</v>
       </c>
       <c r="H104" s="186">
         <f>Data!D79</f>
-        <v>1136250</v>
+        <v>1090144</v>
       </c>
       <c r="I104" s="186">
         <f>Data!E79</f>
-        <v>689466</v>
+        <v>1136250</v>
       </c>
       <c r="J104" s="186">
         <f>Data!F79</f>
+        <v>689466</v>
+      </c>
+      <c r="K104" s="186">
+        <f>Data!G79</f>
         <v>707978</v>
-      </c>
-      <c r="K104" s="186" t="str">
-        <f>Data!G79</f>
-        <v/>
       </c>
       <c r="L104" s="186" t="str">
         <f>Data!H79</f>
@@ -13096,30 +13142,30 @@
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
-        <v>1678153</v>
+        <v>1709863</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C80</f>
-        <v>1630621</v>
+        <v>1709863</v>
       </c>
       <c r="H105" s="186">
         <f>Data!D80</f>
-        <v>1534416</v>
+        <v>1678153</v>
       </c>
       <c r="I105" s="186">
         <f>Data!E80</f>
-        <v>1291608</v>
+        <v>1534416</v>
       </c>
       <c r="J105" s="186">
         <f>Data!F80</f>
+        <v>1291608</v>
+      </c>
+      <c r="K105" s="186">
+        <f>Data!G80</f>
         <v>1238930</v>
-      </c>
-      <c r="K105" s="186" t="str">
-        <f>Data!G80</f>
-        <v/>
       </c>
       <c r="L105" s="186" t="str">
         <f>Data!H80</f>
@@ -13180,30 +13226,30 @@
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>5.8131694557062623E-2</v>
+        <v>4.1619084378332026E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="309"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>3.9148631755702067E-2</v>
+        <v>4.8631696392862987E-2</v>
       </c>
       <c r="H108" s="97">
         <f t="shared" si="43"/>
-        <v>7.3194744204296966E-3</v>
+        <v>3.9148631755702067E-2</v>
       </c>
       <c r="I108" s="97">
         <f t="shared" si="43"/>
+        <v>7.3194744204296966E-3</v>
+      </c>
+      <c r="J108" s="97">
+        <f t="shared" si="43"/>
         <v>1.478757344772067E-2</v>
       </c>
-      <c r="J108" s="97" t="e">
+      <c r="K108" s="97" t="e">
         <f t="shared" si="43"/>
         <v>#VALUE!</v>
-      </c>
-      <c r="K108" s="97" t="str">
-        <f t="shared" si="43"/>
-        <v/>
       </c>
       <c r="L108" s="97" t="str">
         <f t="shared" si="43"/>
@@ -13237,30 +13283,30 @@
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
-        <v>7.4322672831674749E-2</v>
+        <v>6.0993979245894364E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="309"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>5.5712497990708772E-2</v>
+        <v>6.2176712511074782E-2</v>
       </c>
       <c r="H109" s="97">
         <f t="shared" si="44"/>
-        <v>3.4078514630459002E-2</v>
+        <v>5.5712497990708772E-2</v>
       </c>
       <c r="I109" s="97">
         <f t="shared" si="44"/>
+        <v>3.4078514630459002E-2</v>
+      </c>
+      <c r="J109" s="97">
+        <f t="shared" si="44"/>
         <v>5.9062796552176708E-2</v>
       </c>
-      <c r="J109" s="97" t="e">
+      <c r="K109" s="97" t="e">
         <f t="shared" si="44"/>
         <v>#VALUE!</v>
-      </c>
-      <c r="K109" s="97" t="str">
-        <f t="shared" si="44"/>
-        <v/>
       </c>
       <c r="L109" s="97" t="str">
         <f t="shared" si="44"/>
@@ -13334,23 +13380,23 @@
       <c r="E113" s="308"/>
       <c r="G113" s="340">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>2.5325501550271508</v>
+        <v>2.2124551693360979</v>
       </c>
       <c r="H113" s="340">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>2.4106818167904347</v>
+        <v>2.5287631326809223</v>
       </c>
       <c r="I113" s="340">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>2.089210991434657</v>
+        <v>2.4106818167904347</v>
       </c>
       <c r="J113" s="340">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>2.089210991434657</v>
+      </c>
+      <c r="K113" s="340">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.9893115689283667</v>
-      </c>
-      <c r="K113" s="340" t="str">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v/>
       </c>
       <c r="L113" s="340" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
@@ -13386,23 +13432,23 @@
       <c r="E114" s="308"/>
       <c r="G114" s="340">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4946533044928882</v>
+        <v>0.97115695776537569</v>
       </c>
       <c r="H114" s="340">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.3350383877696497</v>
+        <v>1.4868950599058723</v>
       </c>
       <c r="I114" s="340">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>2.1747109009597989</v>
+        <v>2.3224541263283642</v>
       </c>
       <c r="J114" s="340">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>2.5273216075523925</v>
-      </c>
-      <c r="K114" s="340" t="str">
+        <v>2.1682669581796996</v>
+      </c>
+      <c r="K114" s="340">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v/>
+        <v>2.5190360527484983</v>
       </c>
       <c r="L114" s="340" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13494,28 +13540,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>8.3226552201047743E-2</v>
+        <v>7.7304831872868032E-2</v>
       </c>
       <c r="E117" s="308"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12680129733617126</v>
+        <v>0.16863004447362948</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>7.1984089342409463E-2</v>
+        <v>0.12733067095929926</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>8.1732607278169167E-2</v>
+        <v>7.2266183209005769E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>6.8576957689883505E-2</v>
-      </c>
-      <c r="K117" s="23" t="str">
+        <v>8.1936765714542878E-2</v>
+      </c>
+      <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v/>
+        <v>6.8770065678825473E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13548,28 +13594,28 @@
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
-        <v>0.88785641497281542</v>
+        <v>1.0025080757150273</v>
       </c>
       <c r="E118" s="308"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
-        <v>1.0938355293510758</v>
+        <v>1.0671898037309748</v>
       </c>
       <c r="H118" s="42">
         <f t="shared" si="46"/>
-        <v>1.2128686252792376</v>
+        <v>1.0876766474117481</v>
       </c>
       <c r="I118" s="42">
         <f t="shared" si="46"/>
-        <v>0.93458750152694947</v>
+        <v>1.2128686252792376</v>
       </c>
       <c r="J118" s="42">
         <f t="shared" si="46"/>
+        <v>0.93458750152694947</v>
+      </c>
+      <c r="K118" s="42">
+        <f t="shared" si="46"/>
         <v>0.88845235624898555</v>
-      </c>
-      <c r="K118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
       </c>
       <c r="L118" s="42" t="str">
         <f t="shared" si="46"/>
@@ -13602,30 +13648,30 @@
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
-        <v>1.6496094217869288</v>
+        <v>1.6100746083165727</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="312"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.6881359923611925</v>
+        <v>1.6100746083165727</v>
       </c>
       <c r="H119" s="15">
         <f t="shared" si="47"/>
-        <v>1.7405097444239372</v>
+        <v>1.6496094217869288</v>
       </c>
       <c r="I119" s="15">
         <f t="shared" si="47"/>
-        <v>1.5338043740825389</v>
+        <v>1.7405097444239372</v>
       </c>
       <c r="J119" s="15">
         <f t="shared" si="47"/>
+        <v>1.5338043740825389</v>
+      </c>
+      <c r="K119" s="15">
+        <f t="shared" si="47"/>
         <v>1.5714431000944362</v>
-      </c>
-      <c r="K119" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
       </c>
       <c r="L119" s="15" t="str">
         <f t="shared" si="47"/>
@@ -13659,30 +13705,30 @@
       </c>
       <c r="C120" s="105">
         <f>C8/C105</f>
-        <v>0.13507619665462728</v>
+        <v>0.14466529639667791</v>
       </c>
       <c r="D120" s="106"/>
       <c r="E120" s="311"/>
       <c r="F120" s="106"/>
       <c r="G120" s="105">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
-        <v>0.16335616921406015</v>
+        <v>0.14358811203002814</v>
       </c>
       <c r="H120" s="105">
         <f t="shared" si="48"/>
-        <v>0.19258792921867343</v>
+        <v>0.1587292696196354</v>
       </c>
       <c r="I120" s="105">
         <f t="shared" si="48"/>
-        <v>0.12308842930672464</v>
+        <v>0.19258792921867343</v>
       </c>
       <c r="J120" s="105">
         <f t="shared" si="48"/>
+        <v>0.12308842930672464</v>
+      </c>
+      <c r="K120" s="105">
+        <f t="shared" si="48"/>
         <v>0.12088576432889671</v>
-      </c>
-      <c r="K120" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
       </c>
       <c r="L120" s="105" t="str">
         <f t="shared" si="48"/>
@@ -13780,30 +13826,30 @@
       </c>
       <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76687147787947652</v>
+        <v>0.76398301819508896</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="305"/>
       <c r="F124" s="27"/>
       <c r="G124" s="181">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.7751121325138595</v>
+        <v>2.4241962462165407</v>
       </c>
       <c r="H124" s="181">
         <f t="shared" si="49"/>
-        <v>0.97989727852910624</v>
+        <v>1.7783377505569293</v>
       </c>
       <c r="I124" s="181">
         <f t="shared" si="49"/>
-        <v>0.7390660122360998</v>
+        <v>0.98187395266993727</v>
       </c>
       <c r="J124" s="181">
         <f t="shared" si="49"/>
-        <v>0.59010155571059042</v>
-      </c>
-      <c r="K124" s="181" t="str">
+        <v>0.73875480345109634</v>
+      </c>
+      <c r="K124" s="181">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0.59003964653850882</v>
       </c>
       <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13837,30 +13883,30 @@
       </c>
       <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.14227671203700865</v>
+        <v>0.14200427847492361</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="305"/>
       <c r="F125" s="27"/>
       <c r="G125" s="79">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.32933434740516876</v>
+        <v>0.45059409780976595</v>
       </c>
       <c r="H125" s="79">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.18179912403137408</v>
+        <v>0.3305460502893921</v>
       </c>
       <c r="I125" s="79">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.13711799855957327</v>
+        <v>0.18250445216913333</v>
       </c>
       <c r="J125" s="79">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10948080810957152</v>
-      </c>
-      <c r="K125" s="79" t="str">
+        <v>0.13731501922882833</v>
+      </c>
+      <c r="K125" s="79">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v/>
+        <v>0.10967279675436967</v>
       </c>
       <c r="L125" s="79" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13894,23 +13940,23 @@
       <c r="C126" s="173"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18276137259990091</v>
+        <v>0.18661094416227059</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16558114872392748</v>
+        <v>0.18337528606662279</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13420808117982194</v>
+        <v>0.1658889203758307</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1307858227537371</v>
-      </c>
-      <c r="K126" s="23" t="str">
+        <v>0.13445753857978443</v>
+      </c>
+      <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
+        <v>0.13102891907855815</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14680,7 +14726,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>131974.01491799403</v>
+        <v>131923.21948735364</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14712,7 +14758,7 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1649675.1864749254</v>
+        <v>1649040.2435919205</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14730,7 +14776,7 @@
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
-        <v>245714</v>
+        <v>279749</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -14746,7 +14792,7 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>46208.672776167194</v>
+        <v>126.15719684722717</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14762,7 +14808,7 @@
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
-        <v>6352.8</v>
+        <v>2113.7999999999997</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -14778,7 +14824,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>1456522.6592510927</v>
+        <v>1371531.2007887678</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14792,7 +14838,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1.06349396</v>
+        <v>1.0598962000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14806,7 +14852,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14839,7 +14885,7 @@
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="H16" s="124"/>
     </row>
@@ -14859,7 +14905,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>8.2002399621897837</v>
+        <v>7.8632974746718158</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14894,11 +14940,11 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>130771.17465192598</v>
+        <v>131564.60117420033</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14906,7 +14952,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>121084.42097400552</v>
+        <v>121819.07516129658</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14916,11 +14962,11 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>129579.29733721295</v>
+        <v>131206.95772426695</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
@@ -14928,7 +14974,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>111093.36191462015</v>
+        <v>112488.81835070897</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14938,11 +14984,11 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>128398.28305509948</v>
+        <v>130850.28648749834</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
@@ -14950,7 +14996,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>101926.69678077169</v>
+        <v>103873.17616050201</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14960,11 +15006,11 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>127228.03279751168</v>
+        <v>130494.58482104326</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
@@ -14972,7 +15018,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>93516.402218737334</v>
+        <v>95917.415471745713</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14982,11 +15028,11 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>126068.44845875706</v>
+        <v>130139.85008923475</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
@@ -14994,7 +15040,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>85800.067697145802</v>
+        <v>88570.995235224735</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -15004,11 +15050,11 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>124919.43282730001</v>
+        <v>129786.07966357062</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
@@ -15016,7 +15062,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>78720.432375228687</v>
+        <v>81787.245396213184</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -15026,11 +15072,11 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>123780.88957761235</v>
+        <v>129433.27092269396</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
@@ -15038,7 +15084,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>72224.960185539574</v>
+        <v>75523.070410753557</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -15048,11 +15094,11 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>122652.72326209795</v>
+        <v>129081.42125237374</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
@@ -15060,7 +15106,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>66265.449977943194</v>
+        <v>69738.67546994958</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -15070,11 +15116,11 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>121534.83930309111</v>
+        <v>128730.52804548536</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
@@ -15082,7 +15128,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>60797.677831859182</v>
+        <v>64397.313693041375</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -15092,11 +15138,11 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>120427.14398492787</v>
+        <v>128380.58870199148</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
@@ -15104,7 +15150,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>55781.068882455242</v>
+        <v>59465.052683240639</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15554,7 +15600,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1634639.6831490747</v>
+        <v>1644557.5146775041</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15566,7 +15612,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>757154.45659946289</v>
+        <v>761748.33157935238</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15577,7 +15623,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>1604364.9954377692</v>
+        <v>1635329.1696120286</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15598,7 +15644,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>1604364.9954377692</v>
+        <v>1635329.1696120286</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -15606,11 +15652,11 @@
       </c>
       <c r="C55" s="135">
         <f>C77</f>
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="D55" s="135">
         <f>C76</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E55" s="135">
         <f>C75</f>
@@ -15628,19 +15674,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1294776.1537527773</v>
+        <v>1294277.8078295011</v>
       </c>
       <c r="C56" s="127">
-        <v>1405150.1823979535</v>
+        <v>1498313.7984313916</v>
       </c>
       <c r="D56" s="127">
-        <v>1649675.1864749249</v>
+        <v>1675448.6761986823</v>
       </c>
       <c r="E56" s="127">
-        <v>1702902.3435977912</v>
+        <v>1702246.9141336246</v>
       </c>
       <c r="F56" s="127">
-        <v>1814209.0038086427</v>
+        <v>1813510.7335644783</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15649,19 +15695,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>1092754.475188269</v>
+        <v>1092333.8853154378</v>
       </c>
       <c r="C57" s="127">
-        <v>1241004.2970088164</v>
+        <v>1382780.7925548274</v>
       </c>
       <c r="D57" s="127">
-        <v>1649675.1864749247</v>
+        <v>1701012.2101715999</v>
       </c>
       <c r="E57" s="127">
-        <v>1756178.5145211511</v>
+        <v>1755502.5796109191</v>
       </c>
       <c r="F57" s="127">
-        <v>2002486.2278830931</v>
+        <v>2001715.4916865779</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15670,19 +15716,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>916338.55028411746</v>
+        <v>915985.86107251025</v>
       </c>
       <c r="C58" s="127">
-        <v>1085082.6728393636</v>
+        <v>1264047.6678058072</v>
       </c>
       <c r="D58" s="127">
-        <v>1649675.1864749244</v>
+        <v>1731867.6066014508</v>
       </c>
       <c r="E58" s="127">
-        <v>1822122.5481367675</v>
+        <v>1821421.2320514028</v>
       </c>
       <c r="F58" s="127">
-        <v>2261468.8135479582</v>
+        <v>2260598.3976381649</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15691,19 +15737,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>784518.82138253155</v>
+        <v>784216.86821847595</v>
       </c>
       <c r="C59" s="127">
-        <v>961199.35704169539</v>
+        <v>1163208.9906452729</v>
       </c>
       <c r="D59" s="127">
-        <v>1649675.1864749244</v>
+        <v>1762493.2637714255</v>
       </c>
       <c r="E59" s="127">
-        <v>1889308.9431083992</v>
+        <v>1888581.7676758901</v>
       </c>
       <c r="F59" s="127">
-        <v>2556897.5486858366</v>
+        <v>2555913.4253175403</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15712,19 +15758,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>691255.07052868966</v>
+        <v>690989.0136158067</v>
       </c>
       <c r="C60" s="127">
-        <v>869746.82624299312</v>
+        <v>1084574.7886656087</v>
       </c>
       <c r="D60" s="127">
-        <v>1649675.1864749242</v>
+        <v>1790222.0419873991</v>
       </c>
       <c r="E60" s="127">
-        <v>1951796.0186057189</v>
+        <v>1951044.7925454304</v>
       </c>
       <c r="F60" s="127">
-        <v>2866497.8806298133</v>
+        <v>2865394.5953022684</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15733,19 +15779,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>626709.46912966296</v>
+        <v>626468.25514984562</v>
       </c>
       <c r="C61" s="127">
-        <v>804636.51422046276</v>
+        <v>1026060.3009149519</v>
       </c>
       <c r="D61" s="127">
-        <v>1649675.1864749244</v>
+        <v>1814018.9580837078</v>
       </c>
       <c r="E61" s="127">
-        <v>2006918.3116576658</v>
+        <v>2006145.8695980366</v>
       </c>
       <c r="F61" s="127">
-        <v>3176058.8684317451</v>
+        <v>3174836.4362881044</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15773,11 +15819,11 @@
       </c>
       <c r="C64" s="136">
         <f>C55</f>
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="D64" s="136">
         <f>D55</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E64" s="136">
         <f>E55</f>
@@ -15795,23 +15841,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15822,23 +15868,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.4012884587026022</v>
+        <v>5.8882285690866398</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>7.0426472483039735</v>
+        <v>7.0698252017810068</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>8.4635273463407916</v>
+        <v>8.0956342979367122</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>8.7728184493772456</v>
+        <v>8.2508260737242178</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>9.4195965523755056</v>
+        <v>8.8951680547266267</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15849,23 +15895,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>5.2273856771533396</v>
+        <v>4.7187473509358115</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>6.0888322280181892</v>
+        <v>6.4007598554854699</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>8.4635273463407916</v>
+        <v>8.2436757565689014</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>9.0823943606438959</v>
+        <v>8.5592359518748324</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>10.513633383540615</v>
+        <v>9.9850841415803284</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15876,23 +15922,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>4.2022722020742727</v>
+        <v>3.6974950169085359</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>5.1828065498989311</v>
+        <v>5.7131622410701688</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>8.4635273463407898</v>
+        <v>8.4223630186269887</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>9.4655803881930698</v>
+        <v>8.9409786901322299</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>12.01852325399938</v>
+        <v>11.484305769255723</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15903,23 +15949,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>3.4362972457221024</v>
+        <v>2.9344051434476883</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>4.4629483147046747</v>
+        <v>5.1291934960131984</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>8.4635273463407898</v>
+        <v>8.59971983337004</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>9.8559854996637242</v>
+        <v>9.3299133212713148</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>13.735193545980923</v>
+        <v>13.194510136929477</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15930,23 +15976,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>2.8943624527682705</v>
+        <v>2.3945115749312844</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>3.9315381163182881</v>
+        <v>4.673813501534327</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>8.4635273463407881</v>
+        <v>8.7603004783438578</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>10.219083916914821</v>
+        <v>9.6916441102170836</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>15.534211816792675</v>
+        <v>14.986752315662427</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15956,23 +16002,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>2.5193024019980603</v>
+        <v>2.0208642065558742</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>3.5531966584416144</v>
+        <v>4.3349491595814555</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>8.4635273463407898</v>
+        <v>8.8981112432239247</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>10.539387230890066</v>
+        <v>10.010740985778748</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>17.333001467596354</v>
+        <v>16.778766735495974</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16007,7 +16053,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.513633383540615</v>
+        <v>9.9850841415803284</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -16029,7 +16075,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.7728184493772456</v>
+        <v>8.2508260737242178</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16044,7 +16090,7 @@
       </c>
       <c r="C76" s="146">
         <f>Scenarios!C26</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D76" s="149">
         <f>Scenarios!C25</f>
@@ -16052,7 +16098,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.4635273463407916</v>
+        <v>8.0956342979367122</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16067,7 +16113,7 @@
       </c>
       <c r="C77" s="146">
         <f>Scenarios!C32</f>
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="D77" s="149">
         <f>Scenarios!C31</f>
@@ -16075,7 +16121,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.0426472483039735</v>
+        <v>7.0698252017810068</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16098,7 +16144,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>5.2273856771533396</v>
+        <v>4.7187473509358115</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -16199,7 +16245,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-5.39</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16248,7 +16294,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>8.646079056045334</v>
+        <v>8.3064908355065601</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16257,7 +16303,7 @@
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
-        <v>266372</v>
+        <v>245516</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -16282,7 +16328,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>305486.2278947797</v>
+        <v>418605.86669267842</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16304,7 +16350,7 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>131974.01491799403</v>
+        <v>131923.21948735364</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16351,7 +16397,7 @@
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.20294093668232471</v>
+        <v>0.16638727228030792</v>
       </c>
       <c r="D12" s="162"/>
       <c r="E12" s="351"/>
@@ -16370,7 +16416,7 @@
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.21158962892889099</v>
+        <v>0.15587431850223021</v>
       </c>
       <c r="E13" s="351"/>
       <c r="F13" s="351"/>
@@ -16388,7 +16434,7 @@
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.44355392169299579</v>
+        <v>0.48601257847513946</v>
       </c>
       <c r="E14" s="351"/>
       <c r="F14" s="351"/>
@@ -16439,7 +16485,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16454,7 +16500,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>8.463527346340797</v>
+        <v>7.9426999310593978</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16489,7 +16535,7 @@
         <v>136</v>
       </c>
       <c r="C26" s="168">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D26" s="168"/>
       <c r="E26" s="350"/>
@@ -16501,7 +16547,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>8.4635273463407916</v>
+        <v>8.0956342979367122</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -16547,7 +16593,7 @@
         <v>136</v>
       </c>
       <c r="C32" s="168">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="D32" s="168"/>
       <c r="E32" s="350"/>
@@ -16559,7 +16605,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>7.0426472483039735</v>
+        <v>7.0698252017810068</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16617,7 +16663,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>8.7728184493772456</v>
+        <v>8.2508260737242178</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16644,7 +16690,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.2412095473407199</v>
+        <v>7.9215108338630715</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16718,7 +16764,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>5.2273856771533396</v>
+        <v>4.7187473509358115</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16776,7 +16822,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>10.513633383540615</v>
+        <v>9.9850841415803284</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16802,7 +16848,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>8.2041395456413451</v>
+        <v>7.8645513251025703</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16850,7 +16896,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="155">
-        <v>-9.1142204532876307E-3</v>
+        <v>-2.7183866081108938E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
@@ -16863,7 +16909,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>8.2002399621897837</v>
+        <v>7.8632974746718158</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16926,7 +16972,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>-0.13680485575710941</v>
+        <v>-0.20434577001864199</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16977,7 +17023,7 @@
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
@@ -16986,7 +17032,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.93093739460099634</v>
+        <v>0.86266592430858746</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16998,7 +17044,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>4.7477659407646673</v>
+        <v>4.0266502784525162</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -17008,7 +17054,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>5.6787033353656637</v>
+        <v>4.8893162027611039</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17019,7 +17065,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.30782462880185679</v>
+        <v>0.37830958173607732</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17036,7 +17082,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17049,7 +17095,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22246108266706432</v>
+        <v>0.20806555381768388</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529A5DF0-840C-4074-B43E-7977FEC7C02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D259742-C0A4-4759-B181-BB5A71F4D0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1557,10 +1557,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2335,6 +2331,10 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="284" t="s">
         <v>291</v>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>413</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.39</v>
+        <v>5.59</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>986483.07043901994</v>
+        <v>1023087.26600262</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="336" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4151,7 +4151,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0562040500000001</v>
+        <v>1.0614312000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4187,7 +4187,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>4.8752893604858043</v>
+        <v>4.8951478192697992</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4218,11 +4218,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20602353093461256</v>
+        <v>0.19222357225122977</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>377</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="336" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="B26" s="338" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,17 +4352,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,8 +4444,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
-        <v>352</v>
+      <c r="B50" s="337" t="s">
+        <v>351</v>
       </c>
       <c r="C50" s="340"/>
       <c r="D50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>357</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="336" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="336" t="s">
+        <v>377</v>
+      </c>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,11 +4511,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.14124706534453912</v>
+        <v>0.13686752422932275</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>8.1992488015582371E-2</v>
+        <v>7.9058946405006977E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="336" t="s">
+        <v>378</v>
+      </c>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4610,27 +4610,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
+        <v>379</v>
+      </c>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
-        <v>381</v>
-      </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.5165210275883219</v>
+        <v>9.5636182555239273</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
-        <v>382</v>
-      </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="B81" s="336" t="s">
+        <v>381</v>
+      </c>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
-        <v>358</v>
-      </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="B85" s="336" t="s">
+        <v>357</v>
+      </c>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.614416174069804</v>
+        <v>1.6224059138405322</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>7.2804628100715861E-4</v>
+        <v>7.316493794025555E-4</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2198624155041667E-2</v>
+        <v>1.2258995101595059E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
-        <v>383</v>
-      </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="B98" s="336" t="s">
+        <v>382</v>
+      </c>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="B104" s="337" t="s">
+        <v>383</v>
+      </c>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>9.95 HKD</v>
+        <v>10 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.22 HKD</v>
+        <v>8.26 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.07 HKD</v>
+        <v>8.11 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.05 HKD</v>
+        <v>7.08 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.7 HKD</v>
+        <v>4.73 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>7.8371551487836282</v>
+        <v>7.8759412010961185</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,17 +4977,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>387</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="341" t="s">
+        <v>386</v>
+      </c>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
-        <v>386</v>
-      </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>4.0126234361772175</v>
+        <v>4.0324818949612125</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>4.8752893604858043</v>
+        <v>4.8951478192697992</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,12 +5093,12 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.37792613927740382</v>
+        <v>0.37846821169912659</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5107,22 +5107,22 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
-        <v>393</v>
-      </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="B134" s="343" t="s">
+        <v>392</v>
+      </c>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C137" s="340"/>
       <c r="D137" s="340"/>
@@ -5131,78 +5131,89 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
-        <v>398</v>
-      </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="B143" s="337" t="s">
+        <v>397</v>
+      </c>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
+        <v>398</v>
+      </c>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
-        <v>400</v>
-      </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5219,17 +5230,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5753,7 +5753,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C22" s="181">
         <v>406532</v>
@@ -5779,7 +5779,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23" s="181">
         <v>-307347</v>
@@ -5805,7 +5805,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24" s="181">
         <v>-178876</v>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16553619539709205</v>
+        <v>0.16472099180804178</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -5862,7 +5862,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7117,7 +7117,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16553619539709205</v>
+        <v>0.16472099180804178</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8523,11 +8523,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.7451231357979218</v>
+        <v>8.7884027183741171</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7476994819440526</v>
+        <v>-3.7662468330425871</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8781,7 +8781,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8792,12 +8792,12 @@
         <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8808,12 +8808,12 @@
         <v>1.0005837372228803</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8821,12 +8821,12 @@
         <v>216119.84280315277</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8834,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8933,11 +8933,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-295472.02678345004</v>
+        <v>-296934.31676880002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.614416174069804</v>
+        <v>-1.6224059138405322</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8950,11 +8950,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>133.24774224668857</v>
+        <v>133.90718483818856</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>7.2804628100715861E-4</v>
+        <v>7.3164937940255539E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8967,11 +8967,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2232.6041208899996</v>
+        <v>2243.6532705599998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.2198624155041667E-2</v>
+        <v>1.2258995101595059E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8984,11 +8984,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-293106.17492031335</v>
+        <v>-294556.7563134018</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6014895036337553</v>
+        <v>-1.6094152693595347</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10388,7 +10388,7 @@
         <v>-314015.75</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10893,7 +10893,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10948,7 +10948,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11081,7 +11081,7 @@
         <v>4.0689769984184679E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11108,7 +11108,7 @@
         <v>7.4105716195589616E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11423,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16553619539709205</v>
+        <v>0.16472099180804178</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>30296.596345847298</v>
+        <v>30147.396987858574</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29735490740855597</v>
+        <v>0.29589054617227362</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12667,28 +12667,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.1992488015582371E-2</v>
+        <v>7.9058946405006977E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.1992488015582371E-2</v>
+        <v>7.9058946405006977E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6758924950758076E-2</v>
+        <v>7.4012630677027916E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.37199693311167E-2</v>
+        <v>7.1082403344314662E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.9534335391683675E-2</v>
+        <v>3.811986900915474E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>3.0711724563467914E-2</v>
+        <v>2.9467082613245401E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13357,7 +13357,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13409,7 +13409,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13809,30 +13809,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76132168220706586</v>
+        <v>0.76508946044191417</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4157515549623705</v>
+        <v>2.4277071006171345</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7721429083396265</v>
+        <v>1.7809132371442999</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.97845359328535764</v>
+        <v>0.98329595655800528</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.73618134998691565</v>
+        <v>0.73982470880909035</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58798424254614878</v>
+        <v>0.59089417442287773</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13866,30 +13866,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.14124706534453912</v>
+        <v>0.13686752422932275</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.44819138310990181</v>
+        <v>0.43429465127319045</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.32878347093499566</v>
+        <v>0.3185891300794812</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18153127890266377</v>
+        <v>0.17590267559177197</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.13658281075824039</v>
+        <v>0.13234789066352243</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10908798563008326</v>
+        <v>0.10570557681983501</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13918,28 +13918,28 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18626472719722001</v>
+        <v>0.17960051513291872</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18303507217781645</v>
+        <v>0.1764864112770001</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16558114872392748</v>
+        <v>0.15965695735634511</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13420808117982194</v>
+        <v>0.129406360922941</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1307858227537371</v>
+        <v>0.1261065446587912</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0562040500000001</v>
+        <v>1.0614312000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>7.8359056661427262</v>
+        <v>7.8800036473076291</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14923,11 +14923,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>131564.60117420033</v>
+        <v>131277.11532304226</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>121819.07516129658</v>
+        <v>121552.88455837245</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14945,11 +14945,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>131206.95772426695</v>
+        <v>130634.17550381558</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>112488.81835070897</v>
+        <v>111997.74991753735</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14967,11 +14967,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>130850.28648749834</v>
+        <v>129994.38453204895</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>103873.17616050201</v>
+        <v>103193.73359311408</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14989,11 +14989,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>130494.58482104326</v>
+        <v>129357.72698601855</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>95917.415471745713</v>
+        <v>95081.791024617007</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15011,11 +15011,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>130139.85008923475</v>
+        <v>128724.18751952963</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>88570.995235224735</v>
+        <v>87607.519077613804</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15033,19 +15033,19 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>129786.07966357062</v>
+        <v>0</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>81787.245396213184</v>
+        <v>0</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15055,19 +15055,19 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>129433.27092269396</v>
+        <v>0</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>0</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>75523.070410753557</v>
+        <v>0</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15077,19 +15077,19 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>129081.42125237374</v>
+        <v>0</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>0</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>69738.67546994958</v>
+        <v>0</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15099,19 +15099,19 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>128730.52804548536</v>
+        <v>0</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>64397.313693041375</v>
+        <v>0</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15121,19 +15121,19 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>128380.58870199148</v>
+        <v>0</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>-2.7183866081108899E-3</v>
+        <v>0</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>59465.052683240639</v>
+        <v>0</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1644557.5146775041</v>
+        <v>1640963.9415380282</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15591,11 +15591,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.68058319703375303</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>761748.33157935238</v>
+        <v>1116812.4855490599</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1635329.1696120286</v>
+        <v>1636246.1637203146</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15627,7 +15627,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1635329.1696120286</v>
+        <v>1636246.1637203146</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15824,23 +15824,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15851,23 +15851,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.8677169160480185</v>
+        <v>5.896756225713343</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.0451974551028362</v>
+        <v>7.0800641116711773</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.0674331437358315</v>
+        <v>8.1073588410073754</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2220843087399675</v>
+        <v>8.2627753740643524</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.8641817234865865</v>
+        <v>8.9080505265800074</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15878,23 +15878,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7023095874720333</v>
+        <v>4.7255813005090692</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.3784627989431115</v>
+        <v>6.4100297881243176</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2149588997251684</v>
+        <v>8.2556147014262695</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.5294198406181696</v>
+        <v>8.5716319083714474</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>9.9503010860194756</v>
+        <v>9.9995450898857623</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15905,23 +15905,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.6846147874797683</v>
+        <v>3.70284993265496</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.6932604318473716</v>
+        <v>5.7214363570072226</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.3930237044382761</v>
+        <v>8.4345607482099361</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>8.9098327774751489</v>
+        <v>8.953927507468638</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.44430017290963</v>
+        <v>11.500937972820381</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15932,23 +15932,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9241831387359247</v>
+        <v>2.9386549104486388</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1113259427883593</v>
+        <v>5.1366218762794746</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.5697626964515585</v>
+        <v>8.6121744208515523</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.2974125542441932</v>
+        <v>9.3434254151425371</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.148547041107392</v>
+        <v>13.213619152567224</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15959,23 +15959,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.3861702902739919</v>
+        <v>2.3979794383574573</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.6575322652022315</v>
+        <v>4.6805823754342955</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.7297839585081256</v>
+        <v>8.772987627551732</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.6578832534449415</v>
+        <v>9.7056800825219032</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>14.934545941526665</v>
+        <v>15.008456955045549</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15985,23 +15985,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0138245230658915</v>
+        <v>2.0237909333023834</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3198483576920355</v>
+        <v>4.3412272714946383</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.8671146593823469</v>
+        <v>8.9109979775648434</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>9.975868554562707</v>
+        <v>10.025239091737776</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.720317876445002</v>
+        <v>16.803066668771503</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>9.9503010860194756</v>
+        <v>9.9995450898857623</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.2220843087399675</v>
+        <v>8.2627753740643524</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.0674331437358315</v>
+        <v>8.1073588410073754</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.0451974551028362</v>
+        <v>7.0800641116711773</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7023095874720333</v>
+        <v>4.7255813005090692</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-5.39</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.2790946591876171</v>
+        <v>8.3178807115001074</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16436,7 +16436,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16447,7 +16447,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.39</v>
+        <v>5.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9150315239545694</v>
+        <v>7.9542029861643941</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.0674331437358315</v>
+        <v>8.1073588410073754</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.0451974551028362</v>
+        <v>7.0800641116711773</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.2220843087399675</v>
+        <v>8.2627753740643524</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.8939162390100597</v>
+        <v>7.9329832017515312</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7023095874720333</v>
+        <v>4.7255813005090692</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16769,7 +16769,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>9.9503010860194756</v>
+        <v>9.9995450898857623</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.8371551487836282</v>
+        <v>7.8759412010961185</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16847,7 +16847,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16867,11 +16867,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
-        <v>10</v>
+        <f>C18</f>
+        <v>5</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16879,11 +16880,11 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>-2.7183866081108899E-3</v>
+        <v>-4.8975772939903158E-3</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16892,22 +16893,22 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.8359056661427262</v>
+        <v>7.8800036473076291</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16951,11 +16952,11 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864199</v>
+        <v>-0.20434577001864204</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17027,7 +17028,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.0126234361772175</v>
+        <v>4.0324818949612125</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17037,7 +17038,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.8752893604858043</v>
+        <v>4.8951478192697992</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17048,7 +17049,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.37792613927740382</v>
+        <v>0.37846821169912659</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17065,7 +17066,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>5.39</v>
+        <v>5.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17078,7 +17079,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20602353093461256</v>
+        <v>0.19222357225122977</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -17086,7 +17087,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -17094,30 +17095,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D259742-C0A4-4759-B181-BB5A71F4D0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACF13C2-9EA0-4790-8C12-7CCBD723F327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2318,6 +2318,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>中国石油股份</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,10 +2335,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4068,10 +4068,10 @@
         <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.59</v>
+        <v>5.65</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1023087.26600262</v>
+        <v>1034068.5246717001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0614312000000001</v>
+        <v>1.0624809</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4187,7 +4187,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>4.8951478192697992</v>
+        <v>4.8991357331780589</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19222357225122977</v>
+        <v>0.18805346196285577</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.13686752422932275</v>
+        <v>0.13554798122911768</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.9058946405006977E-2</v>
+        <v>7.821938237238743E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.5636182555239273</v>
+        <v>9.5730761743064363</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6224059138405322</v>
+        <v>1.6240103885231663</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>7.316493794025555E-4</v>
+        <v>7.3237294241215863E-4</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2258995101595059E-2</v>
+        <v>1.2271118607252461E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10 HKD</v>
+        <v>10.01 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.26 HKD</v>
+        <v>8.27 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.11 HKD</v>
+        <v>8.12 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.08 HKD</v>
+        <v>7.09 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>7.8759412010961185</v>
+        <v>7.8837300954481879</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>4.0324818949612125</v>
+        <v>4.0364698088694722</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>4.8951478192697992</v>
+        <v>4.8991357331780589</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.37846821169912659</v>
+        <v>0.37857642589684004</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16472099180804178</v>
+        <v>0.16455825229422949</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -5862,7 +5862,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16472099180804178</v>
+        <v>0.16455825229422949</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8523,11 +8523,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.7884027183741171</v>
+        <v>8.7970939894932219</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7662468330425871</v>
+        <v>-3.7699714543846432</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8933,11 +8933,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-296934.31676880002</v>
+        <v>-297227.96929410001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.6224059138405322</v>
+        <v>-1.6240103885231667</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8950,11 +8950,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>133.90718483818856</v>
+        <v>134.03961204771909</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>7.3164937940255539E-4</v>
+        <v>7.3237294241215874E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8967,11 +8967,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2243.6532705599998</v>
+        <v>2245.8721264199994</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.2258995101595059E-2</v>
+        <v>1.2271118607252461E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8984,11 +8984,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-294556.7563134018</v>
+        <v>-294848.05755563232</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6094152693595347</v>
+        <v>-1.6110068969735021</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -10901,11 +10901,11 @@
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>8793.8666926784372</v>
       </c>
       <c r="H48" s="328">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>8260.1782265015663</v>
       </c>
       <c r="I48" s="328">
@@ -11200,7 +11200,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11310,7 +11310,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16472099180804178</v>
+        <v>0.16455825229422949</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>30147.396987858574</v>
+        <v>30117.612242911022</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29589054617227362</v>
+        <v>0.29559821498183342</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12667,28 +12667,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.9058946405006977E-2</v>
+        <v>7.821938237238743E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.9058946405006977E-2</v>
+        <v>7.821938237238743E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4012630677027916E-2</v>
+        <v>7.3226655837979826E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1082403344314662E-2</v>
+        <v>7.0327545963667068E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.811986900915474E-2</v>
+        <v>3.771505624091593E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9467082613245401E-2</v>
+        <v>2.9125354388359202E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13809,30 +13809,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76508946044191417</v>
+        <v>0.76584609394451497</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4277071006171345</v>
+        <v>2.4301079760987649</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7809132371442999</v>
+        <v>1.782674467288119</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98329595655800528</v>
+        <v>0.98426838488458801</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.73982470880909035</v>
+        <v>0.74055635679233855</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59089417442287773</v>
+        <v>0.59147853788882021</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13866,30 +13866,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13686752422932275</v>
+        <v>0.13554798122911768</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.43429465127319045</v>
+        <v>0.4301076063891619</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.3185891300794812</v>
+        <v>0.31551760482975555</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.17590267559177197</v>
+        <v>0.17420679378488282</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.13234789066352243</v>
+        <v>0.13107192155616612</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10570557681983501</v>
+        <v>0.10468646688297702</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13923,23 +13923,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17960051513291872</v>
+        <v>0.1776932530253125</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1764864112770001</v>
+        <v>0.17461221929883725</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15965695735634511</v>
+        <v>0.15796148524282638</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.129406360922941</v>
+        <v>0.12803213408128145</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1261065446587912</v>
+        <v>0.12476736011374209</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0614312000000001</v>
+        <v>1.0624809</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>7.8800036473076291</v>
+        <v>7.8877965592067492</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15824,23 +15824,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15851,23 +15851,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.896756225713343</v>
+        <v>5.9025878095316164</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.0800641116711773</v>
+        <v>7.0870659251641479</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.1073588410073754</v>
+        <v>8.1153765953143946</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2627753740643524</v>
+        <v>8.2709468272024882</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9080505265800074</v>
+        <v>8.9168601231301654</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15878,23 +15878,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7255813005090692</v>
+        <v>4.7302546535169165</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4100297881243176</v>
+        <v>6.4163689726787121</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2556147014262695</v>
+        <v>8.2637790730332892</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.5716319083714474</v>
+        <v>8.5801088044851248</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>9.9995450898857623</v>
+        <v>10.009434117531503</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15905,23 +15905,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.70284993265496</v>
+        <v>3.7065118577748426</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7214363570072226</v>
+        <v>5.7270945586353159</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4345607482099361</v>
+        <v>8.4429020881077967</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>8.953927507468638</v>
+        <v>8.9627824739559507</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.500937972820381</v>
+        <v>11.512311799583781</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15932,23 +15932,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9386549104486388</v>
+        <v>2.9415610866186035</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1366218762794746</v>
+        <v>5.1417017269410428</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6121744208515523</v>
+        <v>8.6206914113918405</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.3434254151425371</v>
+        <v>9.3526655747103682</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.213619152567224</v>
+        <v>13.22668673153461</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15959,23 +15959,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.3979794383574573</v>
+        <v>2.4003509147342998</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.6805823754342955</v>
+        <v>4.6852112268563113</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.772987627551732</v>
+        <v>8.7816636539514068</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.7056800825219032</v>
+        <v>9.7152784930289826</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.008456955045549</v>
+        <v>15.023299534824352</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15985,23 +15985,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0237909333023834</v>
+        <v>2.0257923567980249</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3412272714946383</v>
+        <v>4.3455205184492103</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.9109979775648434</v>
+        <v>8.9198104889900289</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.025239091737776</v>
+        <v>10.035153529408907</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.803066668771503</v>
+        <v>16.819684023793862</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>9.9995450898857623</v>
+        <v>10.009434117531503</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.2627753740643524</v>
+        <v>8.2709468272024882</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.1073588410073754</v>
+        <v>8.1153765953143946</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.0800641116711773</v>
+        <v>7.0870659251641479</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7255813005090692</v>
+        <v>4.7302546535169165</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-5.59</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.3178807115001074</v>
+        <v>8.3256696058521769</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.59</v>
+        <v>5.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9542029861643941</v>
+        <v>7.9620692773329367</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.1073588410073754</v>
+        <v>8.1153765953143946</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.0800641116711773</v>
+        <v>7.0870659251641479</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.2627753740643524</v>
+        <v>8.2709468272024882</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9329832017515312</v>
+        <v>7.9408285076619647</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7255813005090692</v>
+        <v>4.7302546535169165</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>9.9995450898857623</v>
+        <v>10.009434117531503</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.8759412010961185</v>
+        <v>7.8837300954481879</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16880,7 +16880,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>-4.8975772939903158E-3</v>
+        <v>-4.8975772939903201E-3</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.8800036473076291</v>
+        <v>7.8877965592067492</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864204</v>
+        <v>-0.20434577001864201</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.0324818949612125</v>
+        <v>4.0364698088694722</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.8951478192697992</v>
+        <v>4.8991357331780589</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.37846821169912659</v>
+        <v>0.37857642589684004</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>5.59</v>
+        <v>5.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19222357225122977</v>
+        <v>0.18805346196285577</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACF13C2-9EA0-4790-8C12-7CCBD723F327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DD37B7-B487-4EC2-9312-AF2A0EA4FB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.65</v>
+        <v>5.82</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1034068.5246717001</v>
+        <v>1065182.0909007599</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0624809</v>
+        <v>1.0653656200000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>4.8991357331780589</v>
+        <v>4.9100950691878094</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18805346196285577</v>
+        <v>0.17654933116845006</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.13554798122911768</v>
+        <v>0.13194594963823414</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.821938237238743E-2</v>
+        <v>7.5934623780754121E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.5730761743064363</v>
+        <v>9.5990678361815327</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6240103885231663</v>
+        <v>1.6284197056675787</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>7.3237294241215863E-4</v>
+        <v>7.3436139309812892E-4</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2271118607252461E-2</v>
+        <v>1.230443566854619E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.01 HKD</v>
+        <v>10.04 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.27 HKD</v>
+        <v>8.29 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.12 HKD</v>
+        <v>8.14 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.09 HKD</v>
+        <v>7.11 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.73 HKD</v>
+        <v>4.74 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>7.8837300954481879</v>
+        <v>7.905135048592232</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>4.0364698088694722</v>
+        <v>4.0474291448792226</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>4.8991357331780589</v>
+        <v>4.9100950691878094</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.37857642589684004</v>
+        <v>0.3788727151394824</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,17 +5203,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5230,6 +5219,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16455825229422949</v>
+        <v>0.1641126733562136</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16455825229422949</v>
+        <v>0.1641126733562136</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8523,11 +8523,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.7970939894932219</v>
+        <v>8.8209787981268377</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7699714543846432</v>
+        <v>-3.7802072262031232</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8933,11 +8933,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-297227.96929410001</v>
+        <v>-298034.96682938002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.6240103885231667</v>
+        <v>-1.6284197056675787</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8950,11 +8950,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>134.03961204771909</v>
+        <v>134.40354023660822</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>7.3237294241215874E-4</v>
+        <v>7.3436139309812892E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8967,11 +8967,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2245.8721264199994</v>
+        <v>2251.9698475559999</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.2271118607252461E-2</v>
+        <v>1.2304435668546188E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8984,11 +8984,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-294848.05755563232</v>
+        <v>-295648.59344158741</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6110068969735021</v>
+        <v>-1.6153809086059343</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16455825229422949</v>
+        <v>0.1641126733562136</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>30117.612242911022</v>
+        <v>30036.061949980249</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29559821498183342</v>
+        <v>0.29479781550702921</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12667,28 +12667,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.821938237238743E-2</v>
+        <v>7.5934623780754121E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.821938237238743E-2</v>
+        <v>7.5934623780754121E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3226655837979826E-2</v>
+        <v>7.1087732901131614E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0327545963667068E-2</v>
+        <v>6.8273304930364084E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.771505624091593E-2</v>
+        <v>3.6613413704669244E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9125354388359202E-2</v>
+        <v>2.8198053841273812E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13809,30 +13809,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76584609394451497</v>
+        <v>0.76792542689452259</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4301079760987649</v>
+        <v>2.4367059121941921</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.782674467288119</v>
+        <v>1.7875145700036368</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98426838488458801</v>
+        <v>0.98694075169630613</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74055635679233855</v>
+        <v>0.74256702609807967</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59147853788882021</v>
+        <v>0.5930844490800885</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13866,30 +13866,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13554798122911768</v>
+        <v>0.13194594963823414</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.4301076063891619</v>
+        <v>0.41867799178594362</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.31551760482975555</v>
+        <v>0.30713308762949082</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.17420679378488282</v>
+        <v>0.16957744874506978</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.13107192155616612</v>
+        <v>0.12758883609932639</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10468646688297702</v>
+        <v>0.10190454451547912</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13923,23 +13923,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1776932530253125</v>
+        <v>0.17250290027371404</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17461221929883725</v>
+        <v>0.16951186237773722</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15796148524282638</v>
+        <v>0.1533474899694105</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12803213408128145</v>
+        <v>0.12429236384179386</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12476736011374209</v>
+        <v>0.12112295268773932</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0624809</v>
+        <v>1.0653656200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>7.8877965592067492</v>
+        <v>7.9092125531227566</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15824,23 +15824,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15851,23 +15851,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9025878095316164</v>
+        <v>5.9186138040750604</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.0870659251641479</v>
+        <v>7.1063078718340984</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.1153765953143946</v>
+        <v>8.1374104870973305</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2709468272024882</v>
+        <v>8.293403104516619</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9168601231301654</v>
+        <v>8.9410701063255313</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15878,23 +15878,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7302546535169165</v>
+        <v>4.7430976704634746</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4163689726787121</v>
+        <v>6.4337899238721565</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2637790730332892</v>
+        <v>8.2862158893257636</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.5801088044851248</v>
+        <v>8.6034044811137367</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.009434117531503</v>
+        <v>10.036610525867435</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15905,23 +15905,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7065118577748426</v>
+        <v>3.7165753317501027</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7270945586353159</v>
+        <v>5.742644075069153</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4429020881077967</v>
+        <v>8.4658252376078096</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>8.9627824739559507</v>
+        <v>8.9871171399798495</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.512311799583781</v>
+        <v>11.54356864014863</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15932,23 +15932,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9415610866186035</v>
+        <v>2.9495476585163112</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1417017269410428</v>
+        <v>5.1556618553591091</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6206914113918405</v>
+        <v>8.6440972730202912</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.3526655747103682</v>
+        <v>9.378058804307889</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.22668673153461</v>
+        <v>13.26259823615384</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15959,23 +15959,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4003509147342998</v>
+        <v>2.4068680580455375</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.6852112268563113</v>
+        <v>4.6979319473232275</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.7816636539514068</v>
+        <v>8.8055065679989237</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.7152784930289826</v>
+        <v>9.7416562454896738</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.023299534824352</v>
+        <v>15.06408898584799</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15985,23 +15985,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0257923567980249</v>
+        <v>2.0312925438860967</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3455205184492103</v>
+        <v>4.3573189516727924</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.9198104889900289</v>
+        <v>8.9440284826629508</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.035153529408907</v>
+        <v>10.062399767990097</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.819684023793862</v>
+        <v>16.865350801330401</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.009434117531503</v>
+        <v>10.036610525867435</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.2709468272024882</v>
+        <v>8.293403104516619</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.1153765953143946</v>
+        <v>8.1374104870973305</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.0870659251641479</v>
+        <v>7.1063078718340984</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7302546535169165</v>
+        <v>4.7430976704634746</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-5.65</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.3256696058521769</v>
+        <v>8.347074558996221</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.65</v>
+        <v>5.82</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9620692773329367</v>
+        <v>7.9836869275755991</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.1153765953143946</v>
+        <v>8.1374104870973305</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.0870659251641479</v>
+        <v>7.1063078718340984</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.2709468272024882</v>
+        <v>8.293403104516619</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9408285076619647</v>
+        <v>7.9623884875285409</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7302546535169165</v>
+        <v>4.7430976704634746</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.009434117531503</v>
+        <v>10.036610525867435</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.8837300954481879</v>
+        <v>7.905135048592232</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.8877965592067492</v>
+        <v>7.9092125531227566</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864201</v>
+        <v>-0.20434577001864196</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.0364698088694722</v>
+        <v>4.0474291448792226</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.8991357331780589</v>
+        <v>4.9100950691878094</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.37857642589684004</v>
+        <v>0.3788727151394824</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>5.65</v>
+        <v>5.82</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18805346196285577</v>
+        <v>0.17654933116845006</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DD37B7-B487-4EC2-9312-AF2A0EA4FB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BA8395-5C36-4165-9E9E-8E59A2A6D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1065182.0909007599</v>
+        <v>1061521.6713443999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0653656200000001</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>4.9100950691878094</v>
+        <v>4.91520725037517</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17654933116845006</v>
+        <v>0.1784289263913903</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.13194594963823414</v>
+        <v>0.13256816715305939</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.5934623780754121E-2</v>
+        <v>7.6196467311032592E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.5990678361815327</v>
+        <v>9.6111921185968043</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6284197056675787</v>
+        <v>1.6304765116761466</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>7.3436139309812892E-4</v>
+        <v>7.3528894200982991E-4</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.230443566854619E-2</v>
+        <v>1.2319977016472045E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.04 HKD</v>
+        <v>10.05 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.29 HKD</v>
+        <v>8.3 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.14 HKD</v>
+        <v>8.15 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.11 HKD</v>
+        <v>7.12 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.74 HKD</v>
+        <v>4.75 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>7.905135048592232</v>
+        <v>7.9151197774737954</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>4.0474291448792226</v>
+        <v>4.0525413260665832</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>4.9100950691878094</v>
+        <v>4.91520725037517</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.3788727151394824</v>
+        <v>0.37901037652472302</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,6 +5203,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5219,17 +5230,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.1641126733562136</v>
+        <v>0.16390564925606621</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.1641126733562136</v>
+        <v>0.16390564925606621</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8523,11 +8523,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.8209787981268377</v>
+        <v>8.8321203006094535</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7802072262031232</v>
+        <v>-3.7849818877411932</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8933,11 +8933,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-298034.96682938002</v>
+        <v>-298411.40547625005</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.6284197056675787</v>
+        <v>-1.6304765116761466</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8950,11 +8950,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>134.40354023660822</v>
+        <v>134.57330114540179</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>7.3436139309812892E-4</v>
+        <v>7.3528894200982991E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8967,11 +8967,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2251.9698475559999</v>
+        <v>2254.8142402500002</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.2304435668546188E-2</v>
+        <v>1.2319977016472047E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8984,11 +8984,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-295648.59344158741</v>
+        <v>-296022.01793485467</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6153809086059343</v>
+        <v>-1.6174212457176647</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.1641126733562136</v>
+        <v>0.16390564925606621</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>30036.061949980249</v>
+        <v>29998.172196739382</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29479781550702921</v>
+        <v>0.29442593531500844</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12667,28 +12667,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.5934623780754121E-2</v>
+        <v>7.6196467311032592E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.5934623780754121E-2</v>
+        <v>7.6196467311032592E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1087732901131614E-2</v>
+        <v>7.1332863014583803E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.8273304930364084E-2</v>
+        <v>6.8508730119779135E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.6613413704669244E-2</v>
+        <v>3.6739666855375004E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8198053841273812E-2</v>
+        <v>2.8259594699321763E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13809,30 +13809,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76792542689452259</v>
+        <v>0.7688953694877444</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4367059121941921</v>
+        <v>2.4397836392346295</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7875145700036368</v>
+        <v>1.7897723237603556</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98694075169630613</v>
+        <v>0.98818732569754453</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74256702609807967</v>
+        <v>0.74350493928822792</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.5930844490800885</v>
+        <v>0.5938335555016151</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13866,30 +13866,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13194594963823414</v>
+        <v>0.13256816715305939</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.41867799178594362</v>
+        <v>0.42065235159217751</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.30713308762949082</v>
+        <v>0.30858143513109582</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16957744874506978</v>
+        <v>0.17037712512026632</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12758883609932639</v>
+        <v>0.1281905067738324</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10190454451547912</v>
+        <v>0.10238509577614054</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13923,23 +13923,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17250290027371404</v>
+        <v>0.17309773786086477</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16951186237773722</v>
+        <v>0.17009638604110872</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1533474899694105</v>
+        <v>0.15387627441758087</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12429236384179386</v>
+        <v>0.124720958199869</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12112295268773932</v>
+        <v>0.12154061804183497</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0653656200000001</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>7.9092125531227566</v>
+        <v>7.9192024321727867</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15824,23 +15824,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15851,23 +15851,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9186138040750604</v>
+        <v>5.9260894200923842</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1063078718340984</v>
+        <v>7.1152836270885027</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.1374104870973305</v>
+        <v>8.1476885958218777</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.293403104516619</v>
+        <v>8.3038782426382447</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9410701063255313</v>
+        <v>8.9523632923842058</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15878,23 +15878,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7430976704634746</v>
+        <v>4.7490885288115283</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4337899238721565</v>
+        <v>6.4419162427365295</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2862158893257636</v>
+        <v>8.2966819495006305</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6034044811137367</v>
+        <v>8.6142711722802137</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.036610525867435</v>
+        <v>10.049287454771827</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15905,23 +15905,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7165753317501027</v>
+        <v>3.7212696218320964</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.742644075069153</v>
+        <v>5.7498974292244478</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4658252376078096</v>
+        <v>8.4765181567339987</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>8.9871171399798495</v>
+        <v>8.9984684866068143</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.54356864014863</v>
+        <v>11.558148960723686</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15932,23 +15932,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9495476585163112</v>
+        <v>2.9532731399296588</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1556618553591091</v>
+        <v>5.1621738106279746</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6440972730202912</v>
+        <v>8.6550153619797374</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.378058804307889</v>
+        <v>9.3899039371260855</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.26259823615384</v>
+        <v>13.279349809256525</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15959,23 +15959,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4068680580455375</v>
+        <v>2.409908097825447</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.6979319473232275</v>
+        <v>4.7038657582587424</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8055065679989237</v>
+        <v>8.816628527991492</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.7416562454896738</v>
+        <v>9.7539606268659167</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.06408898584799</v>
+        <v>15.083115965582916</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15985,23 +15985,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0312925438860967</v>
+        <v>2.0338582059785431</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3573189516727924</v>
+        <v>4.3628225449846729</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.9440284826629508</v>
+        <v>8.9553254053542677</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.062399767990097</v>
+        <v>10.075109270479771</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.865350801330401</v>
+        <v>16.886652898537925</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.036610525867435</v>
+        <v>10.049287454771827</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.293403104516619</v>
+        <v>8.3038782426382447</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.1374104870973305</v>
+        <v>8.1476885958218777</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1063078718340984</v>
+        <v>7.1152836270885027</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7430976704634746</v>
+        <v>4.7490885288115283</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-5.82</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.347074558996221</v>
+        <v>8.3570592878777852</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9836869275755991</v>
+        <v>7.9937708728791419</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.1374104870973305</v>
+        <v>8.1476885958218777</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1063078718340984</v>
+        <v>7.1152836270885027</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.293403104516619</v>
+        <v>8.3038782426382447</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9623884875285409</v>
+        <v>7.9724455314384759</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7430976704634746</v>
+        <v>4.7490885288115283</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.036610525867435</v>
+        <v>10.049287454771827</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.905135048592232</v>
+        <v>7.9151197774737954</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.9092125531227566</v>
+        <v>7.9192024321727867</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.0474291448792226</v>
+        <v>4.0525413260665832</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.9100950691878094</v>
+        <v>4.91520725037517</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.3788727151394824</v>
+        <v>0.37901037652472302</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17654933116845006</v>
+        <v>0.1784289263913903</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BA8395-5C36-4165-9E9E-8E59A2A6D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B40756-BD1D-43FA-AB3D-16607EDF02CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1825,14 +1821,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2319,6 +2307,45 @@
   </si>
   <si>
     <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3008,7 +3035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3701,29 +3728,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4013,7 +4043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4033,15 +4063,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4065,13 +4095,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4098,7 +4128,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4108,7 +4138,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4134,24 +4164,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4161,10 +4191,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4174,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4187,18 +4217,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4207,10 +4242,10 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>4.91520725037517</v>
+        <v>4.9152072503751691</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4218,11 +4253,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1784289263913903</v>
+        <v>0.17842892639139052</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4233,7 +4268,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4242,22 +4277,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="342" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4304,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4330,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4365,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,17 +4387,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4377,7 +4412,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4410,7 +4445,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4422,13 +4457,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,13 +4479,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4466,26 +4501,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4511,16 +4546,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.13256816715305939</v>
+        <v>0.13256816715305936</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4529,7 +4564,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4542,22 +4577,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4566,7 +4601,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4574,26 +4609,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4610,27 +4645,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,11 +4677,11 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.6111921185968043</v>
+        <v>9.6111921185968026</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4655,7 +4690,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4667,13 +4702,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4721,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="339" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,11 +4744,11 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.6304765116761466</v>
+        <v>1.6304765116761464</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4727,7 +4762,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4740,7 +4775,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4753,11 +4788,11 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>7.3528894200982991E-4</v>
+        <v>7.352889420098298E-4</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4784,11 +4819,11 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2319977016472045E-2</v>
+        <v>1.2319977016472042E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,21 +4831,21 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>382</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4819,7 +4854,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4828,13 +4863,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>383</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="340" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4969,7 +5004,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>7.9151197774737954</v>
+        <v>7.9151197774737936</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,17 +5012,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>386</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="343" t="s">
+        <v>383</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4996,22 +5031,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="344" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>385</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5020,7 +5055,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5029,7 +5064,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5051,7 +5086,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>416</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5071,7 +5106,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>4.0525413260665832</v>
+        <v>4.0525413260665824</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5115,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>4.91520725037517</v>
+        <v>4.9152072503751691</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5096,124 +5131,160 @@
         <v>0.37901037652472302</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>1.2393375918810217</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>7.1493409067304894</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>8.3886784986115117</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-5.9829634225555539E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>389</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>395</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>397</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>398</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>399</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5230,9 +5301,20 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B143:F143"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5753,7 +5835,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181">
         <v>406532</v>
@@ -5779,7 +5861,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181">
         <v>-307347</v>
@@ -5805,7 +5887,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181">
         <v>-178876</v>
@@ -5848,7 +5930,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16390564925606621</v>
+        <v>0.16390564925606624</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -5862,7 +5944,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7117,7 +7199,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7186,7 +7268,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16390564925606621</v>
+        <v>0.16390564925606624</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8490,13 +8572,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8504,7 +8586,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8523,11 +8605,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.8321203006094535</v>
+        <v>8.8321203006094517</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7849818877411932</v>
+        <v>-3.7849818877411923</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8657,7 +8739,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8680,7 +8762,7 @@
         <v>0.12834612777992979</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8702,7 +8784,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8769,7 +8851,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8781,7 +8863,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8792,12 +8874,12 @@
         <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8808,12 +8890,12 @@
         <v>1.0005837372228803</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8821,12 +8903,12 @@
         <v>216119.84280315277</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8834,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8910,7 +8992,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8921,23 +9003,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-298411.40547625005</v>
+        <v>-298411.40547624999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.6304765116761466</v>
+        <v>-1.6304765116761464</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8946,15 +9028,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>134.57330114540179</v>
+        <v>134.57330114540176</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>7.3528894200982991E-4</v>
+        <v>7.352889420098298E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8967,11 +9049,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2254.8142402500002</v>
+        <v>2254.8142402499998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.2319977016472047E-2</v>
+        <v>1.2319977016472045E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8980,15 +9062,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-296022.01793485467</v>
+        <v>-296022.01793485461</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6174212457176647</v>
+        <v>-1.6174212457176644</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9851,7 +9933,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9876,7 +9958,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10204,7 +10286,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10264,7 +10346,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10388,7 +10470,7 @@
         <v>-314015.75</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10446,7 +10528,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10754,7 +10836,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10893,7 +10975,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10948,7 +11030,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11081,7 +11163,7 @@
         <v>4.0689769984184679E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11108,7 +11190,7 @@
         <v>7.4105716195589616E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11423,7 +11505,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11984,7 +12066,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12522,7 +12604,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16390564925606621</v>
+        <v>0.16390564925606624</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12578,7 +12660,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29998.172196739382</v>
+        <v>29998.172196739386</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12633,7 +12715,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29442593531500844</v>
+        <v>0.29442593531500849</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12663,7 +12745,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12688,7 +12770,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8259594699321763E-2</v>
+        <v>2.8259594699321766E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13357,7 +13439,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13409,7 +13491,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13809,30 +13891,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.7688953694877444</v>
+        <v>0.76889536948774428</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4397836392346295</v>
+        <v>2.4397836392346286</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7897723237603556</v>
+        <v>1.7897723237603553</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98818732569754453</v>
+        <v>0.98818732569754431</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74350493928822792</v>
+        <v>0.7435049392882277</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.5938335555016151</v>
+        <v>0.59383355550161498</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13862,34 +13944,34 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13256816715305939</v>
+        <v>0.13256816715305936</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.42065235159217751</v>
+        <v>0.42065235159217734</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.30858143513109582</v>
+        <v>0.30858143513109576</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.17037712512026632</v>
+        <v>0.17037712512026626</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1281905067738324</v>
+        <v>0.12819050677383237</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10238509577614054</v>
+        <v>0.10238509577614052</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13918,7 +14000,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14747,10 +14829,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14765,8 +14847,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14781,8 +14863,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14797,8 +14879,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14821,7 +14903,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14835,7 +14917,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14888,7 +14970,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>7.9192024321727867</v>
+        <v>7.919202432172785</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15824,23 +15906,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15851,23 +15933,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9260894200923842</v>
+        <v>5.9260894200923824</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1152836270885027</v>
+        <v>7.1152836270885009</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.1476885958218777</v>
+        <v>8.1476885958218759</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3038782426382447</v>
+        <v>8.3038782426382429</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9523632923842058</v>
+        <v>8.952363292384204</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15878,23 +15960,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7490885288115283</v>
+        <v>4.7490885288115274</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4419162427365295</v>
+        <v>6.4419162427365286</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2966819495006305</v>
+        <v>8.2966819495006288</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6142711722802137</v>
+        <v>8.6142711722802119</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.049287454771827</v>
+        <v>10.049287454771823</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15905,23 +15987,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7212696218320964</v>
+        <v>3.721269621832096</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7498974292244478</v>
+        <v>5.7498974292244469</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4765181567339987</v>
+        <v>8.4765181567339969</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>8.9984684866068143</v>
+        <v>8.9984684866068125</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.558148960723686</v>
+        <v>11.558148960723685</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15932,23 +16014,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9532731399296588</v>
+        <v>2.9532731399296583</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1621738106279746</v>
+        <v>5.1621738106279738</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6550153619797374</v>
+        <v>8.6550153619797356</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.3899039371260855</v>
+        <v>9.3899039371260837</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.279349809256525</v>
+        <v>13.279349809256523</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15959,23 +16041,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.409908097825447</v>
+        <v>2.4099080978254466</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7038657582587424</v>
+        <v>4.7038657582587415</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.816628527991492</v>
+        <v>8.8166285279914902</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.7539606268659167</v>
+        <v>9.7539606268659149</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.083115965582916</v>
+        <v>15.083115965582913</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15985,23 +16067,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0338582059785431</v>
+        <v>2.0338582059785426</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3628225449846729</v>
+        <v>4.362822544984672</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.9553254053542677</v>
+        <v>8.9553254053542659</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.075109270479771</v>
+        <v>10.075109270479768</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.886652898537925</v>
+        <v>16.886652898537921</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16036,7 +16118,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.049287454771827</v>
+        <v>10.049287454771823</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16058,7 +16140,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3038782426382447</v>
+        <v>8.3038782426382429</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16081,7 +16163,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.1476885958218777</v>
+        <v>8.1476885958218759</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16104,7 +16186,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1152836270885027</v>
+        <v>7.1152836270885009</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16127,7 +16209,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7490885288115283</v>
+        <v>4.7490885288115274</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16143,7 +16225,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16195,7 +16277,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16215,7 +16297,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16269,7 +16351,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16277,12 +16359,12 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.3570592878777852</v>
+        <v>8.3570592878777834</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16292,11 +16374,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16317,8 +16399,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16339,8 +16421,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16350,8 +16432,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16362,10 +16444,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16383,8 +16465,8 @@
         <v>0.16638727228030792</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16401,8 +16483,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15587431850223021</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16419,8 +16501,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.48601257847513946</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16436,7 +16518,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16446,25 +16528,25 @@
       <c r="C18" s="151">
         <v>5</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16474,23 +16556,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9937708728791419</v>
+        <v>7.9937708728791401</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16510,8 +16592,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16521,8 +16603,8 @@
         <v>0.01</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16530,14 +16612,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.1476885958218777</v>
+        <v>8.1476885958218759</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16547,8 +16629,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16568,8 +16650,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16579,8 +16661,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16588,14 +16670,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1152836270885027</v>
+        <v>7.1152836270885009</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16605,8 +16687,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16626,8 +16708,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16637,8 +16719,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16646,14 +16728,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3038782426382447</v>
+        <v>8.3038782426382429</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16664,8 +16746,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16673,7 +16755,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9724455314384759</v>
+        <v>7.9724455314384741</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16727,8 +16809,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16738,8 +16820,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16747,14 +16829,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7490885288115283</v>
+        <v>4.7490885288115274</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16764,12 +16846,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16785,8 +16867,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16796,8 +16878,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16805,14 +16887,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.049287454771827</v>
+        <v>10.049287454771823</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16822,8 +16904,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16831,14 +16913,14 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.9151197774737954</v>
+        <v>7.9151197774737936</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16847,7 +16929,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16856,10 +16938,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16872,7 +16954,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16884,7 +16966,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16893,27 +16975,27 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.9192024321727867</v>
+        <v>7.919202432172785</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16923,19 +17005,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16945,14 +17027,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16975,7 +17057,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16998,12 +17080,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -17028,7 +17110,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.0525413260665832</v>
+        <v>4.0525413260665824</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17038,7 +17120,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.91520725037517</v>
+        <v>4.9152072503751691</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17057,12 +17139,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17075,53 +17157,109 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1784289263913903</v>
+        <v>0.17842892639139052</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>413</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>1.2393375918810217</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>7.1493409067304894</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>414</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>8.3886784986115117</v>
+      </c>
+      <c r="D93" t="s">
+        <v>411</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-5.9829634225555539E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B40756-BD1D-43FA-AB3D-16607EDF02CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B20F9D-FF8A-4485-9A7A-F1970A03E62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="427">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2321,31 +2317,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3035,7 +3047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3731,6 +3743,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4043,7 +4060,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4063,10 +4080,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4095,13 +4112,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4128,7 +4145,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4164,24 +4181,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4191,10 +4208,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4217,19 +4234,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4241,11 +4258,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>4.9152072503751691</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4253,7 +4270,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4268,7 +4285,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4277,22 +4294,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4304,13 +4321,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4330,13 +4347,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4365,13 +4382,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4387,17 +4404,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4412,7 +4429,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4457,13 +4474,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4479,13 +4496,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4501,22 +4518,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4546,7 +4563,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4555,7 +4572,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4564,7 +4581,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4577,22 +4594,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>375</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4601,7 +4618,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4609,26 +4626,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4645,27 +4662,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4677,7 +4694,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4690,7 +4707,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4702,13 +4719,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4721,13 +4738,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4744,7 +4761,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4755,537 +4772,577 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>0.61007460831657279</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>0.16360901428944893</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>422</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>1.1309485990394448</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>216246</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>126.15719684722717</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>7.352889420098298E-4</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>2113.7999999999997</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>1.2319977016472042E-2</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>378</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>7.9937708728791401</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>371</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>380</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>421</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>-3.7849818877411923</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>370</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>379</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.05 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>5</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>8.3 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.01</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>5</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>8.15 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.06</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>5</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>7.12 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.15</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>10</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.75 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>7.9151197774737936</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>383</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>419</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>382</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>417</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>380</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>381</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>0.44193951040398899</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>0.86266592430858646</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>4.0525413260665824</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>4.9152072503751691</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.37901037652472302</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.2393375918810217</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>1.1873458770290581</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>7.1493409067304894</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="239">
+        <v>6.6976802431510594</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>8.3886784986115117</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>7.8850261201801173</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-5.9829634225555539E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>3.8020469859877393E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>388</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>387</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>392</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>395</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5294,24 +5351,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5835,7 +5892,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181">
         <v>406532</v>
@@ -5861,7 +5918,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181">
         <v>-307347</v>
@@ -5887,7 +5944,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181">
         <v>-178876</v>
@@ -5944,7 +6001,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7199,7 +7256,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8578,7 +8635,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>421</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8586,7 +8643,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8739,7 +8796,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8762,7 +8819,7 @@
         <v>0.12834612777992979</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8784,7 +8841,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8851,7 +8908,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8863,7 +8920,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8874,12 +8931,12 @@
         <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8890,12 +8947,12 @@
         <v>1.0005837372228803</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8903,12 +8960,12 @@
         <v>216119.84280315277</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8916,7 +8973,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8992,7 +9049,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9003,15 +9060,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9028,7 +9085,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9062,7 +9119,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9933,7 +9990,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9958,7 +10015,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10286,7 +10343,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10346,7 +10403,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10470,7 +10527,7 @@
         <v>-314015.75</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10528,7 +10585,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10836,7 +10893,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10975,7 +11032,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11030,7 +11087,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11163,7 +11220,7 @@
         <v>4.0689769984184679E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11190,7 +11247,7 @@
         <v>7.4105716195589616E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11505,7 +11562,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12066,7 +12123,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12745,7 +12802,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13439,7 +13496,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13491,7 +13548,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14000,7 +14057,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14829,10 +14886,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14847,8 +14904,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14863,8 +14920,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14879,8 +14936,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16225,7 +16282,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16297,7 +16354,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16351,7 +16408,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16364,7 +16421,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16374,11 +16431,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16399,8 +16456,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16421,8 +16478,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16432,8 +16489,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16444,10 +16501,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16465,8 +16522,8 @@
         <v>0.16638727228030792</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16483,8 +16540,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15587431850223021</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16501,8 +16558,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.48601257847513946</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16518,7 +16575,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16528,25 +16585,25 @@
       <c r="C18" s="151">
         <v>5</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16556,12 +16613,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16571,8 +16628,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16592,8 +16649,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16603,8 +16660,8 @@
         <v>0.01</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16618,8 +16675,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16629,8 +16686,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16650,8 +16707,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16661,8 +16718,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16676,8 +16733,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16687,8 +16744,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16708,8 +16765,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16719,8 +16776,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16734,8 +16791,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16746,8 +16803,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16809,8 +16866,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16820,8 +16877,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16835,8 +16892,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16846,12 +16903,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16867,8 +16924,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16878,8 +16935,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16893,8 +16950,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16904,8 +16961,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16920,7 +16977,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16929,7 +16986,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16938,10 +16995,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16954,7 +17011,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16966,7 +17023,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16982,20 +17039,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17005,19 +17062,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17027,14 +17084,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17057,7 +17114,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17080,15 +17137,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17139,12 +17196,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17157,7 +17214,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17169,16 +17226,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17187,7 +17244,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.2393375918810217</v>
+        <v>1.1873458770290581</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17197,27 +17254,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>7.1493409067304894</v>
+        <v>6.6976802431510594</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>8.3886784986115117</v>
+        <v>7.8850261201801173</v>
       </c>
       <c r="D93" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-5.9829634225555539E-2</v>
+        <v>3.8020469859877393E-3</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17225,7 +17282,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17233,30 +17290,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>337</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>338</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B20F9D-FF8A-4485-9A7A-F1970A03E62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C194B36-B9C0-4D61-8FC5-9A9B6344146C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -180,10 +181,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1417,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1582,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1793,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2282,10 +2267,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO/Net Income</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2361,19 +2342,37 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>中国石油股份</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0857.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNY</t>
   </si>
   <si>
     <t>ENG_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2381,26 +2380,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3075,7 +3074,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3117,23 +3116,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3142,13 +3141,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3219,10 +3218,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3233,7 +3232,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3271,7 +3270,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3281,7 +3280,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3292,29 +3291,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3330,7 +3329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3344,38 +3343,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3395,17 +3394,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3420,11 +3419,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3433,51 +3432,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3493,7 +3492,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3527,21 +3526,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3550,7 +3549,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3560,13 +3559,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3577,7 +3576,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3596,9 +3595,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3607,23 +3606,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3641,13 +3640,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3655,7 +3654,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3692,7 +3691,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3714,21 +3713,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3739,7 +3738,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3747,30 +3746,30 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4061,7 +4060,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4071,24 +4070,24 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="44">
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4100,7 +4099,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>0857.HK Stock Information</v>
@@ -4110,30 +4109,30 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="50">
         <v>5.8</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4143,9 +4142,9 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4153,9 +4152,9 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4164,7 +4163,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (HKD):</v>
@@ -4176,29 +4175,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="340" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4206,17 +4205,17 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4229,30 +4228,30 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
@@ -4262,15 +4261,15 @@
         <v>4.9152072503751691</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4279,13 +4278,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4293,45 +4292,45 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="340" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="108">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="108">
-        <f>Data!C3</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="47" t="s">
         <v>233</v>
-      </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="C30" s="188">
         <f>Normalized_FCF!C8</f>
@@ -4342,22 +4341,22 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="341" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="47" t="s">
         <v>235</v>
-      </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="47" t="s">
-        <v>236</v>
       </c>
       <c r="C33" s="188">
         <f>Normalized_FCF!C9</f>
@@ -4368,9 +4367,9 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="188">
         <f>Normalized_FCF!C10</f>
@@ -4381,18 +4380,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="341" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="47" t="s">
         <v>238</v>
-      </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="47" t="s">
-        <v>239</v>
       </c>
       <c r="C37" s="188">
         <f>Normalized_FCF!C11</f>
@@ -4403,18 +4402,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
+      <c r="B39" s="341" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4427,9 +4426,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4442,9 +4441,9 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
@@ -4455,14 +4454,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4473,18 +4472,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
+      <c r="B47" s="341" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
@@ -4495,18 +4494,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>349</v>
+    <row r="50" spans="1:6">
+      <c r="B50" s="341" t="s">
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4517,27 +4516,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="340" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4548,9 +4547,9 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
@@ -4561,27 +4560,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.13256816715305936</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
         <v>7.6196467311032592E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4589,115 +4588,115 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B63" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="342" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C70" s="263">
         <f>SUM(C67:C69)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="263">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>9.6111921185968026</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4705,9 +4704,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4715,40 +4714,40 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
+      <c r="B81" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C86" s="188">
         <f>Valuation_Model!C7</f>
@@ -4759,12 +4758,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.6304765116761464</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4772,41 +4771,41 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>0.61007460831657279</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>0.16360901428944893</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>1.1309485990394448</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C93" s="188">
         <f>BS!C66</f>
@@ -4817,9 +4816,9 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
@@ -4830,12 +4829,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>7.352889420098298E-4</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4843,14 +4842,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B98" s="47" t="s">
-        <v>259</v>
       </c>
       <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
@@ -4861,12 +4860,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.2319977016472042E-2</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4874,18 +4873,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>378</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
@@ -4896,9 +4895,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4909,9 +4908,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4919,33 +4918,33 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>379</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" s="260" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110" s="260" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F110" s="260" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4967,7 +4966,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4989,7 +4988,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5011,7 +5010,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5033,7 +5032,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5055,9 +5054,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
@@ -5068,18 +5067,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>382</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="345" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5087,50 +5086,50 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
-        <v>380</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>381</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
+      <c r="B123" s="343" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="340" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
@@ -5141,12 +5140,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5156,7 +5162,7 @@
         <v>0.86266592430858646</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5166,9 +5172,9 @@
         <v>4.0525413260665824</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
@@ -5179,65 +5185,72 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.37901037652472302</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1873458770290581</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.1813095922490893</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>6.6976802431510594</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>6.6456871926773378</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>7.8850261201801173</v>
+        <v>7.8269967849264273</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>3.8020469859877393E-3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>1.1133500821827291E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5245,103 +5258,114 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="347" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+    </row>
+    <row r="146" spans="2:6">
+      <c r="B146" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
+      <c r="B147" s="344" t="s">
         <v>388</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B147" s="344" t="s">
-        <v>392</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
+      <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="238" t="s">
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>393</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B155" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>395</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B160" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5358,17 +5382,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5393,7 +5406,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5401,7 +5414,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>CNY</v>
@@ -5450,9 +5463,9 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -5466,7 +5479,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5474,7 +5487,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5500,9 +5513,9 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="181">
         <f>2275223</f>
@@ -5527,9 +5540,9 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="181">
         <f>266012+65026+C7</f>
@@ -5554,9 +5567,9 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="189">
         <v>63190</v>
@@ -5580,9 +5593,9 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="181">
         <v>23014</v>
@@ -5606,9 +5619,9 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="181">
         <v>18644</v>
@@ -5632,9 +5645,9 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="181"/>
       <c r="D10" s="181">
@@ -5656,9 +5669,9 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="181"/>
       <c r="D11" s="181">
@@ -5680,7 +5693,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5706,9 +5719,9 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="181">
         <v>8799</v>
@@ -5732,9 +5745,9 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="181">
         <v>57755</v>
@@ -5758,9 +5771,9 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="182">
         <v>183747</v>
@@ -5784,9 +5797,9 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="181">
         <v>19071</v>
@@ -5810,15 +5823,15 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="181">
         <v>243209</v>
@@ -5842,9 +5855,9 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="181"/>
       <c r="D20" s="181">
@@ -5866,9 +5879,9 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="181"/>
       <c r="D21" s="181">
@@ -5890,9 +5903,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>406532</v>
@@ -5916,9 +5929,9 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-307347</v>
@@ -5942,9 +5955,9 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-178876</v>
@@ -5968,7 +5981,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -5996,7 +6009,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6004,7 +6017,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6031,7 +6044,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6058,7 +6071,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6085,7 +6098,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6112,9 +6125,9 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="183">
         <f>BS!G28</f>
@@ -6139,9 +6152,9 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6155,12 +6168,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6209,9 +6222,9 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="183">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -6258,9 +6271,9 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" s="184">
         <f>IF(C36="","",C36+C37)</f>
@@ -6307,9 +6320,9 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="183">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -6356,9 +6369,9 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="185">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -6405,9 +6418,9 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" s="185">
         <f>IF(C$4="","",C39-C40)</f>
@@ -6454,9 +6467,9 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="183">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -6503,9 +6516,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="186">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6552,9 +6565,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6601,9 +6614,9 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" s="188">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -6650,9 +6663,9 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="183">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -6699,9 +6712,9 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="186">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6748,9 +6761,9 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="183">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6797,12 +6810,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6851,9 +6864,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="183">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6900,14 +6913,14 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" s="188">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6954,9 +6967,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C56" s="188">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7003,9 +7016,9 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" s="188">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7052,9 +7065,9 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7101,15 +7114,15 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" s="183">
         <f>IF(C$4="","",-C19)</f>
@@ -7156,9 +7169,9 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="183">
         <f>IF(C$4="","",-C20)</f>
@@ -7205,9 +7218,9 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="183">
         <f>IF(C$4="","",-C21)</f>
@@ -7254,9 +7267,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7303,7 +7316,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7352,12 +7365,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7407,9 +7420,9 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -7456,7 +7469,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7506,9 +7519,9 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -7555,7 +7568,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7605,9 +7618,9 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -7621,13 +7634,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7676,9 +7689,9 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" s="185">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -7710,9 +7723,9 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" s="185">
         <f t="shared" si="40"/>
@@ -7744,7 +7757,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7793,7 +7806,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7874,7 +7887,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7885,7 +7898,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7898,13 +7911,13 @@
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7913,27 +7926,27 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H3" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7946,7 +7959,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="19">
         <v>216246</v>
@@ -7955,7 +7968,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7976,7 +7989,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -7988,7 +8001,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7997,9 +8010,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8009,7 +8022,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="19">
         <v>2816</v>
@@ -8018,9 +8031,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8030,7 +8043,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8039,7 +8052,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8051,7 +8064,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8060,7 +8073,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8072,7 +8085,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8084,9 +8097,9 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8097,7 +8110,7 @@
         <v>163187.55000000002</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8108,34 +8121,34 @@
         <v>196311</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H14" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8144,7 +8157,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8153,7 +8166,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8164,7 +8177,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8173,9 +8186,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8184,7 +8197,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="19">
         <v>707</v>
@@ -8193,9 +8206,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8204,7 +8217,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="19">
         <v>290077</v>
@@ -8213,7 +8226,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8225,7 +8238,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8234,7 +8247,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8245,7 +8258,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8254,7 +8267,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8265,7 +8278,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8274,7 +8287,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8286,7 +8299,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8299,9 +8312,9 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -8312,7 +8325,7 @@
         <v>199297.30000000002</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -8323,24 +8336,24 @@
         <v>29431.9</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G26" s="206" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H26" s="207" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8359,7 +8372,7 @@
         <v>-454916.25</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8367,14 +8380,14 @@
         <v>0</v>
       </c>
       <c r="F28" s="210" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G28" s="181">
         <v>194492</v>
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8382,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="211" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -8393,7 +8406,7 @@
         <v>-649408.25</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8410,16 +8423,16 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>71709</v>
       </c>
       <c r="F31" s="211" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="212">
         <f>C31+C40</f>
@@ -8427,7 +8440,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8436,7 +8449,7 @@
         <v>565608</v>
       </c>
       <c r="F32" s="213" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="214">
         <f>G35+G40</f>
@@ -8447,7 +8460,7 @@
         <v>588227.75</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8458,25 +8471,25 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G34" s="218" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H34" s="219" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="220" t="s">
         <v>31</v>
@@ -8490,7 +8503,7 @@
         <v>362484.85000000003</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8498,7 +8511,7 @@
         <v>74072</v>
       </c>
       <c r="F36" s="211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G36" s="212">
         <f>C4+C15</f>
@@ -8506,7 +8519,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8514,7 +8527,7 @@
         <v>109968</v>
       </c>
       <c r="F37" s="211" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="212">
         <f>C6</f>
@@ -8522,7 +8535,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8530,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G38" s="212">
         <f>C7+C17</f>
@@ -8538,7 +8551,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8546,7 +8559,7 @@
         <v>24000</v>
       </c>
       <c r="F39" s="211" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" s="212">
         <f>C7+C17+C19+C20</f>
@@ -8557,16 +8570,16 @@
         <v>170569.30000000002</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>208040</v>
       </c>
       <c r="F40" s="220" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G40" s="214">
         <f>G12+G24</f>
@@ -8577,7 +8590,7 @@
         <v>225742.9</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8586,7 +8599,7 @@
         <v>197787</v>
       </c>
       <c r="F41" s="211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G41" s="212">
         <f>C70</f>
@@ -8597,7 +8610,7 @@
         <v>223629.1</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8605,7 +8618,7 @@
         <v>405827</v>
       </c>
       <c r="F42" s="222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="223">
         <f>C82</f>
@@ -8616,9 +8629,9 @@
         <v>2113.7999999999997</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8627,23 +8640,23 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8655,7 +8668,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -8670,25 +8683,25 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -8700,9 +8713,9 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="202"/>
       <c r="D51" s="92">
@@ -8711,24 +8724,24 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -8740,9 +8753,9 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -8754,24 +8767,24 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -8780,9 +8793,9 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -8791,24 +8804,24 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8819,12 +8832,12 @@
         <v>0.12834612777992979</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8833,23 +8846,23 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8860,12 +8873,12 @@
         <v>126.15719684722717</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8873,9 +8886,9 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8883,9 +8896,9 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8893,9 +8906,9 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -8903,24 +8916,24 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8931,12 +8944,12 @@
         <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8947,12 +8960,12 @@
         <v>1.0005837372228803</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8960,12 +8973,12 @@
         <v>216119.84280315277</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8973,27 +8986,27 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C78" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9005,9 +9018,9 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9019,9 +9032,9 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9033,9 +9046,9 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9047,9 +9060,9 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9058,24 +9071,24 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D85" s="270" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-298411.40547624999</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-1.6304765116761464</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -9083,16 +9096,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>134.57330114540176</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>7.352889420098298E-4</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -9100,16 +9113,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>2254.8142402499998</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>1.2319977016472045E-2</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -9117,9 +9130,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9148,7 +9161,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9160,14 +9173,14 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9217,15 +9230,15 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9240,13 +9253,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
@@ -9254,7 +9267,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9311,10 +9324,10 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="191">
         <f>C25</f>
@@ -9366,10 +9379,10 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
@@ -9421,10 +9434,10 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="191">
         <f>C35</f>
@@ -9476,10 +9489,10 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
@@ -9533,10 +9546,10 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="191">
         <f>BS!$G$39*BS!D58</f>
@@ -9588,10 +9601,10 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="191">
         <f>-C4*C78</f>
@@ -9643,10 +9656,10 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" s="193">
         <f>C63</f>
@@ -9700,10 +9713,10 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="191">
         <f>C50</f>
@@ -9755,10 +9768,10 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
@@ -9810,10 +9823,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9865,10 +9878,10 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" s="191">
         <f>-C4*C83</f>
@@ -9922,10 +9935,10 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
@@ -9979,10 +9992,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="191">
         <f>-C4*C85</f>
@@ -9990,7 +10003,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10005,17 +10018,17 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="191">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10030,10 +10043,10 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
@@ -10087,7 +10100,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10106,15 +10119,15 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10129,10 +10142,10 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10150,10 +10163,10 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
@@ -10207,10 +10220,10 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
@@ -10264,10 +10277,10 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
@@ -10321,21 +10334,21 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -10343,7 +10356,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10391,7 +10404,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10403,7 +10416,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10451,10 +10464,10 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -10506,28 +10519,28 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C33" s="198">
         <f>AVERAGE(G33:J33)</f>
         <v>-314015.75</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10574,10 +10587,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="198">
         <f>AVERAGE(G34:J34)</f>
@@ -10585,7 +10598,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10633,10 +10646,10 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
@@ -10690,18 +10703,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10759,7 +10772,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10817,10 +10830,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -10872,28 +10885,28 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="296">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10941,18 +10954,18 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10967,14 +10980,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11029,10 +11042,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11084,10 +11097,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11141,10 +11154,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
@@ -11196,31 +11209,31 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E52" s="302"/>
       <c r="G52" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="87">
         <f>G53</f>
         <v>4.0689769984184679E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11237,17 +11250,17 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>7.4105716195589616E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11264,10 +11277,10 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -11319,24 +11332,24 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57" s="302"/>
       <c r="G57" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="191">
         <f>BS!$C67*C66</f>
@@ -11388,10 +11401,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C59" s="191">
         <f>BS!$C68*C67</f>
@@ -11443,10 +11456,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" s="191">
         <f>BS!$C69*C68</f>
@@ -11498,10 +11511,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C61" s="184">
         <f>SUM(C58:C60)</f>
@@ -11553,16 +11566,16 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" s="297">
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11609,10 +11622,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C63" s="184">
         <f>C61+C62</f>
@@ -11664,24 +11677,24 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65" s="302"/>
       <c r="G65" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66" s="177">
         <f>G66</f>
@@ -11703,10 +11716,10 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" s="177">
         <f>G67</f>
@@ -11728,10 +11741,10 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" s="177">
         <f>G68</f>
@@ -11753,10 +11766,10 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -11780,18 +11793,18 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>60</v>
+        <v>427</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11806,10 +11819,10 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -11827,10 +11840,10 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -11884,10 +11897,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -11941,10 +11954,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -11998,10 +12011,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12055,10 +12068,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12112,10 +12125,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(H78:K78),C77)</f>
@@ -12123,7 +12136,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12171,10 +12184,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12228,10 +12241,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -12285,10 +12298,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12342,10 +12355,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -12399,7 +12412,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12457,10 +12470,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12514,10 +12527,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" s="298">
         <v>0</v>
@@ -12540,10 +12553,10 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -12564,10 +12577,10 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12621,18 +12634,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12688,19 +12701,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (HKD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>80884.201330546246</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>80884.201330546246</v>
       </c>
       <c r="H91" s="74">
@@ -12744,18 +12757,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.61311573235445438</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.19322280877140166</v>
       </c>
       <c r="H92" s="171">
@@ -12799,10 +12812,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12854,14 +12867,14 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
@@ -12879,10 +12892,10 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" s="77">
         <f>C4/G4-1</f>
@@ -12936,10 +12949,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
@@ -12993,18 +13006,18 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -13019,17 +13032,17 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="302"/>
       <c r="G100" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13086,10 +13099,10 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C102" s="200">
         <f>BS!C4</f>
@@ -13143,10 +13156,10 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C103" s="200">
         <f>BS!C6+BS!C7</f>
@@ -13200,7 +13213,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13257,7 +13270,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13314,21 +13327,21 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="303"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -13341,10 +13354,10 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
@@ -13398,10 +13411,10 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13455,10 +13468,10 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C110" s="94">
         <f>BS!$G$38/C$4</f>
@@ -13482,21 +13495,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13545,10 +13558,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13597,11 +13610,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13655,10 +13668,10 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C117" s="23">
         <f>C81</f>
@@ -13710,9 +13723,9 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
@@ -13764,9 +13777,9 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
@@ -13820,10 +13833,10 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
@@ -13877,7 +13890,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13896,15 +13909,15 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C122" s="54"/>
       <c r="D122" s="56"/>
       <c r="E122" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F122" s="56"/>
       <c r="G122" s="37"/>
@@ -13919,10 +13932,10 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
@@ -13940,7 +13953,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -13998,10 +14011,10 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14055,9 +14068,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14105,688 +14118,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14808,7 +14821,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14817,34 +14830,34 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
@@ -14855,7 +14868,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4" s="135">
         <f>Thesis!C76</f>
@@ -14863,9 +14876,9 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="228">
         <f>Thesis!C70</f>
@@ -14874,9 +14887,9 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -14887,14 +14900,14 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="348" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="226">
         <f>BS!G31</f>
@@ -14908,9 +14921,9 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
@@ -14924,9 +14937,9 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="229">
         <f>BS!H42</f>
@@ -14940,9 +14953,9 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
@@ -14954,9 +14967,9 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
@@ -14968,12 +14981,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>7.9937708728791401</v>
       </c>
       <c r="D12" t="str">
@@ -14982,12 +14995,12 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14995,15 +15008,15 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
@@ -15011,9 +15024,9 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
@@ -15021,12 +15034,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>7.919202432172785</v>
       </c>
       <c r="D18" t="str">
@@ -15035,28 +15048,28 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="129" t="s">
+      <c r="D20" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="129" t="s">
+      <c r="F20" s="130" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="130" t="s">
-        <v>112</v>
-      </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15078,7 +15091,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15100,7 +15113,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15122,7 +15135,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15144,7 +15157,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15166,7 +15179,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15188,7 +15201,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15210,7 +15223,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15232,7 +15245,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15254,7 +15267,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15276,7 +15289,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15298,7 +15311,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15320,7 +15333,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15342,7 +15355,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15364,7 +15377,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15386,7 +15399,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15408,7 +15421,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15430,7 +15443,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15452,7 +15465,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15474,7 +15487,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15496,7 +15509,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15518,7 +15531,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15540,7 +15553,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15562,7 +15575,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15584,7 +15597,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15606,7 +15619,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15628,7 +15641,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15650,7 +15663,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15672,7 +15685,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15694,7 +15707,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15716,9 +15729,9 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -15738,10 +15751,10 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
@@ -15749,13 +15762,13 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" s="137"/>
       <c r="D54" s="137"/>
@@ -15763,7 +15776,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>1636246.1637203146</v>
@@ -15790,7 +15803,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15812,7 +15825,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15833,7 +15846,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15854,7 +15867,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15875,7 +15888,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15896,7 +15909,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15917,16 +15930,16 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="115"/>
       <c r="D63" s="115"/>
@@ -15934,7 +15947,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>-0.15</v>
@@ -15957,7 +15970,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -15983,7 +15996,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16010,7 +16023,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16037,7 +16050,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16064,7 +16077,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16091,7 +16104,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16117,7 +16130,7 @@
         <v>15.083115965582913</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16143,24 +16156,24 @@
         <v>16.886652898537921</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" s="172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D73" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="173" t="s">
         <v>114</v>
       </c>
-      <c r="E73" s="173" t="s">
-        <v>115</v>
-      </c>
       <c r="F73" s="173" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16182,7 +16195,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16205,7 +16218,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16228,7 +16241,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16251,7 +16264,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16273,38 +16286,38 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16335,7 +16348,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16345,22 +16358,22 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="276">
         <v>0</v>
@@ -16370,16 +16383,16 @@
         <v>-5.8</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="121">
         <v>3</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="156"/>
       <c r="H4" s="276">
@@ -16390,7 +16403,7 @@
         <v>0.44193951040398899</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16399,16 +16412,16 @@
         <v>0.44193951040398899</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="107">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16419,9 +16432,9 @@
         <v>8.3570592878777834</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16444,9 +16457,9 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
@@ -16466,9 +16479,9 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
@@ -16488,7 +16501,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16499,9 +16512,9 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" s="350"/>
       <c r="F11" s="350"/>
@@ -16513,9 +16526,9 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="159">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16532,9 +16545,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="159">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16550,9 +16563,9 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16561,49 +16574,49 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="151">
         <v>5</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16616,9 +16629,9 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16631,18 +16644,18 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="167">
         <f>C18</f>
@@ -16652,9 +16665,9 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="165">
         <v>0.01</v>
@@ -16663,9 +16676,9 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
@@ -16678,9 +16691,9 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="166">
         <v>0.6</v>
@@ -16689,18 +16702,18 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="167">
         <f>C18</f>
@@ -16710,9 +16723,9 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="165">
         <v>-0.06</v>
@@ -16721,9 +16734,9 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
@@ -16736,9 +16749,9 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="166">
         <v>0.2</v>
@@ -16747,18 +16760,18 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="167">
         <f>C18</f>
@@ -16768,9 +16781,9 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="165">
         <v>0.02</v>
@@ -16779,9 +16792,9 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
@@ -16794,9 +16807,9 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
@@ -16806,9 +16819,9 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -16819,23 +16832,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="151">
         <v>10</v>
@@ -16843,23 +16856,23 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="167">
         <f>C46</f>
@@ -16869,9 +16882,9 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="165">
         <v>-0.15</v>
@@ -16880,9 +16893,9 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
@@ -16895,9 +16908,9 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="166">
         <v>0.05</v>
@@ -16906,18 +16919,18 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" s="167">
         <f>C46</f>
@@ -16927,9 +16940,9 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56" s="165">
         <v>0.06</v>
@@ -16938,9 +16951,9 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
@@ -16953,9 +16966,9 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="166">
         <v>0.05</v>
@@ -16964,9 +16977,9 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -16977,33 +16990,33 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="167">
         <f>C18</f>
@@ -17011,24 +17024,24 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" s="152">
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
@@ -17039,20 +17052,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17060,21 +17073,21 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17082,39 +17095,39 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>-0.20434577001864196</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17122,9 +17135,9 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
@@ -17135,23 +17148,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -17161,9 +17174,9 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
@@ -17171,9 +17184,9 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
@@ -17184,24 +17197,24 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
         <v>0.37901037652472302</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17212,108 +17225,108 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.17842892639139052</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1873458770290581</v>
+        <v>1.1813095922490893</v>
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6976802431510594</v>
+        <v>6.6456871926773378</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>7.8850261201801173</v>
+        <v>7.8269967849264273</v>
       </c>
       <c r="D93" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>3.8020469859877393E-3</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>1.1133500821827291E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F96" s="318" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>336</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C194B36-B9C0-4D61-8FC5-9A9B6344146C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F65100-81E2-44B4-A545-19DC632A652A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F65100-81E2-44B4-A545-19DC632A652A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76754AE5-8FA2-47B0-8574-775AB73D3573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3747,29 +3747,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4180,13 +4180,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4293,22 +4293,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4320,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4346,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4381,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4403,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4473,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4495,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4517,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4593,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4666,22 +4666,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4718,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4874,13 +4874,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4919,13 +4919,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,13 +5068,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5087,22 +5087,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1813095922490893</v>
+        <v>1.1389209808079233</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>6.6456871926773378</v>
+        <v>6.2832772708950877</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>7.8269967849264273</v>
+        <v>7.4221982517030112</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>1.1133500821827291E-2</v>
+        <v>6.227594017889948E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5259,13 +5259,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5302,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5316,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,17 +5355,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5382,6 +5371,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17247,8 +17247,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1813095922490893</v>
+        <v>1.1389209808079233</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6456871926773378</v>
+        <v>6.2832772708950877</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17277,7 +17277,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>7.8269967849264273</v>
+        <v>7.4221982517030112</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>1.1133500821827291E-2</v>
+        <v>6.227594017889948E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76754AE5-8FA2-47B0-8574-775AB73D3573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38C5E74-371A-440C-A637-AD565B406BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3739,37 +3744,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4082,7 +4087,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4114,10 +4119,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4128,7 +4133,7 @@
         <v>5.8</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4180,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4210,7 +4215,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4233,7 +4238,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4245,10 +4250,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4269,7 +4274,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4293,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4632,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4644,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4666,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4772,28 +4777,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.61007460831657279</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.16360901428944893</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>1.1309485990394448</v>
       </c>
@@ -4874,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4896,8 +4901,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4919,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,17 +5073,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5087,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5142,14 +5147,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5196,14 +5201,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5212,7 +5217,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>1.1389209808079233</v>
       </c>
     </row>
@@ -5222,16 +5227,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>6.2832772708950877</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>7.4221982517030112</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5244,7 +5249,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>6.227594017889948E-2</v>
       </c>
     </row>
@@ -5259,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,6 +5360,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5371,17 +5387,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6014,7 +6019,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8648,7 +8653,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11804,7 +11809,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12136,7 +12141,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16347,7 +16352,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17239,16 +17244,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17257,9 +17262,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1389209808079233</v>
+        <v>0.93093739460099523</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17267,69 +17274,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>6.2832772708950877</v>
+        <v>4.5805091304825192</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>7.4221982517030112</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>5.5114465250835147</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>6.227594017889948E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.30368122276949805</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>1.1389209808079233</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>6.2832772708950877</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>7.4221982517030112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>6.227594017889948E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38C5E74-371A-440C-A637-AD565B406BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7033BB-D14F-4025-A480-5F7871596A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3752,29 +3752,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4185,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4225,7 +4225,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06671125</v>
+        <v>1.0671017599999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4247,7 +4247,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>4.9152072503751691</v>
+        <v>4.4066254223755825</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17842892639139052</v>
+        <v>0.17855667472343195</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4298,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4478,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4500,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.13256816715305936</v>
+        <v>0.13261669874486073</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4598,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4671,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.6111921185968026</v>
+        <v>9.6147106590024016</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4723,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6304765116761464</v>
+        <v>1.6310734092738557</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.352889420098298E-4</v>
+        <v>7.3555812233838094E-4</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2319977016472042E-2</v>
+        <v>1.2324487210045705E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4879,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-3.7849818877411923</v>
+        <v>-3.7863675235231167</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4924,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.3 HKD</v>
+        <v>8.31 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>7.9151197774737936</v>
+        <v>7.9180174064472393</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5073,13 +5073,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5092,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0.86266592430858646</v>
+        <v>0.80261203755663024</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>4.0525413260665824</v>
+        <v>3.6040133848189519</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>4.9152072503751691</v>
+        <v>4.4066254223755825</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.37901037652472302</v>
+        <v>0.44346858611506823</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C98</f>
-        <v>6.2832772708950877</v>
+        <v>6.2855775021967233</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C99</f>
-        <v>7.4221982517030112</v>
+        <v>7.4244984830046468</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F99</f>
-        <v>6.227594017889948E-2</v>
+        <v>6.2328597944321884E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5264,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5307,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5321,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5360,17 +5360,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5387,6 +5376,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16390564925606624</v>
+        <v>0.16384566735228701</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16390564925606624</v>
+        <v>0.16384566735228701</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8680,11 +8680,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.8321203006094517</v>
+        <v>8.8353536323087187</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7849818877411923</v>
+        <v>-3.7863675235231167</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9090,11 +9090,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-298411.40547624999</v>
+        <v>-298520.65025824</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6304765116761464</v>
+        <v>-1.6310734092738557</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9107,11 +9107,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>134.57330114540176</v>
+        <v>134.62256679234255</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.352889420098298E-4</v>
+        <v>7.3555812233838094E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9124,11 +9124,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2254.8142402499998</v>
+        <v>2255.6397002879994</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2319977016472045E-2</v>
+        <v>1.2324487210045705E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9141,11 +9141,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-296022.01793485461</v>
+        <v>-296130.38799115963</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6174212457176644</v>
+        <v>-1.6180133639414718</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16390564925606624</v>
+        <v>0.16384566735228701</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29998.172196739386</v>
+        <v>29987.194250058328</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29442593531500849</v>
+        <v>0.29431818900972656</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8259594699321766E-2</v>
+        <v>2.8249252991773624E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13966,30 +13966,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76889536948774428</v>
+        <v>0.76917685272019221</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4397836392346286</v>
+        <v>2.440676814317349</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7897723237603553</v>
+        <v>1.7904275376152305</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98818732569754431</v>
+        <v>0.98854908904499006</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.7435049392882277</v>
+        <v>0.74377712739334179</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59383355550161498</v>
+        <v>0.59405095073557257</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14023,30 +14023,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13256816715305936</v>
+        <v>0.13261669874486073</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.42065235159217734</v>
+        <v>0.42080634729609467</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.30858143513109576</v>
+        <v>0.30869440303710871</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.17037712512026626</v>
+        <v>0.17043949811120518</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12819050677383237</v>
+        <v>0.12823743575747273</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10238509577614052</v>
+        <v>0.10242257771302976</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06671125</v>
+        <v>1.0671017599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.919202432172785</v>
+        <v>7.922101555756405</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15981,23 +15981,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16008,23 +16008,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9260894200923824</v>
+        <v>5.928258889271075</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1152836270885009</v>
+        <v>7.1178884457863578</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.1476885958218759</v>
+        <v>8.1506713654078844</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3038782426382429</v>
+        <v>8.3069181913521355</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.952363292384204</v>
+        <v>8.9556406435786435</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16035,23 +16035,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7490885288115274</v>
+        <v>4.7508271122954699</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4419162427365286</v>
+        <v>6.4442745498341152</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2966819495006288</v>
+        <v>8.2997192637392274</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6142711722802119</v>
+        <v>8.6174247520661993</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.049287454771823</v>
+        <v>10.052966376545605</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16062,23 +16062,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.721269621832096</v>
+        <v>3.7226319333292524</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7498974292244469</v>
+        <v>5.7520023966606546</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4765181567339969</v>
+        <v>8.4796213068183199</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>8.9984684866068125</v>
+        <v>9.0017627163514646</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.558148960723685</v>
+        <v>11.562380258322403</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16089,23 +16089,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9532731399296583</v>
+        <v>2.9543542972661667</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1621738106279738</v>
+        <v>5.164063619603728</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6550153619797356</v>
+        <v>8.6581838577174572</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.3899039371260837</v>
+        <v>9.3933414666229247</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.279349809256523</v>
+        <v>13.284211217527984</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16116,23 +16116,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4099080978254466</v>
+        <v>2.4107903358362313</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7038657582587415</v>
+        <v>4.7055877862370314</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8166285279914902</v>
+        <v>8.8198561883414346</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.7539606268659149</v>
+        <v>9.7575314330839955</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.083115965582913</v>
+        <v>15.08863771068096</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16142,23 +16142,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0338582059785426</v>
+        <v>2.0346027767028287</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.362822544984672</v>
+        <v>4.3644197211952367</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.9553254053542659</v>
+        <v>8.958603840942196</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.075109270479768</v>
+        <v>10.078797645305865</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.886652898537921</v>
+        <v>16.892834896546667</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.049287454771823</v>
+        <v>10.052966376545605</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3038782426382429</v>
+        <v>8.3069181913521355</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.1476885958218759</v>
+        <v>8.1506713654078844</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1152836270885009</v>
+        <v>7.1178884457863578</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7490885288115274</v>
+        <v>4.7508271122954699</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.3570592878777834</v>
+        <v>8.3599569168512282</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9937708728791401</v>
+        <v>7.9966972950609323</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.1476885958218759</v>
+        <v>8.1506713654078844</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1152836270885009</v>
+        <v>7.1178884457863578</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3038782426382429</v>
+        <v>8.3069181913521355</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9724455314384741</v>
+        <v>7.9753641466724297</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7490885288115274</v>
+        <v>4.7508271122954699</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.049287454771823</v>
+        <v>10.052966376545605</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16988,7 +16988,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.9151197774737936</v>
+        <v>7.9180174064472393</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.919202432172785</v>
+        <v>7.922101555756405</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864196</v>
+        <v>-0.20434577001864201</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.86266592430858646</v>
+        <v>0.80261203755663024</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17185,7 +17185,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.0525413260665824</v>
+        <v>3.6040133848189519</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.9152072503751691</v>
+        <v>4.4066254223755825</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.37901037652472302</v>
+        <v>0.44346858611506823</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17842892639139052</v>
+        <v>0.17855667472343195</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.5805091304825192</v>
+        <v>4.5821859991014113</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5114465250835147</v>
+        <v>5.5131233937024069</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17295,7 +17295,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.30368122276949805</v>
+        <v>0.30372426445875822</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.2832772708950877</v>
+        <v>6.2855775021967233</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.4221982517030112</v>
+        <v>7.4244984830046468</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.227594017889948E-2</v>
+        <v>6.2328597944321884E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7033BB-D14F-4025-A480-5F7871596A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E51DC3E-C821-41A2-8F45-6E798C94B91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3752,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,7 +4066,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4087,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4119,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4185,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4215,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4225,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0671017599999999</v>
+        <v>1.06707424</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4238,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4250,7 +4252,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4263,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>4.4066254223755825</v>
+        <v>4.4065324767427771</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4278,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17855667472343195</v>
+        <v>0.17854767299529528</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4298,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4478,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4500,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4571,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.13261669874486073</v>
+        <v>0.1326132786290983</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4598,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4637,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4649,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4671,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4702,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.6147106590024016</v>
+        <v>9.6144627006096286</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4723,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6310734092738557</v>
+        <v>1.6310313447380207</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4778,7 +4780,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4787,7 +4789,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4796,7 +4798,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4840,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.3555812233838094E-4</v>
+        <v>7.3553915267654979E-4</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2324487210045705E-2</v>
+        <v>1.2324169367923486E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4879,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,11 +4904,11 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-3.7863675235231167</v>
+        <v>-3.7862698750718136</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4924,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>7.9180174064472393</v>
+        <v>7.9178132048919672</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5073,17 +5075,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5092,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5145,19 +5147,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5167,199 +5169,264 @@
         <v>0.80261203755663024</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>3.6040133848189519</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>3.603920439186147</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>4.4066254223755825</v>
+        <v>4.4065324767427771</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44346858611506823</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>0.44346597188978509</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>1.1389209808079233</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>0.93093739460099523</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C98</f>
-        <v>6.2855775021967233</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <f>Scenarios!C92</f>
+        <v>4.5820678269050736</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
       <c r="B139" s="80" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C99</f>
-        <v>7.4244984830046468</v>
-      </c>
-      <c r="D139" s="101" t="str">
+        <f>Scenarios!C93</f>
+        <v>5.5130052215060692</v>
+      </c>
+      <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="2:4">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.30372123225894032</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>1.1389209808079233</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
+        <f>Scenarios!C98</f>
+        <v>6.2854154004184819</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
+        <f>Scenarios!C99</f>
+        <v>7.4243363812264054</v>
+      </c>
+      <c r="D145" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>6.2328597944321884E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+        <v>6.2324888311417914E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5376,20 +5443,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -6005,7 +6061,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16384566735228701</v>
+        <v>0.16384989295590155</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -6019,7 +6075,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7343,7 +7399,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16384566735228701</v>
+        <v>0.16384989295590155</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8653,7 +8709,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8680,11 +8736,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.8353536323087187</v>
+        <v>8.835125773128766</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7863675235231167</v>
+        <v>-3.7862698750718136</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9090,11 +9146,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-298520.65025824</v>
+        <v>-298512.95156576001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6310734092738557</v>
+        <v>-1.6310313447380207</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9107,11 +9163,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>134.62256679234255</v>
+        <v>134.61909494628532</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.3555812233838094E-4</v>
+        <v>7.3553915267654969E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9124,11 +9180,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2255.6397002879994</v>
+        <v>2255.5815285119997</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2324487210045705E-2</v>
+        <v>1.2324169367923486E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9141,11 +9197,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-296130.38799115963</v>
+        <v>-296122.7509423017</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6180133639414718</v>
+        <v>-1.6179716362174206</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -11809,7 +11865,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12141,7 +12197,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12679,7 +12735,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16384566735228701</v>
+        <v>0.16384989295590155</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12735,7 +12791,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29987.194250058328</v>
+        <v>29987.967624163732</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12790,7 +12846,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29431818900972656</v>
+        <v>0.29432577951866951</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12845,7 +12901,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8249252991773624E-2</v>
+        <v>2.8249981544120957E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13966,30 +14022,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76917685272019221</v>
+        <v>0.76915701604877029</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.440676814317349</v>
+        <v>2.4406138705303104</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7904275376152305</v>
+        <v>1.7903813634192147</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98854908904499006</v>
+        <v>0.98852359487756369</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74377712739334179</v>
+        <v>0.74375794576764021</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59405095073557257</v>
+        <v>0.59403563047017982</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14023,30 +14079,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13261669874486073</v>
+        <v>0.1326132786290983</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.42080634729609467</v>
+        <v>0.42079549491901908</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.30869440303710871</v>
+        <v>0.30868644196883016</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.17043949811120518</v>
+        <v>0.1704351025650972</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12823743575747273</v>
+        <v>0.12823412858062763</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10242257771302976</v>
+        <v>0.10241993628796205</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14978,7 +15034,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0671017599999999</v>
+        <v>1.06707424</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14992,7 +15048,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15045,7 +15101,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.922101555756405</v>
+        <v>7.9218972488730435</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15981,23 +16037,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16008,23 +16064,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.928258889271075</v>
+        <v>5.928106002554224</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1178884457863578</v>
+        <v>7.1177048791412911</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.1506713654078844</v>
+        <v>8.150461163827881</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3069181913521355</v>
+        <v>8.3067039602476669</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9556406435786435</v>
+        <v>8.9554096822591607</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16035,23 +16091,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7508271122954699</v>
+        <v>4.750704590932437</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4442745498341152</v>
+        <v>6.4441083553414629</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2997192637392274</v>
+        <v>8.2995052182913618</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6174247520661993</v>
+        <v>8.6172025131588477</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.052966376545605</v>
+        <v>10.052707115765562</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16062,23 +16118,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7226319333292524</v>
+        <v>3.7225359285857076</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7520023966606546</v>
+        <v>5.7518540555071773</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4796213068183199</v>
+        <v>8.4794026217902267</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.0017627163514646</v>
+        <v>9.0015305655676876</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.562380258322403</v>
+        <v>11.562082070542536</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16089,23 +16145,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9543542972661667</v>
+        <v>2.9542781060037133</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.164063619603728</v>
+        <v>5.1639304410858591</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6581838577174572</v>
+        <v>8.6579605676539462</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.3933414666229247</v>
+        <v>9.3930992172266148</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.284211217527984</v>
+        <v>13.283868624622219</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16116,23 +16172,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4107903358362313</v>
+        <v>2.4107281628059458</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7055877862370314</v>
+        <v>4.7054664315727148</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8198561883414346</v>
+        <v>8.8196287288325106</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.7575314330839955</v>
+        <v>9.757279791417659</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.08863771068096</v>
+        <v>15.088248582553387</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16142,23 +16198,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0346027767028287</v>
+        <v>2.0345503053542529</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3644197211952367</v>
+        <v>4.3643071650780705</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.958603840942196</v>
+        <v>8.9583728032033925</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.078797645305865</v>
+        <v>10.078537718350821</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.892834896546667</v>
+        <v>16.892399239111004</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16193,7 +16249,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.052966376545605</v>
+        <v>10.052707115765562</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16215,7 +16271,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3069181913521355</v>
+        <v>8.3067039602476669</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16238,7 +16294,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.1506713654078844</v>
+        <v>8.150461163827881</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16261,7 +16317,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1178884457863578</v>
+        <v>7.1177048791412911</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16284,7 +16340,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7508271122954699</v>
+        <v>4.750704590932437</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16434,7 +16490,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.3599569168512282</v>
+        <v>8.3597527152959561</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16640,7 +16696,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9966972950609323</v>
+        <v>7.9964910643922096</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16687,7 +16743,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.1506713654078844</v>
+        <v>8.150461163827881</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16745,7 +16801,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1178884457863578</v>
+        <v>7.1177048791412911</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16803,7 +16859,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3069181913521355</v>
+        <v>8.3067039602476669</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16830,7 +16886,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9753641466724297</v>
+        <v>7.9751584661745198</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16904,7 +16960,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7508271122954699</v>
+        <v>4.750704590932437</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16962,7 +17018,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.052966376545605</v>
+        <v>10.052707115765562</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16988,7 +17044,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.9180174064472393</v>
+        <v>7.9178132048919672</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17050,7 +17106,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.922101555756405</v>
+        <v>7.9218972488730435</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17113,7 +17169,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864201</v>
+        <v>-0.20434577001864199</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17185,7 +17241,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>3.6040133848189519</v>
+        <v>3.603920439186147</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17195,7 +17251,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.4066254223755825</v>
+        <v>4.4065324767427771</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17206,7 +17262,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44346858611506823</v>
+        <v>0.44346597188978509</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17236,7 +17292,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17855667472343195</v>
+        <v>0.17854767299529528</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17244,12 +17300,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17274,7 +17330,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.5821859991014113</v>
+        <v>4.5820678269050736</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17284,7 +17340,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5131233937024069</v>
+        <v>5.5130052215060692</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17295,7 +17351,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.30372426445875822</v>
+        <v>0.30372123225894032</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17307,7 +17363,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17334,7 +17390,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.2855775021967233</v>
+        <v>6.2854154004184819</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17346,7 +17402,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.4244984830046468</v>
+        <v>7.4243363812264054</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17356,7 +17412,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.2328597944321884E-2</v>
+        <v>6.2324888311417914E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E51DC3E-C821-41A2-8F45-6E798C94B91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D521507C-4310-4F40-9914-F1FEE9BF46E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>5.8</v>
+        <v>5.94</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1061521.6713443999</v>
+        <v>1087144.6082389201</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17854767299529528</v>
+        <v>0.1686112219828888</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1326132786290983</v>
+        <v>0.12948771313952359</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.6196467311032592E-2</v>
+        <v>7.4400590977102513E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12880,28 +12880,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.6196467311032592E-2</v>
+        <v>7.4400590977102513E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.6196467311032592E-2</v>
+        <v>7.4400590977102513E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1332863014583803E-2</v>
+        <v>6.9651617084947132E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.8508730119779135E-2</v>
+        <v>6.6894046244902181E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.6739666855375004E-2</v>
+        <v>3.5873748781342592E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8249981544120957E-2</v>
+        <v>2.7584157063283089E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14079,30 +14079,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1326132786290983</v>
+        <v>0.12948771313952359</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.42079549491901908</v>
+        <v>0.4108777559815337</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.30868644196883016</v>
+        <v>0.30141100394262871</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1704351025650972</v>
+        <v>0.16641811361575146</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12823412858062763</v>
+        <v>0.1252117753817576</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10241993628796205</v>
+        <v>0.10000599839565316</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14136,23 +14136,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17309773786086477</v>
+        <v>0.16901799319747737</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17009638604110872</v>
+        <v>0.1660873803095001</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15387627441758087</v>
+        <v>0.15024956087911936</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.124720958199869</v>
+        <v>0.12178140699650508</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12154061804183497</v>
+        <v>0.11867602435061327</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-5.8</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.8</v>
+        <v>5.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>5.8</v>
+        <v>5.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17854767299529528</v>
+        <v>0.1686112219828888</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D521507C-4310-4F40-9914-F1FEE9BF46E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A690C41A-2722-4CA3-80DA-0339F582DA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3754,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4089,7 +4092,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4121,10 +4124,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4187,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4217,7 +4220,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4240,7 +4243,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4300,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4600,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4639,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4651,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4673,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5149,7 +5152,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5203,14 +5206,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5264,7 +5267,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5320,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6075,7 +6078,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11865,7 +11868,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12197,7 +12200,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17300,12 +17303,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A690C41A-2722-4CA3-80DA-0339F582DA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735A7514-FAD5-4D60-91B7-49B42226EEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>5.94</v>
+        <v>6.04</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1087144.6082389201</v>
+        <v>1105446.7060207201</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06707424</v>
+        <v>1.0739449931617173</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>4.4065324767427771</v>
+        <v>4.4297376548118468</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1686112219828888</v>
+        <v>0.16392445461154903</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12948771313952359</v>
+        <v>0.12816382759890571</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.4400590977102513E-2</v>
+        <v>7.3168793113243216E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.6144627006096286</v>
+        <v>9.6763689837173796</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6310313447380207</v>
+        <v>1.6415333448319587</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.3553915267654979E-4</v>
+        <v>7.4027519424645907E-4</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2324169367923486E-2</v>
+        <v>1.24035231021587E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-3.7862698750718136</v>
+        <v>-3.8106491775983788</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.05 HKD</v>
+        <v>10.12 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.31 HKD</v>
+        <v>8.36 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.15 HKD</v>
+        <v>8.2 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.12 HKD</v>
+        <v>7.16 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.75 HKD</v>
+        <v>4.78 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>7.9178132048919672</v>
+        <v>7.9687949811097125</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>3.603920439186147</v>
+        <v>3.6271256172552166</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>4.4065324767427771</v>
+        <v>4.4297376548118468</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44346597188978509</v>
+        <v>0.44411449092206745</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>4.5820678269050736</v>
+        <v>4.6115711696236765</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5130052215060692</v>
+        <v>5.5425085642246721</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30372123225894032</v>
+        <v>0.30447343953968342</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>6.2854154004184819</v>
+        <v>6.3258863780846033</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>7.4243363812264054</v>
+        <v>7.4648073588925268</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>6.2324888311417914E-2</v>
+        <v>6.3245148533988438E-2</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5419,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5435,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16384989295590155</v>
+        <v>0.16280163426738203</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16384989295590155</v>
+        <v>0.16280163426738203</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8739,11 +8739,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.835125773128766</v>
+        <v>8.892014006453465</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.7862698750718136</v>
+        <v>-3.8106491775983788</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9149,11 +9149,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-298512.95156576001</v>
+        <v>-300435.03789199726</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6310313447380207</v>
+        <v>-1.6415333448319587</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9166,11 +9166,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>134.61909494628532</v>
+        <v>135.48588990539682</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.3553915267654969E-4</v>
+        <v>7.4027519424645907E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9183,11 +9183,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2255.5815285119997</v>
+        <v>2270.104926545238</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2324169367923486E-2</v>
+        <v>1.24035231021587E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9200,11 +9200,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-296122.7509423017</v>
+        <v>-298029.4470755466</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6179716362174206</v>
+        <v>-1.6283895465355536</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16384989295590155</v>
+        <v>0.16280163426738203</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29987.967624163732</v>
+        <v>29796.114293984676</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29432577951866951</v>
+        <v>0.29244277825409892</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12883,28 +12883,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.4400590977102513E-2</v>
+        <v>7.3168793113243216E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.4400590977102513E-2</v>
+        <v>7.3168793113243216E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9651617084947132E-2</v>
+        <v>6.8498444616653317E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6894046244902181E-2</v>
+        <v>6.5786528922966714E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.5873748781342592E-2</v>
+        <v>3.5279812543240897E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7584157063283089E-2</v>
+        <v>2.6953912958175834E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14025,30 +14025,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.76915701604877029</v>
+        <v>0.77410951869739031</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4406138705303104</v>
+        <v>2.4563286679069929</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7903813634192147</v>
+        <v>1.8019093976948735</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.98852359487756369</v>
+        <v>0.99488857058434976</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74375794576764021</v>
+        <v>0.74854690708436677</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59403563047017982</v>
+        <v>0.59786054914334141</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14082,30 +14082,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12948771313952359</v>
+        <v>0.12816382759890571</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.4108777559815337</v>
+        <v>0.40667693177268094</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.30141100394262871</v>
+        <v>0.29832937047928371</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16641811361575146</v>
+        <v>0.1647166507589983</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1252117753817576</v>
+        <v>0.1239316071331733</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10000599839565316</v>
+        <v>9.8983534626381028E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14139,23 +14139,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16901799319747737</v>
+        <v>0.1662196820518238</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1660873803095001</v>
+        <v>0.16333758924477329</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15024956087911936</v>
+        <v>0.14776198536787569</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12178140699650508</v>
+        <v>0.11976515853629806</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11867602435061327</v>
+        <v>0.11671118951037134</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06707424</v>
+        <v>1.0739449931617173</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9218972488730435</v>
+        <v>7.97290532172231</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16040,23 +16040,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16067,23 +16067,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.928106002554224</v>
+        <v>5.9662763111730932</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1177048791412911</v>
+        <v>7.1635348612262595</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.150461163827881</v>
+        <v>8.2029409301943019</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3067039602476669</v>
+        <v>8.3601897537931293</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9554096822591607</v>
+        <v>9.0130724081336577</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16094,23 +16094,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.750704590932437</v>
+        <v>4.7812937639861639</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4441083553414629</v>
+        <v>6.4856011364406596</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.2995052182913618</v>
+        <v>8.3529446600674699</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6172025131588477</v>
+        <v>8.6726875667690297</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.052707115765562</v>
+        <v>10.117435198039823</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16121,23 +16121,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7225359285857076</v>
+        <v>3.746504856465493</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7518540555071773</v>
+        <v>5.788889500611365</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4794026217902267</v>
+        <v>8.5340003997041052</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.0015305655676876</v>
+        <v>9.0594902578508307</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.562082070542536</v>
+        <v>11.636528823134197</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16148,23 +16148,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9542781060037133</v>
+        <v>2.9733003210254321</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1639304410858591</v>
+        <v>5.1971803219985304</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6579605676539462</v>
+        <v>8.7137080571109422</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.3930992172266148</v>
+        <v>9.4535801694657806</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.283868624622219</v>
+        <v>13.369401738374886</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16175,23 +16175,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4107281628059458</v>
+        <v>2.4262505299719268</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7054664315727148</v>
+        <v>4.7357643219632495</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8196287288325106</v>
+        <v>8.8764171786912556</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.757279791417659</v>
+        <v>9.8201056553206652</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.088248582553387</v>
+        <v>15.18539986572311</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16201,23 +16201,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0345503053542529</v>
+        <v>2.0476505118995685</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3643071650780705</v>
+        <v>4.3924083750305902</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>8.9583728032033925</v>
+        <v>9.0160546082308031</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.078537718350821</v>
+        <v>10.143432120537728</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.892399239111004</v>
+        <v>17.001167215255865</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.052707115765562</v>
+        <v>10.117435198039823</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3067039602476669</v>
+        <v>8.3601897537931293</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.150461163827881</v>
+        <v>8.2029409301943019</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1177048791412911</v>
+        <v>7.1635348612262595</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.750704590932437</v>
+        <v>4.7812937639861639</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-5.94</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.3597527152959561</v>
+        <v>8.4107344915137023</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.94</v>
+        <v>6.04</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>7.9964910643922096</v>
+        <v>8.0479794371818265</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.150461163827881</v>
+        <v>8.2029409301943019</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1177048791412911</v>
+        <v>7.1635348612262595</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3067039602476669</v>
+        <v>8.3601897537931293</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>7.9751584661745198</v>
+        <v>8.0265094811204598</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.750704590932437</v>
+        <v>4.7812937639861639</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.052707115765562</v>
+        <v>10.117435198039823</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.9178132048919672</v>
+        <v>7.9687949811097125</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.9218972488730435</v>
+        <v>7.97290532172231</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864199</v>
+        <v>-0.20434577001864196</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>3.603920439186147</v>
+        <v>3.6271256172552166</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.4065324767427771</v>
+        <v>4.4297376548118468</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44346597188978509</v>
+        <v>0.44411449092206745</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>5.94</v>
+        <v>6.04</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17295,7 +17295,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1686112219828888</v>
+        <v>0.16392445461154903</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.5820678269050736</v>
+        <v>4.6115711696236765</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5130052215060692</v>
+        <v>5.5425085642246721</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.30372123225894032</v>
+        <v>0.30447343953968342</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.2854154004184819</v>
+        <v>6.3258863780846033</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.4243363812264054</v>
+        <v>7.4648073588925268</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.2324888311417914E-2</v>
+        <v>6.3245148533988438E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735A7514-FAD5-4D60-91B7-49B42226EEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DDFFE7-52BD-441D-A6A7-0967DACFD282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1105446.7060207201</v>
+        <v>1112767.5451334401</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0739449931617173</v>
+        <v>1.0737034399999998</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>4.4297376548118468</v>
+        <v>4.428921836807783</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16392445461154903</v>
+        <v>0.16112633203079096</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12816382759890571</v>
+        <v>0.12729200739087043</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.3168793113243216E-2</v>
+        <v>7.2687419474340292E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.6763689837173796</v>
+        <v>9.6741925617061533</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6415333448319587</v>
+        <v>1.6411641289298093</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.4027519424645907E-4</v>
+        <v>7.4010869054761969E-4</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.24035231021587E-2</v>
+        <v>1.2400733284951265E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-3.8106491775983788</v>
+        <v>-3.8097920812266781</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>7.9687949811097125</v>
+        <v>7.9670026289547851</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>3.6271256172552166</v>
+        <v>3.6263097992511528</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>4.4297376548118468</v>
+        <v>4.428921836807783</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44411449092206745</v>
+        <v>0.44409183188774393</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>4.6115711696236765</v>
+        <v>4.6105339287932781</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5425085642246721</v>
+        <v>5.5414713233942736</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30447343953968342</v>
+        <v>0.3044471576732396</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>6.3258863780846033</v>
+        <v>6.32446355115676</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>7.4648073588925268</v>
+        <v>7.4633845319646834</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>6.3245148533988438E-2</v>
+        <v>6.3212994954938595E-2</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5435,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16280163426738203</v>
+        <v>0.16283826006927948</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16280163426738203</v>
+        <v>0.16283826006927948</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8739,11 +8739,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.892014006453465</v>
+        <v>8.8900140026255485</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.8106491775983788</v>
+        <v>-3.8097920812266781</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9149,11 +9149,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-300435.03789199726</v>
+        <v>-300367.46363655996</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6415333448319587</v>
+        <v>-1.6411641289298093</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9166,11 +9166,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>135.48588990539682</v>
+        <v>135.45541623562494</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4027519424645907E-4</v>
+        <v>7.4010869054761969E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9183,11 +9183,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2270.104926545238</v>
+        <v>2269.5943314719993</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.24035231021587E-2</v>
+        <v>1.2400733284951261E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9200,11 +9200,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-298029.4470755466</v>
+        <v>-297962.41388885234</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6283895465355536</v>
+        <v>-1.6280232869543105</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16280163426738203</v>
+        <v>0.16283826006927948</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29796.114293984676</v>
+        <v>29802.817584061315</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29244277825409892</v>
+        <v>0.29250856967757494</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12883,28 +12883,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.3168793113243216E-2</v>
+        <v>7.2687419474340292E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.3168793113243216E-2</v>
+        <v>7.2687419474340292E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.8498444616653317E-2</v>
+        <v>6.8047796954701645E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5786528922966714E-2</v>
+        <v>6.5353722811631418E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.5279812543240897E-2</v>
+        <v>3.504770851335115E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6953912958175834E-2</v>
+        <v>2.6782608564026231E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14025,30 +14025,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.77410951869739031</v>
+        <v>0.77393540493649238</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4563286679069929</v>
+        <v>2.4557761871377464</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8019093976948735</v>
+        <v>1.8015041097938049</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.99488857058434976</v>
+        <v>0.99466479890022119</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74854690708436677</v>
+        <v>0.74837854290067829</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59786054914334141</v>
+        <v>0.59772607753927298</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14082,30 +14082,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12816382759890571</v>
+        <v>0.12729200739087043</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.40667693177268094</v>
+        <v>0.40391055709502405</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29832937047928371</v>
+        <v>0.29630001805819162</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1647166507589983</v>
+        <v>0.16359618402964163</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1239316071331733</v>
+        <v>0.12308857613497998</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.8983534626381028E-2</v>
+        <v>9.8310210121590955E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14139,23 +14139,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1662196820518238</v>
+        <v>0.16512613151200917</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16333758924477329</v>
+        <v>0.16226299984184714</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14776198536787569</v>
+        <v>0.14678986704308702</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11976515853629806</v>
+        <v>0.11897722986171715</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11671118951037134</v>
+        <v>0.11594335273727679</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0739449931617173</v>
+        <v>1.0737034399999998</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.97290532172231</v>
+        <v>7.9711120450640083</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16040,23 +16040,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16067,23 +16067,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9662763111730932</v>
+        <v>5.9649343682283238</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1635348612262595</v>
+        <v>7.1619236292676201</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2029409301943019</v>
+        <v>8.2010959136155321</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3601897537931293</v>
+        <v>8.3583093685960801</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.0130724081336577</v>
+        <v>9.0110451756861529</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16094,23 +16094,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7812937639861639</v>
+        <v>4.7802183489200809</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4856011364406596</v>
+        <v>6.4841423862531542</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.3529446600674699</v>
+        <v>8.3510659044467097</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6726875667690297</v>
+        <v>8.6707368941408411</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.117435198039823</v>
+        <v>10.11515957081858</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16121,23 +16121,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.746504856465493</v>
+        <v>3.7456621875213369</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.788889500611365</v>
+        <v>5.7875874557481648</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.5340003997041052</v>
+        <v>8.5320809207812811</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.0594902578508307</v>
+        <v>9.0574525850377299</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.636528823134197</v>
+        <v>11.633911519318319</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16148,23 +16148,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9733003210254321</v>
+        <v>2.9726315622921149</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1971803219985304</v>
+        <v>5.1960113651648117</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7137080571109422</v>
+        <v>8.7117481580985352</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.4535801694657806</v>
+        <v>9.4514538574162579</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.369401738374886</v>
+        <v>13.366394674437032</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16175,23 +16175,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4262505299719268</v>
+        <v>2.4257048144181832</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7357643219632495</v>
+        <v>4.7346991474409013</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8764171786912556</v>
+        <v>8.8744206829229544</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.8201056553206652</v>
+        <v>9.81789690386268</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.18539986572311</v>
+        <v>15.181984345028042</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16201,23 +16201,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0476505118995685</v>
+        <v>2.0471899515744205</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3924083750305902</v>
+        <v>4.3914204285926459</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.0160546082308031</v>
+        <v>9.0140267050228147</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.143432120537728</v>
+        <v>10.141150646053481</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.001167215255865</v>
+        <v>16.99734328971044</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.117435198039823</v>
+        <v>10.11515957081858</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3601897537931293</v>
+        <v>8.3583093685960801</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2029409301943019</v>
+        <v>8.2010959136155321</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1635348612262595</v>
+        <v>7.1619236292676201</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7812937639861639</v>
+        <v>4.7802183489200809</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-6.04</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.4107344915137023</v>
+        <v>8.4089421393587749</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0479794371818265</v>
+        <v>8.0461692747518452</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2029409301943019</v>
+        <v>8.2010959136155321</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1635348612262595</v>
+        <v>7.1619236292676201</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3601897537931293</v>
+        <v>8.3583093685960801</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.0265094811204598</v>
+        <v>8.0247041477420584</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7812937639861639</v>
+        <v>4.7802183489200809</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.117435198039823</v>
+        <v>10.11515957081858</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.9687949811097125</v>
+        <v>7.9670026289547851</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.97290532172231</v>
+        <v>7.9711120450640083</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864196</v>
+        <v>-0.20434577001864199</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>3.6271256172552166</v>
+        <v>3.6263097992511528</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.4297376548118468</v>
+        <v>4.428921836807783</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44411449092206745</v>
+        <v>0.44409183188774393</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17295,7 +17295,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16392445461154903</v>
+        <v>0.16112633203079096</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.6115711696236765</v>
+        <v>4.6105339287932781</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5425085642246721</v>
+        <v>5.5414713233942736</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.30447343953968342</v>
+        <v>0.3044471576732396</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.3258863780846033</v>
+        <v>6.32446355115676</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.4648073588925268</v>
+        <v>7.4633845319646834</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.3245148533988438E-2</v>
+        <v>6.3212994954938595E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DDFFE7-52BD-441D-A6A7-0967DACFD282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661C4742-BF90-4FD7-A4AD-64B25E380F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1112767.5451334401</v>
+        <v>1118258.1744679799</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0737034399999998</v>
+        <v>1.0742246600000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>4.428921836807783</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16112633203079096</v>
+        <v>0.15926921829883645</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12729200739087043</v>
+        <v>0.12672849511458295</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.2687419474340292E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.6741925617061533</v>
+        <v>9.6788888143762719</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6411641289298093</v>
+        <v>1.6419608177876577</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.4010869054761969E-4</v>
+        <v>7.404679698768239E-4</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2400733284951265E-2</v>
+        <v>1.2406753113110505E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-3.8097920812266781</v>
+        <v>-3.8116415116695737</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.2 HKD</v>
+        <v>8.21 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.16 HKD</v>
+        <v>7.17 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>7.9670026289547851</v>
+        <v>7.970870141114629</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>3.6263097992511528</v>
+        <v>3.6280701598154881</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>4.428921836807783</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44409183188774393</v>
+        <v>0.4441407125028709</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>4.6105339287932781</v>
+        <v>4.6127720724042991</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5414713233942736</v>
+        <v>5.5437094670052947</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3044471576732396</v>
+        <v>0.3045038535491591</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>6.32446355115676</v>
+        <v>6.3275337070017814</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>7.4633845319646834</v>
+        <v>7.4664546878097049</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>6.3212994954938595E-2</v>
+        <v>6.328235743085231E-2</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5419,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5435,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16283826006927948</v>
+        <v>0.16275925000641858</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16283826006927948</v>
+        <v>0.16275925000641858</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8739,11 +8739,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.8900140026255485</v>
+        <v>8.8943295826319329</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.8097920812266781</v>
+        <v>-3.8116415116695737</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9149,11 +9149,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-300367.46363655996</v>
+        <v>-300513.27441034</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6411641289298093</v>
+        <v>-1.6419608177876577</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9166,11 +9166,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>135.45541623562494</v>
+        <v>135.5211718897657</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4010869054761969E-4</v>
+        <v>7.4046796987682411E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9183,11 +9183,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2269.5943314719993</v>
+        <v>2270.6960863079998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2400733284951261E-2</v>
+        <v>1.2406753113110501E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9200,11 +9200,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-297962.41388885234</v>
+        <v>-298107.05715214222</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6280232869543105</v>
+        <v>-1.6288135967046704</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16283826006927948</v>
+        <v>0.16275925000641858</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29802.817584061315</v>
+        <v>29788.357085099051</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29250856967757494</v>
+        <v>0.2923666428326937</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12883,28 +12883,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.2687419474340292E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.2687419474340292E-2</v>
+        <v>7.2330525434368076E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.8047796954701645E-2</v>
+        <v>6.7713683385365958E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5353722811631418E-2</v>
+        <v>6.5032837102245333E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.504770851335115E-2</v>
+        <v>3.4875624838162846E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6782608564026231E-2</v>
+        <v>2.6638175123800095E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14025,30 +14025,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.77393540493649238</v>
+        <v>0.77431110515010171</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4557761871377464</v>
+        <v>2.4569683223368854</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8015041097938049</v>
+        <v>1.8023786343013422</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.99466479890022119</v>
+        <v>0.99514765027907404</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74837854290067829</v>
+        <v>0.74874183675780781</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59772607753927298</v>
+        <v>0.59801623846688923</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14082,30 +14082,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12729200739087043</v>
+        <v>0.12672849511458295</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.40391055709502405</v>
+        <v>0.40212247501422016</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29630001805819162</v>
+        <v>0.29498831985292012</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16359618402964163</v>
+        <v>0.16287195585582226</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12308857613497998</v>
+        <v>0.12254367213712075</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.8310210121590955E-2</v>
+        <v>9.7874998112420494E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14139,23 +14139,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16512613151200917</v>
+        <v>0.16431536490884055</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16226299984184714</v>
+        <v>0.16146629116831926</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14678986704308702</v>
+        <v>0.14606913119835829</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11897722986171715</v>
+        <v>0.11839305361035028</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11594335273727679</v>
+        <v>0.11537407277293664</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0737034399999998</v>
+        <v>1.0742246600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9711120450640083</v>
+        <v>7.9749815521041727</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16040,23 +16040,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16067,23 +16067,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9649343682283238</v>
+        <v>5.9678299937572961</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1619236292676201</v>
+        <v>7.1654003228265495</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2010959136155321</v>
+        <v>8.2050770643251703</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3583093685960801</v>
+        <v>8.3623668372105993</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.0110451756861529</v>
+        <v>9.0154195092232357</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16094,23 +16094,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7802183489200809</v>
+        <v>4.7825388643575879</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4841423862531542</v>
+        <v>6.4872900568003997</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.3510659044467097</v>
+        <v>8.3551198567845333</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6707368941408411</v>
+        <v>8.674946027981342</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.11515957081858</v>
+        <v>10.120069887089434</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16121,23 +16121,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7456621875213369</v>
+        <v>3.7474804866648888</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7875874557481648</v>
+        <v>5.7903969897603558</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.5320809207812811</v>
+        <v>8.536222745285011</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.0574525850377299</v>
+        <v>9.0618494466482087</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.633911519318319</v>
+        <v>11.639559100518303</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16148,23 +16148,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9726315622921149</v>
+        <v>2.9740746004394998</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1960113651648117</v>
+        <v>5.1985337237070848</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7117481580985352</v>
+        <v>8.7159772005005642</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.4514538574162579</v>
+        <v>9.4560419835189045</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.366394674437032</v>
+        <v>13.372883274522186</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16175,23 +16175,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4257048144181832</v>
+        <v>2.4268823517308804</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7346991474409013</v>
+        <v>4.7369975659778021</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8744206829229544</v>
+        <v>8.8787286932878597</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.81789690386268</v>
+        <v>9.8226629165563093</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.181984345028042</v>
+        <v>15.189354307333758</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16201,23 +16201,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0471899515744205</v>
+        <v>2.0481837421378186</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3914204285926459</v>
+        <v>4.3935522054600007</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.0140267050228147</v>
+        <v>9.0184024859173935</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.141150646053481</v>
+        <v>10.146073579465838</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>16.99734328971044</v>
+        <v>17.005594502232835</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.11515957081858</v>
+        <v>10.120069887089434</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3583093685960801</v>
+        <v>8.3623668372105993</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2010959136155321</v>
+        <v>8.2050770643251703</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1619236292676201</v>
+        <v>7.1654003228265495</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7802183489200809</v>
+        <v>4.7825388643575879</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-6.08</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.4089421393587749</v>
+        <v>8.4128096515186179</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0461692747518452</v>
+        <v>8.0500752176716031</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2010959136155321</v>
+        <v>8.2050770643251703</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1619236292676201</v>
+        <v>7.1654003228265495</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3583093685960801</v>
+        <v>8.3623668372105993</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.0247041477420584</v>
+        <v>8.0285996706025315</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7802183489200809</v>
+        <v>4.7825388643575879</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.11515957081858</v>
+        <v>10.120069887089434</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.9670026289547851</v>
+        <v>7.970870141114629</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.9711120450640083</v>
+        <v>7.9749815521041727</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>3.6263097992511528</v>
+        <v>3.6280701598154881</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.428921836807783</v>
+        <v>4.4306821973721187</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44409183188774393</v>
+        <v>0.4441407125028709</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17295,7 +17295,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16112633203079096</v>
+        <v>0.15926921829883645</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.6105339287932781</v>
+        <v>4.6127720724042991</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5414713233942736</v>
+        <v>5.5437094670052947</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.3044471576732396</v>
+        <v>0.3045038535491591</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.32446355115676</v>
+        <v>6.3275337070017814</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.4633845319646834</v>
+        <v>7.4664546878097049</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.3212994954938595E-2</v>
+        <v>6.328235743085231E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661C4742-BF90-4FD7-A4AD-64B25E380F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76775F2E-D523-4553-97FA-260755239057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="440">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,30 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>ENG_01</t>
+  </si>
+  <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2367,10 +2391,7 @@
     <t>0857.HK</t>
   </si>
   <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>ENG_01</t>
+    <t>601857.SS</t>
   </si>
   <si>
     <t>N</t>
@@ -3056,7 +3077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3757,29 +3778,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4069,13 +4097,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4092,7 +4119,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4110,9 +4137,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>0857.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>426</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4124,340 +4150,338 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>183020977818</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>429</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>435</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>6.11</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D12" s="50">
+        <v>8.1</v>
+      </c>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>183020977818</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D13" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>1118258.1744679799</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="D14" s="35">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v>1482469.9203258001</v>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>CNY/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v>CNY</v>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1.0742246600000001</v>
+      </c>
+      <c r="D16" s="50">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Negative Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1.0742246600000001</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>CNY/HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v>HKD/CNY:</v>
+      </c>
+      <c r="E22" s="341">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v>0.93090396938011077</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>425</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>4.4306821973721187</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.15926921829883645</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>247357.8376927129</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>243208.99999999997</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-283919.19056768838</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="188">
+      <c r="C42" s="188">
         <f>Normalized_FCF!C11</f>
         <v>18644</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>8793.8666926784372</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-20731</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-11937.133307321563</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4465,405 +4489,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-17915.118234001515</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>8793.8666926784372</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-20731</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-11937.133307321563</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-17915.118234001515</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-63516.176096347837</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>418605.86669267842</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>418605.86669267842</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>131923.21948735364</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.12672849511458295</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>7.2330525434368076E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>9.6788888143762719</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>279749</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.6419608177876577</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.61007460831657279</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.16360901428944893</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>1.1309485990394448</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>216246</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>126.15719684722717</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.404679698768239E-4</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>2113.7999999999997</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4872,591 +4904,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2406753113110505E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>126.15719684722717</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>7.404679698768239E-4</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>8.0500752176716031</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>2113.7999999999997</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>-3.8116415116695737</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2406753113110505E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>8.0500752176716031</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>-3.8116415116695737</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.12 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>5</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>8.36 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.01</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>5</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>8.21 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.06</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>5</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>7.17 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.15</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>10</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.78 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>7.970870141114629</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0.44193951040398899</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>0857.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v>601857.SS</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>0.80261203755663024</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>3.6280701598154881</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>4.4306821973721187</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v>4.1245396445954965</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>427</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.4441407125028709</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>0.93093739460099523</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>4.6127720724042991</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>5.5437094670052947</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v>5.1606611479253273</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>427</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.3045038535491591</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>1.1389209808079233</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>6.3275337070017814</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>7.4664546878097049</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v>6.9505523060787899</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>427</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>6.328235743085231E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5480,7 +5609,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6078,7 +6207,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9240,7 +9369,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11868,7 +11997,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12200,7 +12329,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14935,7 +15064,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14945,7 +15074,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -14963,10 +15092,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -14981,8 +15110,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -14997,8 +15126,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15013,8 +15142,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15040,7 +15169,7 @@
         <v>1.0742246600000001</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>CNY/HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16508,11 +16637,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16533,8 +16662,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16555,8 +16684,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16566,8 +16695,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16580,8 +16709,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16599,8 +16728,8 @@
         <v>0.16638727228030792</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16617,8 +16746,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15587431850223021</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16635,8 +16764,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.48601257847513946</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16662,21 +16791,21 @@
       <c r="C18" s="151">
         <v>5</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16690,8 +16819,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16705,8 +16834,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16726,8 +16855,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16737,8 +16866,8 @@
         <v>0.01</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16752,8 +16881,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16763,8 +16892,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16784,8 +16913,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16795,8 +16924,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16810,8 +16939,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16821,8 +16950,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16842,8 +16971,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16853,8 +16982,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16868,8 +16997,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16880,8 +17009,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16943,8 +17072,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -16954,8 +17083,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -16969,8 +17098,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -16980,8 +17109,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17001,8 +17130,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17012,8 +17141,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17027,8 +17156,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17038,8 +17167,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17057,7 +17186,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17222,7 +17351,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17311,7 +17440,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17369,7 +17498,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76775F2E-D523-4553-97FA-260755239057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65B103C-B675-472A-8FED-B5359F138470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4273,13 +4273,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4379,22 +4379,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4406,13 +4406,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4432,13 +4432,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4467,13 +4467,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4489,13 +4489,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4559,13 +4559,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4581,7 +4581,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4603,22 +4603,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4679,22 +4679,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4752,22 +4752,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4804,13 +4804,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4960,13 +4960,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -5005,13 +5005,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5154,13 +5154,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5173,22 +5173,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5452,13 +5452,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5495,13 +5495,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5509,22 +5509,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5548,17 +5548,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5575,6 +5564,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8575,7 +8575,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>194492</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65B103C-B675-472A-8FED-B5359F138470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F5E93-64CB-48F5-A394-B8A93BC98FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>6.11</v>
+        <v>6.29</v>
       </c>
       <c r="D12" s="50">
         <v>8.1</v>
@@ -4233,8 +4233,7 @@
         <v>431</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1118258.1744679799</v>
+        <v>1.08195318</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4273,13 +4272,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4328,7 +4327,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4344,7 +4343,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>4.4306821973721187</v>
+        <v>3.6070431510481131</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,7 +4358,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15926921829883645</v>
+        <v>0.14740643085297989</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4379,22 +4378,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4406,13 +4405,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4432,13 +4431,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4467,13 +4466,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4489,13 +4488,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4559,13 +4558,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4581,7 +4580,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4603,22 +4602,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12672849511458295</v>
+        <v>0.12310192450717039</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4661,7 +4660,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.2330525434368076E-2</v>
+        <v>7.0260653482351193E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4679,22 +4678,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4752,22 +4751,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4804,13 +4803,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4823,13 +4822,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4960,13 +4959,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -5005,13 +5004,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5154,13 +5153,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5173,22 +5172,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5210,7 +5209,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5245,7 +5244,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5255,7 +5254,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.80261203755663024</v>
+        <v>0.70220709379059454</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>3.6280701598154881</v>
+        <v>2.9048360572575187</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5273,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>4.4306821973721187</v>
+        <v>3.6070431510481131</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>4.1245396445954965</v>
+        <v>3.3578107870360312</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5299,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4441407125028709</v>
+        <v>0.5474718459603819</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5452,13 +5451,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5495,13 +5494,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5509,22 +5508,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5548,6 +5547,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5564,17 +5574,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13012,28 +13011,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.2330525434368076E-2</v>
+        <v>7.0260653482351193E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.2330525434368076E-2</v>
+        <v>7.0260653482351193E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.7713683385365958E-2</v>
+        <v>6.5775930919648021E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5032837102245333E-2</v>
+        <v>6.3171802018238313E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4875624838162846E-2</v>
+        <v>3.3877594238660574E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6638175123800095E-2</v>
+        <v>2.5875874404836022E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14211,30 +14210,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12672849511458295</v>
+        <v>0.12310192450717039</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.40212247501422016</v>
+        <v>0.39061499560204854</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29498831985292012</v>
+        <v>0.28654668271881434</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16287195585582226</v>
+        <v>0.15821107317632338</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12254367213712075</v>
+        <v>0.11903685799011253</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.7874998112420494E-2</v>
+        <v>9.5074123762621504E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14268,23 +14267,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16431536490884055</v>
+        <v>0.15961317640588485</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16146629116831926</v>
+        <v>0.15684563418734987</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14606913119835829</v>
+        <v>0.14188909246772163</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11839305361035028</v>
+        <v>0.1150050171000382</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11537407277293664</v>
+        <v>0.11207242999088123</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16573,7 +16572,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-6.11</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16813,7 +16812,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>6.11</v>
+        <v>6.29</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17352,7 +17351,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17361,7 +17360,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.80261203755663024</v>
+        <v>0.70220709379059454</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17373,7 +17372,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>3.6280701598154881</v>
+        <v>2.9048360572575187</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17383,7 +17382,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>4.4306821973721187</v>
+        <v>3.6070431510481131</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17394,7 +17393,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.4441407125028709</v>
+        <v>0.5474718459603819</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17411,7 +17410,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>6.11</v>
+        <v>6.29</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17424,7 +17423,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15926921829883645</v>
+        <v>0.14740643085297989</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F5E93-64CB-48F5-A394-B8A93BC98FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2C819-A2CB-485F-964B-F901392EF0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4233,7 +4233,8 @@
         <v>431</v>
       </c>
       <c r="C14" s="35">
-        <v>1.08195318</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>1151201.9504752199</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4272,13 +4273,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4378,22 +4379,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4405,13 +4406,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4431,13 +4432,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4466,13 +4467,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4488,13 +4489,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4558,13 +4559,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4580,7 +4581,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4602,22 +4603,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4678,22 +4679,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4751,22 +4752,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4803,13 +4804,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4822,13 +4823,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4959,13 +4960,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -5004,13 +5005,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5153,13 +5154,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5172,22 +5173,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5451,13 +5452,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5494,13 +5495,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5508,22 +5509,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5547,17 +5548,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5574,6 +5564,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2C819-A2CB-485F-964B-F901392EF0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B229A6F7-87A6-4E9E-A6F1-C9FCB6302058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>6.29</v>
+        <v>6.26</v>
       </c>
       <c r="D12" s="50">
         <v>8.1</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1151201.9504752199</v>
+        <v>1145711.32114068</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0742246600000001</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E22" s="341">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.93090396938011077</v>
+        <v>0.92345791624048323</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>3.6070431510481131</v>
+        <v>3.63046551092381</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14740643085297989</v>
+        <v>0.15209621087146563</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>418605.86669267842</v>
+        <v>175396.86669267845</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12310192450717039</v>
+        <v>0.12468922576969506</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.0260653482351193E-2</v>
+        <v>7.0597365879231475E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.6788888143762719</v>
+        <v>9.7569319164786368</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6419608177876577</v>
+        <v>1.6552003247401861</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.404679698768239E-4</v>
+        <v>7.4643853307730136E-4</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2406753113110505E-2</v>
+        <v>1.2506791611179324E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-3.8116415116695737</v>
+        <v>-3.842375652062942</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.12 HKD</v>
+        <v>10.2 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.36 HKD</v>
+        <v>8.43 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.21 HKD</v>
+        <v>8.27 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.17 HKD</v>
+        <v>7.22 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.78 HKD</v>
+        <v>4.82 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>7.970870141114629</v>
+        <v>8.0351410966135415</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>2.9048360572575187</v>
+        <v>2.9282584171332156</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5274,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>3.6070431510481131</v>
+        <v>3.63046551092381</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>3.3578107870360312</v>
+        <v>3.3525821157006428</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5474718459603819</v>
+        <v>0.54817650775866378</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>4.6127720724042991</v>
+        <v>4.649965912392096</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5343,11 +5343,11 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5437094670052947</v>
+        <v>5.5809033069930916</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>5.1606611479253273</v>
+        <v>5.1537293386154621</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3045038535491591</v>
+        <v>0.30543804522048823</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>6.3275337070017814</v>
+        <v>6.3785540636379903</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5412,11 +5412,11 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>7.4664546878097049</v>
+        <v>7.5174750444459137</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>6.9505523060787899</v>
+        <v>6.9420718399338579</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>6.328235743085231E-2</v>
+        <v>6.442525973635993E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16275925000641858</v>
+        <v>0.16145738207548607</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7367,11 +7367,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
-        <v>0</v>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
+        <v>-243209</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-115297</v>
       </c>
       <c r="E62" s="183">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16275925000641858</v>
+        <v>0.16145738207548607</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.8943295826319329</v>
+        <v>8.9660466035691293</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.8116415116695737</v>
+        <v>-3.842375652062942</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9278,11 +9278,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-300513.27441034</v>
+        <v>-302936.38191861997</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6419608177876577</v>
+        <v>-1.6552003247401861</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9295,11 +9295,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>135.5211718897657</v>
+        <v>136.61391020484123</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4046796987682411E-4</v>
+        <v>7.4643853307730136E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9312,11 +9312,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2270.6960863079998</v>
+        <v>2289.0052300439997</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2406753113110501E-2</v>
+        <v>1.2506791611179324E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9329,11 +9329,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-298107.05715214222</v>
+        <v>-300510.76277837111</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6288135967046704</v>
+        <v>-1.6419470945959294</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9806,7 +9806,7 @@
       <c r="E10" s="302"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
-        <v>0</v>
+        <v>-243209</v>
       </c>
       <c r="H10" s="191">
         <f>Data!D62</f>
@@ -9973,7 +9973,7 @@
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>495431.86669267842</v>
+        <v>252222.86669267845</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
@@ -10142,7 +10142,7 @@
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>418605.86669267842</v>
+        <v>175396.86669267845</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
@@ -10250,7 +10250,7 @@
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>418605.86669267842</v>
+        <v>175396.86669267845</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
@@ -12334,7 +12334,7 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>0</v>
+        <v>8.2780998243351472E-2</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
@@ -12505,7 +12505,7 @@
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.16863004447362948</v>
+        <v>8.5849046230278017E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
@@ -12677,7 +12677,7 @@
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.14248079435935032</v>
+        <v>5.9699796115998863E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
@@ -12784,7 +12784,7 @@
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.14248079435935032</v>
+        <v>5.9699796115998863E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16275925000641858</v>
+        <v>0.16145738207548607</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29788.357085099051</v>
+        <v>29550.087943389888</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12962,7 +12962,7 @@
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.19322280877140166</v>
+        <v>0.46114963656829444</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.2923666428326937</v>
+        <v>0.29002807985477835</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13012,28 +13012,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.0260653482351193E-2</v>
+        <v>7.0597365879231475E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.0260653482351193E-2</v>
+        <v>7.0597365879231475E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5775930919648021E-2</v>
+        <v>6.6091151035876358E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.3171802018238313E-2</v>
+        <v>6.3474542283501439E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.3877594238660574E-2</v>
+        <v>3.4039946926705276E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.5875874404836022E-2</v>
+        <v>2.5791914069566466E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13149,14 +13149,14 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.569356498519202</v>
+        <v>-0.15410320794717913</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.29222584699757026</v>
+        <v>-0.34213172495365785</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
@@ -13760,7 +13760,7 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>0.97115695776537569</v>
+        <v>2.3177837076890597</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
@@ -13873,7 +13873,7 @@
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.16863004447362948</v>
+        <v>8.5849046230278017E-2</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
@@ -14154,30 +14154,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.77431110515010171</v>
+        <v>0.78055455331829093</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4569683223368854</v>
+        <v>1.037776545074808</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8023786343013422</v>
+        <v>1.8169116269290673</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>0.99514765027907404</v>
+        <v>1.0031717541991749</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.74874183675780781</v>
+        <v>0.75477911404604447</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.59801623846688923</v>
+        <v>0.60283818066011108</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14211,30 +14211,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12310192450717039</v>
+        <v>0.12468922576969506</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.39061499560204854</v>
+        <v>0.16577900081067221</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.28654668271881434</v>
+        <v>0.29024147395033023</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15821107317632338</v>
+        <v>0.1602510789455551</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.11903685799011253</v>
+        <v>0.12057174345783458</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.5074123762621504E-2</v>
+        <v>9.6300028859442666E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14268,23 +14268,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15961317640588485</v>
+        <v>0.1603780957816319</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15684563418734987</v>
+        <v>0.15759729058121896</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14188909246772163</v>
+        <v>0.14256907214408454</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1150050171000382</v>
+        <v>0.11555615935451123</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11207242999088123</v>
+        <v>0.11260951831352123</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0742246600000001</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9749815521041727</v>
+        <v>8.0392856588535846</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16169,23 +16169,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16196,23 +16196,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9678299937572961</v>
+        <v>6.0159499767909441</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.1654003228265495</v>
+        <v>7.2231765903013931</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2050770643251703</v>
+        <v>8.2712364840033636</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3623668372105993</v>
+        <v>8.4297945204302369</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.0154195092232357</v>
+        <v>9.0881129060322667</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16223,23 +16223,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.7825388643575879</v>
+        <v>4.8211015729554179</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.4872900568003997</v>
+        <v>6.539598565553856</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.3551198567845333</v>
+        <v>8.4224891059375988</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.674946027981342</v>
+        <v>8.7448941089623595</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.120069887089434</v>
+        <v>10.201670333445225</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16250,23 +16250,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7474804866648888</v>
+        <v>3.7776972819867858</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7903969897603558</v>
+        <v>5.8370862897566393</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.536222745285011</v>
+        <v>8.6050522685965394</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.0618494466482087</v>
+        <v>9.134917218699746</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.639559100518303</v>
+        <v>11.733411537169813</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16277,23 +16277,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9740746004394998</v>
+        <v>2.9980552465811723</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.1985337237070848</v>
+        <v>5.2404506943390086</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7159772005005642</v>
+        <v>8.7862561252434759</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.4560419835189045</v>
+        <v>9.5322882204741095</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.372883274522186</v>
+        <v>13.480711901837996</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16304,23 +16304,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4268823517308804</v>
+        <v>2.4464508611743652</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7369975659778021</v>
+        <v>4.7751930646337168</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.8787286932878597</v>
+        <v>8.9503199206734081</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.8226629165563093</v>
+        <v>9.9018653022449712</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.189354307333758</v>
+        <v>15.311829557521104</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16330,23 +16330,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0481837421378186</v>
+        <v>2.0646987177695917</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3935522054600007</v>
+        <v>4.4289784253431641</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.0184024859173935</v>
+        <v>9.0911199351521912</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.146073579465838</v>
+        <v>10.227883699561879</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.005594502232835</v>
+        <v>17.142714513992644</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.120069887089434</v>
+        <v>10.201670333445225</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.3623668372105993</v>
+        <v>8.4297945204302369</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2050770643251703</v>
+        <v>8.2712364840033636</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1654003228265495</v>
+        <v>7.2231765903013931</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.7825388643575879</v>
+        <v>4.8211015729554179</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-6.29</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.4128096515186179</v>
+        <v>8.4770806070175304</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>418605.86669267842</v>
+        <v>175396.86669267845</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.48601257847513946</v>
+        <v>0.1119740670927909</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>6.29</v>
+        <v>6.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.0500752176716031</v>
+        <v>8.1149848218827092</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2050770643251703</v>
+        <v>8.2712364840033636</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.1654003228265495</v>
+        <v>7.2231765903013931</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.3623668372105993</v>
+        <v>8.4297945204302369</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.0285996706025315</v>
+        <v>8.0933361125483447</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.7825388643575879</v>
+        <v>4.8211015729554179</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.120069887089434</v>
+        <v>10.201670333445225</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.970870141114629</v>
+        <v>8.0351410966135415</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>7.9749815521041727</v>
+        <v>8.0392856588535846</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864199</v>
+        <v>-0.20434577001864196</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.9048360572575187</v>
+        <v>2.9282584171332156</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>3.6070431510481131</v>
+        <v>3.63046551092381</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.5474718459603819</v>
+        <v>0.54817650775866378</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>6.29</v>
+        <v>6.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14740643085297989</v>
+        <v>0.15209621087146563</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.6127720724042991</v>
+        <v>4.649965912392096</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5437094670052947</v>
+        <v>5.5809033069930916</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.3045038535491591</v>
+        <v>0.30543804522048823</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.3275337070017814</v>
+        <v>6.3785540636379903</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.4664546878097049</v>
+        <v>7.5174750444459137</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.328235743085231E-2</v>
+        <v>6.442525973635993E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B229A6F7-87A6-4E9E-A6F1-C9FCB6302058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B0C119-7A85-4217-9530-E9BF34BBE8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4273,13 +4273,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E22" s="341">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92345791624048323</v>
+        <v>0.92351705994132738</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>3.63046551092381</v>
+        <v>3.630277979964903</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15209621087146563</v>
+        <v>0.15207428234077813</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4379,22 +4379,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4406,13 +4406,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4432,13 +4432,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4467,13 +4467,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4489,13 +4489,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4559,13 +4559,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4581,7 +4581,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4603,22 +4603,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12468922576969506</v>
+        <v>0.12468124044642676</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4679,22 +4679,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4752,22 +4752,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.7569319164786368</v>
+        <v>9.7563070649328925</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4804,13 +4804,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6552003247401861</v>
+        <v>1.6550943227212846</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.4643853307730136E-4</v>
+        <v>7.4639072980520844E-4</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2506791611179324E-2</v>
+        <v>1.2505990653651133E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4960,13 +4960,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-3.842375652062942</v>
+        <v>-3.8421295793849657</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5005,13 +5005,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>8.0351410966135415</v>
+        <v>8.0346265116623012</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5154,13 +5154,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5173,22 +5173,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>2.9282584171332156</v>
+        <v>2.9280708861743086</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5274,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>3.63046551092381</v>
+        <v>3.630277979964903</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>3.3525821157006428</v>
+        <v>3.3526236468269284</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54817650775866378</v>
+        <v>0.54817091065831924</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>4.649965912392096</v>
+        <v>4.649668120174943</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5343,11 +5343,11 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5809033069930916</v>
+        <v>5.5806055147759386</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>5.1537293386154621</v>
+        <v>5.1537843976982325</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30543804522048823</v>
+        <v>0.30543062497358631</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>6.3785540636379903</v>
+        <v>6.3781455695129523</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5412,11 +5412,11 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>7.5174750444459137</v>
+        <v>7.5170665503208758</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>6.9420718399338579</v>
+        <v>6.9421391999356317</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>6.442525973635993E-2</v>
+        <v>6.4416181709278542E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5452,13 +5452,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5495,13 +5495,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5509,22 +5509,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5548,6 +5548,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5564,17 +5575,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16145738207548607</v>
+        <v>0.16146772276014168</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16145738207548607</v>
+        <v>0.16146772276014168</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.9660466035691293</v>
+        <v>8.9654724017475527</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.842375652062942</v>
+        <v>-3.8421295793849657</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9278,11 +9278,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-302936.38191861997</v>
+        <v>-302916.98132546997</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6552003247401861</v>
+        <v>-1.6550943227212846</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9295,11 +9295,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>136.61391020484123</v>
+        <v>136.60516120323987</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4643853307730136E-4</v>
+        <v>7.4639072980520844E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9312,11 +9312,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2289.0052300439997</v>
+        <v>2288.8586380139996</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2506791611179324E-2</v>
+        <v>1.2505990653651133E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9329,11 +9329,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-300510.76277837111</v>
+        <v>-300491.51752625272</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6419470945959294</v>
+        <v>-1.6418419413378282</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16145738207548607</v>
+        <v>0.16146772276014168</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29550.087943389888</v>
+        <v>29551.980505606865</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.29002807985477835</v>
+        <v>0.2900466549665292</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13033,7 +13033,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.5791914069566466E-2</v>
+        <v>2.579356593612487E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14154,30 +14154,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.78055455331829093</v>
+        <v>0.78050456519463141</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.037776545074808</v>
+        <v>1.0377100839901272</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8169116269290673</v>
+        <v>1.8167952686262436</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.0031717541991749</v>
+        <v>1.003107509267815</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.75477911404604447</v>
+        <v>0.75473077662807908</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.60283818066011108</v>
+        <v>0.60279957381399973</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14211,30 +14211,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12468922576969506</v>
+        <v>0.12468124044642676</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.16577900081067221</v>
+        <v>0.16576838402398197</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29024147395033023</v>
+        <v>0.29022288636201976</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1602510789455551</v>
+        <v>0.16024081617696725</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12057174345783458</v>
+        <v>0.12056402182557174</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.6300028859442666E-2</v>
+        <v>9.6293861631629354E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0392856588535846</v>
+        <v>8.0387708084770946</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16169,23 +16169,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16196,23 +16196,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.0159499767909441</v>
+        <v>6.0155647044866694</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.2231765903013931</v>
+        <v>7.2227140050239447</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2712364840033636</v>
+        <v>8.2707067790770115</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.4297945204302369</v>
+        <v>8.4292546611607992</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.0881129060322667</v>
+        <v>9.0875308868641689</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16223,23 +16223,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.8211015729554179</v>
+        <v>4.8207928209014081</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.539598565553856</v>
+        <v>6.5391797578479895</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.4224891059375988</v>
+        <v>8.4219497145201014</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.7448941089623595</v>
+        <v>8.7443340701460457</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.201670333445225</v>
+        <v>10.201017000047843</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16250,23 +16250,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7776972819867858</v>
+        <v>3.7774553514284706</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.8370862897566393</v>
+        <v>5.8367124722059982</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.6050522685965394</v>
+        <v>8.6045011855043079</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.134917218699746</v>
+        <v>9.1343322020989124</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.733411537169813</v>
+        <v>11.732660108298667</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16277,23 +16277,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.9980552465811723</v>
+        <v>2.997863245707221</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.2404506943390086</v>
+        <v>5.2401150864097144</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7862561252434759</v>
+        <v>8.78569343752892</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.5322882204741095</v>
+        <v>9.5316777555164744</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.480711901837996</v>
+        <v>13.479848572695014</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16304,23 +16304,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4464508611743652</v>
+        <v>2.4462941860417233</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7751930646337168</v>
+        <v>4.7748872526435138</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.9503199206734081</v>
+        <v>8.9497467260170147</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.9018653022449712</v>
+        <v>9.901231168903383</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.311829557521104</v>
+        <v>15.310848960295555</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16330,23 +16330,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0646987177695917</v>
+        <v>2.0645664907338457</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.4289784253431641</v>
+        <v>4.428694785563895</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.0911199351521912</v>
+        <v>9.0905377234085165</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.227883699561879</v>
+        <v>10.227228687413177</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.142714513992644</v>
+        <v>17.141616663587005</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.201670333445225</v>
+        <v>10.201017000047843</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.4297945204302369</v>
+        <v>8.4292546611607992</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2712364840033636</v>
+        <v>8.2707067790770115</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.2231765903013931</v>
+        <v>7.2227140050239447</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.8211015729554179</v>
+        <v>4.8207928209014081</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.4770806070175304</v>
+        <v>8.4765660220662902</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.1149848218827092</v>
+        <v>8.1144651235950658</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2712364840033636</v>
+        <v>8.2707067790770115</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.2231765903013931</v>
+        <v>7.2227140050239447</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.4297945204302369</v>
+        <v>8.4292546611607992</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.0933361125483447</v>
+        <v>8.0928178006831555</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.8211015729554179</v>
+        <v>4.8207928209014081</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.201670333445225</v>
+        <v>10.201017000047843</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>8.0351410966135415</v>
+        <v>8.0346265116623012</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>8.0392856588535846</v>
+        <v>8.0387708084770946</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864196</v>
+        <v>-0.20434577001864199</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.9282584171332156</v>
+        <v>2.9280708861743086</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>3.63046551092381</v>
+        <v>3.630277979964903</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.54817650775866378</v>
+        <v>0.54817091065831924</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15209621087146563</v>
+        <v>0.15207428234077813</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.649965912392096</v>
+        <v>4.649668120174943</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5809033069930916</v>
+        <v>5.5806055147759386</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.30543804522048823</v>
+        <v>0.30543062497358631</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.3785540636379903</v>
+        <v>6.3781455695129523</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.5174750444459137</v>
+        <v>7.5170665503208758</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.442525973635993E-2</v>
+        <v>6.4416181709278542E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B0C119-7A85-4217-9530-E9BF34BBE8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58A0C3D-1B5F-4709-9089-5B54CF5FADDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="444">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2380,6 +2380,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4097,7 +4109,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4119,7 +4131,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4162,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4197,10 +4209,10 @@
         <v>428</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4209,7 +4221,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>6.26</v>
+        <v>6.19</v>
       </c>
       <c r="D12" s="50">
         <v>8.1</v>
@@ -4234,7 +4246,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1145711.32114068</v>
+        <v>1132899.8526934201</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4261,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4311,7 +4323,7 @@
       </c>
       <c r="E22" s="341">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92351705994132738</v>
+        <v>0.92202497485361268</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4344,7 +4356,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>3.630277979964903</v>
+        <v>3.6350163883857007</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,10 +4371,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15207428234077813</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.15722725609816002</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12468124044642676</v>
+        <v>0.12629525558807667</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4661,7 +4677,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.0597365879231475E-2</v>
+        <v>7.1395720582227623E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4718,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4730,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4783,7 +4799,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.7563070649328925</v>
+        <v>9.7720954011274337</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4850,7 +4866,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6550943227212846</v>
+        <v>1.6577727117292242</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.4639072980520844E-4</v>
+        <v>7.475985913143043E-4</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4952,7 +4968,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2505990653651133E-2</v>
+        <v>1.2526228719506536E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4990,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +5003,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-3.8421295793849657</v>
+        <v>-3.848347181301202</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5045,7 +5061,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.2 HKD</v>
+        <v>10.22 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5067,7 +5083,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>8.43 HKD</v>
+        <v>8.44 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5089,7 +5105,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>8.27 HKD</v>
+        <v>8.28 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5111,7 +5127,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.22 HKD</v>
+        <v>7.23 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5133,7 +5149,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.82 HKD</v>
+        <v>4.83 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5146,7 +5162,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>8.0346265116623012</v>
+        <v>8.0476287043689698</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5265,7 +5281,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>2.9280708861743086</v>
+        <v>2.9328092945951063</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5290,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>3.630277979964903</v>
+        <v>3.6350163883857007</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>3.3526236468269284</v>
+        <v>3.3515758940937959</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5316,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54817091065831924</v>
+        <v>0.54831211504423782</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5317,7 +5333,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5327,30 +5343,30 @@
         <v>0.93093739460099523</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>4.649668120174943</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>4.6571925372505616</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5806055147759386</v>
+        <v>5.5881299318515572</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>5.1537843976982325</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>5.1523953598941521</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>427</v>
       </c>
@@ -5363,21 +5379,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30543062497358631</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.3056178239413776</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5386,7 +5402,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5396,30 +5412,30 @@
         <v>1.1389209808079233</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>6.3781455695129523</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>6.3884671292874629</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>7.5170665503208758</v>
+        <v>7.5273881100953863</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>6.9421391999356317</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>6.9404398329240813</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>427</v>
       </c>
@@ -5432,127 +5448,196 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>6.4416181709278542E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>6.4645203374150473E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>1.06622464427646</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>5.7682215129807091</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>6.8344461572571689</v>
+      </c>
+      <c r="D163" s="342">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v>6.3015300462834105</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>427</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.15118813413900201</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6193,7 +6278,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16146772276014168</v>
+        <v>0.16120684660340565</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -6207,7 +6292,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7531,7 +7616,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16146772276014168</v>
+        <v>0.16120684660340565</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8868,11 +8953,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.9654724017475527</v>
+        <v>8.97998095416186</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.8421295793849657</v>
+        <v>-3.848347181301202</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9278,11 +9363,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-302916.98132546997</v>
+        <v>-303407.18270068004</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6550943227212846</v>
+        <v>-1.6577727117292242</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9295,11 +9380,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>136.60516120323987</v>
+        <v>136.82622519770334</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4639072980520844E-4</v>
+        <v>7.475985913143043E-4</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9312,11 +9397,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2288.8586380139996</v>
+        <v>2292.562628616</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2505990653651133E-2</v>
+        <v>1.2526228719506536E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9329,11 +9414,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-300491.51752625272</v>
+        <v>-300977.79384686635</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-1.6418419413378282</v>
+        <v>-1.6444988844184034</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -11997,7 +12082,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12329,7 +12414,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12867,7 +12952,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16146772276014168</v>
+        <v>0.16120684660340565</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12923,7 +13008,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29551.980505606865</v>
+        <v>29504.234696311632</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12978,7 +13063,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.2900466549665292</v>
+        <v>0.28957803959666845</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13012,28 +13097,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.0597365879231475E-2</v>
+        <v>7.1395720582227623E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.0597365879231475E-2</v>
+        <v>7.1395720582227623E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6091151035876358E-2</v>
+        <v>6.6838546928042974E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.3474542283501439E-2</v>
+        <v>6.4192348092846352E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4039946926705276E-2</v>
+        <v>3.442488978371163E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.579356593612487E-2</v>
+        <v>2.6043109305881364E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14154,30 +14239,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.78050456519463141</v>
+        <v>0.78176763209019462</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0377100839901272</v>
+        <v>1.0393893787857358</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8167952686262436</v>
+        <v>1.819735333376852</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.003107509267815</v>
+        <v>1.0047308077648982</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.75473077662807908</v>
+        <v>0.7559521345823198</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.60279957381399973</v>
+        <v>0.60377506610487974</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14211,30 +14296,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12468124044642676</v>
+        <v>0.12629525558807667</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.16576838402398197</v>
+        <v>0.1679142776713628</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29022288636201976</v>
+        <v>0.29397985999626042</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16024081617696725</v>
+        <v>0.16231515472777031</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12056402182557174</v>
+        <v>0.12212473902783841</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.6293861631629354E-2</v>
+        <v>9.7540398401434525E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14268,23 +14353,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1603780957816319</v>
+        <v>0.16219174145282966</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15759729058121896</v>
+        <v>0.15937948934384982</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14256907214408454</v>
+        <v>0.1441813233638076</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11555615935451123</v>
+        <v>0.11686293336982878</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11260951831352123</v>
+        <v>0.11388297005535424</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15166,7 +15251,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15180,7 +15265,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15233,7 +15318,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0387708084770946</v>
+        <v>8.051779707773763</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16169,23 +16254,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16196,23 +16281,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.0155647044866694</v>
+        <v>6.0252995106302585</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.2227140050239447</v>
+        <v>7.2344023043147905</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2707067790770115</v>
+        <v>8.2840910133293217</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.4292546611607992</v>
+        <v>8.4428954686481053</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.0875308868641689</v>
+        <v>9.1022369628276625</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16223,23 +16308,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.8207928209014081</v>
+        <v>4.8285941638966676</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.5391797578479895</v>
+        <v>6.5497619143715911</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.4219497145201014</v>
+        <v>8.435578700633533</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.7443340701460457</v>
+        <v>8.7584847610968328</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.201017000047843</v>
+        <v>10.217524996859655</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16250,23 +16335,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7774553514284706</v>
+        <v>3.7835682930006542</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.8367124722059982</v>
+        <v>5.8461578471997058</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.6045011855043079</v>
+        <v>8.6184255891335599</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.1343322020989124</v>
+        <v>9.1491140152131916</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.732660108298667</v>
+        <v>11.751646716757506</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16277,23 +16362,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.997863245707221</v>
+        <v>3.0027145969893678</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.2401150864097144</v>
+        <v>5.2485950059255408</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.78569343752892</v>
+        <v>8.7999110590911247</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.5316777555164744</v>
+        <v>9.5471025809038395</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.479848572695014</v>
+        <v>13.501662603321638</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16304,23 +16389,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4462941860417233</v>
+        <v>2.4502529498222114</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7748872526435138</v>
+        <v>4.7826143080481884</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.9497467260170147</v>
+        <v>8.9642298300466337</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.901231168903383</v>
+        <v>9.9172540313854771</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.310848960295555</v>
+        <v>15.335626043386537</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16330,23 +16415,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0645664907338457</v>
+        <v>2.0679075161479439</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.428694785563895</v>
+        <v>4.4358616081856228</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.0905377234085165</v>
+        <v>9.1052486652445097</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.227228687413177</v>
+        <v>10.243779101804673</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.141616663587005</v>
+        <v>17.169356422596373</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16381,7 +16466,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.201017000047843</v>
+        <v>10.217524996859655</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16403,7 +16488,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.4292546611607992</v>
+        <v>8.4428954686481053</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16426,7 +16511,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2707067790770115</v>
+        <v>8.2840910133293217</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16449,7 +16534,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.2227140050239447</v>
+        <v>7.2344023043147905</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16472,7 +16557,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.8207928209014081</v>
+        <v>4.8285941638966676</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16540,7 +16625,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16573,7 +16658,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-6.26</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16622,7 +16707,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>8.4765660220662902</v>
+        <v>8.4895682147729588</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16813,7 +16898,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>6.26</v>
+        <v>6.19</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16828,7 +16913,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.1144651235950658</v>
+        <v>8.1275965167090316</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16875,7 +16960,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2707067790770115</v>
+        <v>8.2840910133293217</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16933,7 +17018,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.2227140050239447</v>
+        <v>7.2344023043147905</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16991,7 +17076,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.4292546611607992</v>
+        <v>8.4428954686481053</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17018,7 +17103,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.0928178006831555</v>
+        <v>8.1059141625901709</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17092,7 +17177,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.8207928209014081</v>
+        <v>4.8285941638966676</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17150,7 +17235,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.201017000047843</v>
+        <v>10.217524996859655</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17176,7 +17261,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>8.0346265116623012</v>
+        <v>8.0476287043689698</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17238,7 +17323,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>8.0387708084770946</v>
+        <v>8.051779707773763</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17301,7 +17386,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864199</v>
+        <v>-0.20434577001864201</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17373,7 +17458,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.9280708861743086</v>
+        <v>2.9328092945951063</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17383,7 +17468,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>3.630277979964903</v>
+        <v>3.6350163883857007</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17394,7 +17479,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.54817091065831924</v>
+        <v>0.54831211504423782</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17411,7 +17496,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>6.26</v>
+        <v>6.19</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17424,7 +17509,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15207428234077813</v>
+        <v>0.15722725609816002</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17462,7 +17547,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.649668120174943</v>
+        <v>4.6571925372505616</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17472,7 +17557,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5806055147759386</v>
+        <v>5.5881299318515572</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17483,7 +17568,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.30543062497358631</v>
+        <v>0.3056178239413776</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17522,7 +17607,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.3781455695129523</v>
+        <v>6.3884671292874629</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17534,7 +17619,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.5170665503208758</v>
+        <v>7.5273881100953863</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17544,39 +17629,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>6.4416181709278542E-2</v>
+        <v>6.4645203374150473E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>432</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>1.06622464427646</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>5.7682215129807091</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>6.8344461572571689</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.15118813413900201</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58A0C3D-1B5F-4709-9089-5B54CF5FADDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F31C20-0A1C-42A3-8A8B-3A26C000E763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="454">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2385,13 +2362,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>Y</t>
@@ -3089,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3603,14 +3628,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3668,9 +3687,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3678,7 +3694,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3770,9 +3785,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3787,9 +3799,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3797,6 +3806,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4109,10 +4145,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4127,11 +4163,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>436</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4186,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4159,10 +4195,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>437</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4176,9 +4212,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4199,20 +4235,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4230,19 +4266,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4256,14 +4292,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v>CNY</v>
       </c>
       <c r="E15" s="5"/>
@@ -4273,36 +4309,36 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4310,286 +4346,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>419</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v>HKD/CNY:</v>
       </c>
-      <c r="E22" s="341">
+      <c r="E25" s="335">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92202497485361268</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>425</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>3.6350163883857007</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+        <v>0.9220249748536129</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>8.0476287043689698</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.15722725609816002</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0857.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v>601857.SS (CNY)</v>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>434</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>3.6350163883857007</v>
+      </c>
+      <c r="D29" s="339">
+        <f>D144</f>
+        <v>3.3515758940937963</v>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>429</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>5.5881299318515572</v>
+      </c>
+      <c r="D30" s="148">
+        <f>D152</f>
+        <v>5.1523953598941539</v>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>7.5273881100953863</v>
+      </c>
+      <c r="D31" s="148">
+        <f>D160</f>
+        <v>6.9404398329240831</v>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>6.8344461572571689</v>
+      </c>
+      <c r="D32" s="148">
+        <f>D168</f>
+        <v>6.3015300462834123</v>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>443</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>247357.8376927129</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>243208.99999999997</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-283919.19056768838</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>18644</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>8793.8666926784372</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>18644</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>8793.8666926784372</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-20731</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-11937.133307321563</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-17915.118234001515</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-63516.176096347837</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4597,1080 +4685,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-17915.118234001515</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>175396.86669267845</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-63516.176096347837</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>131923.21948735364</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>175396.86669267845</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>131923.21948735364</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12629525558807667</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+        <v>0.12629525558807664</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>7.1395720582227623E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.7720954011274337</v>
-      </c>
-      <c r="D82" s="1" t="str">
+        <v>9.7720954011274301</v>
+      </c>
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>279749</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6577727117292242</v>
-      </c>
-      <c r="D92" s="1" t="str">
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.6577727117292238</v>
+      </c>
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.61007460831657279</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.16360901428944893</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>1.1309485990394448</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>216246</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>126.15719684722717</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.475985913143043E-4</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>2113.7999999999997</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2526228719506536E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>126.15719684722717</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>7.4759859131430409E-4</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>8.1275965167090316</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>2113.7999999999997</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-3.848347181301202</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2526228719506533E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>8.1275965167090298</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-3.8483471813012011</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.22 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>5</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>8.44 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.01</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>5</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>8.28 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.06</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>5</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>7.23 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.15</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>10</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.83 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>8.0476287043689698</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>0.44193951040398899</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>0857.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v>601857.SS</v>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>0.70220709379059454</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>2.9328092945951063</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>3.6350163883857007</v>
       </c>
-      <c r="D139" s="342">
-        <f>IF($D$11="","",C139*$E$22)</f>
-        <v>3.3515758940937959</v>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C140" s="340" t="str">
+      <c r="D144" s="336">
+        <f>IF($D$11="","",C144*$E$25)</f>
+        <v>3.3515758940937963</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.54831211504423782</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>0.93093739460099523</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>4.6571925372505616</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>5.5881299318515572</v>
       </c>
-      <c r="D147" s="342">
-        <f>IF($D$11="","",C147*$E$22)</f>
-        <v>5.1523953598941521</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C148" s="340" t="str">
+      <c r="D152" s="336">
+        <f>IF($D$11="","",C152*$E$25)</f>
+        <v>5.1523953598941539</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.3056178239413776</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>1.1389209808079233</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>6.3884671292874629</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>7.5273881100953863</v>
       </c>
-      <c r="D155" s="342">
-        <f>IF($D$11="","",C155*$E$22)</f>
-        <v>6.9404398329240813</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C156" s="340" t="str">
+      <c r="D160" s="336">
+        <f>IF($D$11="","",C160*$E$25)</f>
+        <v>6.9404398329240831</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>6.4645203374150473E-2</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>1.06622464427646</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>5.7682215129807091</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>6.8344461572571689</v>
       </c>
-      <c r="D163" s="342">
-        <f>IF($D$11="","",C163*$E$22)</f>
-        <v>6.3015300462834105</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C164" s="340" t="str">
+      <c r="D168" s="336">
+        <f>IF($D$11="","",C168*$E$25)</f>
+        <v>6.3015300462834123</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15118813413900201</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+        <v>0.15118813413900167</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5684,17 +5801,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6183,7 +6300,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>406532</v>
@@ -6209,7 +6326,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-307347</v>
@@ -6235,7 +6352,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-178876</v>
@@ -6278,7 +6395,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16120684660340565</v>
+        <v>0.16120684660340567</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -6292,7 +6409,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7547,7 +7664,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7616,7 +7733,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16120684660340565</v>
+        <v>0.16120684660340567</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -7995,11 +8112,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8029,11 +8146,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8165,15 +8282,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8232,7 +8349,7 @@
         <f>71610+8868+34387</f>
         <v>114865</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8242,7 +8359,7 @@
       <c r="G4" s="19">
         <v>216246</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8253,7 +8370,7 @@
       <c r="C5" s="19">
         <v>9020</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8263,7 +8380,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8274,7 +8391,7 @@
       <c r="C6" s="19">
         <v>168338</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8284,7 +8401,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8295,7 +8412,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8305,7 +8422,7 @@
       <c r="G7" s="19">
         <v>2816</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8316,7 +8433,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8326,7 +8443,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8337,7 +8454,7 @@
       <c r="C9" s="19">
         <v>14192</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8347,7 +8464,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8358,10 +8475,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8370,10 +8487,10 @@
       <c r="C11" s="19">
         <v>65367</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8431,7 +8548,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8440,7 +8557,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8451,7 +8568,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8460,7 +8577,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8471,7 +8588,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8480,7 +8597,7 @@
       <c r="G17" s="19">
         <v>707</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8491,7 +8608,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8500,7 +8617,7 @@
       <c r="G18" s="19">
         <v>290077</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8512,7 +8629,7 @@
         <f>480407+875436+214967+120865+14018</f>
         <v>1705693</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8521,7 +8638,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8532,7 +8649,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8541,7 +8658,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8552,7 +8669,7 @@
       <c r="C21" s="19">
         <v>92790</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8561,7 +8678,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8572,10 +8689,10 @@
       <c r="C22" s="19">
         <v>26765</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8585,10 +8702,10 @@
         <f>7436+38695</f>
         <v>46131</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8922,13 +9039,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8944,7 +9061,7 @@
         <f>H29</f>
         <v>-649408.25</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -8953,29 +9070,29 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.97998095416186</v>
+        <v>8.9799809541618583</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.848347181301202</v>
-      </c>
-      <c r="F47" s="283"/>
+        <v>-3.8483471813012011</v>
+      </c>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -8989,7 +9106,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.1394328679189951</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9000,22 +9117,22 @@
         <f>G29/G32</f>
         <v>0.55044211656563169</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9029,7 +9146,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.1094509043265285</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9043,22 +9160,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>3.656790481831769E-2</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9080,22 +9197,22 @@
         <f>G39/G32</f>
         <v>0.6195745234211173</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9109,7 +9226,7 @@
         <f>G28/G29</f>
         <v>0.12834612777992979</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9128,13 +9245,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9162,7 +9279,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9172,7 +9289,7 @@
         <f>G18</f>
         <v>290077</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9182,7 +9299,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9192,26 +9309,26 @@
         <f>SUM(C66:C69)</f>
         <v>506323</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9222,65 +9339,65 @@
         <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>0.93567445410590266</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>1.0005837372228803</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>216119.84280315277</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9294,7 +9411,7 @@
         <f>G7*H7+G17*H17</f>
         <v>2113.7999999999997</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9308,7 +9425,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9322,7 +9439,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9336,11 +9453,11 @@
         <f>SUM(D79:D81)</f>
         <v>2113.7999999999997</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9351,76 +9468,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-303407.18270068004</v>
+        <v>-303407.18270067999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6577727117292242</v>
-      </c>
-      <c r="E86" s="269" t="str">
+        <v>-1.6577727117292238</v>
+      </c>
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>136.82622519770334</v>
+        <v>136.82622519770331</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.475985913143043E-4</v>
-      </c>
-      <c r="E87" s="269" t="str">
+        <v>7.4759859131430409E-4</v>
+      </c>
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2292.562628616</v>
+        <v>2292.5626286159995</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2526228719506536E-2</v>
-      </c>
-      <c r="E88" s="269" t="str">
+        <v>1.2526228719506533E-2</v>
+      </c>
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-300977.79384686635</v>
-      </c>
-      <c r="D89" s="271">
+        <v>-300977.79384686629</v>
+      </c>
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>-1.6444988844184034</v>
-      </c>
-      <c r="E89" s="269" t="str">
+        <v>-1.644498884418403</v>
+      </c>
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9439,22 +9556,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9541,7 +9658,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9555,7 +9672,7 @@
         <v>2759911.75</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9611,7 +9728,7 @@
         <f>C25</f>
         <v>-2178092.4123072871</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-2338413</v>
@@ -9666,7 +9783,7 @@
         <f>C4+C5</f>
         <v>581819.3376927129</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>599568</v>
@@ -9721,7 +9838,7 @@
         <f>C35</f>
         <v>-334461.5</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-354052</v>
@@ -9777,7 +9894,7 @@
         <v>247357.8376927129</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9833,7 +9950,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>243208.99999999997</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>243209</v>
@@ -9888,7 +10005,7 @@
         <f>-C4*C78</f>
         <v>-283919.19056768838</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-243209</v>
@@ -9944,7 +10061,7 @@
         <v>18644</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10000,7 +10117,7 @@
         <f>C50</f>
         <v>-11937.133307321563</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-11937.133307321563</v>
@@ -10055,7 +10172,7 @@
         <f>SUM(C8:C12)</f>
         <v>213354.51381770297</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>252222.86669267845</v>
@@ -10110,7 +10227,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-63516.176096347837</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-57755</v>
@@ -10166,7 +10283,7 @@
         <v>-17915.118234001515</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10223,7 +10340,7 @@
         <v>131923.21948735364</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10280,8 +10397,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10305,8 +10422,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10331,7 +10448,7 @@
         <v>131923.21948735364</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10427,7 +10544,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10451,7 +10568,7 @@
         <v>-2114499.0205040863</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10508,7 +10625,7 @@
         <v>-63593.391803200633</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10565,7 +10682,7 @@
         <v>-2178092.4123072871</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10614,14 +10731,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10633,8 +10750,8 @@
         <v>0.76614733079928599</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10693,8 +10810,8 @@
         <v>2.3041820740536588E-2</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10751,7 +10868,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.78918915153982261</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.79592516085025733</v>
@@ -10799,14 +10916,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10817,8 +10934,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-314015.75</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10875,8 +10992,8 @@
         <v>-20445.75</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10934,7 +11051,7 @@
         <v>-334461.5</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -10983,14 +11100,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11003,7 +11120,7 @@
         <v>0.11377746045684251</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11061,7 +11178,7 @@
         <v>7.4081173066493887E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11117,7 +11234,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1211855777634919</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12050860778201085</v>
@@ -11165,26 +11282,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11263,7 +11380,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11274,7 +11391,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-20731</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-20731</v>
@@ -11323,111 +11440,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>8793.8666926784372</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>8793.8666926784372</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>8260.1782265015663</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>4735.2358665655684</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>1958.8565425218476</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>1730.9895569631838</v>
       </c>
-      <c r="L48" s="328" t="str">
+      <c r="L48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="328" t="str">
+      <c r="M48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="328" t="str">
+      <c r="N48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="328" t="str">
+      <c r="O48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="328" t="str">
+      <c r="P48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>8799</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>8799</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>8265</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>4738</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>1960</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>1732</v>
       </c>
-      <c r="L49" s="324" t="str">
+      <c r="L49" s="320" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="324" t="str">
+      <c r="M49" s="320" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="324" t="str">
+      <c r="N49" s="320" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="324" t="str">
+      <c r="O49" s="320" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="324" t="str">
+      <c r="P49" s="320" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11441,7 +11558,7 @@
         <f>C47+C48</f>
         <v>-11937.133307321563</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-11937.133307321563</v>
@@ -11489,14 +11606,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11510,8 +11627,8 @@
         <f>G53</f>
         <v>4.0689769984184679E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11537,8 +11654,8 @@
         <f>G54</f>
         <v>7.4105716195589616E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11564,7 +11681,7 @@
         <f>-C8/C47</f>
         <v>11.931785137847326</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>11.842940523853168</v>
@@ -11612,14 +11729,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11633,7 +11750,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11688,7 +11805,7 @@
         <f>BS!$C68*C67</f>
         <v>18644</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>18644</v>
@@ -11743,7 +11860,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11798,7 +11915,7 @@
         <f>SUM(C58:C60)</f>
         <v>18644</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>18644</v>
@@ -11849,11 +11966,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11909,7 +12026,7 @@
         <f>C61+C62</f>
         <v>18644</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>7918</v>
@@ -11957,14 +12074,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -11978,7 +12095,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12003,7 +12120,7 @@
         <f>G67</f>
         <v>6.4272589691702547E-2</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>6.4272589691702547E-2</v>
@@ -12028,7 +12145,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12054,7 +12171,7 @@
         <v>3.6822344629811404E-2</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12082,7 +12199,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12104,7 +12221,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12128,7 +12245,7 @@
         <v>0.78918915153982261</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12185,7 +12302,7 @@
         <v>0.21081084846017736</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12242,7 +12359,7 @@
         <v>0.1211855777634919</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12299,7 +12416,7 @@
         <v>8.9625270696685466E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12356,7 +12473,7 @@
         <v>8.8122020568230111E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12413,8 +12530,8 @@
         <v>0.10287256125768818</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>443</v>
+      <c r="E78" s="296" t="s">
+        <v>453</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12472,7 +12589,7 @@
         <v>6.7552884616691091E-3</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12529,7 +12646,7 @@
         <v>4.3251865960285008E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12586,7 +12703,7 @@
         <v>7.7304831872868032E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12643,7 +12760,7 @@
         <v>2.3013843140581518E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12696,12 +12813,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>6.4911924209176304E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12758,7 +12875,7 @@
         <v>4.7799796311368881E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12810,26 +12927,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12839,7 +12956,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12865,7 +12982,7 @@
         <v>4.7799796311368881E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12914,14 +13031,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12933,7 +13050,7 @@
         <f>G90</f>
         <v>0.44193951040398899</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.44193951040398899</v>
@@ -12952,7 +13069,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16120684660340565</v>
+        <v>0.16120684660340567</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12989,7 +13106,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>80884.201330546246</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>80884.201330546246</v>
@@ -13008,7 +13125,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29504.234696311632</v>
+        <v>29504.234696311636</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13044,7 +13161,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.61311573235445438</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.46114963656829444</v>
@@ -13063,7 +13180,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.28957803959666845</v>
+        <v>0.2895780395966685</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13093,13 +13210,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>7.1395720582227623E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.1395720582227623E-2</v>
@@ -13118,7 +13235,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6043109305881364E-2</v>
+        <v>2.6043109305881367E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13147,7 +13264,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13156,7 +13273,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13180,7 +13297,7 @@
         <v>-6.0609394682947237E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13237,7 +13354,7 @@
         <v>-0.15410320794717913</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13315,7 +13432,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13330,7 +13447,7 @@
         <v>2753007</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13387,7 +13504,7 @@
         <v>114865</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13444,7 +13561,7 @@
         <v>168338</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13501,7 +13618,7 @@
         <v>1043144</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13558,7 +13675,7 @@
         <v>1709863</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13607,7 +13724,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13616,7 +13733,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13642,7 +13759,7 @@
         <v>4.1619084378332026E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13699,7 +13816,7 @@
         <v>6.0993979245894364E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13756,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13775,63 +13892,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.2124551693360979</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>2.5287631326809223</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>2.4106818167904347</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.089210991434657</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.9893115689283667</v>
       </c>
-      <c r="L113" s="334" t="str">
+      <c r="L113" s="329" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v/>
       </c>
-      <c r="M113" s="334" t="str">
+      <c r="M113" s="329" t="str">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v/>
       </c>
-      <c r="N113" s="334" t="str">
+      <c r="N113" s="329" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="334" t="str">
+      <c r="O113" s="329" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="334" t="str">
+      <c r="P113" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13839,58 +13956,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.3177837076890597</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.4868950599058723</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.3224541263283642</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>2.1682669581796996</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.5190360527484983</v>
       </c>
-      <c r="L114" s="334" t="str">
+      <c r="L114" s="329" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="334" t="str">
+      <c r="M114" s="329" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="334" t="str">
+      <c r="N114" s="329" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="334" t="str">
+      <c r="O114" s="329" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="334" t="str">
+      <c r="P114" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13899,7 +14016,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -13955,7 +14072,7 @@
         <f>C81</f>
         <v>7.7304831872868032E-2</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>8.5849046230278017E-2</v>
@@ -14009,7 +14126,7 @@
         <f>C4/C101</f>
         <v>1.0025080757150273</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.0671898037309748</v>
@@ -14064,7 +14181,7 @@
         <v>1.6100746083165727</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14121,7 +14238,7 @@
         <v>0.14466529639667791</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14217,7 +14334,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14239,30 +14356,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.78176763209019462</v>
+        <v>0.78176763209019451</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0393893787857358</v>
+        <v>1.0393893787857356</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.819735333376852</v>
+        <v>1.8197353333768518</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.0047308077648982</v>
+        <v>1.004730807764898</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.7559521345823198</v>
+        <v>0.75595213458231958</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.60377506610487974</v>
+        <v>0.60377506610487963</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14296,30 +14413,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12629525558807667</v>
+        <v>0.12629525558807664</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1679142776713628</v>
+        <v>0.16791427767136277</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29397985999626042</v>
+        <v>0.29397985999626036</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16231515472777031</v>
+        <v>0.16231515472777025</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12212473902783841</v>
+        <v>0.12212473902783837</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.7540398401434525E-2</v>
+        <v>9.7540398401434511E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14348,7 +14465,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15099,13 +15216,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15149,7 +15266,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15159,7 +15276,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15177,10 +15294,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15195,8 +15312,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15211,8 +15328,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15227,8 +15344,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15251,7 +15368,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15265,7 +15382,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15292,7 +15409,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15302,7 +15419,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15312,13 +15429,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.051779707773763</v>
+        <v>8.0517797077737594</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16254,23 +16371,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16281,23 +16398,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.0252995106302585</v>
+        <v>6.0252995106302567</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.2344023043147905</v>
+        <v>7.2344023043147887</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2840910133293217</v>
+        <v>8.28409101332932</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.4428954686481053</v>
+        <v>8.4428954686481035</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.1022369628276625</v>
+        <v>9.1022369628276607</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16308,23 +16425,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.8285941638966676</v>
+        <v>4.8285941638966667</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.5497619143715911</v>
+        <v>6.5497619143715893</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.435578700633533</v>
+        <v>8.4355787006335312</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.7584847610968328</v>
+        <v>8.7584847610968311</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.217524996859655</v>
+        <v>10.217524996859654</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16335,23 +16452,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7835682930006542</v>
+        <v>3.7835682930006533</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.8461578471997058</v>
+        <v>5.8461578471997049</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.6184255891335599</v>
+        <v>8.6184255891335582</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.1491140152131916</v>
+        <v>9.1491140152131898</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.751646716757506</v>
+        <v>11.751646716757504</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16362,23 +16479,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0027145969893678</v>
+        <v>3.0027145969893669</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.2485950059255408</v>
+        <v>5.24859500592554</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7999110590911247</v>
+        <v>8.7999110590911229</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.5471025809038395</v>
+        <v>9.5471025809038377</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.501662603321638</v>
+        <v>13.501662603321636</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16389,23 +16506,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4502529498222114</v>
+        <v>2.450252949822211</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7826143080481884</v>
+        <v>4.7826143080481875</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.9642298300466337</v>
+        <v>8.9642298300466319</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.9172540313854771</v>
+        <v>9.9172540313854753</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.335626043386537</v>
+        <v>15.335626043386533</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16415,23 +16532,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0679075161479439</v>
+        <v>2.0679075161479434</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.4358616081856228</v>
+        <v>4.4358616081856219</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.1052486652445097</v>
+        <v>9.1052486652445079</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.243779101804673</v>
+        <v>10.243779101804671</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.169356422596373</v>
+        <v>17.169356422596369</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16466,7 +16583,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.217524996859655</v>
+        <v>10.217524996859654</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16488,7 +16605,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.4428954686481053</v>
+        <v>8.4428954686481035</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16511,7 +16628,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2840910133293217</v>
+        <v>8.28409101332932</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16534,7 +16651,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.2344023043147905</v>
+        <v>7.2344023043147887</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16557,7 +16674,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.8285941638966676</v>
+        <v>4.8285941638966667</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16573,7 +16690,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16626,12 +16743,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16644,19 +16761,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-6.19</v>
       </c>
@@ -16673,19 +16790,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.44193951040398899</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>0.44193951040398899</v>
       </c>
@@ -16699,13 +16816,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>8.4895682147729588</v>
       </c>
@@ -16722,15 +16839,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16747,12 +16864,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16769,37 +16886,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16813,12 +16930,12 @@
         <v>0.16638727228030792</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16831,12 +16948,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15587431850223021</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16849,8 +16966,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.1119740670927909</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16866,7 +16983,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16876,25 +16993,25 @@
       <c r="C18" s="151">
         <v>5</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16904,23 +17021,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.1275965167090316</v>
+        <v>8.1275965167090298</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16940,8 +17057,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16951,8 +17068,8 @@
         <v>0.01</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16960,14 +17077,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2840910133293217</v>
+        <v>8.28409101332932</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16977,8 +17094,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16998,8 +17115,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17009,8 +17126,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17018,14 +17135,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.2344023043147905</v>
+        <v>7.2344023043147887</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17035,8 +17152,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17056,8 +17173,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17067,8 +17184,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17076,14 +17193,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.4428954686481053</v>
+        <v>8.4428954686481035</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17094,8 +17211,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17157,8 +17274,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17168,8 +17285,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17177,14 +17294,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.8285941638966676</v>
+        <v>4.8285941638966667</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17194,12 +17311,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17215,8 +17332,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17226,8 +17343,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17235,14 +17352,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.217524996859655</v>
+        <v>10.217524996859654</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17252,8 +17369,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17268,16 +17385,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17286,10 +17403,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17301,8 +17418,8 @@
         <v>5</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17313,8 +17430,8 @@
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17323,29 +17440,29 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>8.051779707773763</v>
+        <v>8.0517797077737594</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>Y</v>
       </c>
@@ -17353,40 +17470,40 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864201</v>
+        <v>-0.20434577001864196</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17404,10 +17521,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17428,15 +17545,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17477,7 +17594,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.54831211504423782</v>
       </c>
@@ -17487,14 +17604,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>6.19</v>
       </c>
@@ -17505,9 +17622,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.15722725609816002</v>
       </c>
@@ -17517,15 +17634,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17566,28 +17683,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.3056178239413776</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17599,7 +17716,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17611,23 +17728,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>7.5273881100953863</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>6.4645203374150473E-2</v>
       </c>
@@ -17637,15 +17754,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17671,54 +17788,54 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>6.8344461572571689</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.15118813413900201</v>
+        <v>0.15118813413900167</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F31C20-0A1C-42A3-8A8B-3A26C000E763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2060EDCD-2FD7-4D7E-9FD6-2C64C448D770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3833,29 +3833,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4309,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4321,13 +4321,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="E25" s="335">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.9220249748536129</v>
+        <v>0.922701545375611</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="C26" s="341">
         <f>C127</f>
-        <v>8.0476287043689698</v>
+        <v>8.0417277839894048</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15722725609816002</v>
+        <v>0.15697506257755256</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4438,11 +4438,11 @@
       </c>
       <c r="C29" s="339">
         <f>C144</f>
-        <v>3.6350163883857007</v>
+        <v>3.6328659071978127</v>
       </c>
       <c r="D29" s="339">
         <f>D144</f>
-        <v>3.3515758940937963</v>
+        <v>3.3520509867137926</v>
       </c>
       <c r="E29" s="343" t="s">
         <v>429</v>
@@ -4457,17 +4457,17 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>5.5881299318515572</v>
+        <v>5.3632233497418689</v>
       </c>
       <c r="D30" s="148">
         <f>D152</f>
-        <v>5.1523953598941539</v>
+        <v>4.9486544730013833</v>
       </c>
       <c r="E30" s="344" t="s">
         <v>442</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4476,11 +4476,11 @@
       </c>
       <c r="C31" s="148">
         <f>C160</f>
-        <v>7.5273881100953863</v>
+        <v>7.5227037692463945</v>
       </c>
       <c r="D31" s="148">
         <f>D160</f>
-        <v>6.9404398329240831</v>
+        <v>6.9412103932865818</v>
       </c>
       <c r="E31" s="344" t="s">
         <v>441</v>
@@ -4495,11 +4495,11 @@
       </c>
       <c r="C32" s="148">
         <f>C168</f>
-        <v>6.8344461572571689</v>
+        <v>6.8302166112467635</v>
       </c>
       <c r="D32" s="148">
         <f>D168</f>
-        <v>6.3015300462834123</v>
+        <v>6.3022514224475579</v>
       </c>
       <c r="E32" s="344" t="s">
         <v>443</v>
@@ -4523,22 +4523,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4576,13 +4576,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4611,13 +4611,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4633,13 +4633,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4703,13 +4703,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4725,7 +4725,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4747,22 +4747,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12629525558807664</v>
+        <v>0.12620264964477099</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4823,22 +4823,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4882,22 +4882,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.7720954011274301</v>
+        <v>9.7649300162641559</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4934,13 +4934,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4953,13 +4953,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6577727117292238</v>
+        <v>1.6565571505821226</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.4759859131430409E-4</v>
+        <v>7.4705041496009132E-4</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2526228719506533E-2</v>
+        <v>1.2517043867540155E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>-3.8483471813012011</v>
+        <v>-3.8455253823410374</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5135,13 +5135,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.22 HKD</v>
+        <v>10.21 HKD</v>
       </c>
       <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>8.0476287043689698</v>
+        <v>8.0417277839894048</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5284,13 +5284,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5303,22 +5303,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>2.9328092945951063</v>
+        <v>2.9306588134072182</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5404,11 +5404,11 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>3.6350163883857007</v>
+        <v>3.6328659071978127</v>
       </c>
       <c r="D144" s="336">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>3.3515758940937963</v>
+        <v>3.3520509867137926</v>
       </c>
     </row>
     <row r="145" spans="2:4">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54831211504423782</v>
+        <v>0.54824808737860664</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>0.93093739460099523</v>
+        <v>0.90615313623080584</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>4.6571925372505616</v>
+        <v>4.4570702135110629</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5473,11 +5473,11 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>5.5881299318515572</v>
+        <v>5.3632233497418689</v>
       </c>
       <c r="D152" s="336">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>5.1523953598941539</v>
+        <v>4.9486544730013833</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3056178239413776</v>
+        <v>0.33307574021347464</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>6.3884671292874629</v>
+        <v>6.383782788438471</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5542,11 +5542,11 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>7.5273881100953863</v>
+        <v>7.5227037692463945</v>
       </c>
       <c r="D160" s="336">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>6.9404398329240831</v>
+        <v>6.9412103932865818</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>6.4645203374150473E-2</v>
+        <v>6.4541355873342976E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>5.7682215129807091</v>
+        <v>5.7639919669703037</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5611,11 +5611,11 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>6.8344461572571689</v>
+        <v>6.8302166112467635</v>
       </c>
       <c r="D168" s="336">
         <f>IF($D$11="","",C168*$E$25)</f>
-        <v>6.3015300462834123</v>
+        <v>6.3022514224475579</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15118813413900167</v>
+        <v>0.15109096525408372</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5651,13 +5651,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5694,13 +5694,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5708,22 +5708,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5747,17 +5747,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5774,6 +5763,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16120684660340567</v>
+        <v>0.16132513819347183</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16120684660340567</v>
+        <v>0.16132513819347183</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -9070,11 +9070,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.9799809541618583</v>
+        <v>8.9733963868853213</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.8483471813012011</v>
+        <v>-3.8455253823410374</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9480,11 +9480,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-303407.18270067999</v>
+        <v>-303184.70951093995</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6577727117292238</v>
+        <v>-1.6565571505821226</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>136.82622519770331</v>
+        <v>136.72589742533856</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4759859131430409E-4</v>
+        <v>7.4705041496009132E-4</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9514,11 +9514,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2292.5626286159995</v>
+        <v>2290.8816080279994</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2526228719506533E-2</v>
+        <v>1.2517043867540155E-2</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9531,11 +9531,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-300977.79384686629</v>
+        <v>-300757.10200548661</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>-1.644498884418403</v>
+        <v>-1.6432930562996224</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16120684660340567</v>
+        <v>0.16132513819347183</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29504.234696311636</v>
+        <v>29525.884538793194</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.2895780395966685</v>
+        <v>0.28979052838032671</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6043109305881367E-2</v>
+        <v>2.6062219417362167E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14356,30 +14356,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.78176763209019451</v>
+        <v>0.78119440130113238</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0393893787857356</v>
+        <v>1.038627246958723</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8197353333768518</v>
+        <v>1.8184010132052084</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.004730807764898</v>
+        <v>1.0039940893205821</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.75595213458231958</v>
+        <v>0.75539783299600149</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.60377506610487963</v>
+        <v>0.60333234829033677</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14413,30 +14413,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12629525558807664</v>
+        <v>0.12620264964477099</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.16791427767136277</v>
+        <v>0.16779115459753197</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29397985999626036</v>
+        <v>0.29376429938694804</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16231515472777025</v>
+        <v>0.16219613720849468</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12212473902783837</v>
+        <v>0.12203519111405516</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.7540398401434511E-2</v>
+        <v>9.7468876945127098E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0517797077737594</v>
+        <v>8.0458757436726884</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16371,23 +16371,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16398,23 +16398,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.0252995106302567</v>
+        <v>6.0208814622856623</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.2344023043147887</v>
+        <v>7.2290976818527319</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.28409101332932</v>
+        <v>8.2780167070606705</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.4428954686481035</v>
+        <v>8.4367047190790512</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.1022369628276607</v>
+        <v>9.0955627513839339</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16425,23 +16425,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.8285941638966667</v>
+        <v>4.825053599246746</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.5497619143715893</v>
+        <v>6.5449593041889376</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.4355787006335312</v>
+        <v>8.4293933160815637</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.7584847610968311</v>
+        <v>8.7520626058111635</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.217524996859654</v>
+        <v>10.210033000931718</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16452,23 +16452,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7835682930006533</v>
+        <v>3.7807939931332255</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.8461578471997049</v>
+        <v>5.8418711544048501</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.6184255891335582</v>
+        <v>8.6121061321771197</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.1491140152131898</v>
+        <v>9.1424054311904186</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.751646716757504</v>
+        <v>11.74302982672048</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16479,23 +16479,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0027145969893669</v>
+        <v>3.0005128577677542</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.24859500592554</v>
+        <v>5.2447464758339706</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7999110590911229</v>
+        <v>8.7934585279897881</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.5471025809038377</v>
+        <v>9.5401021719318315</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.501662603321636</v>
+        <v>13.491762514868167</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16506,23 +16506,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.450252949822211</v>
+        <v>2.4484563028721795</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7826143080481875</v>
+        <v>4.7791074581083253</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.9642298300466319</v>
+        <v>8.9576568122752622</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.9172540313854753</v>
+        <v>9.9099822090173113</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.335626043386533</v>
+        <v>15.324381202008146</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16532,23 +16532,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0679075161479434</v>
+        <v>2.0663912238271429</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.4358616081856219</v>
+        <v>4.4326090145178183</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.1052486652445079</v>
+        <v>9.0985722454712441</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.243779101804671</v>
+        <v>10.236267855065272</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.169356422596369</v>
+        <v>17.156766999184839</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.217524996859654</v>
+        <v>10.210033000931718</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.4428954686481035</v>
+        <v>8.4367047190790512</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.28409101332932</v>
+        <v>8.2780167070606705</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.2344023043147887</v>
+        <v>7.2290976818527319</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.8285941638966667</v>
+        <v>4.825053599246746</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>8.4895682147729588</v>
+        <v>8.4836672943933937</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.1275965167090298</v>
+        <v>8.1216369599645351</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.28409101332932</v>
+        <v>8.2780167070606705</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.2344023043147887</v>
+        <v>7.2290976818527319</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.4428954686481035</v>
+        <v>8.4367047190790512</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.1059141625901709</v>
+        <v>8.0999705044227586</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.8285941638966667</v>
+        <v>4.825053599246746</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.217524996859654</v>
+        <v>10.210033000931718</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>8.0476287043689698</v>
+        <v>8.0417277839894048</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>8.0517797077737594</v>
+        <v>8.0458757436726884</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>-0.20434577001864196</v>
+        <v>-0.20434577001864199</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.9328092945951063</v>
+        <v>2.9306588134072182</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>3.6350163883857007</v>
+        <v>3.6328659071978127</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.54831211504423782</v>
+        <v>0.54824808737860664</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15722725609816002</v>
+        <v>0.15697506257755256</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.93093739460099523</v>
+        <v>0.90615313623080584</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.6571925372505616</v>
+        <v>4.4570702135110629</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.5881299318515572</v>
+        <v>5.3632233497418689</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.3056178239413776</v>
+        <v>0.33307574021347464</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.3884671292874629</v>
+        <v>6.383782788438471</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.5273881100953863</v>
+        <v>7.5227037692463945</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="F99" s="325">
         <f>(1-C99/C60)</f>
-        <v>6.4645203374150473E-2</v>
+        <v>6.4541355873342976E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>5.7682215129807091</v>
+        <v>5.7639919669703037</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>6.8344461572571689</v>
+        <v>6.8302166112467635</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.15118813413900167</v>
+        <v>0.15109096525408372</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2060EDCD-2FD7-4D7E-9FD6-2C64C448D770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998511B5-7DA6-41CA-8FBB-850DDE01F7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3114,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3748,7 +3748,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3812,9 +3811,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3833,29 +3829,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4163,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4197,7 +4203,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>447</v>
       </c>
     </row>
@@ -4309,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4356,7 +4362,7 @@
       <c r="D22" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>444</v>
       </c>
     </row>
@@ -4387,9 +4393,9 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v>HKD/CNY:</v>
       </c>
-      <c r="E25" s="335">
+      <c r="E25" s="334">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.922701545375611</v>
+        <v>0.92270154537561078</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4397,16 +4403,16 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
-        <v>8.0417277839894048</v>
+        <v>8.0417277839894066</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15697506257755256</v>
+        <v>0.15697506257755278</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4417,18 +4423,18 @@
       <c r="B28" s="45" t="s">
         <v>438</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0857.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v>601857.SS (CNY)</v>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>434</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4436,18 +4442,18 @@
       <c r="B29" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
-        <v>3.6328659071978127</v>
-      </c>
-      <c r="D29" s="339">
+        <v>3.6328659071978131</v>
+      </c>
+      <c r="D29" s="345">
         <f>D144</f>
-        <v>3.3520509867137926</v>
-      </c>
-      <c r="E29" s="343" t="s">
+        <v>3.3520509867137922</v>
+      </c>
+      <c r="E29" s="341" t="s">
         <v>429</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4455,18 +4461,18 @@
       <c r="B30" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
-        <v>5.3632233497418689</v>
-      </c>
-      <c r="D30" s="148">
+        <v>5.3632233497418698</v>
+      </c>
+      <c r="D30" s="346">
         <f>D152</f>
         <v>4.9486544730013833</v>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>442</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4474,18 +4480,18 @@
       <c r="B31" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
-        <v>7.5227037692463945</v>
-      </c>
-      <c r="D31" s="148">
+        <v>7.5227037692463963</v>
+      </c>
+      <c r="D31" s="346">
         <f>D160</f>
         <v>6.9412103932865818</v>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4493,18 +4499,18 @@
       <c r="B32" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
-        <v>6.8302166112467635</v>
-      </c>
-      <c r="D32" s="148">
+        <v>6.8302166112467644</v>
+      </c>
+      <c r="D32" s="346">
         <f>D168</f>
-        <v>6.3022514224475579</v>
-      </c>
-      <c r="E32" s="344" t="s">
+        <v>6.302251422447557</v>
+      </c>
+      <c r="E32" s="342" t="s">
         <v>443</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4532,13 +4538,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4645,7 +4651,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>8793.8666926784372</v>
       </c>
@@ -4653,14 +4659,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-20731</v>
       </c>
@@ -4668,8 +4674,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4728,10 +4734,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4796,7 +4802,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.12620264964477099</v>
+        <v>0.12620264964477101</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4832,13 +4838,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4876,7 +4882,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4913,7 +4919,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.7649300162641559</v>
+        <v>9.7649300162641577</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4980,7 +4986,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.6565571505821226</v>
+        <v>1.6565571505821228</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -4988,28 +4994,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.61007460831657279</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.16360901428944893</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>1.1309485990394448</v>
       </c>
@@ -5051,7 +5057,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.4705041496009132E-4</v>
+        <v>7.4705041496009143E-4</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5082,7 +5088,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2517043867540155E-2</v>
+        <v>1.2517043867540156E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5104,7 +5110,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5112,12 +5118,12 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>-3.8455253823410374</v>
+        <v>-3.8455253823410378</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5276,7 +5282,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>8.0417277839894048</v>
+        <v>8.0417277839894066</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5284,13 +5290,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5303,13 +5309,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5373,7 +5379,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5395,7 +5401,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>2.9306588134072182</v>
+        <v>2.9306588134072187</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5404,22 +5410,22 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>3.6328659071978127</v>
-      </c>
-      <c r="D144" s="336">
+        <v>3.6328659071978131</v>
+      </c>
+      <c r="D144" s="335">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>3.3520509867137926</v>
+        <v>3.3520509867137922</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5442,7 +5448,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5464,7 +5470,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>4.4570702135110629</v>
+        <v>4.4570702135110638</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5473,9 +5479,9 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>5.3632233497418689</v>
-      </c>
-      <c r="D152" s="336">
+        <v>5.3632233497418698</v>
+      </c>
+      <c r="D152" s="335">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v>4.9486544730013833</v>
       </c>
@@ -5484,11 +5490,11 @@
       <c r="B153" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5533,7 +5539,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>6.383782788438471</v>
+        <v>6.3837827884384728</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5542,9 +5548,9 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>7.5227037692463945</v>
-      </c>
-      <c r="D160" s="336">
+        <v>7.5227037692463963</v>
+      </c>
+      <c r="D160" s="335">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v>6.9412103932865818</v>
       </c>
@@ -5553,11 +5559,11 @@
       <c r="B161" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5602,7 +5608,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>5.7639919669703037</v>
+        <v>5.7639919669703046</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5611,22 +5617,22 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>6.8302166112467635</v>
-      </c>
-      <c r="D168" s="336">
+        <v>6.8302166112467644</v>
+      </c>
+      <c r="D168" s="335">
         <f>IF($D$11="","",C168*$E$25)</f>
-        <v>6.3022514224475579</v>
+        <v>6.302251422447557</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="B169" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5651,7 +5657,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5665,13 +5671,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5708,22 +5714,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5747,6 +5753,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5763,17 +5780,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6395,7 +6401,7 @@
       </c>
       <c r="G25" s="39">
         <f>(0.08742+0.08742)/Exchange_Rate</f>
-        <v>0.16132513819347183</v>
+        <v>0.16132513819347177</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7733,7 +7739,7 @@
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.16132513819347183</v>
+        <v>0.16132513819347177</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8112,11 +8118,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8146,11 +8152,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9070,11 +9076,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.9733963868853213</v>
+        <v>8.973396386885323</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.8455253823410374</v>
+        <v>-3.8455253823410378</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9376,7 +9382,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
@@ -9480,11 +9486,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-303184.70951093995</v>
+        <v>-303184.70951094001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.6565571505821226</v>
+        <v>-1.6565571505821228</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9497,11 +9503,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>136.72589742533856</v>
+        <v>136.72589742533859</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>7.4705041496009132E-4</v>
+        <v>7.4705041496009143E-4</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9514,11 +9520,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2290.8816080279994</v>
+        <v>2290.8816080279998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2517043867540155E-2</v>
+        <v>1.2517043867540156E-2</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9531,11 +9537,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-300757.10200548661</v>
+        <v>-300757.10200548667</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>-1.6432930562996224</v>
+        <v>-1.6432930562996226</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -11447,104 +11453,104 @@
         <v>8793.8666926784372</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>8793.8666926784372</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>8260.1782265015663</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>4735.2358665655684</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>1958.8565425218476</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>1730.9895569631838</v>
       </c>
-      <c r="L48" s="324" t="str">
+      <c r="L48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="324" t="str">
+      <c r="M48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="324" t="str">
+      <c r="N48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="324" t="str">
+      <c r="O48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="324" t="str">
+      <c r="P48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>8799</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>8799</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>8265</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>4738</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>1960</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>1732</v>
       </c>
-      <c r="L49" s="320" t="str">
+      <c r="L49" s="319" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="320" t="str">
+      <c r="M49" s="319" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="320" t="str">
+      <c r="N49" s="319" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="320" t="str">
+      <c r="O49" s="319" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="320" t="str">
+      <c r="P49" s="319" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13069,7 +13075,7 @@
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.16132513819347183</v>
+        <v>0.16132513819347177</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -13125,7 +13131,7 @@
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>29525.884538793194</v>
+        <v>29525.884538793183</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -13180,7 +13186,7 @@
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.28979052838032671</v>
+        <v>0.2897905283803266</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13235,7 +13241,7 @@
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>2.6062219417362167E-2</v>
+        <v>2.606221941736216E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13908,47 +13914,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.2124551693360979</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>2.5287631326809223</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>2.4106818167904347</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.089210991434657</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.9893115689283667</v>
       </c>
-      <c r="L113" s="329" t="str">
+      <c r="L113" s="328" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v/>
       </c>
-      <c r="M113" s="329" t="str">
+      <c r="M113" s="328" t="str">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v/>
       </c>
-      <c r="N113" s="329" t="str">
+      <c r="N113" s="328" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="329" t="str">
+      <c r="O113" s="328" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="329" t="str">
+      <c r="P113" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13960,47 +13966,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.3177837076890597</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.4868950599058723</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.3224541263283642</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>2.1682669581796996</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.5190360527484983</v>
       </c>
-      <c r="L114" s="329" t="str">
+      <c r="L114" s="328" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="329" t="str">
+      <c r="M114" s="328" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="329" t="str">
+      <c r="N114" s="328" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="329" t="str">
+      <c r="O114" s="328" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="329" t="str">
+      <c r="P114" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -14356,30 +14362,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.78119440130113238</v>
+        <v>0.7811944013011326</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.038627246958723</v>
+        <v>1.0386272469587232</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>1.8184010132052084</v>
+        <v>1.8184010132052089</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.0039940893205821</v>
+        <v>1.0039940893205823</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>0.75539783299600149</v>
+        <v>0.75539783299600161</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.60333234829033677</v>
+        <v>0.60333234829033688</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14413,30 +14419,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12620264964477099</v>
+        <v>0.12620264964477101</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.16779115459753197</v>
+        <v>0.16779115459753202</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29376429938694804</v>
+        <v>0.29376429938694809</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.16219613720849468</v>
+        <v>0.16219613720849471</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12203519111405516</v>
+        <v>0.12203519111405518</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.7468876945127098E-2</v>
+        <v>9.7468876945127111E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -15294,10 +15300,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15312,8 +15318,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15328,8 +15334,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15344,8 +15350,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15368,7 +15374,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15382,7 +15388,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15435,7 +15441,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0458757436726884</v>
+        <v>8.0458757436726902</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16371,23 +16377,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16398,23 +16404,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.0208814622856623</v>
+        <v>6.0208814622856632</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>7.2290976818527319</v>
+        <v>7.2290976818527337</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.2780167070606705</v>
+        <v>8.2780167070606723</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>8.4367047190790512</v>
+        <v>8.4367047190790529</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>9.0955627513839339</v>
+        <v>9.0955627513839357</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16425,23 +16431,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.825053599246746</v>
+        <v>4.8250535992467469</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>6.5449593041889376</v>
+        <v>6.5449593041889393</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>8.4293933160815637</v>
+        <v>8.4293933160815655</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>8.7520626058111635</v>
+        <v>8.7520626058111652</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>10.210033000931718</v>
+        <v>10.210033000931722</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16452,23 +16458,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>3.7807939931332255</v>
+        <v>3.7807939931332264</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.8418711544048501</v>
+        <v>5.8418711544048518</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>8.6121061321771197</v>
+        <v>8.6121061321771215</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>9.1424054311904186</v>
+        <v>9.1424054311904204</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>11.74302982672048</v>
+        <v>11.743029826720482</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16479,23 +16485,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>3.0005128577677542</v>
+        <v>3.0005128577677547</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.2447464758339706</v>
+        <v>5.2447464758339715</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>8.7934585279897881</v>
+        <v>8.7934585279897899</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>9.5401021719318315</v>
+        <v>9.5401021719318333</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>13.491762514868167</v>
+        <v>13.491762514868169</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16506,23 +16512,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4484563028721795</v>
+        <v>2.44845630287218</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>4.7791074581083253</v>
+        <v>4.7791074581083262</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>8.9576568122752622</v>
+        <v>8.957656812275264</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>9.9099822090173113</v>
+        <v>9.9099822090173131</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>15.324381202008146</v>
+        <v>15.32438120200815</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16532,23 +16538,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0663912238271429</v>
+        <v>2.0663912238271434</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>4.4326090145178183</v>
+        <v>4.4326090145178192</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>9.0985722454712441</v>
+        <v>9.0985722454712459</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>10.236267855065272</v>
+        <v>10.236267855065275</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>17.156766999184839</v>
+        <v>17.156766999184843</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16583,7 +16589,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.210033000931718</v>
+        <v>10.210033000931722</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16605,7 +16611,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>8.4367047190790512</v>
+        <v>8.4367047190790529</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16628,7 +16634,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>8.2780167070606705</v>
+        <v>8.2780167070606723</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16651,7 +16657,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.2290976818527319</v>
+        <v>7.2290976818527337</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16674,7 +16680,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.825053599246746</v>
+        <v>4.8250535992467469</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16824,7 +16830,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>8.4836672943933937</v>
+        <v>8.4836672943933955</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16839,11 +16845,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16864,8 +16870,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16886,8 +16892,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16897,8 +16903,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16911,8 +16917,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -16930,8 +16936,8 @@
         <v>0.16638727228030792</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -16948,8 +16954,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15587431850223021</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -16966,8 +16972,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.1119740670927909</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16993,21 +16999,21 @@
       <c r="C18" s="151">
         <v>5</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17021,8 +17027,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17030,14 +17036,14 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>8.1216369599645351</v>
+        <v>8.1216369599645368</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17057,8 +17063,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17068,8 +17074,8 @@
         <v>0.01</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17077,14 +17083,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>8.2780167070606705</v>
+        <v>8.2780167070606723</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17094,8 +17100,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17115,8 +17121,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17126,8 +17132,8 @@
         <v>-0.06</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17135,14 +17141,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>7.2290976818527319</v>
+        <v>7.2290976818527337</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17152,8 +17158,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17173,8 +17179,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17184,8 +17190,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17193,14 +17199,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>8.4367047190790512</v>
+        <v>8.4367047190790529</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17211,8 +17217,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17220,7 +17226,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>8.0999705044227586</v>
+        <v>8.0999705044227603</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17274,8 +17280,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17285,8 +17291,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17294,14 +17300,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>4.825053599246746</v>
+        <v>4.8250535992467469</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17311,8 +17317,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17332,8 +17338,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17343,8 +17349,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17352,14 +17358,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>10.210033000931718</v>
+        <v>10.210033000931722</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17369,8 +17375,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17378,7 +17384,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>8.0417277839894048</v>
+        <v>8.0417277839894066</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17387,7 +17393,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17440,7 +17446,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>8.0458757436726884</v>
+        <v>8.0458757436726902</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17501,7 +17507,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>-0.20434577001864199</v>
       </c>
@@ -17575,7 +17581,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.9306588134072182</v>
+        <v>2.9306588134072187</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17585,7 +17591,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>3.6328659071978127</v>
+        <v>3.6328659071978131</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17594,7 +17600,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.54824808737860664</v>
       </c>
@@ -17626,7 +17632,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15697506257755256</v>
+        <v>0.15697506257755278</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17664,7 +17670,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>4.4570702135110629</v>
+        <v>4.4570702135110638</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17674,7 +17680,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>5.3632233497418689</v>
+        <v>5.3632233497418698</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17683,7 +17689,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.33307574021347464</v>
       </c>
@@ -17693,7 +17699,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17704,7 +17710,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17716,7 +17722,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17724,11 +17730,11 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>6.383782788438471</v>
+        <v>6.3837827884384728</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17736,7 +17742,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>7.5227037692463945</v>
+        <v>7.5227037692463963</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17744,7 +17750,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>6.4541355873342976E-2</v>
       </c>
@@ -17782,7 +17788,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>5.7639919669703037</v>
+        <v>5.7639919669703046</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17792,7 +17798,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>6.8302166112467635</v>
+        <v>6.8302166112467644</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17800,7 +17806,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.15109096525408372</v>
       </c>
@@ -17809,32 +17815,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998511B5-7DA6-41CA-8FBB-850DDE01F7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA43671-D3EB-4B77-AD91-6791DDA0E96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4918,7 +4918,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>9.7649300162641577</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4972,7 +4972,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>279749</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5043,7 +5043,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>126.15719684722717</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5074,7 +5074,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>2113.7999999999997</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5109,7 +5109,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>8.1216369599645368</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5168,111 +5168,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.06</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>10</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.21 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.02</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>5</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>8.44 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.01</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>5</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>8.28 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>-0.06</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>5</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>7.23 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>-0.15</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>10</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.83 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-303184.70951094001</v>
       </c>
       <c r="D86" s="248">
@@ -9502,7 +9502,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>136.72589742533859</v>
       </c>
       <c r="D87" s="248">
@@ -9519,7 +9519,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>2290.8816080279998</v>
       </c>
       <c r="D88" s="248">
@@ -15479,7 +15479,7 @@
         <v>131277.11532304226</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E21" s="125">
@@ -15501,7 +15501,7 @@
         <v>130634.17550381558</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E22" s="125">
@@ -15523,7 +15523,7 @@
         <v>129994.38453204895</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E23" s="125">
@@ -15545,7 +15545,7 @@
         <v>129357.72698601855</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E24" s="125">
@@ -15567,7 +15567,7 @@
         <v>128724.18751952963</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>-4.8975772939903201E-3</v>
       </c>
       <c r="E25" s="125">
@@ -15589,7 +15589,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E26" s="125">
@@ -15611,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E27" s="125">
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E28" s="125">
@@ -15655,7 +15655,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E29" s="125">
@@ -15677,7 +15677,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E30" s="125">
@@ -15699,7 +15699,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15721,7 +15721,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15743,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15765,7 +15765,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15787,7 +15787,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15809,7 +15809,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15853,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15875,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15897,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -15919,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -15941,7 +15941,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -15963,7 +15963,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -15985,7 +15985,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16007,7 +16007,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16029,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16073,7 +16073,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16095,7 +16095,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16818,7 +16818,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17035,7 +17035,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>8.1216369599645368</v>
       </c>
       <c r="D22" t="str">
@@ -17082,7 +17082,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>8.2780167070606723</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17140,7 +17140,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>7.2290976818527337</v>
       </c>
       <c r="D33" t="str">
@@ -17198,7 +17198,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>8.4367047190790529</v>
       </c>
       <c r="D39" t="str">
@@ -17299,7 +17299,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>4.8250535992467469</v>
       </c>
       <c r="D51" t="str">
@@ -17357,7 +17357,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>10.210033000931722</v>
       </c>
       <c r="D57" t="str">
@@ -17445,7 +17445,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>8.0458757436726902</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA43671-D3EB-4B77-AD91-6791DDA0E96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91220A5C-9586-4F71-AD62-299741367283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/0857.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0857.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91220A5C-9586-4F71-AD62-299741367283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6D39CA-9A71-4463-B588-C33C6F122641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="462">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2338,100 +2333,130 @@
     <t>CNY</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>中国石油股份</t>
+  </si>
+  <si>
+    <t>0857.HK</t>
+  </si>
+  <si>
+    <t>601857.SS</t>
+  </si>
+  <si>
     <t>ENG_01</t>
   </si>
   <si>
-    <t>Company Information</t>
-  </si>
-  <si>
-    <t>Market Currency</t>
-  </si>
-  <si>
-    <t>Symbol:</t>
-  </si>
-  <si>
-    <t>Listing Information</t>
-  </si>
-  <si>
-    <t>Forex Symbol:</t>
-  </si>
-  <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
+    <t>N</t>
   </si>
   <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>中国石油股份</t>
-  </si>
-  <si>
-    <t>0857.HK</t>
-  </si>
-  <si>
-    <t>601857.SS</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2447,7 +2472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2466,6 +2491,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3114,7 +3140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3620,9 +3646,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3839,29 +3862,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3880,7 +3910,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3927,8 +3971,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4169,15 +4213,15 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>446</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4192,7 +4236,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4201,10 +4245,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>447</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4218,9 +4262,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4241,20 +4285,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4272,19 +4316,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4298,7 +4342,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4327,73 +4371,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Negative Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>419</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>444</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>450</v>
+        <v>436</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>450</v>
+        <v>437</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v>HKD/CNY:</v>
       </c>
-      <c r="E25" s="334">
+      <c r="E25" s="333">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v>0.92270154537561078</v>
       </c>
@@ -4403,14 +4451,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>8.0417277839894066</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.15697506257755278</v>
       </c>
@@ -4421,96 +4469,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>438</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>435</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0857.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v>601857.SS (CNY)</v>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>434</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C29" s="345">
+        <v>427</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>3.6328659071978131</v>
       </c>
-      <c r="D29" s="345">
+      <c r="D29" s="344">
         <f>D144</f>
         <v>3.3520509867137922</v>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>429</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C30" s="346">
+        <v>428</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>5.3632233497418698</v>
       </c>
-      <c r="D30" s="346">
+      <c r="D30" s="345">
         <f>D152</f>
         <v>4.9486544730013833</v>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>442</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C31" s="346">
+        <v>429</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>7.5227037692463963</v>
       </c>
-      <c r="D31" s="346">
+      <c r="D31" s="345">
         <f>D160</f>
         <v>6.9412103932865818</v>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C32" s="346">
+        <v>430</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>6.8302166112467644</v>
       </c>
-      <c r="D32" s="346">
+      <c r="D32" s="345">
         <f>D168</f>
         <v>6.302251422447557</v>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4519,8 +4567,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4529,22 +4577,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4556,13 +4604,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4582,13 +4630,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4617,13 +4665,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4639,19 +4687,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>8793.8666926784372</v>
       </c>
@@ -4659,14 +4707,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-20731</v>
       </c>
@@ -4674,8 +4722,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4709,13 +4757,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4731,13 +4779,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4753,22 +4801,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4797,26 +4845,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.12620264964477101</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>7.1395720582227623E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.61311573235445438</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4829,22 +4885,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4853,7 +4909,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4862,7 +4918,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4873,7 +4929,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4882,42 +4938,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>9.7649300162641577</v>
       </c>
@@ -4927,8 +4983,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4940,13 +4996,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4959,13 +5015,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4982,9 +5038,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.6565571505821228</v>
       </c>
@@ -4994,28 +5050,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.61007460831657279</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.16360901428944893</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>1.1309485990394448</v>
       </c>
@@ -5053,9 +5109,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>7.4705041496009143E-4</v>
       </c>
@@ -5084,9 +5140,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.2517043867540156E-2</v>
       </c>
@@ -5096,20 +5152,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>451</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>8.1216369599645368</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5118,10 +5174,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-3.8455253823410378</v>
       </c>
@@ -5131,8 +5187,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5141,49 +5197,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>10</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>10.21 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5201,11 +5257,11 @@
         <f>DCF!D75</f>
         <v>5</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>8.44 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5223,11 +5279,11 @@
         <f>DCF!D76</f>
         <v>5</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>8.28 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5245,11 +5301,11 @@
         <f>DCF!D77</f>
         <v>5</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>7.23 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5267,11 +5323,11 @@
         <f>DCF!D78</f>
         <v>10</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>4.83 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5290,17 +5346,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5309,22 +5365,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5335,7 +5391,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5344,7 +5400,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5364,22 +5420,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>0857.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v>601857.SS</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5412,20 +5468,20 @@
         <f>Scenarios!C83</f>
         <v>3.6328659071978131</v>
       </c>
-      <c r="D144" s="335">
+      <c r="D144" s="334">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v>3.3520509867137922</v>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5441,14 +5497,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5481,20 +5537,20 @@
         <f>Scenarios!C93</f>
         <v>5.3632233497418698</v>
       </c>
-      <c r="D152" s="335">
+      <c r="D152" s="334">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v>4.9486544730013833</v>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5510,12 +5566,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5544,26 +5600,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>7.5227037692463963</v>
       </c>
-      <c r="D160" s="335">
+      <c r="D160" s="334">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v>6.9412103932865818</v>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5579,12 +5635,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5613,26 +5669,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>6.8302166112467644</v>
       </c>
-      <c r="D168" s="335">
+      <c r="D168" s="334">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v>6.302251422447557</v>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5647,8 +5703,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5657,113 +5713,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5780,6 +5825,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5792,7 +5848,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6306,7 +6362,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>406532</v>
@@ -6332,7 +6388,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-307347</v>
@@ -6358,7 +6414,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-178876</v>
@@ -6415,7 +6471,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7670,7 +7726,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8118,11 +8174,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8152,11 +8208,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8259,17 +8315,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8355,7 +8411,7 @@
         <f>71610+8868+34387</f>
         <v>114865</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8365,7 +8421,7 @@
       <c r="G4" s="19">
         <v>216246</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8376,7 +8432,7 @@
       <c r="C5" s="19">
         <v>9020</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8386,7 +8442,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8397,7 +8453,7 @@
       <c r="C6" s="19">
         <v>168338</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8407,7 +8463,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8418,7 +8474,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8428,7 +8484,7 @@
       <c r="G7" s="19">
         <v>2816</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8439,7 +8495,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8449,7 +8505,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8460,7 +8516,7 @@
       <c r="C9" s="19">
         <v>14192</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8470,7 +8526,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8481,10 +8537,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8493,10 +8549,10 @@
       <c r="C11" s="19">
         <v>65367</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8554,7 +8610,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8563,7 +8619,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8574,7 +8630,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8583,7 +8639,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8594,7 +8650,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8603,7 +8659,7 @@
       <c r="G17" s="19">
         <v>707</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8614,7 +8670,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8623,7 +8679,7 @@
       <c r="G18" s="19">
         <v>290077</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8635,7 +8691,7 @@
         <f>480407+875436+214967+120865+14018</f>
         <v>1705693</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8644,7 +8700,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8655,7 +8711,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8664,7 +8720,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8675,7 +8731,7 @@
       <c r="C21" s="19">
         <v>92790</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8684,7 +8740,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8695,10 +8751,10 @@
       <c r="C22" s="19">
         <v>26765</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8708,10 +8764,10 @@
         <f>7436+38695</f>
         <v>46131</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9045,13 +9101,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9067,7 +9123,7 @@
         <f>H29</f>
         <v>-649408.25</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9082,23 +9138,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-3.8455253823410378</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9112,7 +9168,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.1394328679189951</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9123,22 +9179,22 @@
         <f>G29/G32</f>
         <v>0.55044211656563169</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9152,7 +9208,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.1094509043265285</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9166,22 +9222,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>3.656790481831769E-2</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9203,22 +9259,22 @@
         <f>G39/G32</f>
         <v>0.6195745234211173</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9232,7 +9288,7 @@
         <f>G28/G29</f>
         <v>0.12834612777992979</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9251,13 +9307,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9285,7 +9341,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9295,7 +9351,7 @@
         <f>G18</f>
         <v>290077</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9305,7 +9361,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9315,26 +9371,26 @@
         <f>SUM(C66:C69)</f>
         <v>506323</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9345,65 +9401,65 @@
         <v>-216119.84280315277</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>0.93567445410590266</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>1.0005837372228803</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>216119.84280315277</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9417,7 +9473,7 @@
         <f>G7*H7+G17*H17</f>
         <v>2113.7999999999997</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9431,7 +9487,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9445,7 +9501,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9459,11 +9515,11 @@
         <f>SUM(D79:D81)</f>
         <v>2113.7999999999997</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9474,76 +9530,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-303184.70951094001</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-1.6565571505821228</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>136.72589742533859</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>7.4705041496009143E-4</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>2290.8816080279998</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.2517043867540156E-2</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-300757.10200548667</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>-1.6432930562996226</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9664,7 +9720,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9678,7 +9734,7 @@
         <v>2759911.75</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9734,7 +9790,7 @@
         <f>C25</f>
         <v>-2178092.4123072871</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-2338413</v>
@@ -9789,7 +9845,7 @@
         <f>C4+C5</f>
         <v>581819.3376927129</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>599568</v>
@@ -9844,7 +9900,7 @@
         <f>C35</f>
         <v>-334461.5</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-354052</v>
@@ -9900,7 +9956,7 @@
         <v>247357.8376927129</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9956,7 +10012,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>243208.99999999997</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>243209</v>
@@ -10011,7 +10067,7 @@
         <f>-C4*C78</f>
         <v>-283919.19056768838</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-243209</v>
@@ -10067,7 +10123,7 @@
         <v>18644</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10123,7 +10179,7 @@
         <f>C50</f>
         <v>-11937.133307321563</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-11937.133307321563</v>
@@ -10178,7 +10234,7 @@
         <f>SUM(C8:C12)</f>
         <v>213354.51381770297</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>252222.86669267845</v>
@@ -10233,7 +10289,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-63516.176096347837</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-57755</v>
@@ -10289,7 +10345,7 @@
         <v>-17915.118234001515</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10346,7 +10402,7 @@
         <v>131923.21948735364</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10403,8 +10459,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10428,8 +10484,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10454,7 +10510,7 @@
         <v>131923.21948735364</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10550,7 +10606,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10574,7 +10630,7 @@
         <v>-2114499.0205040863</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10631,7 +10687,7 @@
         <v>-63593.391803200633</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10688,7 +10744,7 @@
         <v>-2178092.4123072871</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10737,14 +10793,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10756,8 +10812,8 @@
         <v>0.76614733079928599</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10816,8 +10872,8 @@
         <v>2.3041820740536588E-2</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10874,7 +10930,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.78918915153982261</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.79592516085025733</v>
@@ -10922,14 +10978,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10940,8 +10996,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-314015.75</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10998,8 +11054,8 @@
         <v>-20445.75</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11057,7 +11113,7 @@
         <v>-334461.5</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11106,14 +11162,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11126,7 +11182,7 @@
         <v>0.11377746045684251</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11184,7 +11240,7 @@
         <v>7.4081173066493887E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11240,7 +11296,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1211855777634919</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12050860778201085</v>
@@ -11288,26 +11344,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11386,7 +11442,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11397,7 +11453,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-20731</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-20731</v>
@@ -11446,111 +11502,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>8793.8666926784372</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>8793.8666926784372</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>8260.1782265015663</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>4735.2358665655684</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>1958.8565425218476</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>1730.9895569631838</v>
       </c>
-      <c r="L48" s="323" t="str">
+      <c r="L48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="323" t="str">
+      <c r="N48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="323" t="str">
+      <c r="O48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="323" t="str">
+      <c r="P48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>8799</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>8799</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>8265</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>4738</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>1960</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>1732</v>
       </c>
-      <c r="L49" s="319" t="str">
+      <c r="L49" s="318" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="319" t="str">
+      <c r="M49" s="318" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="319" t="str">
+      <c r="N49" s="318" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="319" t="str">
+      <c r="O49" s="318" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="319" t="str">
+      <c r="P49" s="318" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11564,7 +11620,7 @@
         <f>C47+C48</f>
         <v>-11937.133307321563</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-11937.133307321563</v>
@@ -11612,14 +11668,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11633,8 +11689,8 @@
         <f>G53</f>
         <v>4.0689769984184679E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11660,8 +11716,8 @@
         <f>G54</f>
         <v>7.4105716195589616E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11687,7 +11743,7 @@
         <f>-C8/C47</f>
         <v>11.931785137847326</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>11.842940523853168</v>
@@ -11735,14 +11791,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11756,7 +11812,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11811,7 +11867,7 @@
         <f>BS!$C68*C67</f>
         <v>18644</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>18644</v>
@@ -11866,7 +11922,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11921,7 +11977,7 @@
         <f>SUM(C58:C60)</f>
         <v>18644</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>18644</v>
@@ -11972,11 +12028,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12032,7 +12088,7 @@
         <f>C61+C62</f>
         <v>18644</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>7918</v>
@@ -12080,14 +12136,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12101,7 +12157,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12126,7 +12182,7 @@
         <f>G67</f>
         <v>6.4272589691702547E-2</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>6.4272589691702547E-2</v>
@@ -12151,7 +12207,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12177,7 +12233,7 @@
         <v>3.6822344629811404E-2</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12205,7 +12261,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12227,7 +12283,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12251,7 +12307,7 @@
         <v>0.78918915153982261</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12308,7 +12364,7 @@
         <v>0.21081084846017736</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12365,7 +12421,7 @@
         <v>0.1211855777634919</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12422,7 +12478,7 @@
         <v>8.9625270696685466E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12479,7 +12535,7 @@
         <v>8.8122020568230111E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12536,8 +12592,8 @@
         <v>0.10287256125768818</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>453</v>
+      <c r="E78" s="295" t="s">
+        <v>461</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12595,7 +12651,7 @@
         <v>6.7552884616691091E-3</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12652,7 +12708,7 @@
         <v>4.3251865960285008E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12709,7 +12765,7 @@
         <v>7.7304831872868032E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12766,7 +12822,7 @@
         <v>2.3013843140581518E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12819,12 +12875,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>6.4911924209176304E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12881,7 +12937,7 @@
         <v>4.7799796311368881E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12933,26 +12989,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12962,7 +13018,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12988,7 +13044,7 @@
         <v>4.7799796311368881E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13037,14 +13093,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13056,7 +13112,7 @@
         <f>G90</f>
         <v>0.44193951040398899</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.44193951040398899</v>
@@ -13112,7 +13168,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>80884.201330546246</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>80884.201330546246</v>
@@ -13167,7 +13223,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.61311573235445438</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.46114963656829444</v>
@@ -13216,13 +13272,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>7.1395720582227623E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.1395720582227623E-2</v>
@@ -13270,7 +13326,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13279,7 +13335,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13303,7 +13359,7 @@
         <v>-6.0609394682947237E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13360,7 +13416,7 @@
         <v>-0.15410320794717913</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13438,7 +13494,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13453,7 +13509,7 @@
         <v>2753007</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13510,7 +13566,7 @@
         <v>114865</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13567,7 +13623,7 @@
         <v>168338</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13624,7 +13680,7 @@
         <v>1043144</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13681,7 +13737,7 @@
         <v>1709863</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13730,7 +13786,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13739,7 +13795,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13765,7 +13821,7 @@
         <v>4.1619084378332026E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13822,7 +13878,7 @@
         <v>6.0993979245894364E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13879,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13898,63 +13954,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.2124551693360979</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>2.5287631326809223</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>2.4106818167904347</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.089210991434657</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.9893115689283667</v>
       </c>
-      <c r="L113" s="328" t="str">
+      <c r="L113" s="327" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v/>
       </c>
-      <c r="M113" s="328" t="str">
+      <c r="M113" s="327" t="str">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v/>
       </c>
-      <c r="N113" s="328" t="str">
+      <c r="N113" s="327" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="328" t="str">
+      <c r="O113" s="327" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="328" t="str">
+      <c r="P113" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13962,58 +14018,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.3177837076890597</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.4868950599058723</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.3224541263283642</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>2.1682669581796996</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.5190360527484983</v>
       </c>
-      <c r="L114" s="328" t="str">
+      <c r="L114" s="327" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="328" t="str">
+      <c r="M114" s="327" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="328" t="str">
+      <c r="N114" s="327" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="328" t="str">
+      <c r="O114" s="327" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="328" t="str">
+      <c r="P114" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14022,7 +14078,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14078,7 +14134,7 @@
         <f>C81</f>
         <v>7.7304831872868032E-2</v>
       </c>
-      <c r="E11